--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC19" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Mexico_Lig" displayName="AveragesTable_Mexico_Lig" ref="A1:EC19" headerRowCount="1">
   <autoFilter ref="A1:EC19"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0.11</v>
@@ -3484,139 +3484,139 @@
         <v>2.67</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="AH7" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AI7" t="n">
-        <v>83.88</v>
+        <v>83.33</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.25</v>
+        <v>2.89</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.12</v>
+        <v>3.89</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>42.25</v>
+        <v>40.56</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.75</v>
+        <v>13.67</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.88</v>
+        <v>12.67</v>
       </c>
       <c r="AS7" t="n">
-        <v>9</v>
+        <v>9.67</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>44.75</v>
+        <v>43.22</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="BA7" t="n">
-        <v>11</v>
+        <v>10.22</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.25</v>
+        <v>6.67</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="BD7" t="n">
-        <v>20</v>
+        <v>19.56</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="BF7" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.06</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BL7" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.53</v>
+        <v>4.39</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT7" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU7" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BV7" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW7" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX7" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BY7" t="n">
         <v>2.44</v>
@@ -3625,31 +3625,31 @@
         <v>2.52</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.14</v>
+        <v>4.03</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.87</v>
+        <v>4.71</v>
       </c>
       <c r="CE7" t="n">
         <v>1.35</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CH7" t="n">
         <v>1.44</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.79</v>
@@ -3670,19 +3670,19 @@
         <v>1.26</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS7" t="n">
         <v>2.82</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CU7" t="n">
         <v>1.47</v>
@@ -3691,16 +3691,16 @@
         <v>2.08</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CY7" t="n">
         <v>2</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DA7" t="n">
         <v>1.82</v>
@@ -3712,82 +3712,82 @@
         <v>1.94</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="DH7" t="n">
-        <v>92.77</v>
+        <v>92</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.47</v>
+        <v>2.78</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.53</v>
+        <v>4.39</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM7" t="n">
-        <v>41.18</v>
+        <v>40.39</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.71</v>
+        <v>12.23</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.89</v>
+        <v>12.78</v>
       </c>
       <c r="DR7" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="DY7" t="n">
         <v>8.17</v>
       </c>
-      <c r="DS7" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="DT7" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="DU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV7" t="n">
-        <v>49.29</v>
-      </c>
-      <c r="DW7" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DX7" t="n">
-        <v>12.41</v>
-      </c>
-      <c r="DY7" t="n">
-        <v>8.529999999999999</v>
-      </c>
       <c r="DZ7" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.88</v>
+        <v>21.56</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="8">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="G12" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="H12" t="n">
-        <v>91.62</v>
+        <v>91.22</v>
       </c>
       <c r="I12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>5.78</v>
       </c>
       <c r="L12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M12" t="n">
-        <v>40.88</v>
+        <v>41.11</v>
       </c>
       <c r="N12" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="O12" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="P12" t="n">
-        <v>11.25</v>
+        <v>11.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.88</v>
+        <v>12.33</v>
       </c>
       <c r="R12" t="n">
-        <v>7.88</v>
+        <v>7.67</v>
       </c>
       <c r="S12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T12" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>57</v>
+        <v>55.22</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.75</v>
+        <v>15.22</v>
       </c>
       <c r="AA12" t="n">
-        <v>11.5</v>
+        <v>10.89</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>15.38</v>
+        <v>15.11</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AF12" t="n">
         <v>0.11</v>
@@ -5580,70 +5580,70 @@
         <v>2.56</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.24</v>
+        <v>9.33</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.12</v>
+        <v>4.22</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT12" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="CC12" t="n">
         <v>2.61</v>
@@ -5655,13 +5655,13 @@
         <v>1.31</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI12" t="n">
         <v>2.12</v>
@@ -5670,16 +5670,16 @@
         <v>1.68</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CO12" t="n">
         <v>1.22</v>
@@ -5688,121 +5688,121 @@
         <v>1.75</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CX12" t="n">
         <v>1.5</v>
       </c>
       <c r="CY12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DC12" t="n">
         <v>1.78</v>
       </c>
-      <c r="CZ12" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="DA12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="DB12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="DC12" t="n">
-        <v>1.76</v>
-      </c>
       <c r="DD12" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="DE12" t="n">
         <v>0.06</v>
       </c>
       <c r="DF12" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DH12" t="n">
-        <v>84.23</v>
+        <v>84.44</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.94</v>
+        <v>4.89</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DM12" t="n">
-        <v>41.06</v>
+        <v>41.16</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.41</v>
+        <v>11.5</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.41</v>
+        <v>12.16</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.24</v>
+        <v>9.06</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>53.65</v>
+        <v>52.94</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.88</v>
+        <v>14.66</v>
       </c>
       <c r="DY12" t="n">
-        <v>10.29</v>
+        <v>10.06</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.59</v>
+        <v>4.61</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.59</v>
+        <v>17.33</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="13">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>0.12</v>
@@ -6305,139 +6305,139 @@
         <v>2.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AI14" t="n">
-        <v>71.22</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="AL14" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.67</v>
+        <v>40.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AP14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14.78</v>
+        <v>14.1</v>
       </c>
       <c r="AR14" t="n">
-        <v>11.11</v>
+        <v>11.3</v>
       </c>
       <c r="AS14" t="n">
-        <v>13.56</v>
+        <v>12.7</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>45</v>
+        <v>46.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.11</v>
+        <v>10.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.89</v>
+        <v>7</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.89</v>
+        <v>17.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.289999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.12</v>
+        <v>4.17</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.06</v>
+        <v>4.17</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS14" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BV14" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BY14" t="n">
         <v>2.01</v>
@@ -6449,28 +6449,28 @@
         <v>3.48</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="CE14" t="n">
         <v>1.37</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.8</v>
@@ -6479,10 +6479,10 @@
         <v>1.51</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CN14" t="n">
         <v>1.83</v>
@@ -6491,28 +6491,28 @@
         <v>1.29</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="CR14" t="n">
         <v>1.4</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX14" t="n">
         <v>1.57</v>
@@ -6530,85 +6530,85 @@
         <v>1.31</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="DE14" t="n">
         <v>0.11</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="DH14" t="n">
-        <v>85.47</v>
+        <v>86</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.41</v>
+        <v>4.56</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="DM14" t="n">
-        <v>44.06</v>
+        <v>44.78</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.53</v>
+        <v>13.22</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.88</v>
+        <v>11</v>
       </c>
       <c r="DR14" t="n">
-        <v>11.36</v>
+        <v>11</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.82</v>
+        <v>52.22</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.76</v>
+        <v>11.83</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.24</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.53</v>
+        <v>3.61</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.24</v>
+        <v>19.17</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="15">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F18" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>87.44</v>
+        <v>89.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J18" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="L18" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M18" t="n">
-        <v>37.11</v>
+        <v>39.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="O18" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="P18" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.67</v>
+        <v>14.3</v>
       </c>
       <c r="R18" t="n">
-        <v>7.67</v>
+        <v>7.6</v>
       </c>
       <c r="S18" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="V18" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.78</v>
+        <v>14.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.779999999999999</v>
+        <v>9</v>
       </c>
       <c r="AB18" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>17.11</v>
+        <v>17.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,70 +7998,70 @@
         <v>2.25</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="BH18" t="n">
-        <v>8</v>
+        <v>7.89</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN18" t="n">
         <v>2.06</v>
       </c>
       <c r="BO18" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.94</v>
+        <v>3.83</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS18" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT18" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU18" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BV18" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW18" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX18" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="CC18" t="n">
         <v>4.36</v>
@@ -8073,154 +8073,154 @@
         <v>1.27</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL18" t="n">
         <v>1.85</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CT18" t="n">
         <v>3.25</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DE18" t="n">
         <v>0.06</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DH18" t="n">
-        <v>78.64</v>
+        <v>80.11</v>
       </c>
       <c r="DI18" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="DL18" t="n">
         <v>0.17</v>
       </c>
       <c r="DM18" t="n">
-        <v>36.17</v>
+        <v>37.33</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.88</v>
+        <v>12.78</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12.59</v>
+        <v>13</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.65</v>
+        <v>9.5</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.23</v>
+        <v>47.5</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.35</v>
+        <v>12.67</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.23</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.12</v>
+        <v>4.28</v>
       </c>
       <c r="EA18" t="n">
-        <v>18.12</v>
+        <v>18.11</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F7" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="G7" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>100.67</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>4.89</v>
+        <v>4.4</v>
       </c>
       <c r="L7" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>40.22</v>
+        <v>37.3</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="P7" t="n">
-        <v>10.78</v>
+        <v>10.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.89</v>
+        <v>12.9</v>
       </c>
       <c r="R7" t="n">
-        <v>7.44</v>
+        <v>7.6</v>
       </c>
       <c r="S7" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>53.33</v>
+        <v>52.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.67</v>
+        <v>13.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.67</v>
+        <v>9.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>23.56</v>
+        <v>22.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="AF7" t="n">
         <v>0.22</v>
@@ -3565,70 +3565,70 @@
         <v>2.44</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.890000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.44</v>
+        <v>4.16</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.39</v>
+        <v>4.11</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT7" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU7" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV7" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW7" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX7" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="CC7" t="n">
         <v>4.03</v>
@@ -3637,16 +3637,16 @@
         <v>4.71</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF7" t="n">
         <v>2.67</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI7" t="n">
         <v>1.97</v>
@@ -3661,7 +3661,7 @@
         <v>1.94</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CN7" t="n">
         <v>1.85</v>
@@ -3670,22 +3670,22 @@
         <v>1.26</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV7" t="n">
         <v>2.08</v>
@@ -3694,100 +3694,100 @@
         <v>1.81</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY7" t="n">
         <v>2</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DA7" t="n">
         <v>1.82</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="DE7" t="n">
         <v>0.16</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="DH7" t="n">
-        <v>92</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.39</v>
+        <v>4.16</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="DM7" t="n">
-        <v>40.39</v>
+        <v>38.84</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.23</v>
+        <v>12.05</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.78</v>
+        <v>12.79</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.56</v>
+        <v>8.58</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.28</v>
+        <v>47.95</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.94</v>
+        <v>11.79</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.17</v>
+        <v>7.95</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.56</v>
+        <v>21.11</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="8">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5499,139 +5499,139 @@
         <v>2.56</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>77.67</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AL12" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>41.22</v>
+        <v>39</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11.56</v>
+        <v>11.1</v>
       </c>
       <c r="AR12" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.44</v>
+        <v>10.3</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>50.67</v>
+        <v>51.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>14.11</v>
+        <v>13.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.220000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.89</v>
+        <v>4.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>19.56</v>
+        <v>21.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.33</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.22</v>
+        <v>3.95</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.22</v>
+        <v>3.95</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU12" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY12" t="n">
         <v>1.93</v>
@@ -5640,43 +5640,43 @@
         <v>2.08</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="CC12" t="n">
         <v>2.61</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="CH12" t="n">
         <v>1.49</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK12" t="n">
         <v>1.41</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CN12" t="n">
         <v>2.03</v>
@@ -5685,91 +5685,91 @@
         <v>1.22</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="CR12" t="n">
         <v>1.37</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="CU12" t="n">
         <v>1.52</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CX12" t="n">
         <v>1.5</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="DH12" t="n">
-        <v>84.44</v>
+        <v>82.89</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.89</v>
+        <v>4.74</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="DM12" t="n">
-        <v>41.16</v>
+        <v>40</v>
       </c>
       <c r="DN12" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.5</v>
+        <v>11.26</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.16</v>
+        <v>12.37</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.06</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DS12" t="n">
         <v>0.16</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.94</v>
+        <v>53.21</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.66</v>
+        <v>14.42</v>
       </c>
       <c r="DY12" t="n">
-        <v>10.06</v>
+        <v>9.84</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.61</v>
+        <v>4.58</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.33</v>
+        <v>18.47</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="13">

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="H7" t="n">
-        <v>93.59999999999999</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="M7" t="n">
-        <v>37.3</v>
+        <v>36.91</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="O7" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="P7" t="n">
-        <v>10.6</v>
+        <v>11.09</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.9</v>
+        <v>12.64</v>
       </c>
       <c r="R7" t="n">
-        <v>7.6</v>
+        <v>7.73</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>52.2</v>
+        <v>51.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.2</v>
+        <v>12.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.1</v>
+        <v>8.73</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AC7" t="n">
-        <v>22.5</v>
+        <v>22.27</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AF7" t="n">
         <v>0.22</v>
@@ -3565,70 +3565,70 @@
         <v>2.44</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.529999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BL7" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.16</v>
+        <v>4.3</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT7" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU7" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV7" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW7" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX7" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CC7" t="n">
         <v>4.03</v>
@@ -3643,7 +3643,7 @@
         <v>2.67</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CH7" t="n">
         <v>1.43</v>
@@ -3658,10 +3658,10 @@
         <v>1.54</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN7" t="n">
         <v>1.85</v>
@@ -3715,16 +3715,16 @@
         <v>3.3</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="DH7" t="n">
-        <v>88.73999999999999</v>
+        <v>88</v>
       </c>
       <c r="DI7" t="n">
         <v>0.1</v>
@@ -3733,61 +3733,61 @@
         <v>2.95</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="DM7" t="n">
-        <v>38.84</v>
+        <v>38.55</v>
       </c>
       <c r="DN7" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.05</v>
+        <v>12.25</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.79</v>
+        <v>12.65</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.58</v>
+        <v>8.6</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.95</v>
+        <v>47.55</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.79</v>
+        <v>11.5</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.95</v>
+        <v>7.8</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.11</v>
+        <v>21.05</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="8">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
         <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>0.11</v>
@@ -8320,49 +8320,49 @@
         <v>1.78</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="n">
-        <v>61.5</v>
+        <v>65.89</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.88</v>
+        <v>5.33</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN19" t="n">
-        <v>25.75</v>
+        <v>28.44</v>
       </c>
       <c r="AO19" t="n">
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14.38</v>
+        <v>13.89</v>
       </c>
       <c r="AR19" t="n">
-        <v>11.88</v>
+        <v>12.33</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.880000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AU19" t="n">
         <v>2</v>
@@ -8377,82 +8377,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>52.5</v>
+        <v>53.33</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA19" t="n">
-        <v>13.88</v>
+        <v>14.89</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.119999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="BD19" t="n">
-        <v>19.75</v>
+        <v>19.78</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.289999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="BJ19" t="n">
         <v>1.06</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.18</v>
+        <v>4.33</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.59</v>
+        <v>4.67</v>
       </c>
       <c r="BR19" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS19" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT19" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BV19" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW19" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BX19" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY19" t="n">
         <v>1.62</v>
@@ -8461,73 +8461,73 @@
         <v>1.62</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.19</v>
+        <v>4.14</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.51</v>
+        <v>4.46</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CE19" t="n">
         <v>1.26</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.58</v>
+        <v>3.53</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CM19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CQ19" t="n">
         <v>2.43</v>
       </c>
-      <c r="CN19" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CO19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="CP19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CQ19" t="n">
-        <v>2.38</v>
-      </c>
       <c r="CR19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CX19" t="n">
         <v>1.55</v>
@@ -8536,94 +8536,94 @@
         <v>1.89</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="DE19" t="n">
         <v>0.11</v>
       </c>
       <c r="DF19" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="DH19" t="n">
-        <v>76.81999999999999</v>
+        <v>78.17</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.12</v>
+        <v>5.33</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DM19" t="n">
-        <v>38.59</v>
+        <v>39.22</v>
       </c>
       <c r="DN19" t="n">
         <v>1.06</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.53</v>
+        <v>13.34</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.06</v>
+        <v>11.33</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.470000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.59</v>
+        <v>54.88</v>
       </c>
       <c r="DW19" t="n">
         <v>0.11</v>
       </c>
       <c r="DX19" t="n">
-        <v>17</v>
+        <v>17.33</v>
       </c>
       <c r="DY19" t="n">
-        <v>11</v>
+        <v>11.23</v>
       </c>
       <c r="DZ19" t="n">
-        <v>6</v>
+        <v>6.11</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.53</v>
+        <v>17.67</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0.12</v>
@@ -1469,139 +1469,139 @@
         <v>1.62</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="AI2" t="n">
-        <v>102.56</v>
+        <v>102.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.56</v>
+        <v>5.4</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>51.11</v>
+        <v>51.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.67</v>
+        <v>10.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.44</v>
+        <v>12.7</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.78</v>
+        <v>6.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>54.89</v>
+        <v>54.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.44</v>
+        <v>11.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.56</v>
+        <v>8.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.89</v>
+        <v>3.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>16</v>
+        <v>16.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="BF2" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.24</v>
+        <v>10.06</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL2" t="n">
         <v>1.06</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.76</v>
+        <v>5.61</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT2" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU2" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX2" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY2" t="n">
         <v>1.42</v>
@@ -1610,43 +1610,43 @@
         <v>1.47</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.15</v>
+        <v>4.08</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.52</v>
+        <v>4.45</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="CE2" t="n">
         <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN2" t="n">
         <v>1.96</v>
@@ -1655,22 +1655,22 @@
         <v>1.22</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CV2" t="n">
         <v>2.12</v>
@@ -1679,7 +1679,7 @@
         <v>1.8</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY2" t="n">
         <v>1.83</v>
@@ -1688,91 +1688,91 @@
         <v>2.43</v>
       </c>
       <c r="DA2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB2" t="n">
         <v>1.24</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="DE2" t="n">
         <v>0.11</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="DG2" t="n">
-        <v>4.06</v>
+        <v>3.95</v>
       </c>
       <c r="DH2" t="n">
-        <v>102.88</v>
+        <v>102.67</v>
       </c>
       <c r="DI2" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="DK2" t="n">
-        <v>7.12</v>
+        <v>6.95</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="DM2" t="n">
-        <v>58.59</v>
+        <v>58.39</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.47</v>
+        <v>10.5</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.88</v>
+        <v>12.06</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.59</v>
+        <v>6.39</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>56.77</v>
+        <v>56.39</v>
       </c>
       <c r="DW2" t="n">
         <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.47</v>
+        <v>14.89</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.76</v>
+        <v>9.44</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.71</v>
+        <v>5.44</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.83</v>
+        <v>18.22</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="3">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0.11</v>
@@ -2678,139 +2678,139 @@
         <v>2.22</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>94.25</v>
+        <v>96</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN5" t="n">
-        <v>41.12</v>
+        <v>40</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AP5" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.75</v>
+        <v>10.44</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.88</v>
+        <v>13.44</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.5</v>
+        <v>8.56</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.75</v>
+        <v>14</v>
       </c>
       <c r="BB5" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.38</v>
+        <v>21.22</v>
       </c>
       <c r="BE5" t="n">
         <v>1.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.35</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.35</v>
+        <v>5.33</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.12</v>
+        <v>88.89</v>
       </c>
       <c r="BS5" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BT5" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU5" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV5" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX5" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY5" t="n">
         <v>1.65</v>
@@ -2819,166 +2819,166 @@
         <v>1.74</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.1</v>
+        <v>4.06</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.34</v>
+        <v>4.29</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI5" t="n">
         <v>2.11</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO5" t="n">
         <v>1.19</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CW5" t="n">
         <v>1.7</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="DB5" t="n">
         <v>1.22</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="DE5" t="n">
         <v>0.11</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="DH5" t="n">
-        <v>101.59</v>
+        <v>102.06</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.88</v>
+        <v>5.72</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM5" t="n">
-        <v>53.12</v>
+        <v>51.89</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.24</v>
+        <v>11.06</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.77</v>
+        <v>11.66</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.88</v>
+        <v>7.94</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57.94</v>
+        <v>57.28</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DX5" t="n">
-        <v>17.06</v>
+        <v>17</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.94</v>
+        <v>11</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.59</v>
+        <v>21.5</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="EC5" t="n">
         <v>1.94</v>
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F6" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="G6" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="H6" t="n">
-        <v>73.67</v>
+        <v>72.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J6" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="K6" t="n">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="M6" t="n">
-        <v>36.44</v>
+        <v>36.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="O6" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="P6" t="n">
-        <v>11.11</v>
+        <v>11</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.89</v>
+        <v>11.5</v>
       </c>
       <c r="R6" t="n">
-        <v>8.44</v>
+        <v>8.4</v>
       </c>
       <c r="S6" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="U6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>53.22</v>
+        <v>53.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.22</v>
+        <v>13.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.109999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.11</v>
+        <v>4.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>14.67</v>
+        <v>15.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AF6" t="n">
         <v>0.12</v>
@@ -3162,70 +3162,70 @@
         <v>1.62</v>
       </c>
       <c r="BG6" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.82</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="BJ6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BM6" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="BK6" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1</v>
-      </c>
       <c r="BN6" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.82</v>
+        <v>4.72</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.12</v>
+        <v>88.89</v>
       </c>
       <c r="BS6" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU6" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV6" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW6" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BX6" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="CC6" t="n">
         <v>2.39</v>
@@ -3237,13 +3237,13 @@
         <v>1.35</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI6" t="n">
         <v>2.05</v>
@@ -3252,22 +3252,22 @@
         <v>1.74</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CQ6" t="n">
         <v>2.99</v>
@@ -3276,82 +3276,82 @@
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CW6" t="n">
         <v>1.75</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="DA6" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="DB6" t="n">
         <v>1.26</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="DH6" t="n">
-        <v>87.59</v>
+        <v>86.17</v>
       </c>
       <c r="DI6" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DK6" t="n">
-        <v>6</v>
+        <v>5.94</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DM6" t="n">
-        <v>43.76</v>
+        <v>43.22</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.76</v>
+        <v>11.67</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.88</v>
+        <v>10.72</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DS6" t="n">
         <v>0.06</v>
@@ -3363,25 +3363,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>53.64</v>
+        <v>53.66</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.59</v>
+        <v>14.22</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.29</v>
+        <v>10.11</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.3</v>
+        <v>4.11</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.94</v>
+        <v>17.06</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="EC6" t="n">
         <v>2</v>
@@ -3628,7 +3628,7 @@
         <v>3.5</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CC7" t="n">
         <v>4.03</v>
@@ -3679,7 +3679,7 @@
         <v>1.39</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CT7" t="n">
         <v>3.14</v>
@@ -3712,7 +3712,7 @@
         <v>1.96</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="DE7" t="n">
         <v>0.2</v>
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F10" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="G10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="H10" t="n">
-        <v>88.62</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="K10" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="L10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M10" t="n">
-        <v>44.62</v>
+        <v>45</v>
       </c>
       <c r="N10" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="P10" t="n">
-        <v>10.62</v>
+        <v>11.11</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.62</v>
+        <v>12.44</v>
       </c>
       <c r="R10" t="n">
-        <v>5.38</v>
+        <v>5.56</v>
       </c>
       <c r="S10" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="U10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>58.38</v>
+        <v>57.44</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.5</v>
+        <v>13.89</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.75</v>
+        <v>8.33</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.75</v>
+        <v>5.56</v>
       </c>
       <c r="AC10" t="n">
-        <v>16.25</v>
+        <v>16.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AF10" t="n">
         <v>0.11</v>
@@ -4774,70 +4774,70 @@
         <v>2.11</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.76</v>
+        <v>8.67</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BO10" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT10" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU10" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BV10" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW10" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BX10" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.86</v>
+        <v>3.81</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.19</v>
+        <v>4.14</v>
       </c>
       <c r="CC10" t="n">
         <v>2.54</v>
@@ -4846,61 +4846,61 @@
         <v>3.11</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.68</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN10" t="n">
         <v>1.94</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CV10" t="n">
         <v>2.27</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX10" t="n">
         <v>1.51</v>
@@ -4909,94 +4909,94 @@
         <v>1.82</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB10" t="n">
         <v>1.22</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="DE10" t="n">
         <v>0.11</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="DH10" t="n">
-        <v>70.41</v>
+        <v>72.11</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.12</v>
+        <v>4.06</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM10" t="n">
-        <v>33.88</v>
+        <v>34.66</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.47</v>
+        <v>10.72</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.88</v>
+        <v>12.77</v>
       </c>
       <c r="DR10" t="n">
         <v>7</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>56.71</v>
+        <v>56.33</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.94</v>
+        <v>13.66</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.35</v>
+        <v>8.16</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.59</v>
+        <v>5.5</v>
       </c>
       <c r="EA10" t="n">
-        <v>16</v>
+        <v>16.05</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="11">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>0.33</v>
@@ -7517,49 +7517,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="AI17" t="n">
-        <v>94.5</v>
+        <v>93.67</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.75</v>
+        <v>5.89</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN17" t="n">
-        <v>48.62</v>
+        <v>46.44</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.88</v>
+        <v>12.22</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.62</v>
+        <v>11.78</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.38</v>
+        <v>7.22</v>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>57.12</v>
+        <v>58.11</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA17" t="n">
         <v>16</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.25</v>
+        <v>9.67</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.75</v>
+        <v>6.33</v>
       </c>
       <c r="BD17" t="n">
-        <v>15.12</v>
+        <v>16.89</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="BG17" t="n">
         <v>3</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.06</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI17" t="n">
         <v>3</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.18</v>
+        <v>5.28</v>
       </c>
       <c r="BR17" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS17" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT17" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU17" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV17" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW17" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BX17" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>1.6</v>
@@ -7655,73 +7655,73 @@
         <v>1.59</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.19</v>
+        <v>4.16</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="CE17" t="n">
         <v>1.32</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CG17" t="n">
         <v>3.16</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CK17" t="n">
         <v>1.45</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO17" t="n">
         <v>1.23</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CR17" t="n">
         <v>1.37</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CT17" t="n">
         <v>3.19</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX17" t="n">
         <v>1.5</v>
@@ -7745,46 +7745,46 @@
         <v>2.88</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.70999999999999</v>
+        <v>96.17</v>
       </c>
       <c r="DI17" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.35</v>
+        <v>5.44</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM17" t="n">
-        <v>51.41</v>
+        <v>50.16</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.71</v>
+        <v>11.89</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.23</v>
+        <v>12.28</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.18</v>
+        <v>7.11</v>
       </c>
       <c r="DS17" t="n">
         <v>0.06</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>56.29</v>
+        <v>56.84</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX17" t="n">
-        <v>16.88</v>
+        <v>16.84</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.41</v>
+        <v>10.56</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6.47</v>
+        <v>6.28</v>
       </c>
       <c r="EA17" t="n">
-        <v>16.64</v>
+        <v>17.44</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="18">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="H18" t="n">
-        <v>89.2</v>
+        <v>85.36</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M18" t="n">
-        <v>39.1</v>
+        <v>37.18</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O18" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>12.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.3</v>
+        <v>14.36</v>
       </c>
       <c r="R18" t="n">
-        <v>7.6</v>
+        <v>7.73</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>51</v>
+        <v>49.45</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>14.2</v>
+        <v>13.73</v>
       </c>
       <c r="AA18" t="n">
-        <v>9</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.2</v>
+        <v>5.27</v>
       </c>
       <c r="AC18" t="n">
-        <v>17.2</v>
+        <v>17.27</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -8001,67 +8001,67 @@
         <v>3.11</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.89</v>
+        <v>8</v>
       </c>
       <c r="BI18" t="n">
         <v>3.11</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BN18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU18" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV18" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW18" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX18" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="CC18" t="n">
         <v>4.36</v>
@@ -8070,13 +8070,13 @@
         <v>4.85</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF18" t="n">
         <v>2.32</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CH18" t="n">
         <v>1.58</v>
@@ -8085,16 +8085,16 @@
         <v>2.31</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CN18" t="n">
         <v>1.95</v>
@@ -8103,7 +8103,7 @@
         <v>1.16</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CQ18" t="n">
         <v>2.49</v>
@@ -8148,79 +8148,79 @@
         <v>2.58</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DH18" t="n">
-        <v>80.11</v>
+        <v>78.37</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM18" t="n">
-        <v>37.33</v>
+        <v>36.31</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.78</v>
+        <v>12.79</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13</v>
+        <v>13.11</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.5</v>
+        <v>9.48</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.5</v>
+        <v>46.78</v>
       </c>
       <c r="DW18" t="n">
         <v>0.11</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.67</v>
+        <v>12.48</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.390000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.28</v>
+        <v>4.36</v>
       </c>
       <c r="EA18" t="n">
-        <v>18.11</v>
+        <v>18.1</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="19">
@@ -8359,7 +8359,7 @@
         <v>12.33</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.44</v>
+        <v>9.56</v>
       </c>
       <c r="AT19" t="n">
         <v>0.78</v>
@@ -8386,16 +8386,16 @@
         <v>14.89</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.890000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC19" t="n">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="BD19" t="n">
         <v>19.78</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BF19" t="n">
         <v>2</v>
@@ -8464,7 +8464,7 @@
         <v>4.14</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
       <c r="CC19" t="n">
         <v>2.05</v>
@@ -8515,10 +8515,10 @@
         <v>1.36</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="CU19" t="n">
         <v>1.66</v>
@@ -8527,13 +8527,13 @@
         <v>2.37</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CX19" t="n">
         <v>1.55</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.39</v>
@@ -8548,7 +8548,7 @@
         <v>1.61</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="DE19" t="n">
         <v>0.11</v>
@@ -8590,7 +8590,7 @@
         <v>11.33</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.27</v>
+        <v>9.34</v>
       </c>
       <c r="DS19" t="n">
         <v>0.16</v>
@@ -8611,16 +8611,16 @@
         <v>17.33</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.23</v>
+        <v>11.28</v>
       </c>
       <c r="DZ19" t="n">
-        <v>6.11</v>
+        <v>6.06</v>
       </c>
       <c r="EA19" t="n">
         <v>17.67</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="EC19" t="n">
         <v>1.89</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F2" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="G2" t="n">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>103.25</v>
+        <v>101.78</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="K2" t="n">
-        <v>8.880000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="M2" t="n">
-        <v>67</v>
+        <v>66.44</v>
       </c>
       <c r="N2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="O2" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>10.25</v>
+        <v>10.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.25</v>
+        <v>12</v>
       </c>
       <c r="R2" t="n">
-        <v>6.38</v>
+        <v>6.11</v>
       </c>
       <c r="S2" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="T2" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="U2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>58.88</v>
+        <v>58.11</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.88</v>
+        <v>18.11</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.12</v>
+        <v>10.89</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.75</v>
+        <v>7.22</v>
       </c>
       <c r="AC2" t="n">
-        <v>19.88</v>
+        <v>21</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AF2" t="n">
         <v>0.1</v>
@@ -1550,70 +1550,70 @@
         <v>2.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.06</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.28</v>
+        <v>4.21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.61</v>
+        <v>5.42</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT2" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU2" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX2" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BZ2" t="n">
         <v>1.47</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.08</v>
+        <v>4.1</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.45</v>
+        <v>4.47</v>
       </c>
       <c r="CC2" t="n">
         <v>2.26</v>
@@ -1625,7 +1625,7 @@
         <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CG2" t="n">
         <v>3.3</v>
@@ -1637,55 +1637,55 @@
         <v>2.02</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CK2" t="n">
         <v>1.45</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM2" t="n">
         <v>2.53</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CO2" t="n">
         <v>1.22</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CR2" t="n">
         <v>1.39</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CT2" t="n">
         <v>3.16</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CW2" t="n">
         <v>1.8</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY2" t="n">
         <v>1.83</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="DA2" t="n">
         <v>1.99</v>
@@ -1694,85 +1694,85 @@
         <v>1.24</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.95</v>
+        <v>3.79</v>
       </c>
       <c r="DH2" t="n">
-        <v>102.67</v>
+        <v>102</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.95</v>
+        <v>6.74</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM2" t="n">
-        <v>58.39</v>
+        <v>58.58</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.5</v>
+        <v>10.63</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.06</v>
+        <v>12.37</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.39</v>
+        <v>6.26</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>56.39</v>
+        <v>56.16</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.89</v>
+        <v>14.74</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.44</v>
+        <v>9.42</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.44</v>
+        <v>5.31</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.22</v>
+        <v>18.84</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H5" t="n">
-        <v>108.11</v>
+        <v>106.3</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="K5" t="n">
-        <v>7.33</v>
+        <v>7.1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>63.78</v>
+        <v>60.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>11.67</v>
+        <v>11.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.890000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="R5" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD5" t="n">
         <v>2.11</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>60.56</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>12.67</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>21.78</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.23</v>
-      </c>
       <c r="AE5" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="AF5" t="n">
         <v>0.11</v>
@@ -2759,70 +2759,70 @@
         <v>1.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.279999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.83</v>
+        <v>3.89</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.33</v>
+        <v>5.37</v>
       </c>
       <c r="BR5" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS5" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT5" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU5" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BV5" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX5" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.06</v>
+        <v>4.03</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="CC5" t="n">
         <v>2.19</v>
@@ -2834,25 +2834,25 @@
         <v>1.3</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK5" t="n">
         <v>1.47</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CM5" t="n">
         <v>2.54</v>
@@ -2861,25 +2861,25 @@
         <v>1.95</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV5" t="n">
         <v>2.27</v>
@@ -2900,88 +2900,88 @@
         <v>2</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="DH5" t="n">
-        <v>102.06</v>
+        <v>101.42</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.72</v>
+        <v>5.68</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM5" t="n">
-        <v>51.89</v>
+        <v>50.89</v>
       </c>
       <c r="DN5" t="n">
         <v>0.84</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.06</v>
+        <v>11.05</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.66</v>
+        <v>11.68</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.94</v>
+        <v>8</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57.28</v>
+        <v>56.74</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX5" t="n">
-        <v>17</v>
+        <v>16.58</v>
       </c>
       <c r="DY5" t="n">
-        <v>11</v>
+        <v>10.74</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6</v>
+        <v>5.84</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.5</v>
+        <v>21.1</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0.2</v>
@@ -3081,52 +3081,52 @@
         <v>2.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AH6" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AI6" t="n">
-        <v>103.25</v>
+        <v>101.56</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AL6" t="n">
-        <v>6.25</v>
+        <v>6.22</v>
       </c>
       <c r="AM6" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AN6" t="n">
-        <v>52</v>
+        <v>50.11</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP6" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.5</v>
+        <v>12.33</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.75</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.119999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>54.12</v>
+        <v>54</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA6" t="n">
-        <v>15</v>
+        <v>14.67</v>
       </c>
       <c r="BB6" t="n">
-        <v>11.62</v>
+        <v>11.33</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.5</v>
+        <v>19.22</v>
       </c>
       <c r="BE6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BF6" t="n">
         <v>1.56</v>
       </c>
-      <c r="BF6" t="n">
-        <v>1.62</v>
-      </c>
       <c r="BG6" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.720000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.89</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.72</v>
+        <v>4.74</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.72</v>
+        <v>4.79</v>
       </c>
       <c r="BR6" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT6" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU6" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BV6" t="n">
-        <v>22.22</v>
+        <v>26.32</v>
       </c>
       <c r="BW6" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY6" t="n">
         <v>2.03</v>
@@ -3225,13 +3225,13 @@
         <v>3.5</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.39</v>
+        <v>2.54</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
       <c r="CE6" t="n">
         <v>1.35</v>
@@ -3240,7 +3240,7 @@
         <v>2.61</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CH6" t="n">
         <v>1.45</v>
@@ -3252,31 +3252,31 @@
         <v>1.74</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL6" t="n">
         <v>1.75</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP6" t="n">
         <v>1.81</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CT6" t="n">
         <v>3.17</v>
@@ -3285,7 +3285,7 @@
         <v>1.48</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CW6" t="n">
         <v>1.75</v>
@@ -3303,7 +3303,7 @@
         <v>1.98</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC6" t="n">
         <v>1.86</v>
@@ -3312,79 +3312,79 @@
         <v>3.08</v>
       </c>
       <c r="DE6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>42.79</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>53.63</v>
+      </c>
+      <c r="DW6" t="n">
         <v>0.16</v>
       </c>
-      <c r="DF6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="DG6" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>86.17</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="DM6" t="n">
-        <v>43.22</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="DP6" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="DQ6" t="n">
-        <v>10.72</v>
-      </c>
-      <c r="DR6" t="n">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="DS6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DT6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV6" t="n">
-        <v>53.66</v>
-      </c>
-      <c r="DW6" t="n">
-        <v>0.17</v>
-      </c>
       <c r="DX6" t="n">
-        <v>14.22</v>
+        <v>14.11</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.11</v>
+        <v>10.05</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.06</v>
+        <v>17.05</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="EC6" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0.18</v>
@@ -3484,139 +3484,139 @@
         <v>2.82</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AI7" t="n">
-        <v>83.33</v>
+        <v>78.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN7" t="n">
-        <v>40.56</v>
+        <v>37.7</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.67</v>
+        <v>13.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.67</v>
+        <v>12.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.67</v>
+        <v>10.3</v>
       </c>
       <c r="AT7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>43.22</v>
+        <v>42.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.67</v>
+        <v>6.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.56</v>
+        <v>20.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.75</v>
+        <v>8.76</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BJ7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BL7" t="n">
         <v>0.9</v>
       </c>
-      <c r="BK7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.95</v>
-      </c>
       <c r="BM7" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="BR7" t="n">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>90</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BU7" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW7" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX7" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BY7" t="n">
         <v>2.53</v>
@@ -3625,40 +3625,40 @@
         <v>2.67</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.76</v>
+        <v>3.86</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.03</v>
+        <v>4.38</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.71</v>
+        <v>5.14</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CI7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CL7" t="n">
         <v>1.97</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>1.96</v>
       </c>
       <c r="CM7" t="n">
         <v>2.35</v>
@@ -3667,25 +3667,25 @@
         <v>1.85</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="CR7" t="n">
         <v>1.39</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="CT7" t="n">
         <v>3.14</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CV7" t="n">
         <v>2.08</v>
@@ -3697,97 +3697,97 @@
         <v>1.59</v>
       </c>
       <c r="CY7" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="DH7" t="n">
-        <v>88</v>
+        <v>85.38</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ7" t="n">
         <v>2.95</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM7" t="n">
-        <v>38.55</v>
+        <v>37.29</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.25</v>
+        <v>12.14</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.65</v>
+        <v>12.76</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.6</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.55</v>
+        <v>47.05</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.5</v>
+        <v>11.24</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.8</v>
+        <v>7.72</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.05</v>
+        <v>21.24</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="8">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0.11</v>
@@ -4693,139 +4693,139 @@
         <v>1.78</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>54.22</v>
+        <v>58.7</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AL10" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>24.33</v>
+        <v>26.8</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.33</v>
+        <v>11.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.11</v>
+        <v>13.1</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.44</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>55.22</v>
+        <v>54.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>13.44</v>
+        <v>13.1</v>
       </c>
       <c r="BB10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.44</v>
+        <v>5.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>15.78</v>
+        <v>17.4</v>
       </c>
       <c r="BE10" t="n">
         <v>1.19</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.67</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BL10" t="n">
         <v>0.89</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BO10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.28</v>
+        <v>4.21</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.33</v>
+        <v>4.21</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU10" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BV10" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW10" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BX10" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY10" t="n">
         <v>1.74</v>
@@ -4834,40 +4834,40 @@
         <v>1.82</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.81</v>
+        <v>3.84</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.14</v>
+        <v>4.18</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="CE10" t="n">
         <v>1.31</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CG10" t="n">
         <v>3.21</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK10" t="n">
         <v>1.43</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CM10" t="n">
         <v>2.53</v>
@@ -4888,7 +4888,7 @@
         <v>1.36</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CT10" t="n">
         <v>3.29</v>
@@ -4897,7 +4897,7 @@
         <v>1.58</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CW10" t="n">
         <v>1.69</v>
@@ -4909,10 +4909,10 @@
         <v>1.82</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DB10" t="n">
         <v>1.22</v>
@@ -4921,82 +4921,82 @@
         <v>1.72</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="DH10" t="n">
-        <v>72.11</v>
+        <v>73.53</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.06</v>
+        <v>3.95</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM10" t="n">
-        <v>34.66</v>
+        <v>35.42</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.72</v>
+        <v>11.1</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.77</v>
+        <v>12.79</v>
       </c>
       <c r="DR10" t="n">
         <v>7</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>56.33</v>
+        <v>55.89</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.66</v>
+        <v>13.47</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.16</v>
+        <v>8.1</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.5</v>
+        <v>5.37</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.05</v>
+        <v>16.89</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="11">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F17" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="G17" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="H17" t="n">
-        <v>98.67</v>
+        <v>96.2</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L17" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="M17" t="n">
-        <v>53.89</v>
+        <v>53.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="O17" t="n">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>11.56</v>
+        <v>11.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.78</v>
+        <v>12.9</v>
       </c>
       <c r="R17" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AB17" t="n">
         <v>7</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>55.56</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>17.67</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>11.44</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>6.22</v>
       </c>
       <c r="AC17" t="n">
         <v>18</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,70 +7595,70 @@
         <v>3</v>
       </c>
       <c r="BG17" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.109999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.83</v>
+        <v>4.05</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.28</v>
+        <v>5.11</v>
       </c>
       <c r="BR17" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS17" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT17" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU17" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BV17" t="n">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
       <c r="BW17" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.87</v>
+        <v>3.95</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.16</v>
+        <v>4.25</v>
       </c>
       <c r="CC17" t="n">
         <v>2.36</v>
@@ -7667,16 +7667,16 @@
         <v>2.58</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="CI17" t="n">
         <v>2.03</v>
@@ -7685,25 +7685,25 @@
         <v>1.74</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="CR17" t="n">
         <v>1.37</v>
@@ -7748,76 +7748,76 @@
         <v>0.16</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.17</v>
+        <v>95</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.44</v>
+        <v>5.58</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="DM17" t="n">
-        <v>50.16</v>
+        <v>50</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.61</v>
+        <v>2.9</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.89</v>
+        <v>11.95</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.28</v>
+        <v>12.37</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.11</v>
+        <v>7.05</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>56.84</v>
+        <v>56.74</v>
       </c>
       <c r="DW17" t="n">
         <v>0.16</v>
       </c>
       <c r="DX17" t="n">
-        <v>16.84</v>
+        <v>17.32</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.56</v>
+        <v>10.63</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6.28</v>
+        <v>6.68</v>
       </c>
       <c r="EA17" t="n">
-        <v>17.44</v>
+        <v>17.47</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
         <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>0.09</v>
@@ -7920,136 +7920,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AI18" t="n">
-        <v>68.75</v>
+        <v>68.56</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="AL18" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>35.12</v>
+        <v>33.78</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.75</v>
+        <v>12.11</v>
       </c>
       <c r="AR18" t="n">
-        <v>11.38</v>
+        <v>12.22</v>
       </c>
       <c r="AS18" t="n">
-        <v>11.88</v>
+        <v>11.33</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>43.12</v>
+        <v>43.33</v>
       </c>
       <c r="AZ18" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BK18" t="n">
         <v>0.25</v>
       </c>
-      <c r="BA18" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>19.25</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>8</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0.26</v>
-      </c>
       <c r="BL18" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BN18" t="n">
         <v>2.05</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.32</v>
+        <v>3.55</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS18" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT18" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU18" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BV18" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BW18" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX18" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY18" t="n">
         <v>2.4</v>
@@ -8058,55 +8058,55 @@
         <v>2.53</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.73</v>
+        <v>3.82</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.99</v>
+        <v>4.08</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.36</v>
+        <v>4.77</v>
       </c>
       <c r="CD18" t="n">
-        <v>4.85</v>
+        <v>5.24</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.39</v>
+        <v>3.22</v>
       </c>
       <c r="CH18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="CP18" t="n">
         <v>1.58</v>
       </c>
-      <c r="CI18" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="CJ18" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CK18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="CL18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="CM18" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="CN18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="CO18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="CP18" t="n">
-        <v>1.59</v>
-      </c>
       <c r="CQ18" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
@@ -8151,76 +8151,76 @@
         <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="DH18" t="n">
-        <v>78.37</v>
+        <v>77.8</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM18" t="n">
-        <v>36.31</v>
+        <v>35.65</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.79</v>
+        <v>12.5</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.11</v>
+        <v>13.4</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.48</v>
+        <v>9.35</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.78</v>
+        <v>46.7</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.48</v>
+        <v>12.15</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.1</v>
+        <v>7.95</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.36</v>
+        <v>4.2</v>
       </c>
       <c r="EA18" t="n">
         <v>18.1</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="19">
@@ -8230,94 +8230,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="G19" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="H19" t="n">
-        <v>90.44</v>
+        <v>87.2</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K19" t="n">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="L19" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="M19" t="n">
-        <v>50</v>
+        <v>47.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>12.78</v>
+        <v>12.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>10.33</v>
+        <v>10.8</v>
       </c>
       <c r="R19" t="n">
-        <v>9.109999999999999</v>
+        <v>9</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="U19" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V19" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>56.44</v>
+        <v>57.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.78</v>
+        <v>20.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>13.56</v>
+        <v>14.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.22</v>
+        <v>6</v>
       </c>
       <c r="AC19" t="n">
-        <v>15.56</v>
+        <v>16.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
         <v>0.11</v>
@@ -8401,70 +8401,70 @@
         <v>2</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.56</v>
+        <v>3.37</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.5</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.56</v>
+        <v>3.37</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.33</v>
+        <v>4.37</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.67</v>
+        <v>4.63</v>
       </c>
       <c r="BR19" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BT19" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BU19" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BV19" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW19" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BX19" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.14</v>
+        <v>4.17</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.45</v>
+        <v>4.52</v>
       </c>
       <c r="CC19" t="n">
         <v>2.05</v>
@@ -8476,31 +8476,31 @@
         <v>1.26</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK19" t="n">
         <v>1.49</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM19" t="n">
         <v>2.42</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO19" t="n">
         <v>1.16</v>
@@ -8509,13 +8509,13 @@
         <v>1.6</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CR19" t="n">
         <v>1.36</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CT19" t="n">
         <v>3.21</v>
@@ -8524,19 +8524,19 @@
         <v>1.66</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CX19" t="n">
         <v>1.55</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DA19" t="n">
         <v>1.92</v>
@@ -8548,49 +8548,49 @@
         <v>1.61</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="DH19" t="n">
-        <v>78.17</v>
+        <v>77.11</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.33</v>
+        <v>5.42</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM19" t="n">
-        <v>39.22</v>
+        <v>38.47</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.34</v>
+        <v>13.26</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.33</v>
+        <v>11.52</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.34</v>
+        <v>9.27</v>
       </c>
       <c r="DS19" t="n">
         <v>0.16</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.88</v>
+        <v>55.31</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.33</v>
+        <v>17.68</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.28</v>
+        <v>11.74</v>
       </c>
       <c r="DZ19" t="n">
-        <v>6.06</v>
+        <v>5.95</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.67</v>
+        <v>17.84</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -2636,7 +2636,7 @@
         <v>10.1</v>
       </c>
       <c r="R5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="S5" t="n">
         <v>1.3</v>
@@ -2948,7 +2948,7 @@
         <v>11.68</v>
       </c>
       <c r="DR5" t="n">
-        <v>8</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS5" t="n">
         <v>0.21</v>
@@ -3144,19 +3144,19 @@
         <v>0.22</v>
       </c>
       <c r="BA6" t="n">
-        <v>14.67</v>
+        <v>14.78</v>
       </c>
       <c r="BB6" t="n">
-        <v>11.33</v>
+        <v>11.44</v>
       </c>
       <c r="BC6" t="n">
         <v>3.33</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.22</v>
+        <v>19.33</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BF6" t="n">
         <v>1.56</v>
@@ -3369,19 +3369,19 @@
         <v>0.16</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.11</v>
+        <v>14.16</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.05</v>
+        <v>10.1</v>
       </c>
       <c r="DZ6" t="n">
         <v>4.05</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.05</v>
+        <v>17.1</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="EC6" t="n">
         <v>1.95</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="H5" t="n">
-        <v>106.3</v>
+        <v>106.27</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K5" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="M5" t="n">
-        <v>60.7</v>
+        <v>58.36</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="P5" t="n">
-        <v>11.6</v>
+        <v>11.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.1</v>
+        <v>10.27</v>
       </c>
       <c r="R5" t="n">
-        <v>7.6</v>
+        <v>7.64</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>59.2</v>
+        <v>60</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.9</v>
+        <v>18.91</v>
       </c>
       <c r="AA5" t="n">
-        <v>12</v>
+        <v>12.18</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.9</v>
+        <v>6.73</v>
       </c>
       <c r="AC5" t="n">
-        <v>21</v>
+        <v>21.73</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AF5" t="n">
         <v>0.11</v>
@@ -2759,70 +2759,70 @@
         <v>1.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.369999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="BI5" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.37</v>
+        <v>5.35</v>
       </c>
       <c r="BR5" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS5" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT5" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU5" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV5" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX5" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.24</v>
+        <v>4.18</v>
       </c>
       <c r="CC5" t="n">
         <v>2.19</v>
@@ -2831,16 +2831,16 @@
         <v>2.4</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI5" t="n">
         <v>2.1</v>
@@ -2849,139 +2849,139 @@
         <v>1.72</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL5" t="n">
         <v>1.9</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO5" t="n">
         <v>1.2</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DA5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB5" t="n">
         <v>1.23</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="DE5" t="n">
         <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="DH5" t="n">
-        <v>101.42</v>
+        <v>101.65</v>
       </c>
       <c r="DI5" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.68</v>
+        <v>5.7</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="DM5" t="n">
-        <v>50.89</v>
+        <v>50.1</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.05</v>
+        <v>11.25</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.68</v>
+        <v>11.7</v>
       </c>
       <c r="DR5" t="n">
         <v>8.050000000000001</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.74</v>
+        <v>57.3</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.58</v>
+        <v>16.7</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.74</v>
+        <v>10.9</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.84</v>
+        <v>5.8</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="EB5" t="n">
         <v>1.82</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="6">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="G10" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="H10" t="n">
-        <v>90</v>
+        <v>89.7</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>43.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
-        <v>11.11</v>
+        <v>10.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.44</v>
+        <v>12.4</v>
       </c>
       <c r="R10" t="n">
-        <v>5.56</v>
+        <v>5.5</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>57.44</v>
+        <v>56.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.89</v>
+        <v>13.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.33</v>
+        <v>7.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.56</v>
+        <v>5.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>16.33</v>
+        <v>17.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AF10" t="n">
         <v>0.1</v>
@@ -4774,70 +4774,70 @@
         <v>2.3</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.470000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.21</v>
+        <v>4.15</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.21</v>
+        <v>4.35</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>84.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT10" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BV10" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW10" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BX10" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.18</v>
+        <v>4.14</v>
       </c>
       <c r="CC10" t="n">
         <v>2.9</v>
@@ -4849,19 +4849,19 @@
         <v>1.31</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CG10" t="n">
         <v>3.21</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CK10" t="n">
         <v>1.43</v>
@@ -4870,7 +4870,7 @@
         <v>1.88</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CN10" t="n">
         <v>1.94</v>
@@ -4879,7 +4879,7 @@
         <v>1.2</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CQ10" t="n">
         <v>2.69</v>
@@ -4897,7 +4897,7 @@
         <v>1.58</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CW10" t="n">
         <v>1.69</v>
@@ -4906,13 +4906,13 @@
         <v>1.51</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB10" t="n">
         <v>1.22</v>
@@ -4927,76 +4927,76 @@
         <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="DH10" t="n">
-        <v>73.53</v>
+        <v>74.2</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="DM10" t="n">
-        <v>35.42</v>
+        <v>35.25</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DO10" t="n">
         <v>2.1</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.79</v>
+        <v>12.75</v>
       </c>
       <c r="DR10" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.89</v>
+        <v>55.5</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.47</v>
+        <v>13.1</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.1</v>
+        <v>7.85</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.37</v>
+        <v>5.25</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.89</v>
+        <v>17.3</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>0.3</v>
@@ -7517,49 +7517,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="AI17" t="n">
-        <v>93.67</v>
+        <v>89.2</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.89</v>
+        <v>5.4</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN17" t="n">
-        <v>46.44</v>
+        <v>43.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.22</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.78</v>
+        <v>12.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.22</v>
+        <v>7.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>58.11</v>
+        <v>55.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>16</v>
+        <v>15.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.67</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.33</v>
+        <v>5.9</v>
       </c>
       <c r="BD17" t="n">
-        <v>16.89</v>
+        <v>17.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="BF17" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.16</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="BR17" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS17" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT17" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU17" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV17" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW17" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BX17" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>1.57</v>
@@ -7655,40 +7655,40 @@
         <v>1.56</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.58</v>
+        <v>2.67</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CG17" t="n">
         <v>2.99</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.74</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM17" t="n">
         <v>2.37</v>
@@ -7697,127 +7697,127 @@
         <v>1.85</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CW17" t="n">
         <v>1.77</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="DB17" t="n">
         <v>1.24</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="DH17" t="n">
-        <v>95</v>
+        <v>92.7</v>
       </c>
       <c r="DI17" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.58</v>
+        <v>5.35</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DM17" t="n">
-        <v>50</v>
+        <v>48.35</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.95</v>
+        <v>11.85</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.37</v>
+        <v>12.55</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.05</v>
+        <v>7.25</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>56.74</v>
+        <v>55.5</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX17" t="n">
-        <v>17.32</v>
+        <v>16.85</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.63</v>
+        <v>10.4</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6.68</v>
+        <v>6.45</v>
       </c>
       <c r="EA17" t="n">
-        <v>17.47</v>
+        <v>17.65</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="18">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
         <v>0.1</v>
@@ -8320,52 +8320,52 @@
         <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AI19" t="n">
-        <v>65.89</v>
+        <v>69</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN19" t="n">
-        <v>28.44</v>
+        <v>30.3</v>
       </c>
       <c r="AO19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.89</v>
+        <v>13.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>12.33</v>
+        <v>12.9</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.56</v>
+        <v>9</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8377,82 +8377,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>53.33</v>
+        <v>53.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA19" t="n">
-        <v>14.89</v>
+        <v>14.8</v>
       </c>
       <c r="BB19" t="n">
         <v>9</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.89</v>
+        <v>5.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>19.78</v>
+        <v>20.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BF19" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.470000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="BJ19" t="n">
         <v>1</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.37</v>
+        <v>4.3</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.63</v>
+        <v>4.75</v>
       </c>
       <c r="BR19" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS19" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT19" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU19" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BV19" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW19" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BX19" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY19" t="n">
         <v>1.58</v>
@@ -8461,16 +8461,16 @@
         <v>1.59</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.17</v>
+        <v>4.12</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.52</v>
+        <v>4.47</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="CE19" t="n">
         <v>1.26</v>
@@ -8479,16 +8479,16 @@
         <v>2.28</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CI19" t="n">
         <v>2.24</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CK19" t="n">
         <v>1.49</v>
@@ -8500,7 +8500,7 @@
         <v>2.42</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO19" t="n">
         <v>1.16</v>
@@ -8509,7 +8509,7 @@
         <v>1.6</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CR19" t="n">
         <v>1.36</v>
@@ -8524,7 +8524,7 @@
         <v>1.66</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CW19" t="n">
         <v>1.64</v>
@@ -8533,10 +8533,10 @@
         <v>1.55</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DA19" t="n">
         <v>1.92</v>
@@ -8548,82 +8548,82 @@
         <v>1.61</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="DE19" t="n">
         <v>0.1</v>
       </c>
       <c r="DF19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="DN19" t="n">
         <v>0.95</v>
       </c>
-      <c r="DG19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="DH19" t="n">
-        <v>77.11</v>
-      </c>
-      <c r="DI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="DK19" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="DL19" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="DM19" t="n">
-        <v>38.47</v>
-      </c>
-      <c r="DN19" t="n">
-        <v>1</v>
-      </c>
       <c r="DO19" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.26</v>
+        <v>12.95</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.52</v>
+        <v>11.85</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.27</v>
+        <v>9</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.31</v>
+        <v>55.15</v>
       </c>
       <c r="DW19" t="n">
         <v>0.1</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.68</v>
+        <v>17.5</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.74</v>
+        <v>11.6</v>
       </c>
       <c r="DZ19" t="n">
-        <v>5.95</v>
+        <v>5.9</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.84</v>
+        <v>18.1</v>
       </c>
       <c r="EB19" t="n">
         <v>1.62</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0.09</v>
@@ -2678,139 +2678,139 @@
         <v>2.45</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>96</v>
+        <v>96.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.11</v>
+        <v>4.3</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AN5" t="n">
-        <v>40</v>
+        <v>41.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.44</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.44</v>
+        <v>13.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.56</v>
+        <v>8.4</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>54</v>
+        <v>54.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.33</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.67</v>
+        <v>4.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.22</v>
+        <v>22.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.25</v>
+        <v>9.43</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.35</v>
+        <v>5.52</v>
       </c>
       <c r="BR5" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS5" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT5" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU5" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV5" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BW5" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX5" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY5" t="n">
         <v>1.73</v>
@@ -2819,31 +2819,31 @@
         <v>1.83</v>
       </c>
       <c r="CA5" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.18</v>
+        <v>4.16</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="CE5" t="n">
         <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CH5" t="n">
         <v>1.51</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.72</v>
@@ -2855,133 +2855,133 @@
         <v>1.9</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO5" t="n">
         <v>1.2</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="CR5" t="n">
         <v>1.37</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB5" t="n">
         <v>1.23</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="DH5" t="n">
-        <v>101.65</v>
+        <v>101.62</v>
       </c>
       <c r="DI5" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.7</v>
+        <v>5.71</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="DM5" t="n">
-        <v>50.1</v>
+        <v>50.28</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.25</v>
+        <v>11</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.050000000000001</v>
+        <v>8</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57.3</v>
+        <v>57.38</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.7</v>
+        <v>16.62</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.9</v>
+        <v>10.81</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.8</v>
+        <v>5.81</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.5</v>
+        <v>22.05</v>
       </c>
       <c r="EB5" t="n">
         <v>1.82</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="6">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0.1</v>
@@ -4693,139 +4693,139 @@
         <v>1.7</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AH10" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AI10" t="n">
-        <v>58.7</v>
+        <v>61.82</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AN10" t="n">
-        <v>26.8</v>
+        <v>27.45</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.1</v>
+        <v>10.73</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.1</v>
+        <v>13.18</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>54.5</v>
+        <v>54.09</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA10" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.9</v>
+        <v>7.91</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.2</v>
+        <v>5.09</v>
       </c>
       <c r="BD10" t="n">
-        <v>17.4</v>
+        <v>18</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.550000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BO10" t="n">
         <v>1.9</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.35</v>
+        <v>4.24</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT10" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU10" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BV10" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BW10" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY10" t="n">
         <v>1.83</v>
@@ -4834,31 +4834,31 @@
         <v>1.92</v>
       </c>
       <c r="CA10" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="CD10" t="n">
         <v>3.81</v>
       </c>
-      <c r="CB10" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="CC10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>3.5</v>
-      </c>
       <c r="CE10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.68</v>
@@ -4870,25 +4870,25 @@
         <v>1.88</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="CR10" t="n">
         <v>1.36</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CT10" t="n">
         <v>3.29</v>
@@ -4900,7 +4900,7 @@
         <v>2.27</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX10" t="n">
         <v>1.51</v>
@@ -4918,85 +4918,85 @@
         <v>1.22</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="DH10" t="n">
-        <v>74.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.9</v>
+        <v>3.81</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM10" t="n">
-        <v>35.25</v>
+        <v>35.19</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="DP10" t="n">
-        <v>11</v>
+        <v>10.81</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.75</v>
+        <v>12.81</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.9</v>
+        <v>6.86</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.5</v>
+        <v>55.24</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.1</v>
+        <v>13.05</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.85</v>
+        <v>7.86</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.3</v>
+        <v>17.62</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="EC10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="11">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="H17" t="n">
-        <v>96.2</v>
+        <v>95.91</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="K17" t="n">
-        <v>5.3</v>
+        <v>5.45</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="M17" t="n">
-        <v>53.2</v>
+        <v>52.82</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="P17" t="n">
-        <v>11.7</v>
+        <v>11.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.9</v>
+        <v>12.45</v>
       </c>
       <c r="R17" t="n">
-        <v>6.9</v>
+        <v>7.09</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="T17" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>55.5</v>
+        <v>54.18</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z17" t="n">
-        <v>18.5</v>
+        <v>17.73</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.5</v>
+        <v>11.27</v>
       </c>
       <c r="AB17" t="n">
-        <v>7</v>
+        <v>6.45</v>
       </c>
       <c r="AC17" t="n">
-        <v>18</v>
+        <v>17.45</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,70 +7595,70 @@
         <v>2.9</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.050000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP17" t="n">
         <v>3.95</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.1</v>
+        <v>5.29</v>
       </c>
       <c r="BR17" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS17" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT17" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU17" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV17" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW17" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="CC17" t="n">
         <v>2.4</v>
@@ -7670,10 +7670,10 @@
         <v>1.26</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CH17" t="n">
         <v>1.42</v>
@@ -7685,37 +7685,37 @@
         <v>1.74</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM17" t="n">
         <v>2.37</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO17" t="n">
         <v>1.17</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CR17" t="n">
         <v>1.38</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV17" t="n">
         <v>2.13</v>
@@ -7724,100 +7724,100 @@
         <v>1.77</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.7</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="DI17" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.35</v>
+        <v>5.43</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DM17" t="n">
-        <v>48.35</v>
+        <v>48.38</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.85</v>
+        <v>11.86</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.55</v>
+        <v>12.33</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.25</v>
+        <v>7.33</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>55.5</v>
+        <v>54.81</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX17" t="n">
-        <v>16.85</v>
+        <v>16.53</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.4</v>
+        <v>10.33</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6.45</v>
+        <v>6.19</v>
       </c>
       <c r="EA17" t="n">
-        <v>17.65</v>
+        <v>17.38</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="18">
@@ -8230,94 +8230,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="H19" t="n">
-        <v>87.2</v>
+        <v>85.91</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="K19" t="n">
-        <v>5.5</v>
+        <v>5.36</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="M19" t="n">
-        <v>47.5</v>
+        <v>45.36</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P19" t="n">
-        <v>12.7</v>
+        <v>12.36</v>
       </c>
       <c r="Q19" t="n">
-        <v>10.8</v>
+        <v>10.64</v>
       </c>
       <c r="R19" t="n">
-        <v>9</v>
+        <v>9.18</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>57.1</v>
+        <v>56.45</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z19" t="n">
-        <v>20.2</v>
+        <v>19.36</v>
       </c>
       <c r="AA19" t="n">
-        <v>14.2</v>
+        <v>13.45</v>
       </c>
       <c r="AB19" t="n">
-        <v>6</v>
+        <v>5.91</v>
       </c>
       <c r="AC19" t="n">
-        <v>16.1</v>
+        <v>16.64</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AF19" t="n">
         <v>0.1</v>
@@ -8401,70 +8401,70 @@
         <v>2.1</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.5</v>
+        <v>9.33</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="BR19" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT19" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU19" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BV19" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BW19" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BX19" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.12</v>
+        <v>4.14</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="CC19" t="n">
         <v>2.09</v>
@@ -8479,13 +8479,13 @@
         <v>2.28</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.62</v>
@@ -8494,10 +8494,10 @@
         <v>1.49</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CN19" t="n">
         <v>1.85</v>
@@ -8506,25 +8506,25 @@
         <v>1.16</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CR19" t="n">
         <v>1.36</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CT19" t="n">
         <v>3.21</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CW19" t="n">
         <v>1.64</v>
@@ -8539,7 +8539,7 @@
         <v>2.39</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB19" t="n">
         <v>1.19</v>
@@ -8548,82 +8548,82 @@
         <v>1.61</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF19" t="n">
         <v>1.05</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="DH19" t="n">
-        <v>78.09999999999999</v>
+        <v>77.86</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.5</v>
+        <v>5.43</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DM19" t="n">
-        <v>38.9</v>
+        <v>38.19</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.95</v>
+        <v>12.76</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.85</v>
+        <v>11.72</v>
       </c>
       <c r="DR19" t="n">
-        <v>9</v>
+        <v>9.09</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.15</v>
+        <v>54.9</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.5</v>
+        <v>17.19</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.6</v>
+        <v>11.33</v>
       </c>
       <c r="DZ19" t="n">
-        <v>5.9</v>
+        <v>5.86</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.1</v>
+        <v>18.29</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>54.09</v>
+        <v>54.27</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.18</v>
@@ -4765,7 +4765,7 @@
         <v>5.09</v>
       </c>
       <c r="BD10" t="n">
-        <v>18</v>
+        <v>18.09</v>
       </c>
       <c r="BE10" t="n">
         <v>1.2</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.24</v>
+        <v>55.33</v>
       </c>
       <c r="DW10" t="n">
         <v>0.19</v>
@@ -4990,7 +4990,7 @@
         <v>5.19</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.62</v>
+        <v>17.67</v>
       </c>
       <c r="EB10" t="n">
         <v>1.35</v>
@@ -8296,7 +8296,7 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>56.45</v>
+        <v>56.27</v>
       </c>
       <c r="Y19" t="n">
         <v>0.09</v>
@@ -8602,7 +8602,7 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.9</v>
+        <v>54.81</v>
       </c>
       <c r="DW19" t="n">
         <v>0.09</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F17" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="G17" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="H17" t="n">
-        <v>95.91</v>
+        <v>90.67</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>5.45</v>
+        <v>5.67</v>
       </c>
       <c r="L17" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="M17" t="n">
-        <v>52.82</v>
+        <v>51.83</v>
       </c>
       <c r="N17" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="O17" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="P17" t="n">
-        <v>11.73</v>
+        <v>11.92</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.45</v>
+        <v>12.67</v>
       </c>
       <c r="R17" t="n">
-        <v>7.09</v>
+        <v>6.83</v>
       </c>
       <c r="S17" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="U17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>54.18</v>
+        <v>53.83</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.73</v>
+        <v>17.08</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.27</v>
+        <v>11</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.45</v>
+        <v>6.08</v>
       </c>
       <c r="AC17" t="n">
-        <v>17.45</v>
+        <v>17.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,70 +7595,70 @@
         <v>2.9</v>
       </c>
       <c r="BG17" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.24</v>
+        <v>9.18</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL17" t="n">
         <v>1.14</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.95</v>
+        <v>4.09</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.29</v>
+        <v>5.09</v>
       </c>
       <c r="BR17" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS17" t="n">
-        <v>80.95</v>
+        <v>77.27</v>
       </c>
       <c r="BT17" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU17" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BV17" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW17" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX17" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="CC17" t="n">
         <v>2.4</v>
@@ -7667,13 +7667,13 @@
         <v>2.67</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CH17" t="n">
         <v>1.42</v>
@@ -7691,34 +7691,34 @@
         <v>1.79</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CN17" t="n">
         <v>1.84</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP17" t="n">
         <v>1.76</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CR17" t="n">
         <v>1.38</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CW17" t="n">
         <v>1.77</v>
@@ -7727,7 +7727,7 @@
         <v>1.52</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.45</v>
@@ -7739,52 +7739,52 @@
         <v>1.25</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="DE17" t="n">
         <v>0.14</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.70999999999999</v>
+        <v>90</v>
       </c>
       <c r="DI17" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.43</v>
+        <v>5.55</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="DM17" t="n">
-        <v>48.38</v>
+        <v>48.04</v>
       </c>
       <c r="DN17" t="n">
         <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.76</v>
+        <v>2.95</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.86</v>
+        <v>11.96</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.33</v>
+        <v>12.46</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.33</v>
+        <v>7.18</v>
       </c>
       <c r="DS17" t="n">
         <v>0.09</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.81</v>
+        <v>54.59</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX17" t="n">
-        <v>16.53</v>
+        <v>16.23</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.33</v>
+        <v>10.23</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6.19</v>
+        <v>6</v>
       </c>
       <c r="EA17" t="n">
-        <v>17.38</v>
+        <v>17.59</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="18">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>0.09</v>
@@ -8320,52 +8320,52 @@
         <v>1.64</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AI19" t="n">
-        <v>69</v>
+        <v>66.45</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AN19" t="n">
-        <v>30.3</v>
+        <v>30.36</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.2</v>
+        <v>13.18</v>
       </c>
       <c r="AR19" t="n">
-        <v>12.9</v>
+        <v>13.18</v>
       </c>
       <c r="AS19" t="n">
-        <v>9</v>
+        <v>9.18</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8377,82 +8377,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>53.2</v>
+        <v>52.91</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="BA19" t="n">
-        <v>14.8</v>
+        <v>14.27</v>
       </c>
       <c r="BB19" t="n">
-        <v>9</v>
+        <v>8.91</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.8</v>
+        <v>5.36</v>
       </c>
       <c r="BD19" t="n">
-        <v>20.1</v>
+        <v>19.91</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.33</v>
+        <v>9.27</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.29</v>
+        <v>4.41</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.62</v>
+        <v>4.45</v>
       </c>
       <c r="BR19" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS19" t="n">
-        <v>76.19</v>
+        <v>72.73</v>
       </c>
       <c r="BT19" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU19" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BV19" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW19" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BX19" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY19" t="n">
         <v>1.57</v>
@@ -8461,31 +8461,31 @@
         <v>1.57</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="CE19" t="n">
         <v>1.26</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.62</v>
@@ -8506,28 +8506,28 @@
         <v>1.16</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CX19" t="n">
         <v>1.55</v>
@@ -8545,82 +8545,82 @@
         <v>1.19</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="DE19" t="n">
         <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="DH19" t="n">
-        <v>77.86</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.43</v>
+        <v>5.18</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DM19" t="n">
-        <v>38.19</v>
+        <v>37.86</v>
       </c>
       <c r="DN19" t="n">
         <v>0.91</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.81</v>
+        <v>2.68</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.76</v>
+        <v>12.77</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.72</v>
+        <v>11.91</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.09</v>
+        <v>9.18</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.81</v>
+        <v>54.59</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.19</v>
+        <v>16.81</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.33</v>
+        <v>11.18</v>
       </c>
       <c r="DZ19" t="n">
-        <v>5.86</v>
+        <v>5.64</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.29</v>
+        <v>18.28</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="EC19" t="n">
         <v>1.86</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -8383,10 +8383,10 @@
         <v>0.18</v>
       </c>
       <c r="BA19" t="n">
-        <v>14.27</v>
+        <v>14.18</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.91</v>
+        <v>8.82</v>
       </c>
       <c r="BC19" t="n">
         <v>5.36</v>
@@ -8608,10 +8608,10 @@
         <v>0.13</v>
       </c>
       <c r="DX19" t="n">
-        <v>16.81</v>
+        <v>16.77</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.18</v>
+        <v>11.14</v>
       </c>
       <c r="DZ19" t="n">
         <v>5.64</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
         <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>0.25</v>
@@ -7517,49 +7517,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AI17" t="n">
-        <v>89.2</v>
+        <v>89.45</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.4</v>
+        <v>5.36</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN17" t="n">
-        <v>43.5</v>
+        <v>43.09</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12</v>
+        <v>12.36</v>
       </c>
       <c r="AR17" t="n">
-        <v>12.2</v>
+        <v>12.64</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.6</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>55.5</v>
+        <v>53.45</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA17" t="n">
-        <v>15.2</v>
+        <v>14.45</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.300000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.9</v>
+        <v>5.55</v>
       </c>
       <c r="BD17" t="n">
-        <v>17.3</v>
+        <v>17.27</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="BG17" t="n">
         <v>2.91</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.18</v>
+        <v>9.48</v>
       </c>
       <c r="BI17" t="n">
         <v>2.91</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="BQ17" t="n">
         <v>5.09</v>
       </c>
       <c r="BR17" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS17" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU17" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV17" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW17" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY17" t="n">
         <v>1.65</v>
@@ -7655,16 +7655,16 @@
         <v>1.64</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.13</v>
+        <v>4.14</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.67</v>
+        <v>2.97</v>
       </c>
       <c r="CE17" t="n">
         <v>1.27</v>
@@ -7673,22 +7673,22 @@
         <v>2.41</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CH17" t="n">
         <v>1.42</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.74</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM17" t="n">
         <v>2.36</v>
@@ -7700,10 +7700,10 @@
         <v>1.18</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CR17" t="n">
         <v>1.38</v>
@@ -7721,7 +7721,7 @@
         <v>2.12</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX17" t="n">
         <v>1.52</v>
@@ -7730,10 +7730,10 @@
         <v>1.86</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB17" t="n">
         <v>1.25</v>
@@ -7742,49 +7742,49 @@
         <v>1.81</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="DH17" t="n">
-        <v>90</v>
+        <v>90.09</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.55</v>
+        <v>5.52</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM17" t="n">
-        <v>48.04</v>
+        <v>47.65</v>
       </c>
       <c r="DN17" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.96</v>
+        <v>12.13</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.46</v>
+        <v>12.66</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.18</v>
+        <v>7.65</v>
       </c>
       <c r="DS17" t="n">
         <v>0.09</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.59</v>
+        <v>53.65</v>
       </c>
       <c r="DW17" t="n">
         <v>0.13</v>
       </c>
       <c r="DX17" t="n">
-        <v>16.23</v>
+        <v>15.82</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.23</v>
+        <v>10</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="EA17" t="n">
-        <v>17.59</v>
+        <v>17.56</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="18">
@@ -8230,94 +8230,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
         <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F19" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="G19" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="H19" t="n">
-        <v>85.91</v>
+        <v>90.58</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>5.36</v>
+        <v>5.83</v>
       </c>
       <c r="L19" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="M19" t="n">
-        <v>45.36</v>
+        <v>46.25</v>
       </c>
       <c r="N19" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="P19" t="n">
-        <v>12.36</v>
+        <v>12.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>10.64</v>
+        <v>11.08</v>
       </c>
       <c r="R19" t="n">
-        <v>9.18</v>
+        <v>9.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="U19" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V19" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>56.27</v>
+        <v>57.17</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.36</v>
+        <v>20.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>13.45</v>
+        <v>13.92</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.91</v>
+        <v>6.42</v>
       </c>
       <c r="AC19" t="n">
-        <v>16.64</v>
+        <v>18.08</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AF19" t="n">
         <v>0.09</v>
@@ -8401,70 +8401,70 @@
         <v>2.09</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.27</v>
+        <v>9.57</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="BJ19" t="n">
         <v>1</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.41</v>
+        <v>4.48</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="BR19" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT19" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU19" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BV19" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW19" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BX19" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BZ19" t="n">
         <v>1.57</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.09</v>
+        <v>4.06</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="CC19" t="n">
         <v>2.21</v>
@@ -8473,10 +8473,10 @@
         <v>2.31</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CG19" t="n">
         <v>3.49</v>
@@ -8488,7 +8488,7 @@
         <v>2.24</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK19" t="n">
         <v>1.49</v>
@@ -8509,7 +8509,7 @@
         <v>1.6</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
@@ -8524,7 +8524,7 @@
         <v>1.65</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CW19" t="n">
         <v>1.65</v>
@@ -8548,82 +8548,82 @@
         <v>1.63</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="DH19" t="n">
-        <v>76.18000000000001</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.18</v>
+        <v>5.43</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM19" t="n">
-        <v>37.86</v>
+        <v>38.65</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.68</v>
+        <v>2.83</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.77</v>
+        <v>12.96</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.91</v>
+        <v>12.08</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.18</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.59</v>
+        <v>55.13</v>
       </c>
       <c r="DW19" t="n">
         <v>0.13</v>
       </c>
       <c r="DX19" t="n">
-        <v>16.77</v>
+        <v>17.39</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.14</v>
+        <v>11.48</v>
       </c>
       <c r="DZ19" t="n">
-        <v>5.64</v>
+        <v>5.91</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.28</v>
+        <v>18.96</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.1</v>
@@ -1541,7 +1541,7 @@
         <v>3.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="BE2" t="n">
         <v>1.37</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>56.16</v>
+        <v>56.21</v>
       </c>
       <c r="DW2" t="n">
         <v>0.05</v>
@@ -1766,7 +1766,7 @@
         <v>5.31</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.84</v>
+        <v>18.89</v>
       </c>
       <c r="EB2" t="n">
         <v>1.73</v>
@@ -1911,7 +1911,7 @@
         <v>12.22</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.67</v>
+        <v>10.56</v>
       </c>
       <c r="AT3" t="n">
         <v>2.22</v>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>43.22</v>
+        <v>43.33</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.11</v>
@@ -2142,7 +2142,7 @@
         <v>13.24</v>
       </c>
       <c r="DR3" t="n">
-        <v>10.41</v>
+        <v>10.35</v>
       </c>
       <c r="DS3" t="n">
         <v>0.3</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>41.41</v>
+        <v>41.47</v>
       </c>
       <c r="DW3" t="n">
         <v>0.18</v>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="G4" t="n">
         <v>1.88</v>
@@ -2209,7 +2209,7 @@
         <v>0.12</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>45.12</v>
+        <v>45</v>
       </c>
       <c r="Y4" t="n">
         <v>0.25</v>
@@ -2272,7 +2272,7 @@
         <v>0.84</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AF4" t="n">
         <v>0.22</v>
@@ -2290,7 +2290,7 @@
         <v>0.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="AL4" t="n">
         <v>4.89</v>
@@ -2302,7 +2302,7 @@
         <v>38.33</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AP4" t="n">
         <v>2.44</v>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>47.11</v>
+        <v>47</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.22</v>
@@ -2347,13 +2347,13 @@
         <v>5.33</v>
       </c>
       <c r="BD4" t="n">
-        <v>16.33</v>
+        <v>16.22</v>
       </c>
       <c r="BE4" t="n">
         <v>1.45</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="BG4" t="n">
         <v>3.18</v>
@@ -2509,7 +2509,7 @@
         <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="DG4" t="n">
         <v>2.18</v>
@@ -2533,7 +2533,7 @@
         <v>31.23</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO4" t="n">
         <v>2.29</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.17</v>
+        <v>46.06</v>
       </c>
       <c r="DW4" t="n">
         <v>0.23</v>
@@ -2572,7 +2572,7 @@
         <v>4</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.41</v>
+        <v>19.35</v>
       </c>
       <c r="EB4" t="n">
         <v>1.16</v>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>60</v>
+        <v>59.82</v>
       </c>
       <c r="Y5" t="n">
         <v>0.18</v>
@@ -2741,10 +2741,10 @@
         <v>0.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC5" t="n">
         <v>4.8</v>
@@ -2960,16 +2960,16 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57.38</v>
+        <v>57.29</v>
       </c>
       <c r="DW5" t="n">
         <v>0.24</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.62</v>
+        <v>16.67</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.81</v>
+        <v>10.86</v>
       </c>
       <c r="DZ5" t="n">
         <v>5.81</v>
@@ -3436,7 +3436,7 @@
         <v>2.36</v>
       </c>
       <c r="P7" t="n">
-        <v>11.09</v>
+        <v>11.73</v>
       </c>
       <c r="Q7" t="n">
         <v>12.64</v>
@@ -3460,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>51.09</v>
+        <v>51.27</v>
       </c>
       <c r="Y7" t="n">
         <v>0.09</v>
@@ -3487,7 +3487,7 @@
         <v>0.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="n">
         <v>2.6</v>
@@ -3499,7 +3499,7 @@
         <v>0.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AL7" t="n">
         <v>3.7</v>
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.2</v>
@@ -3562,7 +3562,7 @@
         <v>1.12</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BG7" t="n">
         <v>3.1</v>
@@ -3718,7 +3718,7 @@
         <v>0.19</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="DG7" t="n">
         <v>2.14</v>
@@ -3730,7 +3730,7 @@
         <v>0.09</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="DK7" t="n">
         <v>4.05</v>
@@ -3748,7 +3748,7 @@
         <v>1.76</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.14</v>
+        <v>12.48</v>
       </c>
       <c r="DQ7" t="n">
         <v>12.76</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.05</v>
+        <v>47.19</v>
       </c>
       <c r="DW7" t="n">
         <v>0.14</v>
@@ -3787,7 +3787,7 @@
         <v>1.23</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="8">
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>51.33</v>
+        <v>51.22</v>
       </c>
       <c r="Y8" t="n">
         <v>0.11</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>50.5</v>
+        <v>50.62</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.12</v>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>43.33</v>
+        <v>43.44</v>
       </c>
       <c r="Y9" t="n">
         <v>0.22</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.65</v>
+        <v>43.7</v>
       </c>
       <c r="DW9" t="n">
         <v>0.17</v>
@@ -4669,16 +4669,16 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>56.5</v>
+        <v>56.6</v>
       </c>
       <c r="Y10" t="n">
         <v>0.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="AB10" t="n">
         <v>5.3</v>
@@ -4687,7 +4687,7 @@
         <v>17.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE10" t="n">
         <v>1.7</v>
@@ -4975,16 +4975,16 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.33</v>
+        <v>55.38</v>
       </c>
       <c r="DW10" t="n">
         <v>0.19</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.05</v>
+        <v>13</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.86</v>
+        <v>7.81</v>
       </c>
       <c r="DZ10" t="n">
         <v>5.19</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="AH11" t="n">
         <v>3.33</v>
@@ -5111,7 +5111,7 @@
         <v>0.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.33</v>
+        <v>3.44</v>
       </c>
       <c r="AL11" t="n">
         <v>5.11</v>
@@ -5153,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>49</v>
+        <v>48.89</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.33</v>
@@ -5162,19 +5162,19 @@
         <v>14.89</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.779999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.11</v>
+        <v>5.22</v>
       </c>
       <c r="BD11" t="n">
         <v>19.89</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="BG11" t="n">
         <v>3.29</v>
@@ -5330,7 +5330,7 @@
         <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="DG11" t="n">
         <v>2.76</v>
@@ -5342,7 +5342,7 @@
         <v>0.11</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="DK11" t="n">
         <v>5.24</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.94</v>
+        <v>49.88</v>
       </c>
       <c r="DW11" t="n">
         <v>0.17</v>
@@ -5387,19 +5387,19 @@
         <v>16.59</v>
       </c>
       <c r="DY11" t="n">
-        <v>11.53</v>
+        <v>11.47</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.06</v>
+        <v>5.12</v>
       </c>
       <c r="EA11" t="n">
         <v>22.12</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="12">
@@ -5481,10 +5481,10 @@
         <v>0.44</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.22</v>
+        <v>15.11</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.89</v>
+        <v>10.78</v>
       </c>
       <c r="AB12" t="n">
         <v>4.33</v>
@@ -5556,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>51.4</v>
+        <v>51.2</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.4</v>
@@ -5781,16 +5781,16 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>53.21</v>
+        <v>53.1</v>
       </c>
       <c r="DW12" t="n">
         <v>0.42</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.42</v>
+        <v>14.37</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.84</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="DZ12" t="n">
         <v>4.58</v>
@@ -5884,19 +5884,19 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.75</v>
+        <v>12.62</v>
       </c>
       <c r="AA13" t="n">
         <v>8.380000000000001</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.38</v>
+        <v>4.25</v>
       </c>
       <c r="AC13" t="n">
         <v>22.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE13" t="n">
         <v>2.25</v>
@@ -5935,7 +5935,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.44</v>
+        <v>14.22</v>
       </c>
       <c r="AR13" t="n">
         <v>12.22</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>47.33</v>
+        <v>47.44</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.22</v>
@@ -6166,7 +6166,7 @@
         <v>2</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.17</v>
+        <v>12.59</v>
       </c>
       <c r="DQ13" t="n">
         <v>12.53</v>
@@ -6184,25 +6184,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>51</v>
+        <v>51.05</v>
       </c>
       <c r="DW13" t="n">
         <v>0.12</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.71</v>
+        <v>11.65</v>
       </c>
       <c r="DY13" t="n">
         <v>7.65</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="EA13" t="n">
         <v>20.35</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="EC13" t="n">
         <v>2.35</v>
@@ -6344,7 +6344,7 @@
         <v>11.3</v>
       </c>
       <c r="AS14" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="AT14" t="n">
         <v>1.9</v>
@@ -6368,16 +6368,16 @@
         <v>0.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="BC14" t="n">
         <v>3.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="BE14" t="n">
         <v>1.19</v>
@@ -6575,7 +6575,7 @@
         <v>11</v>
       </c>
       <c r="DR14" t="n">
-        <v>11</v>
+        <v>10.95</v>
       </c>
       <c r="DS14" t="n">
         <v>0.22</v>
@@ -6593,16 +6593,16 @@
         <v>0.11</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.83</v>
+        <v>11.89</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.220000000000001</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DZ14" t="n">
         <v>3.61</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.17</v>
+        <v>19.22</v>
       </c>
       <c r="EB14" t="n">
         <v>1.33</v>
@@ -6699,7 +6699,7 @@
         <v>3.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>16.75</v>
+        <v>16.88</v>
       </c>
       <c r="AD15" t="n">
         <v>0.98</v>
@@ -6711,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AH15" t="n">
         <v>1.78</v>
@@ -6723,7 +6723,7 @@
         <v>0.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AL15" t="n">
         <v>3.56</v>
@@ -6786,7 +6786,7 @@
         <v>0.86</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="BG15" t="n">
         <v>2.82</v>
@@ -6942,7 +6942,7 @@
         <v>0.06</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="DG15" t="n">
         <v>1.65</v>
@@ -6954,7 +6954,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="DK15" t="n">
         <v>3.06</v>
@@ -7005,13 +7005,13 @@
         <v>3.29</v>
       </c>
       <c r="EA15" t="n">
-        <v>15.12</v>
+        <v>15.18</v>
       </c>
       <c r="EB15" t="n">
         <v>0.92</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="16">
@@ -7087,7 +7087,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>41.56</v>
+        <v>41.44</v>
       </c>
       <c r="Y16" t="n">
         <v>0.44</v>
@@ -7150,7 +7150,7 @@
         <v>14.12</v>
       </c>
       <c r="AS16" t="n">
-        <v>12.62</v>
+        <v>12.75</v>
       </c>
       <c r="AT16" t="n">
         <v>2.25</v>
@@ -7381,7 +7381,7 @@
         <v>14.47</v>
       </c>
       <c r="DR16" t="n">
-        <v>11.29</v>
+        <v>11.35</v>
       </c>
       <c r="DS16" t="n">
         <v>0.12</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44</v>
+        <v>43.94</v>
       </c>
       <c r="DW16" t="n">
         <v>0.35</v>
@@ -7436,7 +7436,7 @@
         <v>0.25</v>
       </c>
       <c r="F17" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="G17" t="n">
         <v>2.42</v>
@@ -7448,7 +7448,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="K17" t="n">
         <v>5.67</v>
@@ -7490,7 +7490,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>53.83</v>
+        <v>53.92</v>
       </c>
       <c r="Y17" t="n">
         <v>0.08</v>
@@ -7505,13 +7505,13 @@
         <v>6.08</v>
       </c>
       <c r="AC17" t="n">
-        <v>17.83</v>
+        <v>17.92</v>
       </c>
       <c r="AD17" t="n">
         <v>1.87</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7748,7 +7748,7 @@
         <v>0.13</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="DG17" t="n">
         <v>2.57</v>
@@ -7760,7 +7760,7 @@
         <v>0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="DK17" t="n">
         <v>5.52</v>
@@ -7796,7 +7796,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>53.65</v>
+        <v>53.7</v>
       </c>
       <c r="DW17" t="n">
         <v>0.13</v>
@@ -7811,13 +7811,13 @@
         <v>5.83</v>
       </c>
       <c r="EA17" t="n">
-        <v>17.56</v>
+        <v>17.61</v>
       </c>
       <c r="EB17" t="n">
         <v>1.75</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="18">
@@ -7893,7 +7893,7 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>49.45</v>
+        <v>49.36</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -7920,7 +7920,7 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="n">
         <v>2.11</v>
@@ -7932,7 +7932,7 @@
         <v>0.11</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.89</v>
+        <v>3.11</v>
       </c>
       <c r="AL18" t="n">
         <v>2.89</v>
@@ -7995,7 +7995,7 @@
         <v>1.09</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="BG18" t="n">
         <v>3.2</v>
@@ -8151,7 +8151,7 @@
         <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="DG18" t="n">
         <v>1.55</v>
@@ -8163,7 +8163,7 @@
         <v>0.1</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="DK18" t="n">
         <v>3.3</v>
@@ -8199,7 +8199,7 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.7</v>
+        <v>46.65</v>
       </c>
       <c r="DW18" t="n">
         <v>0.1</v>
@@ -8220,7 +8220,7 @@
         <v>1.32</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="19">
@@ -8392,7 +8392,7 @@
         <v>5.36</v>
       </c>
       <c r="BD19" t="n">
-        <v>19.91</v>
+        <v>20</v>
       </c>
       <c r="BE19" t="n">
         <v>1.18</v>
@@ -8617,7 +8617,7 @@
         <v>5.91</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.96</v>
+        <v>19</v>
       </c>
       <c r="EB19" t="n">
         <v>1.64</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0.11</v>
@@ -1469,139 +1469,139 @@
         <v>1.78</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="AI2" t="n">
-        <v>102.2</v>
+        <v>101.55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.4</v>
+        <v>5.18</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN2" t="n">
-        <v>51.5</v>
+        <v>49</v>
       </c>
       <c r="AO2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>53.18</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM2" t="n">
         <v>0.7</v>
       </c>
-      <c r="AP2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>9.789999999999999</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.74</v>
-      </c>
       <c r="BN2" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.42</v>
+        <v>5.25</v>
       </c>
       <c r="BR2" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BS2" t="n">
-        <v>89.47</v>
+        <v>85</v>
       </c>
       <c r="BT2" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU2" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV2" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX2" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY2" t="n">
         <v>1.43</v>
@@ -1610,55 +1610,55 @@
         <v>1.47</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.47</v>
+        <v>4.42</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.42</v>
+        <v>2.29</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="CR2" t="n">
         <v>1.39</v>
@@ -1703,73 +1703,73 @@
         <v>0.1</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.79</v>
+        <v>3.65</v>
       </c>
       <c r="DH2" t="n">
-        <v>102</v>
+        <v>101.65</v>
       </c>
       <c r="DI2" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.74</v>
+        <v>6.55</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM2" t="n">
-        <v>58.58</v>
+        <v>56.85</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.63</v>
+        <v>10.55</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.37</v>
+        <v>12.25</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.26</v>
+        <v>6.3</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>56.21</v>
+        <v>55.4</v>
       </c>
       <c r="DW2" t="n">
         <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.74</v>
+        <v>14.2</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.42</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.31</v>
+        <v>5.15</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.89</v>
+        <v>18.85</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="EC2" t="n">
         <v>2</v>
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="H3" t="n">
-        <v>69.5</v>
+        <v>68.89</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="K3" t="n">
-        <v>4.12</v>
+        <v>3.78</v>
       </c>
       <c r="L3" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>35.25</v>
+        <v>34.56</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="P3" t="n">
-        <v>13.75</v>
+        <v>13.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.38</v>
+        <v>14.67</v>
       </c>
       <c r="R3" t="n">
-        <v>10.12</v>
+        <v>10.22</v>
       </c>
       <c r="S3" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="T3" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="U3" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="V3" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>39.38</v>
+        <v>39.56</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.12</v>
+        <v>10.78</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.12</v>
+        <v>6.89</v>
       </c>
       <c r="AB3" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>14.78</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AF3" t="n">
         <v>0.11</v>
@@ -1953,70 +1953,70 @@
         <v>2.22</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.47</v>
+        <v>3.33</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.82</v>
+        <v>9.56</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.47</v>
+        <v>3.33</v>
       </c>
       <c r="BJ3" t="n">
         <v>1.06</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL3" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.06</v>
+        <v>4.72</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.76</v>
+        <v>4.44</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS3" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT3" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU3" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BV3" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BW3" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BX3" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.46</v>
+        <v>3.31</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.78</v>
+        <v>3.62</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="CB3" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="CC3" t="n">
         <v>4.36</v>
@@ -2028,16 +2028,16 @@
         <v>1.31</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.7</v>
@@ -2058,25 +2058,25 @@
         <v>1.22</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CW3" t="n">
         <v>1.71</v>
@@ -2085,97 +2085,97 @@
         <v>1.53</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.44</v>
       </c>
       <c r="DA3" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DB3" t="n">
         <v>1.25</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DG3" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="DH3" t="n">
-        <v>66.18000000000001</v>
+        <v>66.06</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.47</v>
+        <v>3.34</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="DM3" t="n">
-        <v>29.77</v>
+        <v>29.72</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.29</v>
+        <v>11.39</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.24</v>
+        <v>13.44</v>
       </c>
       <c r="DR3" t="n">
-        <v>10.35</v>
+        <v>10.39</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>41.47</v>
+        <v>41.44</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.880000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.64</v>
+        <v>6.56</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="EA3" t="n">
-        <v>15.41</v>
+        <v>15.73</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="4">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0.18</v>
@@ -3484,139 +3484,139 @@
         <v>2.82</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AI7" t="n">
-        <v>78.3</v>
+        <v>79.36</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AN7" t="n">
-        <v>37.7</v>
+        <v>38.45</v>
       </c>
       <c r="AO7" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.3</v>
+        <v>13.18</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.9</v>
+        <v>13.09</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.3</v>
+        <v>9.82</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>42.7</v>
+        <v>43.73</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.6</v>
+        <v>6.45</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="BD7" t="n">
-        <v>20.1</v>
+        <v>20.36</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.76</v>
+        <v>8.68</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="BJ7" t="n">
         <v>0.86</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.19</v>
+        <v>4.14</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS7" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT7" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BV7" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX7" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BY7" t="n">
         <v>2.53</v>
@@ -3625,43 +3625,43 @@
         <v>2.67</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.38</v>
+        <v>4.2</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.14</v>
+        <v>4.91</v>
       </c>
       <c r="CE7" t="n">
         <v>1.35</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.78</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL7" t="n">
         <v>1.97</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CN7" t="n">
         <v>1.85</v>
@@ -3670,22 +3670,22 @@
         <v>1.25</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="CR7" t="n">
         <v>1.39</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV7" t="n">
         <v>2.08</v>
@@ -3694,7 +3694,7 @@
         <v>1.81</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY7" t="n">
         <v>1.99</v>
@@ -3709,85 +3709,85 @@
         <v>1.29</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="DH7" t="n">
-        <v>85.38</v>
+        <v>85.59</v>
       </c>
       <c r="DI7" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DM7" t="n">
-        <v>37.29</v>
+        <v>37.68</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.48</v>
+        <v>12.46</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.76</v>
+        <v>12.87</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.949999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.19</v>
+        <v>47.5</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.24</v>
+        <v>11.1</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.72</v>
+        <v>7.59</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.24</v>
+        <v>21.32</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F9" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>76.11</v>
+        <v>78.3</v>
       </c>
       <c r="I9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.44</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M9" t="n">
-        <v>35.56</v>
+        <v>35.1</v>
       </c>
       <c r="N9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>11.33</v>
+        <v>11.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.22</v>
+        <v>12.4</v>
       </c>
       <c r="R9" t="n">
-        <v>8.220000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="S9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>43.44</v>
+        <v>43.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.44</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.22</v>
+        <v>6.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>15.33</v>
+        <v>16.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AE9" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>2.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.59</v>
+        <v>9.44</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BJ9" t="n">
         <v>1</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.24</v>
+        <v>5.11</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT9" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU9" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.97</v>
+        <v>3.92</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.26</v>
+        <v>4.2</v>
       </c>
       <c r="CC9" t="n">
         <v>6.35</v>
@@ -4443,64 +4443,64 @@
         <v>8.119999999999999</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI9" t="n">
         <v>2.02</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO9" t="n">
         <v>1.23</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CW9" t="n">
         <v>1.78</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY9" t="n">
         <v>1.84</v>
@@ -4509,91 +4509,91 @@
         <v>2.42</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.99</v>
+        <v>3.06</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="DG9" t="n">
         <v>1.94</v>
       </c>
       <c r="DH9" t="n">
-        <v>74.65000000000001</v>
+        <v>75.94</v>
       </c>
       <c r="DI9" t="n">
         <v>0.17</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.23</v>
+        <v>3.11</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM9" t="n">
-        <v>36.76</v>
+        <v>36.44</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.65</v>
+        <v>11.83</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.23</v>
+        <v>12.33</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.529999999999999</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.7</v>
+        <v>43.83</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.41</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.47</v>
+        <v>6.22</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.82</v>
+        <v>17.17</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="10">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.11</v>
+        <v>2.7</v>
       </c>
       <c r="AI13" t="n">
-        <v>73.22</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="AM13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="BJ13" t="n">
         <v>0.67</v>
       </c>
-      <c r="AN13" t="n">
-        <v>26.89</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>14.22</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>47.44</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>18.22</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.65</v>
-      </c>
       <c r="BK13" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BM13" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.12</v>
+        <v>3.83</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.47</v>
+        <v>5.11</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS13" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BT13" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BV13" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW13" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BX13" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY13" t="n">
         <v>3.17</v>
@@ -6043,25 +6043,25 @@
         <v>3.26</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.43</v>
+        <v>5.18</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.02</v>
+        <v>5.74</v>
       </c>
       <c r="CE13" t="n">
         <v>1.33</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="CH13" t="n">
         <v>1.47</v>
@@ -6076,10 +6076,10 @@
         <v>1.44</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CN13" t="n">
         <v>2</v>
@@ -6088,28 +6088,28 @@
         <v>1.25</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CR13" t="n">
         <v>1.38</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV13" t="n">
         <v>2.07</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX13" t="n">
         <v>1.51</v>
@@ -6121,58 +6121,58 @@
         <v>2.45</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB13" t="n">
         <v>1.29</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="DG13" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="DH13" t="n">
-        <v>85</v>
+        <v>87.22</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DK13" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.53</v>
+        <v>0.45</v>
       </c>
       <c r="DM13" t="n">
-        <v>35.29</v>
+        <v>36.61</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DO13" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.59</v>
+        <v>12.72</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.53</v>
+        <v>12.5</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.23</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DS13" t="n">
         <v>0.06</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>51.05</v>
+        <v>51.5</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.65</v>
+        <v>11.83</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.65</v>
+        <v>7.72</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.35</v>
+        <v>20.67</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="14">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
         <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F18" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="G18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="H18" t="n">
-        <v>85.36</v>
+        <v>86.75</v>
       </c>
       <c r="I18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J18" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="L18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="M18" t="n">
-        <v>37.18</v>
+        <v>37.25</v>
       </c>
       <c r="N18" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="P18" t="n">
-        <v>12.82</v>
+        <v>12.58</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.36</v>
+        <v>13.92</v>
       </c>
       <c r="R18" t="n">
-        <v>7.73</v>
+        <v>7.5</v>
       </c>
       <c r="S18" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="T18" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>49.36</v>
+        <v>50.25</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.73</v>
+        <v>13.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.449999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.27</v>
+        <v>5</v>
       </c>
       <c r="AC18" t="n">
-        <v>17.27</v>
+        <v>16.92</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,70 +7998,70 @@
         <v>2.78</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BN18" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.9</v>
+        <v>3.81</v>
       </c>
       <c r="BR18" t="n">
-        <v>95</v>
+        <v>90.48</v>
       </c>
       <c r="BS18" t="n">
-        <v>85</v>
+        <v>80.95</v>
       </c>
       <c r="BT18" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU18" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BV18" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW18" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX18" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="CC18" t="n">
         <v>4.77</v>
@@ -8070,43 +8070,43 @@
         <v>5.24</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.22</v>
+        <v>3.07</v>
       </c>
       <c r="CH18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="CJ18" t="n">
         <v>1.5</v>
       </c>
-      <c r="CI18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CJ18" t="n">
-        <v>1.57</v>
-      </c>
       <c r="CK18" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
@@ -8151,76 +8151,76 @@
         <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DH18" t="n">
-        <v>77.8</v>
+        <v>78.95</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM18" t="n">
-        <v>35.65</v>
+        <v>35.76</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.5</v>
+        <v>12.38</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.4</v>
+        <v>13.19</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.35</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.65</v>
+        <v>47.28</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.15</v>
+        <v>12</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.95</v>
+        <v>7.9</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="EA18" t="n">
-        <v>18.1</v>
+        <v>17.86</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1827,7 +1827,7 @@
         <v>13.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.67</v>
+        <v>14.56</v>
       </c>
       <c r="R3" t="n">
         <v>10.22</v>
@@ -2139,7 +2139,7 @@
         <v>11.39</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.44</v>
+        <v>13.39</v>
       </c>
       <c r="DR3" t="n">
         <v>10.39</v>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="G4" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="H4" t="n">
-        <v>58</v>
+        <v>62.56</v>
       </c>
       <c r="I4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J4" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="L4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>23.25</v>
+        <v>25.11</v>
       </c>
       <c r="N4" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="O4" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="P4" t="n">
-        <v>11.88</v>
+        <v>11</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.12</v>
+        <v>12.33</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>7.78</v>
       </c>
       <c r="S4" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="T4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>45</v>
+        <v>45.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AA4" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>22.88</v>
+        <v>23</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF4" t="n">
         <v>0.22</v>
@@ -2356,70 +2356,70 @@
         <v>2.33</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.880000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.24</v>
+        <v>4.28</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.65</v>
+        <v>4.56</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT4" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU4" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV4" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW4" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX4" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="CC4" t="n">
         <v>3.93</v>
@@ -2431,55 +2431,55 @@
         <v>1.31</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CR4" t="n">
         <v>1.36</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CU4" t="n">
         <v>1.52</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW4" t="n">
         <v>1.66</v>
@@ -2488,97 +2488,97 @@
         <v>1.51</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.45</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DB4" t="n">
         <v>1.23</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="DH4" t="n">
-        <v>65.06</v>
+        <v>66.94</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DM4" t="n">
-        <v>31.23</v>
+        <v>31.72</v>
       </c>
       <c r="DN4" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.06</v>
+        <v>11.61</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.11</v>
+        <v>12.22</v>
       </c>
       <c r="DR4" t="n">
-        <v>9</v>
+        <v>8.84</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.06</v>
+        <v>46.16</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.71</v>
+        <v>10.84</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.35</v>
+        <v>19.61</v>
       </c>
       <c r="EB4" t="n">
         <v>1.16</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0.09</v>
@@ -2678,139 +2678,139 @@
         <v>2.45</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AI5" t="n">
-        <v>96.5</v>
+        <v>98.55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AN5" t="n">
-        <v>41.4</v>
+        <v>42.27</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10</v>
+        <v>10.64</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.7</v>
+        <v>14</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.4</v>
+        <v>7.82</v>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>54.5</v>
+        <v>54.45</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.2</v>
+        <v>14.82</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.4</v>
+        <v>9.82</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BD5" t="n">
-        <v>22.4</v>
+        <v>21.91</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.43</v>
+        <v>9.41</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.52</v>
+        <v>5.59</v>
       </c>
       <c r="BR5" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS5" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU5" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BV5" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX5" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY5" t="n">
         <v>1.73</v>
@@ -2819,16 +2819,16 @@
         <v>1.83</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="CE5" t="n">
         <v>1.31</v>
@@ -2852,28 +2852,28 @@
         <v>1.48</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP5" t="n">
         <v>1.72</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CR5" t="n">
         <v>1.37</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CT5" t="n">
         <v>3.19</v>
@@ -2882,7 +2882,7 @@
         <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CW5" t="n">
         <v>1.72</v>
@@ -2891,97 +2891,97 @@
         <v>1.52</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="DE5" t="n">
         <v>0.09</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="DH5" t="n">
-        <v>101.62</v>
+        <v>102.41</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.71</v>
+        <v>5.72</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM5" t="n">
-        <v>50.28</v>
+        <v>50.32</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DP5" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="DY5" t="n">
         <v>11</v>
       </c>
-      <c r="DQ5" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="DR5" t="n">
-        <v>8</v>
-      </c>
-      <c r="DS5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="DT5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="DU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV5" t="n">
-        <v>57.29</v>
-      </c>
-      <c r="DW5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="DX5" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="DY5" t="n">
-        <v>10.86</v>
-      </c>
       <c r="DZ5" t="n">
-        <v>5.81</v>
+        <v>5.86</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.05</v>
+        <v>21.82</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="H6" t="n">
-        <v>72.5</v>
+        <v>75.91</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="K6" t="n">
-        <v>5.7</v>
+        <v>5.64</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>36.2</v>
+        <v>35.27</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O6" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>10.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.5</v>
+        <v>11.82</v>
       </c>
       <c r="R6" t="n">
-        <v>8.4</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>53.3</v>
+        <v>53.55</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>13.6</v>
+        <v>14</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.9</v>
+        <v>9.18</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="AC6" t="n">
-        <v>15.1</v>
+        <v>16</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AF6" t="n">
         <v>0.22</v>
@@ -3162,70 +3162,70 @@
         <v>1.56</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.789999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
       <c r="BR6" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS6" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU6" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV6" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW6" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BX6" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="CA6" t="n">
         <v>3.5</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="CC6" t="n">
         <v>2.54</v>
@@ -3246,13 +3246,13 @@
         <v>1.45</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL6" t="n">
         <v>1.75</v>
@@ -3276,10 +3276,10 @@
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CU6" t="n">
         <v>1.48</v>
@@ -3312,46 +3312,46 @@
         <v>3.08</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="DH6" t="n">
-        <v>86.27</v>
+        <v>87.45</v>
       </c>
       <c r="DI6" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.95</v>
+        <v>5.9</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DM6" t="n">
-        <v>42.79</v>
+        <v>41.95</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.63</v>
+        <v>11.55</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.69</v>
+        <v>10.9</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.210000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="DS6" t="n">
         <v>0.05</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>53.63</v>
+        <v>53.75</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.16</v>
+        <v>14.35</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.1</v>
+        <v>17.5</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="7">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="G8" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>65.78</v>
+        <v>66.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="K8" t="n">
-        <v>4.89</v>
+        <v>4.7</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M8" t="n">
-        <v>31.89</v>
+        <v>30.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="P8" t="n">
-        <v>11.33</v>
+        <v>11.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.11</v>
+        <v>12.5</v>
       </c>
       <c r="R8" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="S8" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="U8" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="V8" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>51.22</v>
+        <v>50.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.56</v>
+        <v>12.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.44</v>
+        <v>7.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.11</v>
+        <v>4.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>17.33</v>
+        <v>17.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,70 +3968,70 @@
         <v>2.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.94</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.82</v>
+        <v>4.67</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS8" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT8" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU8" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV8" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX8" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.89</v>
+        <v>3.08</v>
       </c>
       <c r="CA8" t="n">
         <v>3.67</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="CC8" t="n">
         <v>4.54</v>
@@ -4046,7 +4046,7 @@
         <v>2.47</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CH8" t="n">
         <v>1.53</v>
@@ -4061,136 +4061,136 @@
         <v>1.45</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO8" t="n">
         <v>1.21</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CR8" t="n">
         <v>1.36</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB8" t="n">
         <v>1.22</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="DH8" t="n">
-        <v>72.59</v>
+        <v>72.61</v>
       </c>
       <c r="DI8" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.71</v>
+        <v>4.61</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM8" t="n">
-        <v>32.29</v>
+        <v>31.56</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.7</v>
+        <v>11.83</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.29</v>
+        <v>12.5</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.710000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.94</v>
+        <v>50.66</v>
       </c>
       <c r="DW8" t="n">
         <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.77</v>
+        <v>11.61</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.94</v>
+        <v>7.67</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.82</v>
+        <v>3.94</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.82</v>
+        <v>18</v>
       </c>
       <c r="EB8" t="n">
         <v>1.18</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="9">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="H10" t="n">
-        <v>89.7</v>
+        <v>93.36</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M10" t="n">
-        <v>43.7</v>
+        <v>43.45</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O10" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="P10" t="n">
-        <v>10.9</v>
+        <v>10.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.4</v>
+        <v>12.82</v>
       </c>
       <c r="R10" t="n">
-        <v>5.5</v>
+        <v>5.82</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="T10" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>56.6</v>
+        <v>57.27</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>13</v>
+        <v>13.27</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.3</v>
+        <v>5.27</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.2</v>
+        <v>17.64</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AF10" t="n">
         <v>0.09</v>
@@ -4774,70 +4774,70 @@
         <v>2.09</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.48</v>
+        <v>3.36</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.43</v>
+        <v>8.32</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.48</v>
+        <v>3.36</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="BP10" t="n">
         <v>4.14</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.24</v>
+        <v>4.14</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>80.95</v>
+        <v>77.27</v>
       </c>
       <c r="BT10" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU10" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BV10" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BW10" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BX10" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.19</v>
+        <v>4.16</v>
       </c>
       <c r="CC10" t="n">
         <v>3.18</v>
@@ -4849,13 +4849,13 @@
         <v>1.3</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CG10" t="n">
         <v>3.23</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI10" t="n">
         <v>2.16</v>
@@ -4864,16 +4864,16 @@
         <v>1.68</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO10" t="n">
         <v>1.19</v>
@@ -4888,10 +4888,10 @@
         <v>1.36</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CU10" t="n">
         <v>1.58</v>
@@ -4906,97 +4906,97 @@
         <v>1.51</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.45</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="DB10" t="n">
         <v>1.22</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="DE10" t="n">
         <v>0.09</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="DH10" t="n">
-        <v>75.09999999999999</v>
+        <v>77.59</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM10" t="n">
-        <v>35.19</v>
+        <v>35.45</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.81</v>
+        <v>10.73</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.81</v>
+        <v>13</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.86</v>
+        <v>6.95</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.38</v>
+        <v>55.77</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX10" t="n">
-        <v>13</v>
+        <v>13.14</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.81</v>
+        <v>7.95</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.67</v>
+        <v>17.87</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0.12</v>
@@ -5096,139 +5096,139 @@
         <v>2.38</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AH11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG11" t="n">
         <v>3.33</v>
       </c>
-      <c r="AI11" t="n">
-        <v>92.56</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>46.33</v>
-      </c>
-      <c r="AO11" t="n">
+      <c r="BH11" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BK11" t="n">
         <v>0.67</v>
       </c>
-      <c r="AP11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>12.11</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>10.89</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>48.89</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>14.89</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>19.89</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.59</v>
-      </c>
       <c r="BL11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.59</v>
+        <v>3.78</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.71</v>
+        <v>4.61</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU11" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BV11" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW11" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX11" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BY11" t="n">
         <v>2.25</v>
@@ -5240,13 +5240,13 @@
         <v>3.82</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.81</v>
+        <v>3.62</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.05</v>
+        <v>3.87</v>
       </c>
       <c r="CE11" t="n">
         <v>1.29</v>
@@ -5267,7 +5267,7 @@
         <v>1.61</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL11" t="n">
         <v>1.77</v>
@@ -5276,16 +5276,16 @@
         <v>2.74</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CO11" t="n">
         <v>1.18</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CR11" t="n">
         <v>1.36</v>
@@ -5327,79 +5327,79 @@
         <v>2.68</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="DH11" t="n">
-        <v>87.59</v>
+        <v>86.11</v>
       </c>
       <c r="DI11" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.24</v>
+        <v>5.11</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DM11" t="n">
-        <v>45.12</v>
+        <v>44</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.24</v>
+        <v>12.34</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.41</v>
+        <v>10.72</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.109999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.88</v>
+        <v>49.61</v>
       </c>
       <c r="DW11" t="n">
         <v>0.17</v>
       </c>
       <c r="DX11" t="n">
-        <v>16.59</v>
+        <v>16.44</v>
       </c>
       <c r="DY11" t="n">
-        <v>11.47</v>
+        <v>11.28</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.12</v>
+        <v>5.17</v>
       </c>
       <c r="EA11" t="n">
-        <v>22.12</v>
+        <v>21.66</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5499,115 +5499,115 @@
         <v>2.56</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AI12" t="n">
-        <v>75.40000000000001</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>39</v>
+        <v>36.18</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11.1</v>
+        <v>11.45</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.4</v>
+        <v>12.18</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.3</v>
+        <v>10.36</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>51.2</v>
+        <v>50.55</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BA12" t="n">
-        <v>13.7</v>
+        <v>13.36</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.9</v>
+        <v>8.82</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.5</v>
+        <v>21.91</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.949999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BN12" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BQ12" t="n">
         <v>3.95</v>
@@ -5616,22 +5616,22 @@
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY12" t="n">
         <v>1.93</v>
@@ -5640,22 +5640,22 @@
         <v>2.08</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.61</v>
+        <v>2.72</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.81</v>
+        <v>3.03</v>
       </c>
       <c r="CE12" t="n">
         <v>1.32</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CG12" t="n">
         <v>3.16</v>
@@ -5682,22 +5682,22 @@
         <v>2.03</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CR12" t="n">
         <v>1.37</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CU12" t="n">
         <v>1.52</v>
@@ -5733,76 +5733,76 @@
         <v>0.05</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DG12" t="n">
         <v>2.05</v>
       </c>
       <c r="DH12" t="n">
-        <v>82.89</v>
+        <v>82.75</v>
       </c>
       <c r="DI12" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.74</v>
+        <v>4.6</v>
       </c>
       <c r="DL12" t="n">
         <v>0.1</v>
       </c>
       <c r="DM12" t="n">
-        <v>40</v>
+        <v>38.4</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.26</v>
+        <v>11.45</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.37</v>
+        <v>12.25</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.050000000000001</v>
+        <v>9.15</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>53.1</v>
+        <v>52.65</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.37</v>
+        <v>14.15</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.789999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.58</v>
+        <v>4.45</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.47</v>
+        <v>18.85</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -5974,7 +5974,7 @@
         <v>4</v>
       </c>
       <c r="BD13" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="BE13" t="n">
         <v>1.11</v>
@@ -6199,7 +6199,7 @@
         <v>4.11</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.67</v>
+        <v>20.78</v>
       </c>
       <c r="EB13" t="n">
         <v>1.25</v>
@@ -6215,61 +6215,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F14" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="H14" t="n">
-        <v>101.5</v>
+        <v>99.22</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="K14" t="n">
-        <v>4.88</v>
+        <v>5.11</v>
       </c>
       <c r="L14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M14" t="n">
-        <v>50.12</v>
+        <v>48</v>
       </c>
       <c r="N14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="O14" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="P14" t="n">
-        <v>12.12</v>
+        <v>12.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.62</v>
+        <v>10.44</v>
       </c>
       <c r="R14" t="n">
-        <v>8.880000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>59.5</v>
+        <v>59.44</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.62</v>
+        <v>13.78</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.75</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.75</v>
+        <v>20</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AF14" t="n">
         <v>0.1</v>
@@ -6386,67 +6386,67 @@
         <v>3.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.44</v>
+        <v>8.58</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL14" t="n">
         <v>0.89</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.17</v>
+        <v>4.26</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU14" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV14" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="CB14" t="n">
         <v>3.65</v>
@@ -6461,25 +6461,25 @@
         <v>1.37</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CH14" t="n">
         <v>1.4</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK14" t="n">
         <v>1.51</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CM14" t="n">
         <v>2.39</v>
@@ -6494,16 +6494,16 @@
         <v>1.93</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CR14" t="n">
         <v>1.4</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CU14" t="n">
         <v>1.43</v>
@@ -6512,16 +6512,16 @@
         <v>2.03</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY14" t="n">
         <v>1.97</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DA14" t="n">
         <v>1.84</v>
@@ -6530,85 +6530,85 @@
         <v>1.31</v>
       </c>
       <c r="DC14" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="DH14" t="n">
-        <v>86</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.56</v>
+        <v>4.68</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM14" t="n">
-        <v>44.78</v>
+        <v>44.05</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.22</v>
+        <v>13.26</v>
       </c>
       <c r="DQ14" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="DR14" t="n">
         <v>11</v>
       </c>
-      <c r="DR14" t="n">
-        <v>10.95</v>
-      </c>
       <c r="DS14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>52.22</v>
+        <v>52.58</v>
       </c>
       <c r="DW14" t="n">
         <v>0.11</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.89</v>
+        <v>12.05</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.279999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.22</v>
+        <v>18.95</v>
       </c>
       <c r="EB14" t="n">
         <v>1.33</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>0.12</v>
@@ -6711,112 +6711,112 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>48.44</v>
+        <v>47.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AN15" t="n">
-        <v>23.22</v>
+        <v>23.1</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.89</v>
+        <v>10.7</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.56</v>
+        <v>12.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>11.44</v>
+        <v>11.1</v>
       </c>
       <c r="AT15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BF15" t="n">
         <v>2</v>
       </c>
-      <c r="AU15" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>31.22</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>2.22</v>
-      </c>
       <c r="BG15" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.24</v>
+        <v>9.33</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BL15" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.24</v>
+        <v>4.33</v>
       </c>
       <c r="BQ15" t="n">
         <v>4.94</v>
@@ -6825,22 +6825,22 @@
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT15" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV15" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX15" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY15" t="n">
         <v>3.51</v>
@@ -6849,28 +6849,28 @@
         <v>4.01</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.36</v>
+        <v>4.32</v>
       </c>
       <c r="CC15" t="n">
-        <v>7.19</v>
+        <v>7.1</v>
       </c>
       <c r="CD15" t="n">
-        <v>7.72</v>
+        <v>7.43</v>
       </c>
       <c r="CE15" t="n">
         <v>1.35</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI15" t="n">
         <v>1.89</v>
@@ -6882,136 +6882,136 @@
         <v>1.42</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CN15" t="n">
         <v>1.98</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CQ15" t="n">
         <v>3.04</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CU15" t="n">
         <v>1.5</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW15" t="n">
         <v>1.92</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DB15" t="n">
         <v>1.28</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="DH15" t="n">
-        <v>61.12</v>
+        <v>59.89</v>
       </c>
       <c r="DI15" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DM15" t="n">
-        <v>25.18</v>
+        <v>25</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.59</v>
+        <v>12.39</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.41</v>
+        <v>12.5</v>
       </c>
       <c r="DR15" t="n">
-        <v>11.18</v>
+        <v>11</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>35.94</v>
+        <v>36.22</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX15" t="n">
-        <v>8.18</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DY15" t="n">
-        <v>4.88</v>
+        <v>5.28</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="EA15" t="n">
-        <v>15.18</v>
+        <v>16.06</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="16">
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -7036,79 +7036,79 @@
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="H16" t="n">
-        <v>66.22</v>
+        <v>68.5</v>
       </c>
       <c r="I16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="M16" t="n">
-        <v>35.22</v>
+        <v>37</v>
       </c>
       <c r="N16" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="P16" t="n">
-        <v>12.78</v>
+        <v>13</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.78</v>
+        <v>14.6</v>
       </c>
       <c r="R16" t="n">
-        <v>10.11</v>
+        <v>9.6</v>
       </c>
       <c r="S16" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>41.44</v>
+        <v>42.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>10.89</v>
+        <v>11.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.11</v>
+        <v>6.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.67</v>
+        <v>18.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AF16" t="n">
         <v>0.12</v>
@@ -7192,70 +7192,70 @@
         <v>2.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.24</v>
+        <v>11.17</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BJ16" t="n">
         <v>1</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.65</v>
+        <v>4.78</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.53</v>
+        <v>6.33</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT16" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU16" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BV16" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX16" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.71</v>
+        <v>3.65</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.12</v>
+        <v>4.1</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.53</v>
+        <v>4.48</v>
       </c>
       <c r="CC16" t="n">
         <v>6.45</v>
@@ -7267,7 +7267,7 @@
         <v>1.28</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CG16" t="n">
         <v>3.46</v>
@@ -7276,22 +7276,22 @@
         <v>1.57</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.65</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CL16" t="n">
         <v>1.7</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CO16" t="n">
         <v>1.17</v>
@@ -7300,25 +7300,25 @@
         <v>1.64</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CT16" t="n">
         <v>3.23</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX16" t="n">
         <v>1.5</v>
@@ -7339,82 +7339,82 @@
         <v>1.64</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DH16" t="n">
-        <v>73.34999999999999</v>
+        <v>74.22</v>
       </c>
       <c r="DI16" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.18</v>
+        <v>4.33</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="DM16" t="n">
-        <v>34.29</v>
+        <v>35.33</v>
       </c>
       <c r="DN16" t="n">
         <v>1</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.65</v>
+        <v>11.84</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.47</v>
+        <v>14.39</v>
       </c>
       <c r="DR16" t="n">
-        <v>11.35</v>
+        <v>11</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.94</v>
+        <v>44.56</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.24</v>
+        <v>10.5</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.06</v>
+        <v>6.33</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.94</v>
+        <v>17.28</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
         <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
         <v>0.25</v>
@@ -7517,49 +7517,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AI17" t="n">
-        <v>89.45</v>
+        <v>92</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.36</v>
+        <v>5.17</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>43.09</v>
+        <v>41.75</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.36</v>
+        <v>12.42</v>
       </c>
       <c r="AR17" t="n">
-        <v>12.64</v>
+        <v>12.08</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.550000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>53.45</v>
+        <v>53.33</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA17" t="n">
-        <v>14.45</v>
+        <v>13.92</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.91</v>
+        <v>8.58</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.55</v>
+        <v>5.33</v>
       </c>
       <c r="BD17" t="n">
-        <v>17.27</v>
+        <v>18.17</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.48</v>
+        <v>9.42</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="BR17" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS17" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT17" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BU17" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV17" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW17" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX17" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY17" t="n">
         <v>1.65</v>
@@ -7655,25 +7655,25 @@
         <v>1.64</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="CE17" t="n">
         <v>1.27</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CH17" t="n">
         <v>1.42</v>
@@ -7700,19 +7700,19 @@
         <v>1.18</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CR17" t="n">
         <v>1.38</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CU17" t="n">
         <v>1.5</v>
@@ -7727,7 +7727,7 @@
         <v>1.52</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.44</v>
@@ -7739,85 +7739,85 @@
         <v>1.25</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="DH17" t="n">
-        <v>90.09</v>
+        <v>91.34</v>
       </c>
       <c r="DI17" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.52</v>
+        <v>5.42</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="DM17" t="n">
-        <v>47.65</v>
+        <v>46.79</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.13</v>
+        <v>12.17</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.66</v>
+        <v>12.38</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.65</v>
+        <v>7.62</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>53.7</v>
+        <v>53.62</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.82</v>
+        <v>15.5</v>
       </c>
       <c r="DY17" t="n">
-        <v>10</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.83</v>
+        <v>5.71</v>
       </c>
       <c r="EA17" t="n">
-        <v>17.61</v>
+        <v>18.05</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="18">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" t="n">
         <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
         <v>0.08</v>
@@ -8320,52 +8320,52 @@
         <v>1.83</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AI19" t="n">
-        <v>66.45</v>
+        <v>68.75</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="AL19" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN19" t="n">
-        <v>30.36</v>
+        <v>31.17</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.18</v>
+        <v>13.42</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.18</v>
+        <v>12.75</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.18</v>
+        <v>9.33</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8377,82 +8377,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>52.91</v>
+        <v>51.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA19" t="n">
-        <v>14.18</v>
+        <v>14.17</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.82</v>
+        <v>9.08</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.36</v>
+        <v>5.08</v>
       </c>
       <c r="BD19" t="n">
-        <v>20</v>
+        <v>19.92</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.22</v>
+        <v>3.12</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.57</v>
+        <v>9.42</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.22</v>
+        <v>3.12</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.48</v>
+        <v>4.46</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.48</v>
+        <v>4.38</v>
       </c>
       <c r="BR19" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS19" t="n">
-        <v>73.91</v>
+        <v>70.83</v>
       </c>
       <c r="BT19" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BU19" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BV19" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW19" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BX19" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY19" t="n">
         <v>1.59</v>
@@ -8461,16 +8461,16 @@
         <v>1.57</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.44</v>
+        <v>4.41</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="CE19" t="n">
         <v>1.27</v>
@@ -8479,10 +8479,10 @@
         <v>2.31</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI19" t="n">
         <v>2.24</v>
@@ -8494,7 +8494,7 @@
         <v>1.49</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM19" t="n">
         <v>2.41</v>
@@ -8506,25 +8506,25 @@
         <v>1.16</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CW19" t="n">
         <v>1.65</v>
@@ -8533,97 +8533,97 @@
         <v>1.55</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.39</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="DE19" t="n">
         <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="DH19" t="n">
-        <v>79.04000000000001</v>
+        <v>79.67</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.43</v>
+        <v>5.38</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="DM19" t="n">
-        <v>38.65</v>
+        <v>38.71</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="DO19" t="n">
         <v>2.83</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.96</v>
+        <v>13.08</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.08</v>
+        <v>11.92</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.220000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.13</v>
+        <v>54.34</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.39</v>
+        <v>17.25</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.48</v>
+        <v>11.5</v>
       </c>
       <c r="DZ19" t="n">
-        <v>5.91</v>
+        <v>5.75</v>
       </c>
       <c r="EA19" t="n">
         <v>19</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="H2" t="n">
-        <v>101.78</v>
+        <v>100.2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="K2" t="n">
-        <v>8.220000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="M2" t="n">
-        <v>66.44</v>
+        <v>62.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>10.56</v>
+        <v>10.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="R2" t="n">
-        <v>6.11</v>
+        <v>6.7</v>
       </c>
       <c r="S2" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>58.11</v>
+        <v>56.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.11</v>
+        <v>17.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.89</v>
+        <v>10.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.22</v>
+        <v>6.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AF2" t="n">
         <v>0.09</v>
@@ -1550,58 +1550,58 @@
         <v>2.18</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.5</v>
+        <v>9.48</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BP2" t="n">
         <v>4.1</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="BR2" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU2" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV2" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW2" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX2" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY2" t="n">
         <v>1.43</v>
@@ -1610,10 +1610,10 @@
         <v>1.47</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="CC2" t="n">
         <v>2.24</v>
@@ -1625,7 +1625,7 @@
         <v>1.25</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CG2" t="n">
         <v>3.14</v>
@@ -1637,13 +1637,13 @@
         <v>1.91</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CM2" t="n">
         <v>2.4</v>
@@ -1655,10 +1655,10 @@
         <v>1.16</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CR2" t="n">
         <v>1.39</v>
@@ -1673,10 +1673,10 @@
         <v>1.57</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX2" t="n">
         <v>1.52</v>
@@ -1697,82 +1697,82 @@
         <v>1.76</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="DH2" t="n">
-        <v>101.65</v>
+        <v>100.91</v>
       </c>
       <c r="DI2" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.55</v>
+        <v>6.28</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM2" t="n">
-        <v>56.85</v>
+        <v>55.29</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.55</v>
+        <v>10.72</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.25</v>
+        <v>12.05</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.3</v>
+        <v>6.57</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>55.4</v>
+        <v>54.95</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.2</v>
+        <v>13.95</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.050000000000001</v>
+        <v>9</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.15</v>
+        <v>4.95</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.85</v>
+        <v>18.76</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="EC2" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0.5600000000000001</v>
@@ -1809,7 +1809,7 @@
         <v>2.89</v>
       </c>
       <c r="K3" t="n">
-        <v>3.78</v>
+        <v>3.89</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1830,7 +1830,7 @@
         <v>14.56</v>
       </c>
       <c r="R3" t="n">
-        <v>10.22</v>
+        <v>10.33</v>
       </c>
       <c r="S3" t="n">
         <v>1.67</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>39.56</v>
+        <v>39.67</v>
       </c>
       <c r="Y3" t="n">
         <v>0.22</v>
@@ -1863,7 +1863,7 @@
         <v>3.89</v>
       </c>
       <c r="AC3" t="n">
-        <v>14.78</v>
+        <v>15</v>
       </c>
       <c r="AD3" t="n">
         <v>1.2</v>
@@ -1872,139 +1872,139 @@
         <v>2.56</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AI3" t="n">
-        <v>63.22</v>
+        <v>63</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>24.89</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AP3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BL3" t="n">
         <v>0.89</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>10.56</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>43.33</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
       <c r="BM3" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.72</v>
+        <v>4.63</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.44</v>
+        <v>4.53</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU3" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BV3" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BW3" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BX3" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY3" t="n">
         <v>3.31</v>
@@ -2013,34 +2013,34 @@
         <v>3.62</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.36</v>
+        <v>4.72</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.07</v>
+        <v>5.42</v>
       </c>
       <c r="CE3" t="n">
         <v>1.31</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CH3" t="n">
         <v>1.49</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CK3" t="n">
         <v>1.44</v>
@@ -2061,13 +2061,13 @@
         <v>1.77</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="CT3" t="n">
         <v>3.17</v>
@@ -2076,10 +2076,10 @@
         <v>1.53</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CX3" t="n">
         <v>1.53</v>
@@ -2097,85 +2097,85 @@
         <v>1.25</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="DH3" t="n">
-        <v>66.06</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="DL3" t="n">
         <v>0.11</v>
       </c>
       <c r="DM3" t="n">
-        <v>29.72</v>
+        <v>28.48</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.39</v>
+        <v>11.58</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.39</v>
+        <v>13.42</v>
       </c>
       <c r="DR3" t="n">
-        <v>10.39</v>
+        <v>10.74</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>41.44</v>
+        <v>42.05</v>
       </c>
       <c r="DW3" t="n">
         <v>0.16</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.779999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.56</v>
+        <v>6.42</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="EA3" t="n">
-        <v>15.73</v>
+        <v>16.05</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,139 +2275,139 @@
         <v>1.33</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AI4" t="n">
-        <v>71.33</v>
+        <v>75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.89</v>
+        <v>5.2</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN4" t="n">
-        <v>38.33</v>
+        <v>39.8</v>
       </c>
       <c r="AO4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.22</v>
+        <v>11.9</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.11</v>
+        <v>12.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>47</v>
+        <v>47.7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.67</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>16.22</v>
+        <v>16.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.83</v>
+        <v>8.84</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="BO4" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.56</v>
+        <v>4.58</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT4" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BU4" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV4" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW4" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX4" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY4" t="n">
         <v>3.14</v>
@@ -2416,16 +2416,16 @@
         <v>3.31</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.71</v>
+        <v>3.74</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.93</v>
+        <v>4.23</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.51</v>
+        <v>4.77</v>
       </c>
       <c r="CE4" t="n">
         <v>1.31</v>
@@ -2440,10 +2440,10 @@
         <v>1.49</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CK4" t="n">
         <v>1.43</v>
@@ -2452,19 +2452,19 @@
         <v>1.84</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CO4" t="n">
         <v>1.2</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CR4" t="n">
         <v>1.36</v>
@@ -2479,10 +2479,10 @@
         <v>1.52</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CX4" t="n">
         <v>1.51</v>
@@ -2500,85 +2500,85 @@
         <v>1.23</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="DE4" t="n">
         <v>0.11</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="DH4" t="n">
-        <v>66.94</v>
+        <v>69.11</v>
       </c>
       <c r="DI4" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.5</v>
+        <v>4.68</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DM4" t="n">
-        <v>31.72</v>
+        <v>32.84</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.61</v>
+        <v>11.47</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.22</v>
+        <v>12.31</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.84</v>
+        <v>8.58</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.16</v>
+        <v>46.58</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.84</v>
+        <v>11.11</v>
       </c>
       <c r="DY4" t="n">
-        <v>7</v>
+        <v>7.11</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.61</v>
+        <v>19.79</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="F5" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="G5" t="n">
-        <v>4.18</v>
+        <v>4.08</v>
       </c>
       <c r="H5" t="n">
-        <v>106.27</v>
+        <v>106.08</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>6.92</v>
       </c>
       <c r="L5" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M5" t="n">
-        <v>58.36</v>
+        <v>55.83</v>
       </c>
       <c r="N5" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="P5" t="n">
-        <v>11.91</v>
+        <v>12.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.27</v>
+        <v>10.58</v>
       </c>
       <c r="R5" t="n">
-        <v>7.64</v>
+        <v>7.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="T5" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>59.82</v>
+        <v>58.83</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.91</v>
+        <v>18.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.18</v>
+        <v>12.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.73</v>
+        <v>6.67</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.73</v>
+        <v>21.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AF5" t="n">
         <v>0.09</v>
@@ -2759,70 +2759,70 @@
         <v>1.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.41</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.59</v>
+        <v>5.61</v>
       </c>
       <c r="BR5" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS5" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT5" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU5" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV5" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX5" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.95</v>
+        <v>3.99</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.15</v>
+        <v>4.21</v>
       </c>
       <c r="CC5" t="n">
         <v>2.33</v>
@@ -2843,10 +2843,10 @@
         <v>1.51</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK5" t="n">
         <v>1.48</v>
@@ -2855,10 +2855,10 @@
         <v>1.92</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CO5" t="n">
         <v>1.21</v>
@@ -2867,13 +2867,13 @@
         <v>1.72</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CR5" t="n">
         <v>1.37</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CT5" t="n">
         <v>3.19</v>
@@ -2882,16 +2882,16 @@
         <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX5" t="n">
         <v>1.52</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.43</v>
@@ -2906,79 +2906,79 @@
         <v>1.76</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="DH5" t="n">
-        <v>102.41</v>
+        <v>102.48</v>
       </c>
       <c r="DI5" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.72</v>
+        <v>5.74</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM5" t="n">
-        <v>50.32</v>
+        <v>49.34</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.28</v>
+        <v>11.39</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.14</v>
+        <v>12.22</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.73</v>
+        <v>7.65</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57.14</v>
+        <v>56.74</v>
       </c>
       <c r="DW5" t="n">
         <v>0.22</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.86</v>
+        <v>16.87</v>
       </c>
       <c r="DY5" t="n">
         <v>11</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.86</v>
+        <v>5.87</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="EC5" t="n">
         <v>2</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0.18</v>
@@ -3081,139 +3081,139 @@
         <v>2.09</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AI6" t="n">
-        <v>101.56</v>
+        <v>101.2</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AL6" t="n">
-        <v>6.22</v>
+        <v>6</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AN6" t="n">
-        <v>50.11</v>
+        <v>49.1</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.33</v>
+        <v>11.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.779999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AU6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO6" t="n">
         <v>1.33</v>
       </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>54</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>14.78</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>11.44</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>19.33</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>9.65</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BP6" t="n">
-        <v>4.65</v>
+        <v>4.52</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="BR6" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS6" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU6" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV6" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW6" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY6" t="n">
         <v>2.01</v>
@@ -3222,136 +3222,136 @@
         <v>2.06</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="CE6" t="n">
         <v>1.35</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI6" t="n">
         <v>2.04</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CU6" t="n">
         <v>1.48</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="DB6" t="n">
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="DG6" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="DH6" t="n">
-        <v>87.45</v>
+        <v>87.95</v>
       </c>
       <c r="DI6" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.9</v>
+        <v>5.81</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DM6" t="n">
-        <v>41.95</v>
+        <v>41.86</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.55</v>
+        <v>11.38</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.9</v>
+        <v>10.86</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.35</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DS6" t="n">
         <v>0.05</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>53.75</v>
+        <v>53.53</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.35</v>
+        <v>14.33</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.2</v>
+        <v>10.09</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.15</v>
+        <v>4.24</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.5</v>
+        <v>17.86</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F7" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="G7" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="H7" t="n">
-        <v>91.81999999999999</v>
+        <v>92.17</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K7" t="n">
-        <v>4.36</v>
+        <v>4.08</v>
       </c>
       <c r="L7" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>36.91</v>
+        <v>36.67</v>
       </c>
       <c r="N7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="O7" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="P7" t="n">
-        <v>11.73</v>
+        <v>11.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.64</v>
+        <v>12.33</v>
       </c>
       <c r="R7" t="n">
-        <v>7.73</v>
+        <v>8.08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T7" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="U7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>51.27</v>
+        <v>51.25</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.55</v>
+        <v>12.08</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.73</v>
+        <v>8.33</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>22.27</v>
+        <v>21.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AF7" t="n">
         <v>0.18</v>
@@ -3565,67 +3565,67 @@
         <v>2.18</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.68</v>
+        <v>8.52</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.32</v>
+        <v>4.22</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>86.36</v>
+        <v>82.61</v>
       </c>
       <c r="BT7" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BU7" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV7" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX7" t="n">
-        <v>77.27</v>
+        <v>73.91</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.53</v>
+        <v>2.72</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.67</v>
+        <v>2.87</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CB7" t="n">
         <v>3.82</v>
@@ -3637,13 +3637,13 @@
         <v>4.91</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CH7" t="n">
         <v>1.44</v>
@@ -3652,7 +3652,7 @@
         <v>1.97</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CK7" t="n">
         <v>1.54</v>
@@ -3667,34 +3667,34 @@
         <v>1.85</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY7" t="n">
         <v>1.99</v>
@@ -3703,91 +3703,91 @@
         <v>2.31</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DH7" t="n">
-        <v>85.59</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.09</v>
+        <v>3.96</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM7" t="n">
-        <v>37.68</v>
+        <v>37.52</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.46</v>
+        <v>12.35</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.87</v>
+        <v>12.69</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.779999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.5</v>
+        <v>47.65</v>
       </c>
       <c r="DW7" t="n">
         <v>0.13</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.1</v>
+        <v>10.91</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.59</v>
+        <v>7.43</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.32</v>
+        <v>20.95</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3890,49 +3890,49 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>80.25</v>
+        <v>77.44</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AN8" t="n">
-        <v>32.75</v>
+        <v>31.56</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.12</v>
+        <v>11.22</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.5</v>
+        <v>12.33</v>
       </c>
       <c r="AS8" t="n">
-        <v>10.5</v>
+        <v>10.11</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>50.62</v>
+        <v>51</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA8" t="n">
-        <v>10.88</v>
+        <v>11.11</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.38</v>
+        <v>7.78</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.38</v>
+        <v>18.67</v>
       </c>
       <c r="BE8" t="n">
         <v>1.17</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BH8" t="n">
         <v>9.890000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BO8" t="n">
         <v>1.11</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.67</v>
+        <v>4.74</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT8" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU8" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV8" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX8" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY8" t="n">
         <v>2.65</v>
@@ -4028,16 +4028,16 @@
         <v>3.08</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.83</v>
+        <v>4.77</v>
       </c>
       <c r="CE8" t="n">
         <v>1.3</v>
@@ -4046,13 +4046,13 @@
         <v>2.47</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CH8" t="n">
         <v>1.53</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.66</v>
@@ -4067,7 +4067,7 @@
         <v>2.57</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO8" t="n">
         <v>1.21</v>
@@ -4076,16 +4076,16 @@
         <v>1.72</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CR8" t="n">
         <v>1.36</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CU8" t="n">
         <v>1.56</v>
@@ -4109,88 +4109,88 @@
         <v>1.96</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC8" t="n">
         <v>1.73</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="DH8" t="n">
-        <v>72.61</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.61</v>
+        <v>4.69</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DM8" t="n">
-        <v>31.56</v>
+        <v>31.05</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.83</v>
+        <v>11.42</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.5</v>
+        <v>12.42</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.609999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.66</v>
+        <v>50.84</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.61</v>
+        <v>11.68</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.67</v>
+        <v>7.84</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="EA8" t="n">
-        <v>18</v>
+        <v>18.16</v>
       </c>
       <c r="EB8" t="n">
         <v>1.18</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0.2</v>
@@ -4293,49 +4293,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AI9" t="n">
-        <v>73</v>
+        <v>75.22</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>38.12</v>
+        <v>37.67</v>
       </c>
       <c r="AO9" t="n">
         <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12</v>
+        <v>11.89</v>
       </c>
       <c r="AR9" t="n">
-        <v>12.25</v>
+        <v>13.22</v>
       </c>
       <c r="AS9" t="n">
         <v>11</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4350,79 +4350,79 @@
         <v>44</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.25</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.62</v>
+        <v>5.22</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="BD9" t="n">
-        <v>18.5</v>
+        <v>19.44</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="BG9" t="n">
         <v>2.89</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.44</v>
+        <v>9.68</v>
       </c>
       <c r="BI9" t="n">
         <v>2.89</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.33</v>
+        <v>4.58</v>
       </c>
       <c r="BQ9" t="n">
         <v>5.11</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT9" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU9" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BY9" t="n">
         <v>2.95</v>
@@ -4431,16 +4431,16 @@
         <v>3.17</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="CC9" t="n">
-        <v>6.35</v>
+        <v>6.08</v>
       </c>
       <c r="CD9" t="n">
-        <v>8.119999999999999</v>
+        <v>7.81</v>
       </c>
       <c r="CE9" t="n">
         <v>1.32</v>
@@ -4449,13 +4449,13 @@
         <v>2.54</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CH9" t="n">
         <v>1.49</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.78</v>
@@ -4464,40 +4464,40 @@
         <v>1.46</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CM9" t="n">
         <v>2.51</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO9" t="n">
         <v>1.23</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CX9" t="n">
         <v>1.53</v>
@@ -4518,49 +4518,49 @@
         <v>1.84</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="DE9" t="n">
         <v>0.11</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DH9" t="n">
-        <v>75.94</v>
+        <v>76.84</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.61</v>
+        <v>3.74</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM9" t="n">
-        <v>36.44</v>
+        <v>36.32</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.83</v>
+        <v>11.79</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.33</v>
+        <v>12.79</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.609999999999999</v>
+        <v>9.68</v>
       </c>
       <c r="DS9" t="n">
         <v>0.11</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.83</v>
+        <v>43.84</v>
       </c>
       <c r="DW9" t="n">
         <v>0.16</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.109999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.22</v>
+        <v>6</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.17</v>
+        <v>17.68</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>0.09</v>
@@ -4693,139 +4693,139 @@
         <v>1.55</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AI10" t="n">
-        <v>61.82</v>
+        <v>61.08</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN10" t="n">
-        <v>27.45</v>
+        <v>28.58</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.73</v>
+        <v>10.83</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.18</v>
+        <v>13.42</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.09</v>
+        <v>8.08</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>54.27</v>
+        <v>53.83</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA10" t="n">
-        <v>13</v>
+        <v>13.17</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.91</v>
+        <v>8.17</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.09</v>
+        <v>17.75</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.32</v>
+        <v>8.57</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.14</v>
+        <v>4.3</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.14</v>
+        <v>4.22</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU10" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BV10" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BW10" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BX10" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY10" t="n">
         <v>1.82</v>
@@ -4834,16 +4834,16 @@
         <v>1.93</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.16</v>
+        <v>4.13</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.81</v>
+        <v>3.72</v>
       </c>
       <c r="CE10" t="n">
         <v>1.3</v>
@@ -4852,19 +4852,19 @@
         <v>2.41</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL10" t="n">
         <v>1.89</v>
@@ -4873,7 +4873,7 @@
         <v>2.52</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CO10" t="n">
         <v>1.19</v>
@@ -4882,7 +4882,7 @@
         <v>1.7</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CR10" t="n">
         <v>1.36</v>
@@ -4897,7 +4897,7 @@
         <v>1.58</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CW10" t="n">
         <v>1.68</v>
@@ -4912,7 +4912,7 @@
         <v>2.45</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DB10" t="n">
         <v>1.22</v>
@@ -4924,79 +4924,79 @@
         <v>2.75</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="DH10" t="n">
-        <v>77.59</v>
+        <v>76.52</v>
       </c>
       <c r="DI10" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DM10" t="n">
-        <v>35.45</v>
+        <v>35.69</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO10" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.73</v>
+        <v>10.78</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13</v>
+        <v>13.13</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.77</v>
+        <v>55.48</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.14</v>
+        <v>13.22</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.95</v>
+        <v>8.09</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.18</v>
+        <v>5.13</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.87</v>
+        <v>17.7</v>
       </c>
       <c r="EB10" t="n">
         <v>1.36</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="11">
@@ -5006,67 +5006,67 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F11" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="G11" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="H11" t="n">
-        <v>82</v>
+        <v>80.89</v>
       </c>
       <c r="I11" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="K11" t="n">
-        <v>5.38</v>
+        <v>5.89</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="M11" t="n">
-        <v>43.75</v>
+        <v>47.11</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P11" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="R11" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="P11" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="R11" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.88</v>
-      </c>
       <c r="T11" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="U11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -5078,22 +5078,22 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.5</v>
+        <v>18.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>13.5</v>
+        <v>13.44</v>
       </c>
       <c r="AB11" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="AC11" t="n">
-        <v>24.62</v>
+        <v>24.44</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AF11" t="n">
         <v>0.1</v>
@@ -5177,70 +5177,70 @@
         <v>2.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.890000000000001</v>
+        <v>10.11</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.61</v>
+        <v>4.68</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU11" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV11" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW11" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX11" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BY11" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BZ11" t="n">
         <v>2.25</v>
       </c>
-      <c r="BZ11" t="n">
-        <v>2.21</v>
-      </c>
       <c r="CA11" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="CC11" t="n">
         <v>3.62</v>
@@ -5255,16 +5255,16 @@
         <v>2.35</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CH11" t="n">
         <v>1.55</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CK11" t="n">
         <v>1.4</v>
@@ -5273,7 +5273,7 @@
         <v>1.77</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CN11" t="n">
         <v>2.07</v>
@@ -5285,7 +5285,7 @@
         <v>1.64</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CR11" t="n">
         <v>1.36</v>
@@ -5300,16 +5300,16 @@
         <v>1.55</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CX11" t="n">
         <v>1.5</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.47</v>
@@ -5327,79 +5327,79 @@
         <v>2.68</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="DH11" t="n">
-        <v>86.11</v>
+        <v>85.37</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.11</v>
+        <v>5.37</v>
       </c>
       <c r="DL11" t="n">
         <v>0.11</v>
       </c>
       <c r="DM11" t="n">
-        <v>44</v>
+        <v>45.58</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.34</v>
+        <v>12.37</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.72</v>
+        <v>10.84</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.16</v>
+        <v>9.26</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.61</v>
+        <v>49.68</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX11" t="n">
-        <v>16.44</v>
+        <v>16.47</v>
       </c>
       <c r="DY11" t="n">
-        <v>11.28</v>
+        <v>11.37</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.17</v>
+        <v>5.11</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.66</v>
+        <v>21.73</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="G12" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="H12" t="n">
-        <v>91.22</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="K12" t="n">
-        <v>5.78</v>
+        <v>5.6</v>
       </c>
       <c r="L12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="M12" t="n">
-        <v>41.11</v>
+        <v>41.2</v>
       </c>
       <c r="N12" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="O12" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>11.44</v>
+        <v>11.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.33</v>
+        <v>12.1</v>
       </c>
       <c r="R12" t="n">
-        <v>7.67</v>
+        <v>7.5</v>
       </c>
       <c r="S12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="U12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>55.22</v>
+        <v>54.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.11</v>
+        <v>15</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.78</v>
+        <v>10.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>15.11</v>
+        <v>15.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AF12" t="n">
         <v>0.09</v>
@@ -5580,34 +5580,34 @@
         <v>2.27</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.85</v>
+        <v>8.9</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BQ12" t="n">
         <v>3.95</v>
@@ -5616,34 +5616,34 @@
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU12" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV12" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="CC12" t="n">
         <v>2.72</v>
@@ -5655,16 +5655,16 @@
         <v>1.32</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CH12" t="n">
         <v>1.49</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.69</v>
@@ -5682,28 +5682,28 @@
         <v>2.03</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP12" t="n">
         <v>1.75</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CR12" t="n">
         <v>1.37</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CU12" t="n">
         <v>1.52</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CW12" t="n">
         <v>1.72</v>
@@ -5724,85 +5724,85 @@
         <v>1.25</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="DE12" t="n">
         <v>0.05</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="DH12" t="n">
-        <v>82.75</v>
+        <v>83.33</v>
       </c>
       <c r="DI12" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.6</v>
+        <v>4.57</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.4</v>
+        <v>38.57</v>
       </c>
       <c r="DN12" t="n">
         <v>0.9</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.45</v>
+        <v>11.28</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.25</v>
+        <v>12.14</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.15</v>
+        <v>9</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.65</v>
+        <v>52.34</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.15</v>
+        <v>14.14</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.45</v>
+        <v>4.62</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.85</v>
+        <v>18.91</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F13" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="G13" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="H13" t="n">
-        <v>98.25</v>
+        <v>96.56</v>
       </c>
       <c r="I13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J13" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="K13" t="n">
-        <v>4.25</v>
+        <v>4.67</v>
       </c>
       <c r="L13" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>44.75</v>
+        <v>45.56</v>
       </c>
       <c r="N13" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="O13" t="n">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="P13" t="n">
-        <v>10.75</v>
+        <v>11.11</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.88</v>
+        <v>12.89</v>
       </c>
       <c r="R13" t="n">
-        <v>7.12</v>
+        <v>6.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="T13" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>55.12</v>
+        <v>55.22</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.62</v>
+        <v>13.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.380000000000001</v>
+        <v>9</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.25</v>
+        <v>4.56</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.75</v>
+        <v>22.78</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.2</v>
@@ -5974,7 +5974,7 @@
         <v>4</v>
       </c>
       <c r="BD13" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="BE13" t="n">
         <v>1.11</v>
@@ -5983,70 +5983,70 @@
         <v>2.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.33</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.83</v>
+        <v>4.11</v>
       </c>
       <c r="BQ13" t="n">
         <v>5.11</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT13" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BU13" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV13" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW13" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BX13" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.17</v>
+        <v>3.03</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.26</v>
+        <v>3.09</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="CC13" t="n">
         <v>5.18</v>
@@ -6061,22 +6061,22 @@
         <v>2.64</v>
       </c>
       <c r="CG13" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CH13" t="n">
         <v>1.47</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CK13" t="n">
         <v>1.44</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM13" t="n">
         <v>2.55</v>
@@ -6088,10 +6088,10 @@
         <v>1.25</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CR13" t="n">
         <v>1.38</v>
@@ -6109,7 +6109,7 @@
         <v>2.07</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CX13" t="n">
         <v>1.51</v>
@@ -6133,79 +6133,79 @@
         <v>3.26</v>
       </c>
       <c r="DE13" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="DH13" t="n">
-        <v>87.22</v>
+        <v>87</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.94</v>
+        <v>5.11</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="DM13" t="n">
-        <v>36.61</v>
+        <v>37.42</v>
       </c>
       <c r="DN13" t="n">
         <v>1</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.72</v>
+        <v>12.79</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.5</v>
+        <v>12.53</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.890000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>51.5</v>
+        <v>51.68</v>
       </c>
       <c r="DW13" t="n">
         <v>0.11</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.83</v>
+        <v>12.32</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.72</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.11</v>
+        <v>4.27</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.78</v>
+        <v>21</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
         <v>0.11</v>
@@ -6305,139 +6305,139 @@
         <v>2.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AI14" t="n">
-        <v>73.59999999999999</v>
+        <v>72.36</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.7</v>
+        <v>3.91</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.3</v>
+        <v>4.09</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AN14" t="n">
-        <v>40.5</v>
+        <v>39.09</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14.1</v>
+        <v>14.18</v>
       </c>
       <c r="AR14" t="n">
-        <v>11.3</v>
+        <v>11.18</v>
       </c>
       <c r="AS14" t="n">
-        <v>12.6</v>
+        <v>13.27</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>46.4</v>
+        <v>45</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.5</v>
+        <v>10.09</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.1</v>
+        <v>6.64</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BD14" t="n">
-        <v>18</v>
+        <v>17.18</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.58</v>
+        <v>9.15</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.26</v>
+        <v>4.45</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.21</v>
+        <v>4.6</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS14" t="n">
-        <v>84.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT14" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU14" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV14" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>73.68000000000001</v>
+        <v>70</v>
       </c>
       <c r="BY14" t="n">
         <v>1.94</v>
@@ -6446,16 +6446,16 @@
         <v>2.05</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="CB14" t="n">
         <v>3.65</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.23</v>
+        <v>3.48</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.54</v>
+        <v>3.74</v>
       </c>
       <c r="CE14" t="n">
         <v>1.37</v>
@@ -6464,16 +6464,16 @@
         <v>2.77</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CH14" t="n">
         <v>1.4</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK14" t="n">
         <v>1.51</v>
@@ -6494,31 +6494,31 @@
         <v>1.93</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CU14" t="n">
         <v>1.43</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX14" t="n">
         <v>1.56</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.34</v>
@@ -6533,82 +6533,82 @@
         <v>2.01</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="DE14" t="n">
         <v>0.1</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="DH14" t="n">
-        <v>85.73999999999999</v>
+        <v>84.45</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.68</v>
+        <v>4.55</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DM14" t="n">
-        <v>44.05</v>
+        <v>43.1</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.26</v>
+        <v>13.35</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.89</v>
+        <v>10.85</v>
       </c>
       <c r="DR14" t="n">
-        <v>11</v>
+        <v>11.45</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>52.58</v>
+        <v>51.5</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.05</v>
+        <v>11.75</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.42</v>
+        <v>8.1</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.95</v>
+        <v>18.45</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="H15" t="n">
-        <v>75.38</v>
+        <v>79.67</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="M15" t="n">
-        <v>27.38</v>
+        <v>29.56</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="P15" t="n">
-        <v>14.5</v>
+        <v>14.11</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.25</v>
+        <v>12.33</v>
       </c>
       <c r="R15" t="n">
-        <v>10.88</v>
+        <v>10.22</v>
       </c>
       <c r="S15" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T15" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="U15" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="V15" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>41.25</v>
+        <v>42.33</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.619999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.38</v>
+        <v>5.56</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="AC15" t="n">
-        <v>16.88</v>
+        <v>17.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6789,70 +6789,70 @@
         <v>2</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.33</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.33</v>
+        <v>4.47</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.94</v>
+        <v>4.95</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU15" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV15" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX15" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.51</v>
+        <v>3.42</v>
       </c>
       <c r="BZ15" t="n">
-        <v>4.01</v>
+        <v>3.88</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.32</v>
+        <v>4.26</v>
       </c>
       <c r="CC15" t="n">
         <v>7.1</v>
@@ -6861,43 +6861,43 @@
         <v>7.43</v>
       </c>
       <c r="CE15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CK15" t="n">
         <v>1.35</v>
       </c>
-      <c r="CF15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="CG15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="CH15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="CI15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="CJ15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="CK15" t="n">
-        <v>1.42</v>
-      </c>
       <c r="CL15" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="CR15" t="n">
         <v>1.4</v>
@@ -6942,76 +6942,76 @@
         <v>0.05</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DH15" t="n">
-        <v>59.89</v>
+        <v>62.74</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.11</v>
+        <v>3.26</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DM15" t="n">
-        <v>25</v>
+        <v>26.16</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.39</v>
+        <v>12.32</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.5</v>
+        <v>12.52</v>
       </c>
       <c r="DR15" t="n">
-        <v>11</v>
+        <v>10.68</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>36.22</v>
+        <v>37</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX15" t="n">
-        <v>8.609999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.28</v>
+        <v>5.37</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.33</v>
+        <v>3.42</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.06</v>
+        <v>16.31</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7111,49 +7111,49 @@
         <v>2.4</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AI16" t="n">
-        <v>81.38</v>
+        <v>81.22</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.62</v>
+        <v>4.22</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN16" t="n">
-        <v>33.25</v>
+        <v>33.11</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.38</v>
+        <v>10.44</v>
       </c>
       <c r="AR16" t="n">
-        <v>14.12</v>
+        <v>14.11</v>
       </c>
       <c r="AS16" t="n">
-        <v>12.75</v>
+        <v>12.78</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AU16" t="n">
         <v>1</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>46.75</v>
+        <v>44.56</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.5</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BB16" t="n">
-        <v>6</v>
+        <v>5.44</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.12</v>
+        <v>15.56</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="BG16" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.17</v>
+        <v>10.89</v>
       </c>
       <c r="BI16" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.83</v>
+        <v>0.95</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.33</v>
+        <v>6.11</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT16" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU16" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BV16" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY16" t="n">
         <v>3.41</v>
@@ -7252,31 +7252,31 @@
         <v>3.65</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.1</v>
+        <v>4.26</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.48</v>
+        <v>4.66</v>
       </c>
       <c r="CC16" t="n">
-        <v>6.45</v>
+        <v>7.06</v>
       </c>
       <c r="CD16" t="n">
-        <v>7.37</v>
+        <v>7.76</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.65</v>
@@ -7291,31 +7291,31 @@
         <v>2.85</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="CT16" t="n">
         <v>3.23</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW16" t="n">
         <v>1.66</v>
@@ -7336,52 +7336,52 @@
         <v>1.2</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="DE16" t="n">
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="DH16" t="n">
-        <v>74.22</v>
+        <v>74.53</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.06</v>
+        <v>3.21</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.33</v>
+        <v>4.16</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM16" t="n">
-        <v>35.33</v>
+        <v>35.16</v>
       </c>
       <c r="DN16" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.84</v>
+        <v>11.79</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.39</v>
+        <v>14.37</v>
       </c>
       <c r="DR16" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="DS16" t="n">
         <v>0.11</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.56</v>
+        <v>43.63</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.5</v>
+        <v>10.11</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.33</v>
+        <v>6.05</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.17</v>
+        <v>4.05</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.28</v>
+        <v>16.95</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="17">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F17" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="G17" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="H17" t="n">
-        <v>90.67</v>
+        <v>92.62</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="K17" t="n">
-        <v>5.67</v>
+        <v>6.62</v>
       </c>
       <c r="L17" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="M17" t="n">
-        <v>51.83</v>
+        <v>54.46</v>
       </c>
       <c r="N17" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="O17" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="P17" t="n">
-        <v>11.92</v>
+        <v>11.69</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.67</v>
+        <v>13.15</v>
       </c>
       <c r="R17" t="n">
-        <v>6.83</v>
+        <v>6.38</v>
       </c>
       <c r="S17" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="T17" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="U17" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V17" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>53.92</v>
+        <v>55.08</v>
       </c>
       <c r="Y17" t="n">
         <v>0.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.08</v>
+        <v>18.23</v>
       </c>
       <c r="AA17" t="n">
-        <v>11</v>
+        <v>12.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.08</v>
+        <v>6.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>17.92</v>
+        <v>18.46</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,70 +7595,70 @@
         <v>2.83</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.42</v>
+        <v>9.84</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="BO17" t="n">
         <v>1.12</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.21</v>
+        <v>4.36</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5</v>
+        <v>5.28</v>
       </c>
       <c r="BR17" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS17" t="n">
-        <v>79.17</v>
+        <v>76</v>
       </c>
       <c r="BT17" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BU17" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BV17" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX17" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="BZ17" t="n">
         <v>1.64</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.12</v>
+        <v>4.1</v>
       </c>
       <c r="CC17" t="n">
         <v>2.47</v>
@@ -7670,7 +7670,7 @@
         <v>1.27</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CG17" t="n">
         <v>2.97</v>
@@ -7679,16 +7679,16 @@
         <v>1.42</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM17" t="n">
         <v>2.36</v>
@@ -7697,31 +7697,31 @@
         <v>1.84</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CX17" t="n">
         <v>1.52</v>
@@ -7730,61 +7730,61 @@
         <v>1.87</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DA17" t="n">
         <v>1.94</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="DE17" t="n">
         <v>0.12</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.54</v>
+        <v>2.92</v>
       </c>
       <c r="DH17" t="n">
-        <v>91.34</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="DI17" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.42</v>
+        <v>5.92</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DM17" t="n">
-        <v>46.79</v>
+        <v>48.36</v>
       </c>
       <c r="DN17" t="n">
         <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.17</v>
+        <v>12.04</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.38</v>
+        <v>12.64</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.62</v>
+        <v>7.36</v>
       </c>
       <c r="DS17" t="n">
         <v>0.08</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>53.62</v>
+        <v>54.24</v>
       </c>
       <c r="DW17" t="n">
         <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.5</v>
+        <v>16.16</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.789999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.71</v>
+        <v>5.76</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.05</v>
+        <v>18.32</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
         <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
         <v>0.08</v>
@@ -7920,136 +7920,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AI18" t="n">
-        <v>68.56</v>
+        <v>67.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>33.78</v>
+        <v>32.5</v>
       </c>
       <c r="AO18" t="n">
         <v>1</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.11</v>
+        <v>12</v>
       </c>
       <c r="AR18" t="n">
-        <v>12.22</v>
+        <v>12.1</v>
       </c>
       <c r="AS18" t="n">
-        <v>11.33</v>
+        <v>11.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>43.33</v>
+        <v>43.9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.22</v>
+        <v>10.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.33</v>
+        <v>7.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BD18" t="n">
-        <v>19.11</v>
+        <v>18.5</v>
       </c>
       <c r="BE18" t="n">
         <v>1.09</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BG18" t="n">
         <v>3.05</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.9</v>
+        <v>8.09</v>
       </c>
       <c r="BI18" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.48</v>
+        <v>3.64</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.81</v>
+        <v>3.86</v>
       </c>
       <c r="BR18" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS18" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU18" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BV18" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW18" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX18" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BY18" t="n">
         <v>2.48</v>
@@ -8058,55 +8058,55 @@
         <v>2.62</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.77</v>
+        <v>4.54</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.24</v>
+        <v>4.98</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="CH18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CJ18" t="n">
         <v>1.43</v>
       </c>
-      <c r="CI18" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="CJ18" t="n">
-        <v>1.5</v>
-      </c>
       <c r="CK18" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
@@ -8148,79 +8148,79 @@
         <v>2.58</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="DH18" t="n">
-        <v>78.95</v>
+        <v>77.86</v>
       </c>
       <c r="DI18" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.19</v>
+        <v>3.32</v>
       </c>
       <c r="DL18" t="n">
         <v>0.14</v>
       </c>
       <c r="DM18" t="n">
-        <v>35.76</v>
+        <v>35.09</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.38</v>
+        <v>12.32</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.19</v>
+        <v>13.09</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.140000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.28</v>
+        <v>47.36</v>
       </c>
       <c r="DW18" t="n">
         <v>0.09</v>
       </c>
       <c r="DX18" t="n">
-        <v>12</v>
+        <v>11.91</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.9</v>
+        <v>7.82</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.86</v>
+        <v>17.64</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="19">
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
         <v>12</v>
@@ -8242,13 +8242,13 @@
         <v>0.08</v>
       </c>
       <c r="F19" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="G19" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="H19" t="n">
-        <v>90.58</v>
+        <v>92.77</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -8257,67 +8257,67 @@
         <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>5.83</v>
+        <v>5.77</v>
       </c>
       <c r="L19" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="M19" t="n">
-        <v>46.25</v>
+        <v>48.15</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="O19" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="P19" t="n">
-        <v>12.75</v>
+        <v>12.92</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.08</v>
+        <v>10.92</v>
       </c>
       <c r="R19" t="n">
-        <v>9.25</v>
+        <v>8.92</v>
       </c>
       <c r="S19" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T19" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="U19" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="V19" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>57.17</v>
+        <v>58.38</v>
       </c>
       <c r="Y19" t="n">
         <v>0.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>20.33</v>
+        <v>20.46</v>
       </c>
       <c r="AA19" t="n">
-        <v>13.92</v>
+        <v>13.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.42</v>
+        <v>6.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.08</v>
+        <v>18.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
         <v>0.08</v>
@@ -8401,70 +8401,70 @@
         <v>2.33</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.42</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.46</v>
+        <v>4.44</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.38</v>
+        <v>4.28</v>
       </c>
       <c r="BR19" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BS19" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BT19" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BU19" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="BV19" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BW19" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BX19" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.05</v>
+        <v>4.18</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.41</v>
+        <v>4.55</v>
       </c>
       <c r="CC19" t="n">
         <v>2.32</v>
@@ -8473,31 +8473,31 @@
         <v>2.4</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.47</v>
+        <v>3.52</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.63</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CN19" t="n">
         <v>1.85</v>
@@ -8506,121 +8506,121 @@
         <v>1.16</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CT19" t="n">
         <v>3.18</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX19" t="n">
         <v>1.55</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.39</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DB19" t="n">
         <v>1.2</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="DE19" t="n">
         <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="DG19" t="n">
         <v>2.16</v>
       </c>
       <c r="DH19" t="n">
-        <v>79.67</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM19" t="n">
-        <v>38.71</v>
+        <v>40</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.08</v>
+        <v>13.16</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.92</v>
+        <v>11.8</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.289999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.34</v>
+        <v>55.08</v>
       </c>
       <c r="DW19" t="n">
         <v>0.12</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.25</v>
+        <v>17.44</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.5</v>
+        <v>11.56</v>
       </c>
       <c r="DZ19" t="n">
-        <v>5.75</v>
+        <v>5.88</v>
       </c>
       <c r="EA19" t="n">
-        <v>19</v>
+        <v>19.12</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="EC19" t="n">
         <v>2.08</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1424,7 +1424,7 @@
         <v>10.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="R2" t="n">
         <v>6.7</v>
@@ -1460,7 +1460,7 @@
         <v>6.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AD2" t="n">
         <v>1.99</v>
@@ -1607,13 +1607,13 @@
         <v>1.43</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CA2" t="n">
         <v>4.08</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="CC2" t="n">
         <v>2.24</v>
@@ -1673,22 +1673,22 @@
         <v>1.57</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX2" t="n">
         <v>1.52</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.44</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB2" t="n">
         <v>1.24</v>
@@ -1697,7 +1697,7 @@
         <v>1.76</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE2" t="n">
         <v>0.09</v>
@@ -1736,7 +1736,7 @@
         <v>10.72</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.05</v>
+        <v>12.09</v>
       </c>
       <c r="DR2" t="n">
         <v>6.57</v>
@@ -1766,7 +1766,7 @@
         <v>4.95</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.76</v>
+        <v>18.81</v>
       </c>
       <c r="EB2" t="n">
         <v>1.63</v>
@@ -1905,7 +1905,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR3" t="n">
         <v>12.4</v>
@@ -2016,13 +2016,13 @@
         <v>3.75</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="CC3" t="n">
         <v>4.72</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.42</v>
+        <v>5.36</v>
       </c>
       <c r="CE3" t="n">
         <v>1.31</v>
@@ -2067,7 +2067,7 @@
         <v>1.38</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CT3" t="n">
         <v>3.17</v>
@@ -2076,10 +2076,10 @@
         <v>1.53</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX3" t="n">
         <v>1.53</v>
@@ -2097,10 +2097,10 @@
         <v>1.25</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="DE3" t="n">
         <v>0.32</v>
@@ -2136,7 +2136,7 @@
         <v>1.26</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.58</v>
+        <v>11.53</v>
       </c>
       <c r="DQ3" t="n">
         <v>13.42</v>
@@ -2419,13 +2419,13 @@
         <v>3.74</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="CC4" t="n">
         <v>4.23</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.77</v>
+        <v>4.7</v>
       </c>
       <c r="CE4" t="n">
         <v>1.31</v>
@@ -2479,31 +2479,31 @@
         <v>1.52</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CW4" t="n">
         <v>1.68</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB4" t="n">
         <v>1.23</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE4" t="n">
         <v>0.11</v>
@@ -2660,16 +2660,16 @@
         <v>0.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.75</v>
+        <v>18.67</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.08</v>
+        <v>12</v>
       </c>
       <c r="AB5" t="n">
         <v>6.67</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.75</v>
+        <v>21.83</v>
       </c>
       <c r="AD5" t="n">
         <v>2.05</v>
@@ -2816,13 +2816,13 @@
         <v>1.7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CA5" t="n">
         <v>3.99</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.21</v>
+        <v>4.18</v>
       </c>
       <c r="CC5" t="n">
         <v>2.33</v>
@@ -2873,7 +2873,7 @@
         <v>1.37</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CT5" t="n">
         <v>3.19</v>
@@ -2882,10 +2882,10 @@
         <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX5" t="n">
         <v>1.52</v>
@@ -2906,7 +2906,7 @@
         <v>1.76</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="DE5" t="n">
         <v>0.13</v>
@@ -2966,16 +2966,16 @@
         <v>0.22</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.87</v>
+        <v>16.83</v>
       </c>
       <c r="DY5" t="n">
-        <v>11</v>
+        <v>10.96</v>
       </c>
       <c r="DZ5" t="n">
         <v>5.87</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.83</v>
+        <v>21.87</v>
       </c>
       <c r="EB5" t="n">
         <v>1.83</v>
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="H9" t="n">
-        <v>78.3</v>
+        <v>78.09</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M9" t="n">
-        <v>35.1</v>
+        <v>35.73</v>
       </c>
       <c r="N9" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="P9" t="n">
-        <v>11.7</v>
+        <v>11.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="R9" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>43.7</v>
+        <v>42.82</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.7</v>
+        <v>6.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.1</v>
+        <v>15.82</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>2.56</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.68</v>
+        <v>9.75</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT9" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU9" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BV9" t="n">
-        <v>10.53</v>
+        <v>15</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BX9" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.95</v>
+        <v>3.09</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.17</v>
+        <v>3.44</v>
       </c>
       <c r="CA9" t="n">
         <v>3.89</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.18</v>
+        <v>4.2</v>
       </c>
       <c r="CC9" t="n">
         <v>6.08</v>
@@ -4467,10 +4467,10 @@
         <v>1.87</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO9" t="n">
         <v>1.23</v>
@@ -4482,13 +4482,13 @@
         <v>2.97</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CU9" t="n">
         <v>1.53</v>
@@ -4497,16 +4497,16 @@
         <v>2.13</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX9" t="n">
         <v>1.53</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DA9" t="n">
         <v>1.96</v>
@@ -4515,85 +4515,85 @@
         <v>1.26</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="DH9" t="n">
-        <v>76.84</v>
+        <v>76.8</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ9" t="n">
         <v>3</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM9" t="n">
-        <v>36.32</v>
+        <v>36.6</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.79</v>
+        <v>11.45</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.79</v>
+        <v>12.55</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.68</v>
+        <v>9.35</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.84</v>
+        <v>43.35</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX9" t="n">
         <v>9.050000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.68</v>
+        <v>17.45</v>
       </c>
       <c r="EB9" t="n">
         <v>1.02</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
         <v>0.09</v>
@@ -4693,139 +4693,139 @@
         <v>1.55</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AI10" t="n">
-        <v>61.08</v>
+        <v>62.38</v>
       </c>
       <c r="AJ10" t="n">
         <v>-0.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.67</v>
+        <v>3.92</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AN10" t="n">
-        <v>28.58</v>
+        <v>29.08</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.83</v>
+        <v>10.31</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.42</v>
+        <v>13.31</v>
       </c>
       <c r="AS10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="BB10" t="n">
         <v>8.08</v>
       </c>
-      <c r="AT10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>53.83</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>8.17</v>
-      </c>
       <c r="BC10" t="n">
-        <v>5</v>
+        <v>5.46</v>
       </c>
       <c r="BD10" t="n">
-        <v>17.75</v>
+        <v>18.23</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.57</v>
+        <v>8.67</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.22</v>
+        <v>4.29</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT10" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BV10" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BW10" t="n">
-        <v>17.39</v>
+        <v>20.83</v>
       </c>
       <c r="BX10" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BY10" t="n">
         <v>1.82</v>
@@ -4834,46 +4834,46 @@
         <v>1.93</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.13</v>
+        <v>4.15</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.72</v>
+        <v>3.55</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF10" t="n">
         <v>2.41</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL10" t="n">
         <v>1.89</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO10" t="n">
         <v>1.19</v>
@@ -4882,16 +4882,16 @@
         <v>1.7</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS10" t="n">
         <v>2.51</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CU10" t="n">
         <v>1.58</v>
@@ -4912,91 +4912,91 @@
         <v>2.45</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB10" t="n">
         <v>1.22</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DH10" t="n">
-        <v>76.52</v>
+        <v>76.58</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.74</v>
+        <v>3.87</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="DM10" t="n">
-        <v>35.69</v>
+        <v>35.67</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.78</v>
+        <v>10.5</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.13</v>
+        <v>13.09</v>
       </c>
       <c r="DR10" t="n">
         <v>7</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.48</v>
+        <v>55.92</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.22</v>
+        <v>13.42</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.09</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.13</v>
+        <v>5.37</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.7</v>
+        <v>17.96</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="11">
@@ -6344,7 +6344,7 @@
         <v>11.18</v>
       </c>
       <c r="AS14" t="n">
-        <v>13.27</v>
+        <v>13.36</v>
       </c>
       <c r="AT14" t="n">
         <v>1.73</v>
@@ -6362,7 +6362,7 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>45</v>
+        <v>45.09</v>
       </c>
       <c r="AZ14" t="n">
         <v>0.27</v>
@@ -6449,13 +6449,13 @@
         <v>3.52</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CC14" t="n">
         <v>3.48</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="CE14" t="n">
         <v>1.37</v>
@@ -6497,28 +6497,28 @@
         <v>3.3</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CU14" t="n">
         <v>1.43</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX14" t="n">
         <v>1.56</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.34</v>
@@ -6530,10 +6530,10 @@
         <v>1.31</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="DE14" t="n">
         <v>0.1</v>
@@ -6575,7 +6575,7 @@
         <v>10.85</v>
       </c>
       <c r="DR14" t="n">
-        <v>11.45</v>
+        <v>11.5</v>
       </c>
       <c r="DS14" t="n">
         <v>0.2</v>
@@ -6587,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.5</v>
+        <v>51.55</v>
       </c>
       <c r="DW14" t="n">
         <v>0.15</v>
@@ -6690,10 +6690,10 @@
         <v>0.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.56</v>
+        <v>5.44</v>
       </c>
       <c r="AB15" t="n">
         <v>3.44</v>
@@ -6702,7 +6702,7 @@
         <v>17.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AE15" t="n">
         <v>3</v>
@@ -6846,7 +6846,7 @@
         <v>3.42</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CA15" t="n">
         <v>4.04</v>
@@ -6996,10 +6996,10 @@
         <v>0.21</v>
       </c>
       <c r="DX15" t="n">
-        <v>8.789999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.37</v>
+        <v>5.31</v>
       </c>
       <c r="DZ15" t="n">
         <v>3.42</v>
@@ -7008,7 +7008,7 @@
         <v>16.31</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="EC15" t="n">
         <v>2.47</v>
@@ -7183,7 +7183,7 @@
         <v>3.33</v>
       </c>
       <c r="BD16" t="n">
-        <v>15.56</v>
+        <v>15.67</v>
       </c>
       <c r="BE16" t="n">
         <v>1.03</v>
@@ -7255,13 +7255,13 @@
         <v>4.26</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.66</v>
+        <v>4.69</v>
       </c>
       <c r="CC16" t="n">
         <v>7.06</v>
       </c>
       <c r="CD16" t="n">
-        <v>7.76</v>
+        <v>7.9</v>
       </c>
       <c r="CE16" t="n">
         <v>1.27</v>
@@ -7306,13 +7306,13 @@
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="CT16" t="n">
         <v>3.23</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="CV16" t="n">
         <v>2.31</v>
@@ -7330,7 +7330,7 @@
         <v>2.5</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DB16" t="n">
         <v>1.2</v>
@@ -7408,7 +7408,7 @@
         <v>4.05</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.95</v>
+        <v>17</v>
       </c>
       <c r="EB16" t="n">
         <v>1.18</v>
@@ -7490,7 +7490,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>55.08</v>
+        <v>55</v>
       </c>
       <c r="Y17" t="n">
         <v>0.08</v>
@@ -7505,7 +7505,7 @@
         <v>6.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.46</v>
+        <v>18.54</v>
       </c>
       <c r="AD17" t="n">
         <v>1.97</v>
@@ -7652,13 +7652,13 @@
         <v>1.64</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CA17" t="n">
         <v>3.8</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="CC17" t="n">
         <v>2.47</v>
@@ -7706,22 +7706,22 @@
         <v>2.86</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CV17" t="n">
         <v>2.11</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX17" t="n">
         <v>1.52</v>
@@ -7736,13 +7736,13 @@
         <v>1.94</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="DE17" t="n">
         <v>0.12</v>
@@ -7796,7 +7796,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.24</v>
+        <v>54.2</v>
       </c>
       <c r="DW17" t="n">
         <v>0.12</v>
@@ -7811,7 +7811,7 @@
         <v>5.76</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.32</v>
+        <v>18.36</v>
       </c>
       <c r="EB17" t="n">
         <v>1.77</v>
@@ -8067,7 +8067,7 @@
         <v>4.54</v>
       </c>
       <c r="CD18" t="n">
-        <v>4.98</v>
+        <v>5</v>
       </c>
       <c r="CE18" t="n">
         <v>1.1</v>
@@ -8464,7 +8464,7 @@
         <v>4.18</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.55</v>
+        <v>4.57</v>
       </c>
       <c r="CC19" t="n">
         <v>2.32</v>
@@ -8515,13 +8515,13 @@
         <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="CT19" t="n">
         <v>3.18</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CV19" t="n">
         <v>2.32</v>
@@ -8539,7 +8539,7 @@
         <v>2.39</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB19" t="n">
         <v>1.2</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
@@ -1469,139 +1469,139 @@
         <v>1.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>49.83</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>54</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BN2" t="n">
         <v>1.64</v>
       </c>
-      <c r="AH2" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>101.55</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AL2" t="n">
+      <c r="BO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="BQ2" t="n">
         <v>5.18</v>
       </c>
-      <c r="AM2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>49</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>10.55</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>12.45</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>53.18</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>17.09</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>5.24</v>
-      </c>
       <c r="BR2" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="BS2" t="n">
-        <v>85.70999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV2" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX2" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY2" t="n">
         <v>1.43</v>
@@ -1610,37 +1610,37 @@
         <v>1.48</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.08</v>
+        <v>4.03</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.43</v>
+        <v>4.36</v>
       </c>
       <c r="CC2" t="n">
         <v>2.24</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CE2" t="n">
         <v>1.25</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.7</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL2" t="n">
         <v>1.72</v>
@@ -1649,130 +1649,130 @@
         <v>2.4</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.16</v>
+        <v>3.09</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY2" t="n">
         <v>1.84</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DA2" t="n">
         <v>1.98</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="DE2" t="n">
         <v>0.09</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="DH2" t="n">
-        <v>100.91</v>
+        <v>101.05</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.28</v>
+        <v>6.27</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DM2" t="n">
-        <v>55.29</v>
+        <v>55.45</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.72</v>
+        <v>10.59</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.09</v>
+        <v>12.32</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.57</v>
+        <v>6.55</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.95</v>
+        <v>55.32</v>
       </c>
       <c r="DW2" t="n">
         <v>0.09</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.95</v>
+        <v>13.77</v>
       </c>
       <c r="DY2" t="n">
-        <v>9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.95</v>
+        <v>4.82</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.81</v>
+        <v>18.82</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>0.5600000000000001</v>
@@ -1872,139 +1872,139 @@
         <v>2.56</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AI3" t="n">
-        <v>63</v>
+        <v>63.82</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN3" t="n">
-        <v>23</v>
+        <v>22.45</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.6</v>
+        <v>9.91</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.4</v>
+        <v>12.18</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.1</v>
+        <v>11.09</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>44.2</v>
+        <v>43.82</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.5</v>
+        <v>8.91</v>
       </c>
       <c r="BB3" t="n">
-        <v>6</v>
+        <v>6.36</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="BD3" t="n">
-        <v>17</v>
+        <v>16.82</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.58</v>
+        <v>9.65</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.53</v>
+        <v>4.65</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS3" t="n">
-        <v>84.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT3" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BV3" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BW3" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BX3" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
         <v>3.31</v>
@@ -2013,16 +2013,16 @@
         <v>3.62</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.72</v>
+        <v>4.65</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.36</v>
+        <v>5.26</v>
       </c>
       <c r="CE3" t="n">
         <v>1.31</v>
@@ -2031,28 +2031,28 @@
         <v>2.51</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CH3" t="n">
         <v>1.49</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.71</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CO3" t="n">
         <v>1.22</v>
@@ -2061,7 +2061,7 @@
         <v>1.77</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -2085,13 +2085,13 @@
         <v>1.53</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.44</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB3" t="n">
         <v>1.25</v>
@@ -2100,82 +2100,82 @@
         <v>1.81</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="DH3" t="n">
-        <v>65.79000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM3" t="n">
-        <v>28.48</v>
+        <v>27.9</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.53</v>
+        <v>11.6</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.42</v>
+        <v>13.25</v>
       </c>
       <c r="DR3" t="n">
-        <v>10.74</v>
+        <v>10.75</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>42.05</v>
+        <v>41.95</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.58</v>
+        <v>9.75</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.42</v>
+        <v>6.6</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.05</v>
+        <v>16</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,139 +2275,139 @@
         <v>1.33</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AI4" t="n">
-        <v>75</v>
+        <v>79.55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.2</v>
+        <v>4.82</v>
       </c>
       <c r="AM4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>48.27</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ4" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN4" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BF4" t="n">
+      <c r="BK4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BN4" t="n">
         <v>2.1</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>8.84</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>2.16</v>
       </c>
       <c r="BO4" t="n">
         <v>0.95</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.26</v>
+        <v>4.1</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.58</v>
+        <v>4.45</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT4" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU4" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV4" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW4" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX4" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY4" t="n">
         <v>3.14</v>
@@ -2416,16 +2416,16 @@
         <v>3.31</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.7</v>
+        <v>4.63</v>
       </c>
       <c r="CE4" t="n">
         <v>1.31</v>
@@ -2434,7 +2434,7 @@
         <v>2.46</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CH4" t="n">
         <v>1.49</v>
@@ -2446,22 +2446,22 @@
         <v>1.66</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CO4" t="n">
         <v>1.2</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CQ4" t="n">
         <v>2.7</v>
@@ -2476,25 +2476,25 @@
         <v>3.23</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CW4" t="n">
         <v>1.68</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="DB4" t="n">
         <v>1.23</v>
@@ -2506,79 +2506,79 @@
         <v>2.83</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="DH4" t="n">
-        <v>69.11</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.68</v>
+        <v>4.5</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM4" t="n">
-        <v>32.84</v>
+        <v>33.25</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.47</v>
+        <v>11.3</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.31</v>
+        <v>12.55</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.58</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.58</v>
+        <v>46.95</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.11</v>
+        <v>11.05</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.11</v>
+        <v>7.15</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.79</v>
+        <v>19.95</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="5">
@@ -2588,61 +2588,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F5" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="G5" t="n">
         <v>4.08</v>
       </c>
       <c r="H5" t="n">
-        <v>106.08</v>
+        <v>107.38</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="K5" t="n">
-        <v>6.92</v>
+        <v>7.15</v>
       </c>
       <c r="L5" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="M5" t="n">
-        <v>55.83</v>
+        <v>59.31</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="O5" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>12.08</v>
+        <v>11.69</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.58</v>
+        <v>10.46</v>
       </c>
       <c r="R5" t="n">
-        <v>7.5</v>
+        <v>7.15</v>
       </c>
       <c r="S5" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>0.08</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58.83</v>
+        <v>59.92</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.67</v>
+        <v>19.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>12</v>
+        <v>12.92</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.67</v>
+        <v>6.92</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.83</v>
+        <v>22.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AF5" t="n">
         <v>0.09</v>
@@ -2759,70 +2759,70 @@
         <v>1.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.87</v>
+        <v>2.79</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.390000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.87</v>
+        <v>2.79</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.61</v>
+        <v>5.62</v>
       </c>
       <c r="BR5" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS5" t="n">
-        <v>82.61</v>
+        <v>79.17</v>
       </c>
       <c r="BT5" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU5" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV5" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX5" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
       <c r="CC5" t="n">
         <v>2.33</v>
@@ -2834,7 +2834,7 @@
         <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CG5" t="n">
         <v>3.2</v>
@@ -2852,7 +2852,7 @@
         <v>1.48</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM5" t="n">
         <v>2.51</v>
@@ -2882,7 +2882,7 @@
         <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CW5" t="n">
         <v>1.74</v>
@@ -2909,46 +2909,46 @@
         <v>2.86</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="DH5" t="n">
-        <v>102.48</v>
+        <v>103.33</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.74</v>
+        <v>5.91</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM5" t="n">
-        <v>49.34</v>
+        <v>51.5</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.31</v>
+        <v>2.46</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.39</v>
+        <v>11.21</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.22</v>
+        <v>12.08</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.65</v>
+        <v>7.46</v>
       </c>
       <c r="DS5" t="n">
         <v>0.21</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.74</v>
+        <v>57.41</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.83</v>
+        <v>17.54</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.96</v>
+        <v>11.5</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.87</v>
+        <v>6.04</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.87</v>
+        <v>22.04</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="EC5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F6" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="G6" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>75.91</v>
+        <v>77.92</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="K6" t="n">
-        <v>5.64</v>
+        <v>5.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="M6" t="n">
-        <v>35.27</v>
+        <v>34.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O6" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>10.91</v>
+        <v>10.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.82</v>
+        <v>11.75</v>
       </c>
       <c r="R6" t="n">
-        <v>8.640000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="S6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>53.55</v>
+        <v>54.67</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>14.67</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.18</v>
+        <v>9.58</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.82</v>
+        <v>5.08</v>
       </c>
       <c r="AC6" t="n">
-        <v>16</v>
+        <v>15.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AF6" t="n">
         <v>0.2</v>
@@ -3162,70 +3162,70 @@
         <v>1.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.43</v>
+        <v>9.41</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM6" t="n">
         <v>0.86</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.52</v>
+        <v>4.64</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.67</v>
+        <v>4.55</v>
       </c>
       <c r="BR6" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU6" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV6" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW6" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX6" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.49</v>
+        <v>3.55</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="CC6" t="n">
         <v>2.5</v>
@@ -3243,22 +3243,22 @@
         <v>2.99</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CK6" t="n">
         <v>1.44</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CN6" t="n">
         <v>2.02</v>
@@ -3267,28 +3267,28 @@
         <v>1.26</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CU6" t="n">
         <v>1.48</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CX6" t="n">
         <v>1.52</v>
@@ -3306,82 +3306,82 @@
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="DH6" t="n">
-        <v>87.95</v>
+        <v>88.5</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
         <v>2.09</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.81</v>
+        <v>5.86</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="DM6" t="n">
-        <v>41.86</v>
+        <v>41.14</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.38</v>
+        <v>11.37</v>
       </c>
       <c r="DQ6" t="n">
         <v>10.86</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>53.53</v>
+        <v>54.14</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.33</v>
+        <v>14.68</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.09</v>
+        <v>10.27</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.24</v>
+        <v>4.41</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.86</v>
+        <v>17.73</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="EC6" t="n">
         <v>1.86</v>
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>0.17</v>
@@ -3484,139 +3484,139 @@
         <v>2.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AI7" t="n">
-        <v>79.36</v>
+        <v>75.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>38.45</v>
+        <v>38.25</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.18</v>
+        <v>13.17</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.09</v>
+        <v>13.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.82</v>
+        <v>9.75</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>43.73</v>
+        <v>45.08</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.640000000000001</v>
+        <v>10.83</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.45</v>
+        <v>7.08</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.18</v>
+        <v>3.75</v>
       </c>
       <c r="BD7" t="n">
-        <v>20.36</v>
+        <v>20.92</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="BG7" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.52</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="BJ7" t="n">
         <v>0.83</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL7" t="n">
         <v>0.83</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS7" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX7" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BY7" t="n">
         <v>2.72</v>
@@ -3625,16 +3625,16 @@
         <v>2.87</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.2</v>
+        <v>4.04</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.91</v>
+        <v>4.69</v>
       </c>
       <c r="CE7" t="n">
         <v>1.36</v>
@@ -3643,7 +3643,7 @@
         <v>2.69</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CH7" t="n">
         <v>1.44</v>
@@ -3658,13 +3658,13 @@
         <v>1.54</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO7" t="n">
         <v>1.26</v>
@@ -3679,7 +3679,7 @@
         <v>1.4</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CT7" t="n">
         <v>3.1</v>
@@ -3718,76 +3718,76 @@
         <v>0.17</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="DH7" t="n">
-        <v>86.04000000000001</v>
+        <v>83.84</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM7" t="n">
-        <v>37.52</v>
+        <v>37.46</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.35</v>
+        <v>12.38</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.69</v>
+        <v>12.92</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.91</v>
+        <v>8.92</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.65</v>
+        <v>48.16</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.91</v>
+        <v>11.46</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.43</v>
+        <v>7.71</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.95</v>
+        <v>21.21</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,52 +3887,52 @@
         <v>2.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>72</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT8" t="n">
         <v>2</v>
       </c>
-      <c r="AI8" t="n">
-        <v>77.44</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>31.56</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>11.22</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>10.11</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AU8" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>51</v>
+        <v>50.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.11</v>
+        <v>11.7</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.78</v>
+        <v>8.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.67</v>
+        <v>18.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.890000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.47</v>
+        <v>4.55</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS8" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT8" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU8" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV8" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX8" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>2.65</v>
@@ -4028,31 +4028,31 @@
         <v>3.08</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.53</v>
+        <v>4.4</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.77</v>
+        <v>4.63</v>
       </c>
       <c r="CE8" t="n">
         <v>1.3</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.66</v>
@@ -4061,10 +4061,10 @@
         <v>1.45</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CN8" t="n">
         <v>1.95</v>
@@ -4073,25 +4073,25 @@
         <v>1.21</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CR8" t="n">
         <v>1.36</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CW8" t="n">
         <v>1.68</v>
@@ -4103,7 +4103,7 @@
         <v>1.84</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DA8" t="n">
         <v>1.96</v>
@@ -4112,85 +4112,85 @@
         <v>1.23</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="DE8" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="DH8" t="n">
-        <v>71.68000000000001</v>
+        <v>69.25</v>
       </c>
       <c r="DI8" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.69</v>
+        <v>4.65</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="DM8" t="n">
-        <v>31.05</v>
+        <v>31.65</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.42</v>
+        <v>11.55</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.42</v>
+        <v>12.4</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.470000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.84</v>
+        <v>50.5</v>
       </c>
       <c r="DW8" t="n">
         <v>0.1</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.68</v>
+        <v>11.95</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.84</v>
+        <v>8</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.16</v>
+        <v>18.2</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="9">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F11" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="H11" t="n">
-        <v>80.89</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="K11" t="n">
-        <v>5.89</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="M11" t="n">
-        <v>47.11</v>
+        <v>43.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="P11" t="n">
-        <v>12.44</v>
+        <v>12.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.22</v>
+        <v>10.5</v>
       </c>
       <c r="R11" t="n">
-        <v>9.33</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>51</v>
+        <v>51.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.33</v>
+        <v>17.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>13.44</v>
+        <v>13.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.89</v>
+        <v>4.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>24.44</v>
+        <v>24.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
         <v>0.1</v>
@@ -5177,70 +5177,70 @@
         <v>2.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.11</v>
+        <v>10.15</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="BP11" t="n">
         <v>4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.68</v>
+        <v>4.8</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>84.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV11" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW11" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX11" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="CC11" t="n">
         <v>3.62</v>
@@ -5252,28 +5252,28 @@
         <v>1.29</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CK11" t="n">
         <v>1.4</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CN11" t="n">
         <v>2.07</v>
@@ -5282,10 +5282,10 @@
         <v>1.18</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="CR11" t="n">
         <v>1.36</v>
@@ -5300,10 +5300,10 @@
         <v>1.55</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CX11" t="n">
         <v>1.5</v>
@@ -5318,55 +5318,55 @@
         <v>2.06</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="DE11" t="n">
         <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="DH11" t="n">
-        <v>85.37</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.37</v>
+        <v>5.45</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM11" t="n">
-        <v>45.58</v>
+        <v>43.95</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.37</v>
+        <v>12.25</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.84</v>
+        <v>10.95</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.26</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DS11" t="n">
         <v>0.1</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.68</v>
+        <v>50.2</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>16.47</v>
+        <v>16.25</v>
       </c>
       <c r="DY11" t="n">
-        <v>11.37</v>
+        <v>11.3</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.11</v>
+        <v>4.95</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.73</v>
+        <v>22.1</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="G12" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="H12" t="n">
-        <v>91.59999999999999</v>
+        <v>89.55</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="K12" t="n">
-        <v>5.6</v>
+        <v>5.36</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M12" t="n">
-        <v>41.2</v>
+        <v>40.18</v>
       </c>
       <c r="N12" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="P12" t="n">
-        <v>11.1</v>
+        <v>11.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.1</v>
+        <v>11.91</v>
       </c>
       <c r="R12" t="n">
-        <v>7.5</v>
+        <v>7.27</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>54.3</v>
+        <v>52.73</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>15</v>
+        <v>14.27</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.3</v>
+        <v>9.82</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="AC12" t="n">
-        <v>15.6</v>
+        <v>15.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AF12" t="n">
         <v>0.09</v>
@@ -5580,70 +5580,70 @@
         <v>2.27</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BN12" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BP12" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="BQ12" t="n">
         <v>3.95</v>
       </c>
       <c r="BR12" t="n">
-        <v>100</v>
+        <v>95.45</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.19</v>
+        <v>72.73</v>
       </c>
       <c r="BT12" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV12" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="CC12" t="n">
         <v>2.72</v>
@@ -5655,13 +5655,13 @@
         <v>1.32</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI12" t="n">
         <v>2.1</v>
@@ -5670,139 +5670,139 @@
         <v>1.69</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CY12" t="n">
         <v>1.81</v>
       </c>
-      <c r="CM12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CP12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CQ12" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CS12" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="CT12" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="CU12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CV12" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="CW12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CX12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="CY12" t="n">
-        <v>1.8</v>
-      </c>
       <c r="CZ12" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DH12" t="n">
-        <v>83.33</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ12" t="n">
         <v>2.86</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="DL12" t="n">
         <v>0.14</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.57</v>
+        <v>38.18</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.28</v>
+        <v>11.5</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.14</v>
+        <v>12.04</v>
       </c>
       <c r="DR12" t="n">
-        <v>9</v>
+        <v>8.82</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.34</v>
+        <v>51.64</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.14</v>
+        <v>13.81</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.52</v>
+        <v>9.32</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.62</v>
+        <v>4.5</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.91</v>
+        <v>18.73</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0.11</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AI13" t="n">
-        <v>78.40000000000001</v>
+        <v>75.73</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.5</v>
+        <v>5.36</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AN13" t="n">
-        <v>30.1</v>
+        <v>28.91</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14.3</v>
+        <v>13.55</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.2</v>
+        <v>12.36</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.3</v>
+        <v>10.82</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AU13" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>48.5</v>
+        <v>46.55</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.2</v>
+        <v>10.64</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="BD13" t="n">
-        <v>19.4</v>
+        <v>19.18</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.630000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.11</v>
+        <v>4.3</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS13" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT13" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BU13" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV13" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW13" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BX13" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY13" t="n">
         <v>3.03</v>
@@ -6043,16 +6043,16 @@
         <v>3.09</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.74</v>
+        <v>5.73</v>
       </c>
       <c r="CE13" t="n">
         <v>1.33</v>
@@ -6061,7 +6061,7 @@
         <v>2.64</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CH13" t="n">
         <v>1.47</v>
@@ -6070,13 +6070,13 @@
         <v>1.95</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK13" t="n">
         <v>1.44</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM13" t="n">
         <v>2.55</v>
@@ -6088,10 +6088,10 @@
         <v>1.25</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CR13" t="n">
         <v>1.38</v>
@@ -6106,7 +6106,7 @@
         <v>1.48</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CW13" t="n">
         <v>1.82</v>
@@ -6127,37 +6127,37 @@
         <v>1.29</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="DE13" t="n">
         <v>0.05</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="DH13" t="n">
-        <v>87</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.11</v>
+        <v>5.05</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM13" t="n">
-        <v>37.42</v>
+        <v>36.4</v>
       </c>
       <c r="DN13" t="n">
         <v>1</v>
@@ -6166,13 +6166,13 @@
         <v>2</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.79</v>
+        <v>12.45</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.53</v>
+        <v>12.6</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.470000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="DS13" t="n">
         <v>0.05</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>51.68</v>
+        <v>50.45</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.32</v>
+        <v>11.95</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.050000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.27</v>
+        <v>4.05</v>
       </c>
       <c r="EA13" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14">
@@ -6215,61 +6215,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="H14" t="n">
-        <v>99.22</v>
+        <v>97.5</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="K14" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="M14" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="N14" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="P14" t="n">
-        <v>12.33</v>
+        <v>12.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.44</v>
+        <v>10.8</v>
       </c>
       <c r="R14" t="n">
-        <v>9.220000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>59.44</v>
+        <v>59.1</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.78</v>
+        <v>13.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.890000000000001</v>
+        <v>10</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AF14" t="n">
         <v>0.09</v>
@@ -6386,64 +6386,64 @@
         <v>3.55</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.15</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.45</v>
+        <v>4.38</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="BR14" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT14" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU14" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV14" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY14" t="n">
         <v>1.94</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CA14" t="n">
         <v>3.52</v>
@@ -6470,10 +6470,10 @@
         <v>1.4</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK14" t="n">
         <v>1.51</v>
@@ -6488,19 +6488,19 @@
         <v>1.83</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CP14" t="n">
         <v>1.93</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CR14" t="n">
         <v>1.4</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CT14" t="n">
         <v>3.07</v>
@@ -6509,16 +6509,16 @@
         <v>1.43</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX14" t="n">
         <v>1.56</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.34</v>
@@ -6533,19 +6533,19 @@
         <v>2</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="DH14" t="n">
-        <v>84.45</v>
+        <v>84.33</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
@@ -6554,61 +6554,61 @@
         <v>3.1</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.55</v>
+        <v>4.57</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DM14" t="n">
-        <v>43.1</v>
+        <v>43.62</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.35</v>
+        <v>13.28</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="DR14" t="n">
-        <v>11.5</v>
+        <v>11.43</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.55</v>
+        <v>51.76</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.75</v>
+        <v>11.81</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.1</v>
+        <v>8.24</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.65</v>
+        <v>3.57</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.45</v>
+        <v>18.43</v>
       </c>
       <c r="EB14" t="n">
         <v>1.31</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>0.11</v>
@@ -6711,136 +6711,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AI15" t="n">
-        <v>47.5</v>
+        <v>50.36</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN15" t="n">
-        <v>23.1</v>
+        <v>22.36</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.7</v>
+        <v>10.73</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.7</v>
+        <v>12.55</v>
       </c>
       <c r="AS15" t="n">
-        <v>11.1</v>
+        <v>11.18</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>32.2</v>
+        <v>32.27</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.6</v>
+        <v>8.82</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.2</v>
+        <v>5.36</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BD15" t="n">
-        <v>15.4</v>
+        <v>16</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="BF15" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.470000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL15" t="n">
         <v>0.95</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.47</v>
+        <v>4.6</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT15" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU15" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV15" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX15" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
         <v>3.42</v>
@@ -6849,43 +6849,43 @@
         <v>3.86</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.26</v>
+        <v>4.32</v>
       </c>
       <c r="CC15" t="n">
-        <v>7.1</v>
+        <v>7.34</v>
       </c>
       <c r="CD15" t="n">
-        <v>7.43</v>
+        <v>7.82</v>
       </c>
       <c r="CE15" t="n">
         <v>1.28</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CH15" t="n">
         <v>1.4</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CK15" t="n">
         <v>1.35</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN15" t="n">
         <v>1.87</v>
@@ -6894,28 +6894,28 @@
         <v>1.19</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CU15" t="n">
         <v>1.5</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CX15" t="n">
         <v>1.5</v>
@@ -6933,85 +6933,85 @@
         <v>1.28</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="DE15" t="n">
         <v>0.05</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="DH15" t="n">
-        <v>62.74</v>
+        <v>63.55</v>
       </c>
       <c r="DI15" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM15" t="n">
-        <v>26.16</v>
+        <v>25.6</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.32</v>
+        <v>12.25</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.52</v>
+        <v>12.45</v>
       </c>
       <c r="DR15" t="n">
-        <v>10.68</v>
+        <v>10.75</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX15" t="n">
-        <v>8.74</v>
+        <v>8.85</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.31</v>
+        <v>5.4</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.31</v>
+        <v>16.6</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="16">
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -7033,82 +7033,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="H16" t="n">
-        <v>68.5</v>
+        <v>65.91</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M16" t="n">
-        <v>37</v>
+        <v>35.82</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="O16" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="P16" t="n">
-        <v>13</v>
+        <v>13.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.6</v>
+        <v>14.36</v>
       </c>
       <c r="R16" t="n">
-        <v>9.6</v>
+        <v>10.18</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>42.8</v>
+        <v>42.55</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.3</v>
+        <v>12.18</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.6</v>
+        <v>7.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="AC16" t="n">
-        <v>18.2</v>
+        <v>18.45</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AF16" t="n">
         <v>0.11</v>
@@ -7192,70 +7192,70 @@
         <v>2.89</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.89</v>
+        <v>10.8</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ16" t="n">
         <v>0.95</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL16" t="n">
         <v>0.95</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.11</v>
+        <v>6.1</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT16" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU16" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BV16" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX16" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.41</v>
+        <v>3.36</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.26</v>
+        <v>4.21</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.69</v>
+        <v>4.63</v>
       </c>
       <c r="CC16" t="n">
         <v>7.06</v>
@@ -7267,10 +7267,10 @@
         <v>1.27</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="CH16" t="n">
         <v>1.59</v>
@@ -7282,43 +7282,43 @@
         <v>1.65</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL16" t="n">
         <v>1.7</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CN16" t="n">
         <v>2.12</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CV16" t="n">
         <v>2.31</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX16" t="n">
         <v>1.5</v>
@@ -7345,76 +7345,76 @@
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="DH16" t="n">
-        <v>74.53</v>
+        <v>72.8</v>
       </c>
       <c r="DI16" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.16</v>
+        <v>4.25</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM16" t="n">
-        <v>35.16</v>
+        <v>34.6</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.79</v>
+        <v>12.1</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.37</v>
+        <v>14.25</v>
       </c>
       <c r="DR16" t="n">
-        <v>11.11</v>
+        <v>11.35</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.63</v>
+        <v>43.45</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.11</v>
+        <v>10.65</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="EA16" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F17" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="G17" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="H17" t="n">
-        <v>92.62</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="K17" t="n">
-        <v>6.62</v>
+        <v>6.36</v>
       </c>
       <c r="L17" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="M17" t="n">
-        <v>54.46</v>
+        <v>52.79</v>
       </c>
       <c r="N17" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="O17" t="n">
-        <v>3.46</v>
+        <v>3.29</v>
       </c>
       <c r="P17" t="n">
-        <v>11.69</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.15</v>
+        <v>13.93</v>
       </c>
       <c r="R17" t="n">
-        <v>6.38</v>
+        <v>6.43</v>
       </c>
       <c r="S17" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="T17" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="U17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="V17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>55</v>
+        <v>54.57</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>18.23</v>
+        <v>17.43</v>
       </c>
       <c r="AA17" t="n">
-        <v>12.08</v>
+        <v>11.57</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.15</v>
+        <v>5.86</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.54</v>
+        <v>19.36</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,70 +7595,70 @@
         <v>2.83</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.84</v>
+        <v>9.69</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO17" t="n">
         <v>1.08</v>
       </c>
-      <c r="BM17" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>1.12</v>
-      </c>
       <c r="BP17" t="n">
-        <v>4.36</v>
+        <v>4.31</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.28</v>
+        <v>5.19</v>
       </c>
       <c r="BR17" t="n">
-        <v>92</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>76</v>
+        <v>73.08</v>
       </c>
       <c r="BT17" t="n">
-        <v>44</v>
+        <v>42.31</v>
       </c>
       <c r="BU17" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="BV17" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BW17" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BX17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.11</v>
+        <v>4.09</v>
       </c>
       <c r="CC17" t="n">
         <v>2.47</v>
@@ -7667,10 +7667,10 @@
         <v>2.92</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG17" t="n">
         <v>2.97</v>
@@ -7679,7 +7679,7 @@
         <v>1.42</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.75</v>
@@ -7694,7 +7694,7 @@
         <v>2.36</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CO17" t="n">
         <v>1.19</v>
@@ -7703,7 +7703,7 @@
         <v>1.77</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CR17" t="n">
         <v>1.38</v>
@@ -7712,13 +7712,13 @@
         <v>2.72</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CU17" t="n">
         <v>1.5</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CW17" t="n">
         <v>1.78</v>
@@ -7745,46 +7745,46 @@
         <v>3</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.31999999999999</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="DI17" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.92</v>
+        <v>5.81</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DM17" t="n">
-        <v>48.36</v>
+        <v>47.69</v>
       </c>
       <c r="DN17" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.04</v>
+        <v>12.19</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.64</v>
+        <v>13.08</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.36</v>
+        <v>7.35</v>
       </c>
       <c r="DS17" t="n">
         <v>0.08</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.2</v>
+        <v>54</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="DX17" t="n">
-        <v>16.16</v>
+        <v>15.81</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.4</v>
+        <v>10.19</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.76</v>
+        <v>5.62</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.36</v>
+        <v>18.81</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="18">
@@ -7827,10 +7827,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
@@ -7839,82 +7839,82 @@
         <v>0.08</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="G18" t="n">
         <v>1.08</v>
       </c>
       <c r="H18" t="n">
-        <v>86.75</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="I18" t="n">
         <v>0.08</v>
       </c>
       <c r="J18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M18" t="n">
+        <v>37.08</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P18" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="T18" t="n">
         <v>2</v>
       </c>
-      <c r="K18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M18" t="n">
-        <v>37.25</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="P18" t="n">
-        <v>12.58</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>13.92</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>50.25</v>
+        <v>49.92</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.33</v>
+        <v>12.92</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="AB18" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="AC18" t="n">
         <v>16.92</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,70 +7998,70 @@
         <v>2.7</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.09</v>
+        <v>7.87</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BN18" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.64</v>
+        <v>3.52</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="BR18" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS18" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT18" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU18" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV18" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW18" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX18" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="CC18" t="n">
         <v>4.54</v>
@@ -8070,157 +8070,157 @@
         <v>5</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="CF18" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="CG18" t="n">
         <v>2.93</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI18" t="n">
         <v>2.09</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN18" t="n">
         <v>1.68</v>
       </c>
       <c r="CO18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CW18" t="n">
         <v>1.6</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="DB18" t="n">
         <v>1.2</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="DH18" t="n">
-        <v>77.86</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="DI18" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM18" t="n">
         <v>35.09</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.32</v>
+        <v>12.48</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.09</v>
+        <v>12.91</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.32</v>
+        <v>9.17</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.36</v>
+        <v>47.3</v>
       </c>
       <c r="DW18" t="n">
         <v>0.09</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.91</v>
+        <v>11.74</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.82</v>
+        <v>7.65</v>
       </c>
       <c r="DZ18" t="n">
         <v>4.09</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.64</v>
+        <v>17.61</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" t="n">
         <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
         <v>0.08</v>
@@ -8323,49 +8323,49 @@
         <v>0.08</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="n">
-        <v>68.75</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.92</v>
+        <v>4.77</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AN19" t="n">
-        <v>31.17</v>
+        <v>32</v>
       </c>
       <c r="AO19" t="n">
         <v>1.08</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.42</v>
+        <v>14.38</v>
       </c>
       <c r="AR19" t="n">
-        <v>12.75</v>
+        <v>13.23</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.33</v>
+        <v>9</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8377,82 +8377,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>51.5</v>
+        <v>51.46</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA19" t="n">
-        <v>14.17</v>
+        <v>13.92</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.08</v>
+        <v>8.92</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="BD19" t="n">
-        <v>19.92</v>
+        <v>19.77</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.279999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.44</v>
+        <v>4.38</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.28</v>
+        <v>4.23</v>
       </c>
       <c r="BR19" t="n">
-        <v>88</v>
+        <v>84.62</v>
       </c>
       <c r="BS19" t="n">
-        <v>72</v>
+        <v>69.23</v>
       </c>
       <c r="BT19" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BU19" t="n">
-        <v>48</v>
+        <v>46.15</v>
       </c>
       <c r="BV19" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BW19" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BX19" t="n">
-        <v>56</v>
+        <v>53.85</v>
       </c>
       <c r="BY19" t="n">
         <v>1.55</v>
@@ -8461,28 +8461,28 @@
         <v>1.54</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.18</v>
+        <v>4.14</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.57</v>
+        <v>4.53</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CI19" t="n">
         <v>2.23</v>
@@ -8500,28 +8500,28 @@
         <v>2.42</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO19" t="n">
         <v>1.16</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CV19" t="n">
         <v>2.32</v>
@@ -8539,7 +8539,7 @@
         <v>2.39</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB19" t="n">
         <v>1.2</v>
@@ -8548,82 +8548,82 @@
         <v>1.63</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="DE19" t="n">
         <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="DH19" t="n">
-        <v>81.23999999999999</v>
+        <v>81.81</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.36</v>
+        <v>5.27</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM19" t="n">
-        <v>40</v>
+        <v>40.07</v>
       </c>
       <c r="DN19" t="n">
         <v>1.08</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.16</v>
+        <v>13.65</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.8</v>
+        <v>12.08</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.119999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.08</v>
+        <v>54.92</v>
       </c>
       <c r="DW19" t="n">
         <v>0.12</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.44</v>
+        <v>17.19</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.56</v>
+        <v>11.38</v>
       </c>
       <c r="DZ19" t="n">
-        <v>5.88</v>
+        <v>5.81</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.12</v>
+        <v>19.08</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -2660,10 +2660,10 @@
         <v>0.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.85</v>
+        <v>19.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.92</v>
+        <v>13</v>
       </c>
       <c r="AB5" t="n">
         <v>6.92</v>
@@ -2672,7 +2672,7 @@
         <v>22.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AE5" t="n">
         <v>2.31</v>
@@ -2966,10 +2966,10 @@
         <v>0.2</v>
       </c>
       <c r="DX5" t="n">
-        <v>17.54</v>
+        <v>17.58</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.5</v>
+        <v>11.54</v>
       </c>
       <c r="DZ5" t="n">
         <v>6.04</v>
@@ -3550,10 +3550,10 @@
         <v>10.83</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.08</v>
+        <v>7.17</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="BD7" t="n">
         <v>20.92</v>
@@ -3775,10 +3775,10 @@
         <v>11.46</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.71</v>
+        <v>7.75</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="EA7" t="n">
         <v>21.21</v>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>42.82</v>
+        <v>42.91</v>
       </c>
       <c r="Y9" t="n">
         <v>0.18</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.35</v>
+        <v>43.4</v>
       </c>
       <c r="DW9" t="n">
         <v>0.15</v>
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>54.77</v>
+        <v>54.69</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.15</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.92</v>
+        <v>55.87</v>
       </c>
       <c r="DW10" t="n">
         <v>0.16</v>
@@ -5078,10 +5078,10 @@
         <v>0.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="AB11" t="n">
         <v>4.6</v>
@@ -5384,10 +5384,10 @@
         <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>16.25</v>
+        <v>16.3</v>
       </c>
       <c r="DY11" t="n">
-        <v>11.3</v>
+        <v>11.35</v>
       </c>
       <c r="DZ11" t="n">
         <v>4.95</v>
@@ -8383,10 +8383,10 @@
         <v>0.15</v>
       </c>
       <c r="BA19" t="n">
-        <v>13.92</v>
+        <v>14</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.92</v>
+        <v>9</v>
       </c>
       <c r="BC19" t="n">
         <v>5</v>
@@ -8608,10 +8608,10 @@
         <v>0.12</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.19</v>
+        <v>17.23</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.38</v>
+        <v>11.42</v>
       </c>
       <c r="DZ19" t="n">
         <v>5.81</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="H2" t="n">
-        <v>100.2</v>
+        <v>101.09</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="K2" t="n">
-        <v>7.5</v>
+        <v>7.27</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="M2" t="n">
-        <v>62.2</v>
+        <v>61.55</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="P2" t="n">
-        <v>10.9</v>
+        <v>11.09</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.7</v>
+        <v>11.73</v>
       </c>
       <c r="R2" t="n">
-        <v>6.7</v>
+        <v>6.64</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>56.9</v>
+        <v>57.55</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.6</v>
+        <v>10.45</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.7</v>
+        <v>20.82</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AF2" t="n">
         <v>0.08</v>
@@ -1550,58 +1550,58 @@
         <v>2.08</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.449999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.18</v>
+        <v>5.13</v>
       </c>
       <c r="BR2" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS2" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU2" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV2" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX2" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY2" t="n">
         <v>1.43</v>
@@ -1622,61 +1622,61 @@
         <v>2.43</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF2" t="n">
         <v>2.33</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CH2" t="n">
         <v>1.44</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CK2" t="n">
         <v>1.39</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CM2" t="n">
         <v>2.4</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP2" t="n">
         <v>1.76</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="CR2" t="n">
         <v>1.4</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CX2" t="n">
         <v>1.53</v>
@@ -1694,85 +1694,85 @@
         <v>1.25</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="DH2" t="n">
-        <v>101.05</v>
+        <v>101.43</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.27</v>
+        <v>6.22</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM2" t="n">
-        <v>55.45</v>
+        <v>55.44</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.59</v>
+        <v>10.69</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.32</v>
+        <v>12.3</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.55</v>
+        <v>6.53</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>55.32</v>
+        <v>55.7</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.77</v>
+        <v>13.83</v>
       </c>
       <c r="DY2" t="n">
         <v>8.949999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.82</v>
+        <v>4.87</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.82</v>
+        <v>18.96</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="F3" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="G3" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="H3" t="n">
-        <v>68.89</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="K3" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>34.56</v>
+        <v>33.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>13.67</v>
+        <v>14.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.56</v>
+        <v>13.7</v>
       </c>
       <c r="R3" t="n">
-        <v>10.33</v>
+        <v>10.1</v>
       </c>
       <c r="S3" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U3" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>39.67</v>
+        <v>41.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.78</v>
+        <v>11.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.89</v>
+        <v>7.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AF3" t="n">
         <v>0.09</v>
@@ -1953,70 +1953,70 @@
         <v>2.36</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.65</v>
+        <v>9.52</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BJ3" t="n">
         <v>1.05</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.65</v>
+        <v>4.38</v>
       </c>
       <c r="BR3" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU3" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BV3" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BW3" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.31</v>
+        <v>3.16</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.62</v>
+        <v>3.45</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CB3" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="CC3" t="n">
         <v>4.65</v>
@@ -2028,7 +2028,7 @@
         <v>1.31</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CG3" t="n">
         <v>3.13</v>
@@ -2037,16 +2037,16 @@
         <v>1.49</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK3" t="n">
         <v>1.43</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM3" t="n">
         <v>2.63</v>
@@ -2058,28 +2058,28 @@
         <v>1.22</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX3" t="n">
         <v>1.53</v>
@@ -2094,88 +2094,88 @@
         <v>2.02</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="DH3" t="n">
-        <v>66.09999999999999</v>
+        <v>67.05</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="DM3" t="n">
-        <v>27.9</v>
+        <v>27.57</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.6</v>
+        <v>11.91</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.25</v>
+        <v>12.9</v>
       </c>
       <c r="DR3" t="n">
-        <v>10.75</v>
+        <v>10.62</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>41.95</v>
+        <v>42.62</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.75</v>
+        <v>10.05</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.6</v>
+        <v>6.76</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.15</v>
+        <v>3.29</v>
       </c>
       <c r="EA3" t="n">
-        <v>16</v>
+        <v>16.05</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="G4" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="H4" t="n">
-        <v>62.56</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J4" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4.11</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>25.11</v>
+        <v>25.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="O4" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="P4" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.33</v>
+        <v>12.3</v>
       </c>
       <c r="R4" t="n">
-        <v>7.78</v>
+        <v>7.7</v>
       </c>
       <c r="S4" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="V4" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>45.33</v>
+        <v>46.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.67</v>
+        <v>6.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF4" t="n">
         <v>0.18</v>
@@ -2356,67 +2356,67 @@
         <v>1.91</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.550000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BN4" t="n">
         <v>2.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.45</v>
+        <v>4.57</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT4" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU4" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BV4" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BW4" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX4" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.14</v>
+        <v>3.26</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.31</v>
+        <v>3.48</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CB4" t="n">
         <v>3.92</v>
@@ -2428,43 +2428,43 @@
         <v>4.63</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="CF4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CM4" t="n">
         <v>2.46</v>
       </c>
-      <c r="CG4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>2.58</v>
-      </c>
       <c r="CN4" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="CP4" t="n">
         <v>1.71</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="CR4" t="n">
         <v>1.36</v>
@@ -2506,79 +2506,79 @@
         <v>2.83</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF4" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="DH4" t="n">
-        <v>71.90000000000001</v>
+        <v>72.34</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM4" t="n">
-        <v>33.25</v>
+        <v>33.19</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.55</v>
+        <v>12.53</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.449999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.95</v>
+        <v>47.33</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.05</v>
+        <v>10.91</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.15</v>
+        <v>7.1</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.9</v>
+        <v>3.81</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.95</v>
+        <v>20</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>0.15</v>
@@ -2678,139 +2678,139 @@
         <v>2.31</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.64</v>
+        <v>2.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>98.55</v>
+        <v>97.25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK5" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.45</v>
+        <v>4.67</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.45</v>
+        <v>0.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>42.27</v>
+        <v>40.58</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.64</v>
+        <v>10.25</v>
       </c>
       <c r="AR5" t="n">
-        <v>14</v>
+        <v>14.08</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.82</v>
+        <v>7.92</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>54.45</v>
+        <v>53.42</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.82</v>
+        <v>15</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.82</v>
+        <v>9.83</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.91</v>
+        <v>21.25</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.79</v>
+        <v>2.96</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.58</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.79</v>
+        <v>2.96</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.88</v>
+        <v>3.68</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.62</v>
+        <v>5.36</v>
       </c>
       <c r="BR5" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS5" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BU5" t="n">
-        <v>29.17</v>
+        <v>32</v>
       </c>
       <c r="BV5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.17</v>
+        <v>8</v>
       </c>
       <c r="BX5" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BY5" t="n">
         <v>1.68</v>
@@ -2819,31 +2819,31 @@
         <v>1.78</v>
       </c>
       <c r="CA5" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="CE5" t="n">
         <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.73</v>
@@ -2852,22 +2852,22 @@
         <v>1.48</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO5" t="n">
         <v>1.21</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CR5" t="n">
         <v>1.37</v>
@@ -2885,97 +2885,97 @@
         <v>2.2</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB5" t="n">
         <v>1.24</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.42</v>
+        <v>3.24</v>
       </c>
       <c r="DH5" t="n">
-        <v>103.33</v>
+        <v>102.52</v>
       </c>
       <c r="DI5" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.91</v>
+        <v>5.96</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="DM5" t="n">
-        <v>51.5</v>
+        <v>50.32</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.21</v>
+        <v>11</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.08</v>
+        <v>12.2</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.46</v>
+        <v>7.52</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57.41</v>
+        <v>56.8</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DX5" t="n">
-        <v>17.58</v>
+        <v>17.56</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.54</v>
+        <v>11.48</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6.04</v>
+        <v>6.08</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.04</v>
+        <v>21.72</v>
       </c>
       <c r="EB5" t="n">
         <v>1.9</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0.17</v>
@@ -3081,52 +3081,52 @@
         <v>2.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AI6" t="n">
-        <v>101.2</v>
+        <v>98.09</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AL6" t="n">
-        <v>6</v>
+        <v>5.73</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AN6" t="n">
-        <v>49.1</v>
+        <v>48</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.9</v>
+        <v>11.91</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.9</v>
+        <v>7.55</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>53.5</v>
+        <v>52.73</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA6" t="n">
-        <v>14.7</v>
+        <v>14.64</v>
       </c>
       <c r="BB6" t="n">
-        <v>11.1</v>
+        <v>10.73</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.6</v>
+        <v>3.91</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.9</v>
+        <v>19.64</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.41</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.91</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.64</v>
+        <v>4.52</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="BR6" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS6" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU6" t="n">
-        <v>27.27</v>
+        <v>30.43</v>
       </c>
       <c r="BV6" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BW6" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY6" t="n">
         <v>1.94</v>
@@ -3222,55 +3222,55 @@
         <v>2</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CB6" t="n">
         <v>3.82</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.99</v>
+        <v>2.86</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="CP6" t="n">
         <v>1.82</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
@@ -3312,46 +3312,46 @@
         <v>3.1</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.5</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="DI6" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.86</v>
+        <v>5.74</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DM6" t="n">
-        <v>41.14</v>
+        <v>40.96</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.37</v>
+        <v>11.39</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.86</v>
+        <v>10.7</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.32</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DS6" t="n">
         <v>0.04</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.14</v>
+        <v>53.74</v>
       </c>
       <c r="DW6" t="n">
         <v>0.13</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.68</v>
+        <v>14.66</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.27</v>
+        <v>10.13</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.41</v>
+        <v>4.52</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.73</v>
+        <v>17.7</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F7" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="G7" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="H7" t="n">
-        <v>92.17</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>0.08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="K7" t="n">
         <v>4.08</v>
       </c>
       <c r="L7" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="M7" t="n">
-        <v>36.67</v>
+        <v>37.31</v>
       </c>
       <c r="N7" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="O7" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="P7" t="n">
-        <v>11.58</v>
+        <v>11.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.33</v>
+        <v>12.46</v>
       </c>
       <c r="R7" t="n">
         <v>8.08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="T7" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="U7" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="V7" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>51.25</v>
+        <v>51.77</v>
       </c>
       <c r="Y7" t="n">
         <v>0.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.08</v>
+        <v>12.46</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.33</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.75</v>
+        <v>4.08</v>
       </c>
       <c r="AC7" t="n">
-        <v>21.5</v>
+        <v>21.46</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AF7" t="n">
         <v>0.17</v>
@@ -3565,70 +3565,70 @@
         <v>2.33</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.539999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.17</v>
+        <v>3.96</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.17</v>
+        <v>3.96</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS7" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT7" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>36</v>
       </c>
       <c r="BV7" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.33</v>
+        <v>12</v>
       </c>
       <c r="BX7" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CC7" t="n">
         <v>4.04</v>
@@ -3640,13 +3640,13 @@
         <v>1.36</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CG7" t="n">
         <v>2.95</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI7" t="n">
         <v>1.97</v>
@@ -3658,7 +3658,7 @@
         <v>1.54</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CM7" t="n">
         <v>2.35</v>
@@ -3670,10 +3670,10 @@
         <v>1.26</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="CR7" t="n">
         <v>1.4</v>
@@ -3709,85 +3709,85 @@
         <v>1.3</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="DH7" t="n">
-        <v>83.84</v>
+        <v>84.84</v>
       </c>
       <c r="DI7" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="DK7" t="n">
         <v>3.92</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="DM7" t="n">
-        <v>37.46</v>
+        <v>37.76</v>
       </c>
       <c r="DN7" t="n">
         <v>1.04</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.38</v>
+        <v>12.08</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.92</v>
+        <v>12.96</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.92</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.16</v>
+        <v>48.56</v>
       </c>
       <c r="DW7" t="n">
         <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.46</v>
+        <v>11.68</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.75</v>
+        <v>7.8</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.21</v>
+        <v>21.2</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="H8" t="n">
-        <v>66.5</v>
+        <v>70.09</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>30.6</v>
+        <v>31.18</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O8" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>11.6</v>
+        <v>11.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.5</v>
+        <v>12.36</v>
       </c>
       <c r="R8" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>50.7</v>
+        <v>50.82</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.2</v>
+        <v>12.36</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.9</v>
+        <v>8.09</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="AC8" t="n">
-        <v>17.7</v>
+        <v>17.82</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AF8" t="n">
         <v>0.1</v>
@@ -3968,70 +3968,70 @@
         <v>2.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.85</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.65</v>
+        <v>4.57</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.55</v>
+        <v>4.62</v>
       </c>
       <c r="BR8" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT8" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BU8" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV8" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW8" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CB8" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="CC8" t="n">
         <v>4.4</v>
@@ -4040,13 +4040,13 @@
         <v>4.63</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF8" t="n">
         <v>2.48</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CH8" t="n">
         <v>1.52</v>
@@ -4061,7 +4061,7 @@
         <v>1.45</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CM8" t="n">
         <v>2.56</v>
@@ -4073,10 +4073,10 @@
         <v>1.21</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CR8" t="n">
         <v>1.36</v>
@@ -4112,85 +4112,85 @@
         <v>1.23</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE8" t="n">
         <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="DH8" t="n">
-        <v>69.25</v>
+        <v>71</v>
       </c>
       <c r="DI8" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.65</v>
+        <v>4.72</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM8" t="n">
-        <v>31.65</v>
+        <v>31.9</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DO8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.55</v>
+        <v>11.57</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.4</v>
+        <v>12.33</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.449999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.5</v>
+        <v>50.57</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.95</v>
+        <v>12.05</v>
       </c>
       <c r="DY8" t="n">
-        <v>8</v>
+        <v>8.09</v>
       </c>
       <c r="DZ8" t="n">
         <v>3.95</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.2</v>
+        <v>18.24</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0.18</v>
@@ -4293,49 +4293,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" t="n">
-        <v>75.22</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AN9" t="n">
-        <v>37.67</v>
+        <v>35.9</v>
       </c>
       <c r="AO9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.89</v>
+        <v>11.3</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.22</v>
+        <v>13.7</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4350,79 +4350,79 @@
         <v>44</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.220000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.22</v>
+        <v>5.4</v>
       </c>
       <c r="BC9" t="n">
         <v>3</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.44</v>
+        <v>18.6</v>
       </c>
       <c r="BE9" t="n">
         <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.75</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="BJ9" t="n">
         <v>1</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.15</v>
+        <v>4.86</v>
       </c>
       <c r="BR9" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BT9" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BU9" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BV9" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW9" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX9" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY9" t="n">
         <v>3.09</v>
@@ -4431,43 +4431,43 @@
         <v>3.44</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="CC9" t="n">
-        <v>6.08</v>
+        <v>5.87</v>
       </c>
       <c r="CD9" t="n">
-        <v>7.81</v>
+        <v>7.46</v>
       </c>
       <c r="CE9" t="n">
         <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.78</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CL9" t="n">
         <v>1.87</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CN9" t="n">
         <v>1.95</v>
@@ -4476,16 +4476,16 @@
         <v>1.23</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CR9" t="n">
         <v>1.39</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CT9" t="n">
         <v>3.14</v>
@@ -4503,7 +4503,7 @@
         <v>1.53</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.41</v>
@@ -4515,85 +4515,85 @@
         <v>1.26</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="DH9" t="n">
-        <v>76.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="DM9" t="n">
-        <v>36.6</v>
+        <v>35.81</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.45</v>
+        <v>11.19</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.55</v>
+        <v>12.81</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.35</v>
+        <v>9.33</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.4</v>
+        <v>43.43</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.050000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.45</v>
+        <v>17.14</v>
       </c>
       <c r="EB9" t="n">
         <v>1.02</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F10" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="G10" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="H10" t="n">
-        <v>93.36</v>
+        <v>93.5</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="K10" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="M10" t="n">
-        <v>43.45</v>
+        <v>42.92</v>
       </c>
       <c r="N10" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="O10" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="P10" t="n">
-        <v>10.73</v>
+        <v>10.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.82</v>
+        <v>12.92</v>
       </c>
       <c r="R10" t="n">
-        <v>5.82</v>
+        <v>6.08</v>
       </c>
       <c r="S10" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>57.27</v>
+        <v>57.33</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.27</v>
+        <v>13.92</v>
       </c>
       <c r="AA10" t="n">
-        <v>8</v>
+        <v>8.42</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.27</v>
+        <v>5.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.64</v>
+        <v>17.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AF10" t="n">
         <v>0.15</v>
@@ -4774,67 +4774,67 @@
         <v>1.85</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.67</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BO10" t="n">
         <v>1.88</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.29</v>
+        <v>4.36</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT10" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="BV10" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BW10" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BX10" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="CB10" t="n">
         <v>4.15</v>
@@ -4891,13 +4891,13 @@
         <v>2.51</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CW10" t="n">
         <v>1.68</v>
@@ -4921,19 +4921,19 @@
         <v>1.71</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="DE10" t="n">
         <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="DH10" t="n">
-        <v>76.58</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.04</v>
@@ -4942,61 +4942,61 @@
         <v>1.96</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.87</v>
+        <v>3.96</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="DM10" t="n">
-        <v>35.67</v>
+        <v>35.72</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.5</v>
+        <v>10.56</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.09</v>
+        <v>13.12</v>
       </c>
       <c r="DR10" t="n">
-        <v>7</v>
+        <v>7.08</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.87</v>
+        <v>55.96</v>
       </c>
       <c r="DW10" t="n">
         <v>0.16</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.42</v>
+        <v>13.72</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.039999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.37</v>
+        <v>5.48</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.96</v>
+        <v>17.76</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>0.1</v>
@@ -5096,139 +5096,139 @@
         <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AH11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>86.81999999999999</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>41.82</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>47.36</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BG11" t="n">
         <v>3.1</v>
       </c>
-      <c r="AI11" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BH11" t="n">
-        <v>10.15</v>
+        <v>9.9</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BP11" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.8</v>
+        <v>4.76</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU11" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV11" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW11" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX11" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY11" t="n">
         <v>2.21</v>
@@ -5237,73 +5237,73 @@
         <v>2.21</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.62</v>
+        <v>3.78</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.87</v>
+        <v>4.2</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF11" t="n">
         <v>2.36</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CH11" t="n">
         <v>1.54</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CK11" t="n">
         <v>1.4</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CN11" t="n">
         <v>2.07</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="CX11" t="n">
         <v>1.5</v>
@@ -5315,91 +5315,91 @@
         <v>2.47</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DB11" t="n">
         <v>1.22</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="DH11" t="n">
-        <v>85.90000000000001</v>
+        <v>84.72</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.45</v>
+        <v>5.19</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DM11" t="n">
-        <v>43.95</v>
+        <v>42.72</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.65</v>
+        <v>0.76</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.25</v>
+        <v>12.24</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.95</v>
+        <v>11.05</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.24</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>50.2</v>
+        <v>49.52</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DX11" t="n">
-        <v>16.3</v>
+        <v>15.81</v>
       </c>
       <c r="DY11" t="n">
-        <v>11.35</v>
+        <v>11.05</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.95</v>
+        <v>4.76</v>
       </c>
       <c r="EA11" t="n">
-        <v>22.1</v>
+        <v>21.95</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5499,139 +5499,139 @@
         <v>2.45</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.09</v>
+        <v>0.92</v>
       </c>
       <c r="AI12" t="n">
-        <v>75.81999999999999</v>
+        <v>77.42</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AN12" t="n">
-        <v>36.18</v>
+        <v>34.17</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11.45</v>
+        <v>11.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.18</v>
+        <v>12.58</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.36</v>
+        <v>10.17</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>50.55</v>
+        <v>50.83</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BA12" t="n">
-        <v>13.36</v>
+        <v>13.33</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.82</v>
+        <v>9.08</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.91</v>
+        <v>21.42</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.91</v>
+        <v>8.83</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.05</v>
+        <v>3.83</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.95</v>
+        <v>3.74</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.45</v>
+        <v>91.3</v>
       </c>
       <c r="BS12" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU12" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV12" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BY12" t="n">
         <v>2</v>
@@ -5640,55 +5640,55 @@
         <v>2.16</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="CE12" t="n">
         <v>1.32</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK12" t="n">
         <v>1.42</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="CR12" t="n">
         <v>1.38</v>
@@ -5703,73 +5703,73 @@
         <v>1.51</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX12" t="n">
         <v>1.51</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DB12" t="n">
         <v>1.26</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="DE12" t="n">
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="DH12" t="n">
-        <v>82.68000000000001</v>
+        <v>83.22</v>
       </c>
       <c r="DI12" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.18</v>
+        <v>37.04</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.5</v>
+        <v>11.52</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.04</v>
+        <v>12.26</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.82</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DS12" t="n">
         <v>0.13</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>51.64</v>
+        <v>51.74</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.81</v>
+        <v>13.78</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.32</v>
+        <v>9.43</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.73</v>
+        <v>18.61</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F13" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G13" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="H13" t="n">
-        <v>96.56</v>
+        <v>93.3</v>
       </c>
       <c r="I13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="K13" t="n">
-        <v>4.67</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M13" t="n">
-        <v>45.56</v>
+        <v>42.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="O13" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="P13" t="n">
-        <v>11.11</v>
+        <v>11</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.89</v>
+        <v>12.6</v>
       </c>
       <c r="R13" t="n">
-        <v>6.44</v>
+        <v>7.6</v>
       </c>
       <c r="S13" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>55.22</v>
+        <v>52.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.56</v>
+        <v>12.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.56</v>
+        <v>4.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.78</v>
+        <v>22</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>2.36</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.85</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.15</v>
+        <v>5.24</v>
       </c>
       <c r="BR13" t="n">
-        <v>95</v>
+        <v>90.48</v>
       </c>
       <c r="BS13" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT13" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BU13" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV13" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW13" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BX13" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.03</v>
+        <v>3.25</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.09</v>
+        <v>3.49</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.71</v>
+        <v>3.74</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="CC13" t="n">
         <v>5.21</v>
@@ -6067,10 +6067,10 @@
         <v>1.47</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CK13" t="n">
         <v>1.44</v>
@@ -6079,7 +6079,7 @@
         <v>1.82</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CN13" t="n">
         <v>2</v>
@@ -6088,10 +6088,10 @@
         <v>1.25</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CR13" t="n">
         <v>1.38</v>
@@ -6106,73 +6106,73 @@
         <v>1.48</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CX13" t="n">
         <v>1.51</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.45</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB13" t="n">
         <v>1.29</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="DE13" t="n">
         <v>0.05</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="DH13" t="n">
-        <v>85.09999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.05</v>
+        <v>4.81</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM13" t="n">
-        <v>36.4</v>
+        <v>35.52</v>
       </c>
       <c r="DN13" t="n">
         <v>1</v>
       </c>
       <c r="DO13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.45</v>
+        <v>12.34</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.6</v>
+        <v>12.47</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.85</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DS13" t="n">
         <v>0.05</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.45</v>
+        <v>49.48</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.95</v>
+        <v>11.57</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.9</v>
+        <v>7.67</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.05</v>
+        <v>3.91</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.8</v>
+        <v>20.52</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="14">
@@ -6215,61 +6215,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F14" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H14" t="n">
+        <v>94.09</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M14" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P14" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="R14" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M14" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P14" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="R14" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.1</v>
-      </c>
       <c r="T14" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>59.1</v>
+        <v>58.45</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.7</v>
+        <v>13.18</v>
       </c>
       <c r="AA14" t="n">
-        <v>10</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="AC14" t="n">
-        <v>19.8</v>
+        <v>19.73</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AF14" t="n">
         <v>0.09</v>
@@ -6386,70 +6386,70 @@
         <v>3.55</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.140000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.62</v>
+        <v>0.77</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.38</v>
+        <v>4.27</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS14" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU14" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BV14" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="CC14" t="n">
         <v>3.48</v>
@@ -6461,52 +6461,52 @@
         <v>1.37</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI14" t="n">
         <v>1.98</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CO14" t="n">
         <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="CR14" t="n">
         <v>1.4</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="CT14" t="n">
         <v>3.07</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CV14" t="n">
         <v>2.03</v>
@@ -6530,85 +6530,85 @@
         <v>1.31</v>
       </c>
       <c r="DC14" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="DE14" t="n">
         <v>0.09</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="DH14" t="n">
-        <v>84.33</v>
+        <v>83.22</v>
       </c>
       <c r="DI14" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.57</v>
+        <v>4.36</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM14" t="n">
-        <v>43.62</v>
+        <v>42.91</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.28</v>
+        <v>12.96</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11</v>
+        <v>11.36</v>
       </c>
       <c r="DR14" t="n">
-        <v>11.43</v>
+        <v>11.46</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.76</v>
+        <v>51.77</v>
       </c>
       <c r="DW14" t="n">
         <v>0.14</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.81</v>
+        <v>11.63</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.24</v>
+        <v>8</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.57</v>
+        <v>3.64</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.43</v>
+        <v>18.45</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="H15" t="n">
-        <v>79.67</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>29.56</v>
+        <v>28.9</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="P15" t="n">
-        <v>14.11</v>
+        <v>14.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.33</v>
+        <v>12.3</v>
       </c>
       <c r="R15" t="n">
-        <v>10.22</v>
+        <v>10.7</v>
       </c>
       <c r="S15" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="U15" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>42.33</v>
+        <v>42.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.890000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.44</v>
+        <v>5.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.33</v>
+        <v>19.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="AE15" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6789,70 +6789,70 @@
         <v>2.09</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.449999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.8</v>
+        <v>4.52</v>
       </c>
       <c r="BR15" t="n">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS15" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT15" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU15" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW15" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX15" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.32</v>
+        <v>4.27</v>
       </c>
       <c r="CC15" t="n">
         <v>7.34</v>
@@ -6861,28 +6861,28 @@
         <v>7.82</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CH15" t="n">
         <v>1.4</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.81</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CM15" t="n">
         <v>2.53</v>
@@ -6891,13 +6891,13 @@
         <v>1.87</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
@@ -6915,103 +6915,103 @@
         <v>1.94</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DB15" t="n">
         <v>1.28</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="DE15" t="n">
         <v>0.05</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="DH15" t="n">
-        <v>63.55</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="DI15" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="DM15" t="n">
-        <v>25.6</v>
+        <v>25.47</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.25</v>
+        <v>12.48</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.45</v>
+        <v>12.43</v>
       </c>
       <c r="DR15" t="n">
-        <v>10.75</v>
+        <v>10.95</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>36.8</v>
+        <v>37.24</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DX15" t="n">
-        <v>8.85</v>
+        <v>8.67</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.4</v>
+        <v>5.33</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.6</v>
+        <v>17.48</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7111,52 +7111,52 @@
         <v>2.55</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>81.22</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.22</v>
+        <v>4.5</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>33.11</v>
+        <v>33</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AP16" t="n">
         <v>2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.44</v>
+        <v>10.3</v>
       </c>
       <c r="AR16" t="n">
-        <v>14.11</v>
+        <v>13.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>12.78</v>
+        <v>12.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>44.56</v>
+        <v>44.9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.779999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.44</v>
+        <v>5.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>15.67</v>
+        <v>16.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.8</v>
+        <v>10.62</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.95</v>
+        <v>1.1</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.65</v>
+        <v>4.52</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT16" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU16" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BV16" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW16" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX16" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY16" t="n">
         <v>3.36</v>
@@ -7252,16 +7252,16 @@
         <v>3.62</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="CB16" t="n">
         <v>4.63</v>
       </c>
       <c r="CC16" t="n">
-        <v>7.06</v>
+        <v>6.82</v>
       </c>
       <c r="CD16" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="CE16" t="n">
         <v>1.27</v>
@@ -7273,7 +7273,7 @@
         <v>3.48</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI16" t="n">
         <v>2.2</v>
@@ -7288,7 +7288,7 @@
         <v>1.7</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CN16" t="n">
         <v>2.12</v>
@@ -7315,7 +7315,7 @@
         <v>1.61</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CW16" t="n">
         <v>1.67</v>
@@ -7345,76 +7345,76 @@
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="DH16" t="n">
-        <v>72.8</v>
+        <v>73.62</v>
       </c>
       <c r="DI16" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM16" t="n">
-        <v>34.6</v>
+        <v>34.48</v>
       </c>
       <c r="DN16" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.1</v>
+        <v>11.95</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.25</v>
+        <v>13.95</v>
       </c>
       <c r="DR16" t="n">
-        <v>11.35</v>
+        <v>11.24</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.45</v>
+        <v>43.67</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.65</v>
+        <v>10.62</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.5</v>
+        <v>6.47</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.2</v>
+        <v>17.43</v>
       </c>
       <c r="EB16" t="n">
         <v>1.21</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="n">
         <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
         <v>0.21</v>
@@ -7517,13 +7517,13 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AI17" t="n">
-        <v>92</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="AJ17" t="n">
         <v>0.08</v>
@@ -7532,34 +7532,34 @@
         <v>3</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.17</v>
+        <v>5.08</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AN17" t="n">
-        <v>41.75</v>
+        <v>41.85</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.42</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
-        <v>12.08</v>
+        <v>12.31</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.42</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>53.33</v>
+        <v>52.92</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="BA17" t="n">
-        <v>13.92</v>
+        <v>14.08</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.58</v>
+        <v>8.69</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="BD17" t="n">
-        <v>18.17</v>
+        <v>17.85</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.69</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BL17" t="n">
         <v>1.04</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.19</v>
+        <v>5.22</v>
       </c>
       <c r="BR17" t="n">
-        <v>88.45999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS17" t="n">
-        <v>73.08</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>42.31</v>
+        <v>44.44</v>
       </c>
       <c r="BU17" t="n">
-        <v>26.92</v>
+        <v>25.93</v>
       </c>
       <c r="BV17" t="n">
-        <v>15.38</v>
+        <v>14.81</v>
       </c>
       <c r="BW17" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>51.85</v>
       </c>
       <c r="BY17" t="n">
         <v>1.68</v>
@@ -7655,16 +7655,16 @@
         <v>1.67</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="CE17" t="n">
         <v>1.28</v>
@@ -7682,16 +7682,16 @@
         <v>2.03</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK17" t="n">
         <v>1.42</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CN17" t="n">
         <v>1.85</v>
@@ -7700,10 +7700,10 @@
         <v>1.19</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CR17" t="n">
         <v>1.38</v>
@@ -7718,10 +7718,10 @@
         <v>1.5</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX17" t="n">
         <v>1.52</v>
@@ -7739,7 +7739,7 @@
         <v>1.25</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DD17" t="n">
         <v>3</v>
@@ -7748,76 +7748,76 @@
         <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.84999999999999</v>
+        <v>92.89</v>
       </c>
       <c r="DI17" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.81</v>
+        <v>5.74</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DM17" t="n">
-        <v>47.69</v>
+        <v>47.52</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.97</v>
+        <v>0.93</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.19</v>
+        <v>12</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.08</v>
+        <v>13.15</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.35</v>
+        <v>7.41</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54</v>
+        <v>53.78</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.81</v>
+        <v>15.82</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.62</v>
+        <v>5.63</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.81</v>
+        <v>18.63</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
         <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
         <v>0.08</v>
@@ -7917,139 +7917,139 @@
         <v>2.15</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AI18" t="n">
-        <v>67.2</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK18" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AN18" t="n">
-        <v>32.5</v>
+        <v>33.82</v>
       </c>
       <c r="AO18" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AP18" t="n">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AQ18" t="n">
         <v>12</v>
       </c>
       <c r="AR18" t="n">
-        <v>12.1</v>
+        <v>12.09</v>
       </c>
       <c r="AS18" t="n">
-        <v>11.5</v>
+        <v>11.45</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>43.9</v>
+        <v>43.73</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.2</v>
+        <v>10.73</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.2</v>
+        <v>7.55</v>
       </c>
       <c r="BC18" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="BD18" t="n">
-        <v>18.5</v>
+        <v>18.45</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="BG18" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.87</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="BJ18" t="n">
         <v>0.83</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN18" t="n">
         <v>1.96</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.52</v>
+        <v>3.62</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.78</v>
+        <v>3.88</v>
       </c>
       <c r="BR18" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS18" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT18" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BU18" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BV18" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX18" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BY18" t="n">
         <v>2.43</v>
@@ -8058,25 +8058,25 @@
         <v>2.57</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="CB18" t="n">
         <v>4</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.54</v>
+        <v>4.59</v>
       </c>
       <c r="CD18" t="n">
         <v>5</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CH18" t="n">
         <v>1.37</v>
@@ -8085,55 +8085,55 @@
         <v>2.09</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN18" t="n">
         <v>1.68</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="CP18" t="n">
         <v>1.63</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CU18" t="n">
         <v>1.6</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY18" t="n">
         <v>1.84</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA18" t="n">
         <v>1.97</v>
@@ -8145,82 +8145,82 @@
         <v>1.66</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="DH18" t="n">
-        <v>77.34999999999999</v>
+        <v>77.67</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.26</v>
+        <v>3.37</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DM18" t="n">
-        <v>35.09</v>
+        <v>35.59</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.48</v>
+        <v>12.46</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12.91</v>
+        <v>12.88</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.17</v>
+        <v>9.25</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.3</v>
+        <v>47.08</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.74</v>
+        <v>11.92</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.65</v>
+        <v>7.79</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.09</v>
+        <v>4.12</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.61</v>
+        <v>17.62</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="n">
         <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
         <v>0.08</v>
@@ -8320,52 +8320,52 @@
         <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="AI19" t="n">
-        <v>70.84999999999999</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.77</v>
+        <v>5.29</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AN19" t="n">
-        <v>32</v>
+        <v>35.57</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14.38</v>
+        <v>14</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.23</v>
+        <v>13.07</v>
       </c>
       <c r="AS19" t="n">
-        <v>9</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8377,82 +8377,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>51.46</v>
+        <v>52.79</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BA19" t="n">
-        <v>14</v>
+        <v>14.93</v>
       </c>
       <c r="BB19" t="n">
-        <v>9</v>
+        <v>9.93</v>
       </c>
       <c r="BC19" t="n">
         <v>5</v>
       </c>
       <c r="BD19" t="n">
-        <v>19.77</v>
+        <v>19.64</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.15</v>
+        <v>9.26</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.23</v>
+        <v>4.33</v>
       </c>
       <c r="BR19" t="n">
-        <v>84.62</v>
+        <v>81.48</v>
       </c>
       <c r="BS19" t="n">
-        <v>69.23</v>
+        <v>66.67</v>
       </c>
       <c r="BT19" t="n">
-        <v>57.69</v>
+        <v>55.56</v>
       </c>
       <c r="BU19" t="n">
-        <v>46.15</v>
+        <v>44.44</v>
       </c>
       <c r="BV19" t="n">
-        <v>19.23</v>
+        <v>18.52</v>
       </c>
       <c r="BW19" t="n">
-        <v>15.38</v>
+        <v>14.81</v>
       </c>
       <c r="BX19" t="n">
-        <v>53.85</v>
+        <v>51.85</v>
       </c>
       <c r="BY19" t="n">
         <v>1.55</v>
@@ -8461,31 +8461,31 @@
         <v>1.54</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
       <c r="CB19" t="n">
         <v>4.53</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="CE19" t="n">
         <v>1.27</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.63</v>
@@ -8506,10 +8506,10 @@
         <v>1.16</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
@@ -8524,106 +8524,106 @@
         <v>1.63</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY19" t="n">
         <v>1.9</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB19" t="n">
         <v>1.2</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="DH19" t="n">
-        <v>81.81</v>
+        <v>83.52</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.27</v>
+        <v>5.52</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="DM19" t="n">
-        <v>40.07</v>
+        <v>41.63</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.65</v>
+        <v>13.48</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.08</v>
+        <v>12.03</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.960000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.92</v>
+        <v>55.48</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.23</v>
+        <v>17.59</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.42</v>
+        <v>11.82</v>
       </c>
       <c r="DZ19" t="n">
-        <v>5.81</v>
+        <v>5.78</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.08</v>
+        <v>19.03</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1827,7 +1827,7 @@
         <v>14.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="R3" t="n">
         <v>10.1</v>
@@ -1854,19 +1854,19 @@
         <v>0.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="AB3" t="n">
         <v>4.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
         <v>2.4</v>
@@ -1956,7 +1956,7 @@
         <v>3.05</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.52</v>
+        <v>9.57</v>
       </c>
       <c r="BI3" t="n">
         <v>3.05</v>
@@ -2139,7 +2139,7 @@
         <v>11.91</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="DR3" t="n">
         <v>10.62</v>
@@ -2160,16 +2160,16 @@
         <v>0.19</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.05</v>
+        <v>10.1</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.76</v>
+        <v>6.81</v>
       </c>
       <c r="DZ3" t="n">
         <v>3.29</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.05</v>
+        <v>16.14</v>
       </c>
       <c r="EB3" t="n">
         <v>1.07</v>
@@ -3466,10 +3466,10 @@
         <v>0.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.46</v>
+        <v>12.54</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.380000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AB7" t="n">
         <v>4.08</v>
@@ -3772,10 +3772,10 @@
         <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.68</v>
+        <v>11.72</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.8</v>
+        <v>7.84</v>
       </c>
       <c r="DZ7" t="n">
         <v>3.88</v>
@@ -4308,7 +4308,7 @@
         <v>2.6</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AM9" t="n">
         <v>-0.1</v>
@@ -4323,13 +4323,13 @@
         <v>1.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="AR9" t="n">
         <v>13.7</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="AT9" t="n">
         <v>1.6</v>
@@ -4353,19 +4353,19 @@
         <v>0.1</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="BB9" t="n">
         <v>5.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BF9" t="n">
         <v>2.4</v>
@@ -4374,7 +4374,7 @@
         <v>2.95</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.619999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="BI9" t="n">
         <v>2.95</v>
@@ -4539,7 +4539,7 @@
         <v>2.9</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.71</v>
+        <v>3.76</v>
       </c>
       <c r="DL9" t="n">
         <v>0.14</v>
@@ -4554,13 +4554,13 @@
         <v>1.57</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.19</v>
+        <v>11.29</v>
       </c>
       <c r="DQ9" t="n">
         <v>12.81</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.33</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DS9" t="n">
         <v>0.09</v>
@@ -4578,19 +4578,19 @@
         <v>0.14</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.1</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DY9" t="n">
         <v>6</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.09</v>
+        <v>3.14</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.14</v>
+        <v>17.24</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="EC9" t="n">
         <v>2.62</v>
@@ -5505,7 +5505,7 @@
         <v>2.42</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.92</v>
+        <v>1.17</v>
       </c>
       <c r="AI12" t="n">
         <v>77.42</v>
@@ -5520,7 +5520,7 @@
         <v>3.58</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
         <v>34.17</v>
@@ -5529,7 +5529,7 @@
         <v>0.25</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AQ12" t="n">
         <v>11.5</v>
@@ -5583,7 +5583,7 @@
         <v>2.35</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.83</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="BI12" t="n">
         <v>2.35</v>
@@ -5607,10 +5607,10 @@
         <v>1.43</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.83</v>
+        <v>4.09</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.74</v>
+        <v>3.91</v>
       </c>
       <c r="BR12" t="n">
         <v>91.3</v>
@@ -5694,13 +5694,13 @@
         <v>1.38</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV12" t="n">
         <v>2.2</v>
@@ -5736,7 +5736,7 @@
         <v>1.91</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="DH12" t="n">
         <v>83.22</v>
@@ -5751,7 +5751,7 @@
         <v>4.43</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DM12" t="n">
         <v>37.04</v>
@@ -5760,7 +5760,7 @@
         <v>0.82</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DP12" t="n">
         <v>11.52</v>
@@ -6281,7 +6281,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>58.45</v>
+        <v>58.55</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -6587,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.77</v>
+        <v>51.82</v>
       </c>
       <c r="DW14" t="n">
         <v>0.14</v>
@@ -6633,7 +6633,7 @@
         <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="H15" t="n">
         <v>80.59999999999999</v>
@@ -6645,10 +6645,10 @@
         <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M15" t="n">
         <v>28.9</v>
@@ -6657,7 +6657,7 @@
         <v>0.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="P15" t="n">
         <v>14.4</v>
@@ -6699,7 +6699,7 @@
         <v>3.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AD15" t="n">
         <v>0.98</v>
@@ -6792,7 +6792,7 @@
         <v>2.67</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.33</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI15" t="n">
         <v>2.67</v>
@@ -6816,10 +6816,10 @@
         <v>1.29</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.33</v>
+        <v>4.62</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.52</v>
+        <v>4.71</v>
       </c>
       <c r="BR15" t="n">
         <v>95.23999999999999</v>
@@ -6846,7 +6846,7 @@
         <v>3.4</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="CA15" t="n">
         <v>4.05</v>
@@ -6900,16 +6900,16 @@
         <v>2.9</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV15" t="n">
         <v>1.94</v>
@@ -6945,7 +6945,7 @@
         <v>1.48</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="DH15" t="n">
         <v>64.76000000000001</v>
@@ -6957,10 +6957,10 @@
         <v>2.91</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="DM15" t="n">
         <v>25.47</v>
@@ -6969,7 +6969,7 @@
         <v>1.19</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="DP15" t="n">
         <v>12.48</v>
@@ -7005,7 +7005,7 @@
         <v>3.33</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.48</v>
+        <v>17.52</v>
       </c>
       <c r="EB15" t="n">
         <v>0.95</v>
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.2</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.67</v>
+        <v>43.62</v>
       </c>
       <c r="DW16" t="n">
         <v>0.33</v>
@@ -8383,10 +8383,10 @@
         <v>0.14</v>
       </c>
       <c r="BA19" t="n">
-        <v>14.93</v>
+        <v>15</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.93</v>
+        <v>10</v>
       </c>
       <c r="BC19" t="n">
         <v>5</v>
@@ -8395,7 +8395,7 @@
         <v>19.64</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BF19" t="n">
         <v>2.5</v>
@@ -8608,10 +8608,10 @@
         <v>0.11</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.59</v>
+        <v>17.63</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.82</v>
+        <v>11.85</v>
       </c>
       <c r="DZ19" t="n">
         <v>5.78</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -3863,16 +3863,16 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>50.82</v>
+        <v>50.73</v>
       </c>
       <c r="Y8" t="n">
         <v>0.09</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.36</v>
+        <v>12.27</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.09</v>
+        <v>8</v>
       </c>
       <c r="AB8" t="n">
         <v>4.27</v>
@@ -3881,7 +3881,7 @@
         <v>17.82</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
         <v>2.36</v>
@@ -4169,16 +4169,16 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.57</v>
+        <v>50.53</v>
       </c>
       <c r="DW8" t="n">
         <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.05</v>
+        <v>12</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.09</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DZ8" t="n">
         <v>3.95</v>
@@ -4187,7 +4187,7 @@
         <v>18.24</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="EC8" t="n">
         <v>2.24</v>
@@ -5538,7 +5538,7 @@
         <v>12.58</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.17</v>
+        <v>10.25</v>
       </c>
       <c r="AT12" t="n">
         <v>1.33</v>
@@ -5769,7 +5769,7 @@
         <v>12.26</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.779999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="DS12" t="n">
         <v>0.13</v>
@@ -6699,7 +6699,7 @@
         <v>3.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AD15" t="n">
         <v>0.98</v>
@@ -7005,7 +7005,7 @@
         <v>3.33</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.52</v>
+        <v>17.57</v>
       </c>
       <c r="EB15" t="n">
         <v>0.95</v>
@@ -7571,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>52.92</v>
+        <v>53</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.23</v>
@@ -7796,7 +7796,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>53.78</v>
+        <v>53.81</v>
       </c>
       <c r="DW17" t="n">
         <v>0.18</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="G2" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="H2" t="n">
-        <v>101.09</v>
+        <v>100.08</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="K2" t="n">
-        <v>7.27</v>
+        <v>7.17</v>
       </c>
       <c r="L2" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="M2" t="n">
-        <v>61.55</v>
+        <v>59.58</v>
       </c>
       <c r="N2" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="O2" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="P2" t="n">
-        <v>11.09</v>
+        <v>11.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.73</v>
+        <v>11.75</v>
       </c>
       <c r="R2" t="n">
-        <v>6.64</v>
+        <v>6.42</v>
       </c>
       <c r="S2" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>57.55</v>
+        <v>56.58</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>17</v>
+        <v>16.92</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.45</v>
+        <v>10.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.55</v>
+        <v>6.42</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.82</v>
+        <v>20.33</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AF2" t="n">
         <v>0.08</v>
@@ -1550,70 +1550,70 @@
         <v>2.08</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.26</v>
+        <v>9.25</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>91.67</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>79.17</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>45.83</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>25</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CA2" t="n">
         <v>4</v>
       </c>
-      <c r="BQ2" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>82.61</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>47.83</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>26.09</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>52.17</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>4.03</v>
-      </c>
       <c r="CB2" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="CC2" t="n">
         <v>2.24</v>
@@ -1622,13 +1622,13 @@
         <v>2.43</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CH2" t="n">
         <v>1.44</v>
@@ -1643,34 +1643,34 @@
         <v>1.39</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CM2" t="n">
         <v>2.4</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO2" t="n">
         <v>1.18</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CR2" t="n">
         <v>1.4</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV2" t="n">
         <v>2.08</v>
@@ -1679,100 +1679,100 @@
         <v>1.83</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB2" t="n">
         <v>1.25</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="DE2" t="n">
         <v>0.08</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="DH2" t="n">
-        <v>101.43</v>
+        <v>100.92</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.22</v>
+        <v>6.21</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="DM2" t="n">
-        <v>55.44</v>
+        <v>54.71</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.69</v>
+        <v>10.79</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.3</v>
+        <v>12.29</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.53</v>
+        <v>6.42</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>55.7</v>
+        <v>55.29</v>
       </c>
       <c r="DW2" t="n">
         <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.83</v>
+        <v>13.92</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.949999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.96</v>
+        <v>18.79</v>
       </c>
       <c r="EB2" t="n">
         <v>1.62</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="H3" t="n">
-        <v>70.59999999999999</v>
+        <v>75.91</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>33.2</v>
+        <v>35.91</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>14.1</v>
+        <v>13.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.9</v>
+        <v>13.64</v>
       </c>
       <c r="R3" t="n">
-        <v>10.1</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>41.3</v>
+        <v>43.45</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.4</v>
+        <v>11.18</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.3</v>
+        <v>7.18</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.4</v>
+        <v>16.09</v>
       </c>
       <c r="AD3" t="n">
         <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AF3" t="n">
         <v>0.09</v>
@@ -1953,70 +1953,70 @@
         <v>2.36</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.57</v>
+        <v>9.32</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="BJ3" t="n">
         <v>1.05</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.33</v>
+        <v>4.18</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.38</v>
+        <v>4.32</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS3" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT3" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BV3" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BW3" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX3" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.45</v>
+        <v>3.39</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="CC3" t="n">
         <v>4.65</v>
@@ -2025,19 +2025,19 @@
         <v>5.26</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.72</v>
@@ -2046,136 +2046,136 @@
         <v>1.43</v>
       </c>
       <c r="CL3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CP3" t="n">
         <v>1.8</v>
       </c>
-      <c r="CM3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="CN3" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="CO3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>1.78</v>
-      </c>
       <c r="CQ3" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="DB3" t="n">
         <v>1.26</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DD3" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DH3" t="n">
-        <v>67.05</v>
+        <v>69.86</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DM3" t="n">
-        <v>27.57</v>
+        <v>29.18</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.91</v>
+        <v>11.73</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13</v>
+        <v>12.91</v>
       </c>
       <c r="DR3" t="n">
-        <v>10.62</v>
+        <v>10.32</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>42.62</v>
+        <v>43.64</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.1</v>
+        <v>10.04</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.81</v>
+        <v>6.77</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.14</v>
+        <v>16.45</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,139 +2275,139 @@
         <v>1.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>79.17</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>48.08</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BM4" t="n">
         <v>1.27</v>
       </c>
-      <c r="AH4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>79.55</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AK4" t="n">
+      <c r="BN4" t="n">
         <v>2.18</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>39.91</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>12.73</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>48.27</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>12.73</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>17.45</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>2.1</v>
       </c>
       <c r="BO4" t="n">
         <v>1.05</v>
       </c>
       <c r="BP4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.57</v>
+        <v>4.45</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU4" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BV4" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX4" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY4" t="n">
         <v>3.26</v>
@@ -2416,64 +2416,64 @@
         <v>3.48</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.15</v>
+        <v>4.04</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.63</v>
+        <v>4.49</v>
       </c>
       <c r="CE4" t="n">
         <v>1.25</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CH4" t="n">
         <v>1.42</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.58</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM4" t="n">
         <v>2.46</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CU4" t="n">
         <v>1.51</v>
@@ -2491,94 +2491,94 @@
         <v>1.82</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DA4" t="n">
         <v>1.99</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="DE4" t="n">
         <v>0.09</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="DH4" t="n">
-        <v>72.34</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="DI4" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DM4" t="n">
-        <v>33.19</v>
+        <v>33.14</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.1</v>
+        <v>11.32</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.53</v>
+        <v>12.59</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.380000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.33</v>
+        <v>47.27</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.91</v>
+        <v>10.73</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="EA4" t="n">
-        <v>20</v>
+        <v>20.09</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n">
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
         <v>0.15</v>
@@ -2678,139 +2678,139 @@
         <v>2.31</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>97.25</v>
+        <v>97.31</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.67</v>
+        <v>4.38</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AN5" t="n">
-        <v>40.58</v>
+        <v>38.77</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.25</v>
+        <v>9.77</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.08</v>
+        <v>14.15</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.92</v>
+        <v>8.23</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>53.42</v>
+        <v>52.77</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BA5" t="n">
-        <v>15</v>
+        <v>14.54</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.83</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.25</v>
+        <v>21.92</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.640000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.36</v>
+        <v>5.38</v>
       </c>
       <c r="BR5" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS5" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BT5" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BU5" t="n">
-        <v>32</v>
+        <v>30.77</v>
       </c>
       <c r="BV5" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="BW5" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX5" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BY5" t="n">
         <v>1.68</v>
@@ -2819,25 +2819,25 @@
         <v>1.78</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="CE5" t="n">
         <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CH5" t="n">
         <v>1.5</v>
@@ -2846,16 +2846,16 @@
         <v>2.06</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN5" t="n">
         <v>1.92</v>
@@ -2876,7 +2876,7 @@
         <v>2.63</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CU5" t="n">
         <v>1.54</v>
@@ -2888,16 +2888,16 @@
         <v>1.75</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB5" t="n">
         <v>1.24</v>
@@ -2906,49 +2906,49 @@
         <v>1.78</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="DH5" t="n">
-        <v>102.52</v>
+        <v>102.35</v>
       </c>
       <c r="DI5" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.96</v>
+        <v>5.76</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="DM5" t="n">
-        <v>50.32</v>
+        <v>49.04</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="DP5" t="n">
-        <v>11</v>
+        <v>10.73</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.2</v>
+        <v>12.31</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.52</v>
+        <v>7.69</v>
       </c>
       <c r="DS5" t="n">
         <v>0.2</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.8</v>
+        <v>56.34</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DX5" t="n">
-        <v>17.56</v>
+        <v>17.23</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.48</v>
+        <v>11.27</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6.08</v>
+        <v>5.96</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.72</v>
+        <v>22.04</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0.17</v>
@@ -3081,16 +3081,16 @@
         <v>2.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AI6" t="n">
-        <v>98.09</v>
+        <v>98.33</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
@@ -3099,121 +3099,121 @@
         <v>2</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.73</v>
+        <v>5.42</v>
       </c>
       <c r="AM6" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AN6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="AP6" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.91</v>
+        <v>11.75</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.550000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.55</v>
+        <v>7.17</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>52.73</v>
+        <v>54</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA6" t="n">
-        <v>14.64</v>
+        <v>14.58</v>
       </c>
       <c r="BB6" t="n">
-        <v>10.73</v>
+        <v>10.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.91</v>
+        <v>4.08</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.64</v>
+        <v>19.08</v>
       </c>
       <c r="BE6" t="n">
         <v>1.55</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.390000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.52</v>
+        <v>4.38</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.65</v>
+        <v>4.54</v>
       </c>
       <c r="BR6" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS6" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT6" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV6" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BW6" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX6" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY6" t="n">
         <v>1.94</v>
@@ -3222,16 +3222,16 @@
         <v>2</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.82</v>
+        <v>3.87</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="CE6" t="n">
         <v>1.29</v>
@@ -3240,10 +3240,10 @@
         <v>2.51</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CI6" t="n">
         <v>1.93</v>
@@ -3255,7 +3255,7 @@
         <v>1.38</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CM6" t="n">
         <v>2.52</v>
@@ -3267,10 +3267,10 @@
         <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
@@ -3315,76 +3315,76 @@
         <v>0.17</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="DH6" t="n">
-        <v>87.56999999999999</v>
+        <v>88.12</v>
       </c>
       <c r="DI6" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.74</v>
+        <v>5.58</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.96</v>
+        <v>40.75</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.87</v>
+        <v>2.79</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.39</v>
+        <v>11.34</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.7</v>
+        <v>10.75</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.130000000000001</v>
+        <v>7.92</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>53.74</v>
+        <v>54.34</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.66</v>
+        <v>14.62</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.13</v>
+        <v>10.04</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.52</v>
+        <v>4.58</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="EB6" t="n">
         <v>1.4</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n">
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
         <v>0.15</v>
@@ -3484,52 +3484,52 @@
         <v>2.62</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AI7" t="n">
-        <v>75.5</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AN7" t="n">
-        <v>38.25</v>
+        <v>38.15</v>
       </c>
       <c r="AO7" t="n">
         <v>0.92</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.17</v>
+        <v>12.69</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.5</v>
+        <v>13.69</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.75</v>
+        <v>10.15</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AV7" t="n">
         <v>0.08</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>45.08</v>
+        <v>46</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.83</v>
+        <v>10.92</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.17</v>
+        <v>7.31</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="BD7" t="n">
-        <v>20.92</v>
+        <v>20.77</v>
       </c>
       <c r="BE7" t="n">
         <v>1.22</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.640000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BL7" t="n">
         <v>0.88</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="BR7" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BT7" t="n">
-        <v>64</v>
+        <v>61.54</v>
       </c>
       <c r="BU7" t="n">
-        <v>36</v>
+        <v>34.62</v>
       </c>
       <c r="BV7" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BW7" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BX7" t="n">
-        <v>76</v>
+        <v>73.08</v>
       </c>
       <c r="BY7" t="n">
         <v>2.77</v>
@@ -3628,22 +3628,22 @@
         <v>3.5</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.69</v>
+        <v>4.63</v>
       </c>
       <c r="CE7" t="n">
         <v>1.36</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CH7" t="n">
         <v>1.43</v>
@@ -3652,13 +3652,13 @@
         <v>1.97</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK7" t="n">
         <v>1.54</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CM7" t="n">
         <v>2.35</v>
@@ -3673,7 +3673,7 @@
         <v>1.9</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CR7" t="n">
         <v>1.4</v>
@@ -3694,7 +3694,7 @@
         <v>1.82</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY7" t="n">
         <v>1.99</v>
@@ -3703,7 +3703,7 @@
         <v>2.31</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DB7" t="n">
         <v>1.3</v>
@@ -3712,49 +3712,49 @@
         <v>1.97</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DG7" t="n">
         <v>1.84</v>
       </c>
       <c r="DH7" t="n">
-        <v>84.84</v>
+        <v>84.8</v>
       </c>
       <c r="DI7" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="DK7" t="n">
         <v>3.92</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DM7" t="n">
-        <v>37.76</v>
+        <v>37.73</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.08</v>
+        <v>11.88</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.96</v>
+        <v>13.08</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.880000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DS7" t="n">
         <v>0.2</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.56</v>
+        <v>48.88</v>
       </c>
       <c r="DW7" t="n">
         <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.72</v>
+        <v>11.73</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.84</v>
+        <v>7.89</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.2</v>
+        <v>21.12</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,43 +3887,43 @@
         <v>2.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AI8" t="n">
-        <v>72</v>
+        <v>75.36</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.6</v>
+        <v>4.82</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="AN8" t="n">
-        <v>32.7</v>
+        <v>31.36</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.5</v>
+        <v>10.91</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.3</v>
+        <v>12.55</v>
       </c>
       <c r="AS8" t="n">
         <v>10</v>
@@ -3932,7 +3932,7 @@
         <v>2</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>50.3</v>
+        <v>52</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.7</v>
+        <v>12.18</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.1</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.859999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BO8" t="n">
         <v>1.05</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.57</v>
+        <v>4.55</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.62</v>
+        <v>4.64</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS8" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BU8" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV8" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX8" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>2.71</v>
@@ -4028,28 +4028,28 @@
         <v>3.14</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.4</v>
+        <v>4.22</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.63</v>
+        <v>4.45</v>
       </c>
       <c r="CE8" t="n">
         <v>1.31</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI8" t="n">
         <v>2.13</v>
@@ -4058,10 +4058,10 @@
         <v>1.66</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CM8" t="n">
         <v>2.56</v>
@@ -4073,28 +4073,28 @@
         <v>1.21</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX8" t="n">
         <v>1.51</v>
@@ -4109,88 +4109,88 @@
         <v>1.96</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="DH8" t="n">
-        <v>71</v>
+        <v>72.73</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.72</v>
+        <v>4.82</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="DM8" t="n">
-        <v>31.9</v>
+        <v>31.27</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.57</v>
+        <v>11.28</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.33</v>
+        <v>12.46</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.43</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.53</v>
+        <v>51.36</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DX8" t="n">
-        <v>12</v>
+        <v>12.22</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.050000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.24</v>
+        <v>18.41</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F9" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="H9" t="n">
-        <v>78.09</v>
+        <v>78.92</v>
       </c>
       <c r="I9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="J9" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="K9" t="n">
-        <v>4.18</v>
+        <v>3.92</v>
       </c>
       <c r="L9" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M9" t="n">
-        <v>35.73</v>
+        <v>35.42</v>
       </c>
       <c r="N9" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="P9" t="n">
-        <v>11.09</v>
+        <v>11.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>11.75</v>
       </c>
       <c r="R9" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="S9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="T9" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>42.91</v>
+        <v>42</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.73</v>
+        <v>9.42</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.55</v>
+        <v>6.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="AC9" t="n">
-        <v>15.82</v>
+        <v>15.42</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4374,67 +4374,67 @@
         <v>2.95</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.67</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI9" t="n">
         <v>2.95</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.33</v>
+        <v>4.18</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.86</v>
+        <v>4.73</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT9" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU9" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BV9" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX9" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.09</v>
+        <v>3.42</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.44</v>
+        <v>3.82</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.87</v>
+        <v>3.9</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="CC9" t="n">
         <v>5.87</v>
@@ -4446,10 +4446,10 @@
         <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CH9" t="n">
         <v>1.48</v>
@@ -4464,22 +4464,22 @@
         <v>1.45</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM9" t="n">
         <v>2.51</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO9" t="n">
         <v>1.23</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CR9" t="n">
         <v>1.39</v>
@@ -4494,10 +4494,10 @@
         <v>1.53</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CX9" t="n">
         <v>1.53</v>
@@ -4524,43 +4524,43 @@
         <v>0.09</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="DH9" t="n">
-        <v>76.90000000000001</v>
+        <v>77.41</v>
       </c>
       <c r="DI9" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.76</v>
+        <v>3.64</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.81</v>
+        <v>35.64</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.29</v>
+        <v>11.27</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.81</v>
+        <v>12.64</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.380000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0.09</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.43</v>
+        <v>42.91</v>
       </c>
       <c r="DW9" t="n">
         <v>0.14</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.140000000000001</v>
+        <v>9</v>
       </c>
       <c r="DY9" t="n">
-        <v>6</v>
+        <v>5.86</v>
       </c>
       <c r="DZ9" t="n">
         <v>3.14</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.24</v>
+        <v>16.96</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
         <v>0.08</v>
@@ -4693,139 +4693,139 @@
         <v>1.58</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AI10" t="n">
-        <v>62.38</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AN10" t="n">
-        <v>29.08</v>
+        <v>28.71</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.31</v>
+        <v>10.36</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.31</v>
+        <v>13.29</v>
       </c>
       <c r="AS10" t="n">
-        <v>8</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>54.69</v>
+        <v>54.64</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BA10" t="n">
-        <v>13.54</v>
+        <v>12.86</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.08</v>
+        <v>7.64</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.46</v>
+        <v>5.21</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.23</v>
+        <v>19.14</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.36</v>
+        <v>4.42</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>80</v>
+        <v>76.92</v>
       </c>
       <c r="BT10" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BU10" t="n">
-        <v>48</v>
+        <v>46.15</v>
       </c>
       <c r="BV10" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="BW10" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BY10" t="n">
         <v>1.8</v>
@@ -4834,169 +4834,169 @@
         <v>1.91</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="CC10" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.55</v>
+        <v>3.63</v>
       </c>
       <c r="CE10" t="n">
         <v>1.31</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CH10" t="n">
         <v>1.52</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.68</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CU10" t="n">
         <v>1.57</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB10" t="n">
         <v>1.22</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DH10" t="n">
-        <v>77.31999999999999</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DM10" t="n">
-        <v>35.72</v>
+        <v>35.27</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.56</v>
+        <v>10.58</v>
       </c>
       <c r="DQ10" t="n">
         <v>13.12</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.08</v>
+        <v>7.19</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.96</v>
+        <v>55.88</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.72</v>
+        <v>13.35</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.24</v>
+        <v>8</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.48</v>
+        <v>5.34</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.76</v>
+        <v>18.27</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="11">
@@ -5006,91 +5006,91 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="H11" t="n">
-        <v>82.40000000000001</v>
+        <v>82.09</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>5.64</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2</v>
+        <v>-0.09</v>
       </c>
       <c r="M11" t="n">
-        <v>43.7</v>
+        <v>42.09</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>12.2</v>
+        <v>12.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.5</v>
+        <v>11.09</v>
       </c>
       <c r="R11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.09</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>51.9</v>
+        <v>52.09</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.8</v>
+        <v>17.09</v>
       </c>
       <c r="AA11" t="n">
-        <v>13.2</v>
+        <v>12.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>24.9</v>
+        <v>24.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -5177,70 +5177,70 @@
         <v>2.64</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.9</v>
+        <v>9.68</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.76</v>
+        <v>4.64</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BV11" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX11" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="CC11" t="n">
         <v>3.78</v>
@@ -5252,16 +5252,16 @@
         <v>1.3</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.63</v>
@@ -5270,103 +5270,103 @@
         <v>1.4</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO11" t="n">
         <v>1.19</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CW11" t="n">
         <v>1.66</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CY11" t="n">
         <v>1.75</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DB11" t="n">
         <v>1.22</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DD11" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DG11" t="n">
         <v>2.73</v>
       </c>
-      <c r="DE11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DF11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="DG11" t="n">
-        <v>2.81</v>
-      </c>
       <c r="DH11" t="n">
-        <v>84.72</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.19</v>
+        <v>5.05</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DM11" t="n">
-        <v>42.72</v>
+        <v>41.96</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.24</v>
+        <v>12.31</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.05</v>
+        <v>11.32</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.24</v>
+        <v>9.18</v>
       </c>
       <c r="DS11" t="n">
         <v>0.09</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.52</v>
+        <v>49.72</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.81</v>
+        <v>15.54</v>
       </c>
       <c r="DY11" t="n">
-        <v>11.05</v>
+        <v>10.77</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.76</v>
+        <v>4.78</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.95</v>
+        <v>21.72</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>12</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="G12" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="H12" t="n">
-        <v>89.55</v>
+        <v>89.58</v>
       </c>
       <c r="I12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J12" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="K12" t="n">
-        <v>5.36</v>
+        <v>5.5</v>
       </c>
       <c r="L12" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="M12" t="n">
-        <v>40.18</v>
+        <v>39.75</v>
       </c>
       <c r="N12" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="O12" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>11.55</v>
+        <v>11.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.91</v>
+        <v>11.58</v>
       </c>
       <c r="R12" t="n">
-        <v>7.27</v>
+        <v>7.75</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="T12" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="U12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.73</v>
+        <v>51.92</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.27</v>
+        <v>14.67</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.82</v>
+        <v>10.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>15.55</v>
+        <v>16.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AF12" t="n">
         <v>0.08</v>
@@ -5580,70 +5580,70 @@
         <v>2.25</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.869999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.09</v>
+        <v>4.12</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="BR12" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS12" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT12" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU12" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV12" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BY12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="CC12" t="n">
         <v>2.67</v>
@@ -5652,34 +5652,34 @@
         <v>2.96</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CH12" t="n">
         <v>1.47</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.7</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CO12" t="n">
         <v>1.24</v>
@@ -5688,7 +5688,7 @@
         <v>1.79</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CR12" t="n">
         <v>1.38</v>
@@ -5715,94 +5715,94 @@
         <v>1.82</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DA12" t="n">
         <v>2</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="DE12" t="n">
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DH12" t="n">
-        <v>83.22</v>
+        <v>83.5</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.43</v>
+        <v>4.54</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DM12" t="n">
-        <v>37.04</v>
+        <v>36.96</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="DO12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.52</v>
+        <v>11.71</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.26</v>
+        <v>12.08</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.82</v>
+        <v>9</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>51.74</v>
+        <v>51.38</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.78</v>
+        <v>14</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.43</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.61</v>
+        <v>18.88</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>0.1</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="AI13" t="n">
-        <v>75.73</v>
+        <v>75.5</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.36</v>
+        <v>5.58</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN13" t="n">
-        <v>28.91</v>
+        <v>29.25</v>
       </c>
       <c r="AO13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BL13" t="n">
         <v>1.09</v>
       </c>
-      <c r="AP13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>13.55</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>12.36</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>10.82</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>46.55</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>10.64</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>19.18</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BM13" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BN13" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.33</v>
+        <v>4.18</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.24</v>
+        <v>5.45</v>
       </c>
       <c r="BR13" t="n">
-        <v>90.48</v>
+        <v>86.36</v>
       </c>
       <c r="BS13" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT13" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU13" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV13" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW13" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BX13" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>3.25</v>
@@ -6046,43 +6046,43 @@
         <v>3.74</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.21</v>
+        <v>5.15</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.73</v>
+        <v>5.66</v>
       </c>
       <c r="CE13" t="n">
         <v>1.33</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CG13" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CH13" t="n">
         <v>1.47</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK13" t="n">
         <v>1.44</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CM13" t="n">
         <v>2.54</v>
       </c>
       <c r="CN13" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CO13" t="n">
         <v>1.25</v>
@@ -6091,7 +6091,7 @@
         <v>1.83</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="CR13" t="n">
         <v>1.38</v>
@@ -6106,106 +6106,106 @@
         <v>1.48</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="DE13" t="n">
         <v>0.05</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="DH13" t="n">
-        <v>84.09999999999999</v>
+        <v>83.59</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.81</v>
+        <v>4.95</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="DM13" t="n">
-        <v>35.52</v>
+        <v>35.41</v>
       </c>
       <c r="DN13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.34</v>
+        <v>12.23</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.47</v>
+        <v>12.64</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.289999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.48</v>
+        <v>49.23</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.57</v>
+        <v>11.63</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.67</v>
+        <v>7.73</v>
       </c>
       <c r="DZ13" t="n">
         <v>3.91</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.52</v>
+        <v>20.27</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
         <v>0.09</v>
@@ -6305,139 +6305,139 @@
         <v>2.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" t="n">
-        <v>72.36</v>
+        <v>71.75</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.91</v>
+        <v>3.75</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.09</v>
+        <v>3.83</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN14" t="n">
-        <v>39.09</v>
+        <v>37.33</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14.18</v>
+        <v>13.83</v>
       </c>
       <c r="AR14" t="n">
-        <v>11.18</v>
+        <v>10.83</v>
       </c>
       <c r="AS14" t="n">
-        <v>13.36</v>
+        <v>13.33</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>45.09</v>
+        <v>44.25</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.09</v>
+        <v>9.75</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.64</v>
+        <v>6.33</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.18</v>
+        <v>17.58</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.050000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.27</v>
+        <v>4.13</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.68</v>
+        <v>4.61</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS14" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT14" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU14" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BV14" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY14" t="n">
         <v>1.91</v>
@@ -6446,28 +6446,28 @@
         <v>2.01</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.48</v>
+        <v>3.39</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="CE14" t="n">
         <v>1.37</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI14" t="n">
         <v>1.98</v>
@@ -6479,10 +6479,10 @@
         <v>1.5</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CN14" t="n">
         <v>1.85</v>
@@ -6491,19 +6491,19 @@
         <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CU14" t="n">
         <v>1.44</v>
@@ -6512,13 +6512,13 @@
         <v>2.03</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX14" t="n">
         <v>1.56</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.34</v>
@@ -6530,85 +6530,85 @@
         <v>1.31</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="DH14" t="n">
-        <v>83.22</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="DI14" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.36</v>
+        <v>4.22</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DM14" t="n">
-        <v>42.91</v>
+        <v>41.83</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.96</v>
+        <v>12.83</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.36</v>
+        <v>11.17</v>
       </c>
       <c r="DR14" t="n">
-        <v>11.46</v>
+        <v>11.52</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.82</v>
+        <v>51.09</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.63</v>
+        <v>11.39</v>
       </c>
       <c r="DY14" t="n">
-        <v>8</v>
+        <v>7.78</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.45</v>
+        <v>18.61</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="H15" t="n">
-        <v>80.59999999999999</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="M15" t="n">
-        <v>28.9</v>
+        <v>27.64</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="O15" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="P15" t="n">
-        <v>14.4</v>
+        <v>13.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.3</v>
+        <v>11.91</v>
       </c>
       <c r="R15" t="n">
-        <v>10.7</v>
+        <v>10.82</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>42.7</v>
+        <v>41.64</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.3</v>
+        <v>5.64</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.3</v>
+        <v>18.55</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6789,70 +6789,70 @@
         <v>2.09</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.380000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.62</v>
+        <v>4.59</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.71</v>
+        <v>4.73</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS15" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT15" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX15" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.81</v>
+        <v>3.72</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.27</v>
+        <v>4.23</v>
       </c>
       <c r="CC15" t="n">
         <v>7.34</v>
@@ -6864,28 +6864,28 @@
         <v>1.29</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CH15" t="n">
         <v>1.4</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CN15" t="n">
         <v>1.87</v>
@@ -6897,25 +6897,25 @@
         <v>1.85</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="CR15" t="n">
         <v>1.4</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CU15" t="n">
         <v>1.49</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX15" t="n">
         <v>1.51</v>
@@ -6933,85 +6933,85 @@
         <v>1.28</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="DH15" t="n">
-        <v>64.76000000000001</v>
+        <v>64.59</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DM15" t="n">
-        <v>25.47</v>
+        <v>25</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.48</v>
+        <v>12.32</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.43</v>
+        <v>12.23</v>
       </c>
       <c r="DR15" t="n">
-        <v>10.95</v>
+        <v>11</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>37.24</v>
+        <v>36.96</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX15" t="n">
-        <v>8.67</v>
+        <v>8.91</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.57</v>
+        <v>17.28</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7111,52 +7111,52 @@
         <v>2.55</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AI16" t="n">
-        <v>82.09999999999999</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.5</v>
+        <v>4.18</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN16" t="n">
-        <v>33</v>
+        <v>31.45</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AP16" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.3</v>
+        <v>9.91</v>
       </c>
       <c r="AR16" t="n">
-        <v>13.5</v>
+        <v>13.36</v>
       </c>
       <c r="AS16" t="n">
-        <v>12.4</v>
+        <v>12.45</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>44.8</v>
+        <v>43.27</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.9</v>
+        <v>8.82</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.3</v>
+        <v>15.91</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.62</v>
+        <v>10.36</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.52</v>
+        <v>4.45</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.05</v>
+        <v>5.86</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT16" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU16" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BV16" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="BX16" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY16" t="n">
         <v>3.36</v>
@@ -7252,31 +7252,31 @@
         <v>3.62</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.2</v>
+        <v>4.26</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.63</v>
+        <v>4.71</v>
       </c>
       <c r="CC16" t="n">
-        <v>6.82</v>
+        <v>6.88</v>
       </c>
       <c r="CD16" t="n">
-        <v>7.7</v>
+        <v>7.91</v>
       </c>
       <c r="CE16" t="n">
         <v>1.27</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.65</v>
@@ -7285,22 +7285,22 @@
         <v>1.39</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CO16" t="n">
         <v>1.17</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
@@ -7315,10 +7315,10 @@
         <v>1.61</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX16" t="n">
         <v>1.5</v>
@@ -7330,58 +7330,58 @@
         <v>2.5</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DB16" t="n">
         <v>1.2</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="DH16" t="n">
-        <v>73.62</v>
+        <v>72.36</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM16" t="n">
-        <v>34.48</v>
+        <v>33.64</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.95</v>
+        <v>11.68</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.95</v>
+        <v>13.86</v>
       </c>
       <c r="DR16" t="n">
-        <v>11.24</v>
+        <v>11.32</v>
       </c>
       <c r="DS16" t="n">
         <v>0.09</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.62</v>
+        <v>42.91</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.62</v>
+        <v>10.5</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.47</v>
+        <v>6.41</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.43</v>
+        <v>17.18</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="17">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
         <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F17" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="G17" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>93.56999999999999</v>
+        <v>93.67</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="K17" t="n">
-        <v>6.36</v>
+        <v>6.2</v>
       </c>
       <c r="L17" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="M17" t="n">
-        <v>52.79</v>
+        <v>53.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="O17" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="Q17" t="n">
         <v>13.93</v>
       </c>
       <c r="R17" t="n">
-        <v>6.43</v>
+        <v>6.2</v>
       </c>
       <c r="S17" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="T17" t="n">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="U17" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="V17" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>54.57</v>
+        <v>55.73</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.43</v>
+        <v>17.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.57</v>
+        <v>11.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.86</v>
+        <v>5.93</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.36</v>
+        <v>19.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,70 +7595,70 @@
         <v>2.77</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.699999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.26</v>
+        <v>4.21</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.22</v>
+        <v>5.11</v>
       </c>
       <c r="BR17" t="n">
-        <v>88.89</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="BS17" t="n">
-        <v>74.06999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT17" t="n">
-        <v>44.44</v>
+        <v>46.43</v>
       </c>
       <c r="BU17" t="n">
-        <v>25.93</v>
+        <v>28.57</v>
       </c>
       <c r="BV17" t="n">
-        <v>14.81</v>
+        <v>17.86</v>
       </c>
       <c r="BW17" t="n">
-        <v>11.11</v>
+        <v>14.29</v>
       </c>
       <c r="BX17" t="n">
-        <v>51.85</v>
+        <v>53.57</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.76</v>
+        <v>3.82</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.07</v>
+        <v>4.15</v>
       </c>
       <c r="CC17" t="n">
         <v>2.45</v>
@@ -7670,13 +7670,13 @@
         <v>1.28</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI17" t="n">
         <v>2.03</v>
@@ -7691,19 +7691,19 @@
         <v>1.82</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO17" t="n">
         <v>1.19</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="CR17" t="n">
         <v>1.38</v>
@@ -7718,106 +7718,106 @@
         <v>1.5</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX17" t="n">
         <v>1.52</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.43</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DB17" t="n">
         <v>1.25</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="DD17" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="DE17" t="n">
         <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.89</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="DI17" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.74</v>
+        <v>5.68</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DM17" t="n">
-        <v>47.52</v>
+        <v>48.04</v>
       </c>
       <c r="DN17" t="n">
         <v>0.93</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="DP17" t="n">
-        <v>12</v>
+        <v>11.79</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.15</v>
+        <v>13.18</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.41</v>
+        <v>7.25</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>53.81</v>
+        <v>54.46</v>
       </c>
       <c r="DW17" t="n">
         <v>0.18</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.82</v>
+        <v>15.97</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.18</v>
+        <v>10.29</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.63</v>
+        <v>5.67</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.63</v>
+        <v>18.57</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="18">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
         <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="G18" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="H18" t="n">
-        <v>85.15000000000001</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="K18" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="L18" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="M18" t="n">
-        <v>37.08</v>
+        <v>38.36</v>
       </c>
       <c r="N18" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="O18" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="P18" t="n">
-        <v>12.85</v>
+        <v>12.79</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.54</v>
+        <v>13.64</v>
       </c>
       <c r="R18" t="n">
-        <v>7.38</v>
+        <v>7.21</v>
       </c>
       <c r="S18" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="U18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="V18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>49.92</v>
+        <v>50.36</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>12.92</v>
+        <v>12.79</v>
       </c>
       <c r="AA18" t="n">
         <v>8</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.92</v>
+        <v>4.79</v>
       </c>
       <c r="AC18" t="n">
-        <v>16.92</v>
+        <v>16.79</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AF18" t="n">
         <v>0.09</v>
@@ -7998,70 +7998,70 @@
         <v>2.91</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.039999999999999</v>
+        <v>8.16</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.62</v>
+        <v>3.52</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.88</v>
+        <v>4.12</v>
       </c>
       <c r="BR18" t="n">
-        <v>91.67</v>
+        <v>88</v>
       </c>
       <c r="BS18" t="n">
-        <v>83.33</v>
+        <v>80</v>
       </c>
       <c r="BT18" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BU18" t="n">
-        <v>41.67</v>
+        <v>40</v>
       </c>
       <c r="BV18" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX18" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="CA18" t="n">
         <v>3.76</v>
       </c>
       <c r="CB18" t="n">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="CC18" t="n">
         <v>4.59</v>
@@ -8070,34 +8070,34 @@
         <v>5</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI18" t="n">
         <v>2.09</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CM18" t="n">
         <v>2.22</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO18" t="n">
         <v>1.02</v>
@@ -8106,7 +8106,7 @@
         <v>1.63</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
@@ -8121,7 +8121,7 @@
         <v>1.6</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CW18" t="n">
         <v>1.61</v>
@@ -8130,7 +8130,7 @@
         <v>1.55</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.36</v>
@@ -8151,76 +8151,76 @@
         <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="DH18" t="n">
-        <v>77.67</v>
+        <v>78.84</v>
       </c>
       <c r="DI18" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM18" t="n">
-        <v>35.59</v>
+        <v>36.36</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.46</v>
+        <v>12.44</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12.88</v>
+        <v>12.96</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.25</v>
+        <v>9.08</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.08</v>
+        <v>47.44</v>
       </c>
       <c r="DW18" t="n">
         <v>0.08</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.92</v>
+        <v>11.88</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.79</v>
+        <v>7.8</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.62</v>
+        <v>17.52</v>
       </c>
       <c r="EB18" t="n">
         <v>1.3</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="19">
@@ -8230,94 +8230,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
         <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="G19" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="H19" t="n">
-        <v>92.77</v>
+        <v>92</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="K19" t="n">
-        <v>5.77</v>
+        <v>5.79</v>
       </c>
       <c r="L19" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="M19" t="n">
-        <v>48.15</v>
+        <v>46.07</v>
       </c>
       <c r="N19" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>3.38</v>
+        <v>3.14</v>
       </c>
       <c r="P19" t="n">
-        <v>12.92</v>
+        <v>12.29</v>
       </c>
       <c r="Q19" t="n">
-        <v>10.92</v>
+        <v>11.07</v>
       </c>
       <c r="R19" t="n">
-        <v>8.92</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="T19" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="U19" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="V19" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>58.38</v>
+        <v>58.14</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z19" t="n">
-        <v>20.46</v>
+        <v>20.07</v>
       </c>
       <c r="AA19" t="n">
-        <v>13.85</v>
+        <v>13.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.62</v>
+        <v>6.57</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.38</v>
+        <v>18.57</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AF19" t="n">
         <v>0.07000000000000001</v>
@@ -8401,70 +8401,70 @@
         <v>2.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.26</v>
+        <v>9.18</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.41</v>
+        <v>4.29</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.33</v>
+        <v>4.39</v>
       </c>
       <c r="BR19" t="n">
-        <v>81.48</v>
+        <v>82.14</v>
       </c>
       <c r="BS19" t="n">
-        <v>66.67</v>
+        <v>67.86</v>
       </c>
       <c r="BT19" t="n">
-        <v>55.56</v>
+        <v>53.57</v>
       </c>
       <c r="BU19" t="n">
-        <v>44.44</v>
+        <v>42.86</v>
       </c>
       <c r="BV19" t="n">
-        <v>18.52</v>
+        <v>17.86</v>
       </c>
       <c r="BW19" t="n">
-        <v>14.81</v>
+        <v>14.29</v>
       </c>
       <c r="BX19" t="n">
-        <v>51.85</v>
+        <v>53.57</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.15</v>
+        <v>4.12</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="CC19" t="n">
         <v>2.33</v>
@@ -8476,10 +8476,10 @@
         <v>1.27</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="CH19" t="n">
         <v>1.59</v>
@@ -8491,16 +8491,16 @@
         <v>1.63</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO19" t="n">
         <v>1.16</v>
@@ -8509,88 +8509,88 @@
         <v>1.61</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CW19" t="n">
         <v>1.67</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY19" t="n">
         <v>1.9</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB19" t="n">
         <v>1.2</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="DE19" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="DH19" t="n">
-        <v>83.52</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.52</v>
+        <v>5.54</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="DM19" t="n">
-        <v>41.63</v>
+        <v>40.82</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.89</v>
+        <v>2.78</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.48</v>
+        <v>13.14</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.03</v>
+        <v>12.07</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.77</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DS19" t="n">
         <v>0.18</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.48</v>
+        <v>55.46</v>
       </c>
       <c r="DW19" t="n">
         <v>0.11</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.63</v>
+        <v>17.54</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.85</v>
+        <v>11.75</v>
       </c>
       <c r="DZ19" t="n">
-        <v>5.78</v>
+        <v>5.79</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.03</v>
+        <v>19.1</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1451,10 +1451,10 @@
         <v>0.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.92</v>
+        <v>17</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.5</v>
+        <v>10.58</v>
       </c>
       <c r="AB2" t="n">
         <v>6.42</v>
@@ -1757,10 +1757,10 @@
         <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.92</v>
+        <v>13.96</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.039999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="DZ2" t="n">
         <v>4.88</v>
@@ -2338,10 +2338,10 @@
         <v>0.25</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.25</v>
+        <v>12.33</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.33</v>
+        <v>7.42</v>
       </c>
       <c r="BC4" t="n">
         <v>4.92</v>
@@ -2350,7 +2350,7 @@
         <v>17.83</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BF4" t="n">
         <v>1.83</v>
@@ -2563,10 +2563,10 @@
         <v>0.23</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.73</v>
+        <v>10.77</v>
       </c>
       <c r="DY4" t="n">
-        <v>7</v>
+        <v>7.05</v>
       </c>
       <c r="DZ4" t="n">
         <v>3.73</v>
@@ -2575,7 +2575,7 @@
         <v>20.09</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="EC4" t="n">
         <v>1.59</v>
@@ -2744,16 +2744,16 @@
         <v>14.54</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.539999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="BD5" t="n">
         <v>21.92</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BF5" t="n">
         <v>1.54</v>
@@ -2969,10 +2969,10 @@
         <v>17.23</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.27</v>
+        <v>11.23</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.96</v>
+        <v>6</v>
       </c>
       <c r="EA5" t="n">
         <v>22.04</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>52</v>
+        <v>52.09</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.18</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.18</v>
+        <v>12.09</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.359999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="BC8" t="n">
         <v>3.82</v>
@@ -3962,7 +3962,7 @@
         <v>19</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BF8" t="n">
         <v>2.27</v>
@@ -4169,16 +4169,16 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.36</v>
+        <v>51.41</v>
       </c>
       <c r="DW8" t="n">
         <v>0.13</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.22</v>
+        <v>12.18</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.18</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ8" t="n">
         <v>4.04</v>
@@ -4187,7 +4187,7 @@
         <v>18.41</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="EC8" t="n">
         <v>2.31</v>
@@ -5484,16 +5484,16 @@
         <v>14.67</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.17</v>
+        <v>10.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.5</v>
+        <v>4.58</v>
       </c>
       <c r="AC12" t="n">
         <v>16.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE12" t="n">
         <v>2.33</v>
@@ -5790,10 +5790,10 @@
         <v>14</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.619999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.38</v>
+        <v>4.42</v>
       </c>
       <c r="EA12" t="n">
         <v>18.88</v>
@@ -6684,7 +6684,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>41.64</v>
+        <v>41.55</v>
       </c>
       <c r="Y15" t="n">
         <v>0.18</v>
@@ -6990,7 +6990,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>36.96</v>
+        <v>36.91</v>
       </c>
       <c r="DW15" t="n">
         <v>0.22</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
         <v>0.45</v>
@@ -1872,139 +1872,139 @@
         <v>2.27</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AI3" t="n">
-        <v>63.82</v>
+        <v>65.42</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="AL3" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="AN3" t="n">
-        <v>22.45</v>
+        <v>21.67</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.91</v>
+        <v>9.75</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.18</v>
+        <v>12.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.09</v>
+        <v>10.75</v>
       </c>
       <c r="AT3" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>43.82</v>
+        <v>45.42</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.91</v>
+        <v>9.42</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.36</v>
+        <v>6.67</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="BD3" t="n">
-        <v>16.82</v>
+        <v>17</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.32</v>
+        <v>9.17</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.18</v>
+        <v>3.96</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.32</v>
+        <v>4.09</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS3" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU3" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BV3" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BW3" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY3" t="n">
         <v>3.11</v>
@@ -2013,43 +2013,43 @@
         <v>3.39</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.26</v>
+        <v>5.23</v>
       </c>
       <c r="CE3" t="n">
         <v>1.32</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CN3" t="n">
         <v>2</v>
@@ -2058,10 +2058,10 @@
         <v>1.23</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CR3" t="n">
         <v>1.39</v>
@@ -2076,10 +2076,10 @@
         <v>1.51</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX3" t="n">
         <v>1.54</v>
@@ -2094,88 +2094,88 @@
         <v>2</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="DH3" t="n">
-        <v>69.86</v>
+        <v>70.44</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.41</v>
+        <v>3.52</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>29.18</v>
+        <v>28.48</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.73</v>
+        <v>11.57</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.91</v>
+        <v>13.05</v>
       </c>
       <c r="DR3" t="n">
-        <v>10.32</v>
+        <v>10.18</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.64</v>
+        <v>44.48</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.04</v>
+        <v>10.26</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.77</v>
+        <v>6.91</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.45</v>
+        <v>16.56</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="H4" t="n">
-        <v>64.40000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>25.8</v>
+        <v>24.91</v>
       </c>
       <c r="N4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P4" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>12</v>
+      </c>
+      <c r="R4" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>47.36</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD4" t="n">
         <v>0.9</v>
       </c>
-      <c r="O4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.88</v>
-      </c>
       <c r="AE4" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF4" t="n">
         <v>0.17</v>
@@ -2356,70 +2356,70 @@
         <v>1.83</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.41</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.95</v>
+        <v>3.74</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.45</v>
+        <v>4.22</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT4" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU4" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV4" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX4" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.26</v>
+        <v>3.13</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="CC4" t="n">
         <v>4.04</v>
@@ -2428,31 +2428,31 @@
         <v>4.49</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CH4" t="n">
         <v>1.42</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CN4" t="n">
         <v>1.87</v>
@@ -2461,10 +2461,10 @@
         <v>1.15</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CR4" t="n">
         <v>1.37</v>
@@ -2479,7 +2479,7 @@
         <v>1.51</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CW4" t="n">
         <v>1.68</v>
@@ -2488,97 +2488,97 @@
         <v>1.53</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB4" t="n">
         <v>1.24</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="DE4" t="n">
         <v>0.09</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="DH4" t="n">
-        <v>72.45999999999999</v>
+        <v>73.91</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ4" t="n">
         <v>1.96</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.37</v>
+        <v>0.31</v>
       </c>
       <c r="DM4" t="n">
-        <v>33.14</v>
+        <v>32.39</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.32</v>
+        <v>11.26</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.59</v>
+        <v>12.43</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.32</v>
+        <v>8.74</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.27</v>
+        <v>47.74</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.77</v>
+        <v>10.74</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.05</v>
+        <v>6.91</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.73</v>
+        <v>3.83</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.09</v>
+        <v>20.3</v>
       </c>
       <c r="EB4" t="n">
         <v>1.17</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="5">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
         <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F7" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="H7" t="n">
-        <v>93.45999999999999</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="J7" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="K7" t="n">
-        <v>4.08</v>
+        <v>4.29</v>
       </c>
       <c r="L7" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="M7" t="n">
-        <v>37.31</v>
+        <v>36.93</v>
       </c>
       <c r="N7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="O7" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="P7" t="n">
-        <v>11.08</v>
+        <v>11.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.46</v>
+        <v>12.29</v>
       </c>
       <c r="R7" t="n">
-        <v>8.08</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="T7" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="V7" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>51.77</v>
+        <v>51.64</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.54</v>
+        <v>12.71</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.460000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.08</v>
+        <v>4.21</v>
       </c>
       <c r="AC7" t="n">
-        <v>21.46</v>
+        <v>22</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="AF7" t="n">
         <v>0.15</v>
@@ -3568,7 +3568,7 @@
         <v>3.15</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.73</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI7" t="n">
         <v>3.15</v>
@@ -3577,58 +3577,58 @@
         <v>0.85</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BP7" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.04</v>
+        <v>4.15</v>
       </c>
       <c r="BR7" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS7" t="n">
-        <v>84.62</v>
+        <v>85.19</v>
       </c>
       <c r="BT7" t="n">
-        <v>61.54</v>
+        <v>62.96</v>
       </c>
       <c r="BU7" t="n">
-        <v>34.62</v>
+        <v>33.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>15.38</v>
+        <v>14.81</v>
       </c>
       <c r="BW7" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BX7" t="n">
-        <v>73.08</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CC7" t="n">
         <v>4.02</v>
@@ -3643,7 +3643,7 @@
         <v>2.71</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CH7" t="n">
         <v>1.43</v>
@@ -3655,7 +3655,7 @@
         <v>1.78</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL7" t="n">
         <v>1.98</v>
@@ -3697,10 +3697,10 @@
         <v>1.58</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DA7" t="n">
         <v>1.83</v>
@@ -3715,79 +3715,79 @@
         <v>3.35</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="DH7" t="n">
-        <v>84.8</v>
+        <v>84.59</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.92</v>
+        <v>4.04</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="DM7" t="n">
-        <v>37.73</v>
+        <v>37.52</v>
       </c>
       <c r="DN7" t="n">
         <v>1.03</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.88</v>
+        <v>12.07</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.08</v>
+        <v>12.96</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.119999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.88</v>
+        <v>48.92</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.73</v>
+        <v>11.85</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.89</v>
+        <v>7.93</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.85</v>
+        <v>3.93</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.12</v>
+        <v>21.41</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,52 +3887,52 @@
         <v>2.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.36</v>
+        <v>75.67</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.82</v>
+        <v>4.75</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.36</v>
+        <v>30.58</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10.91</v>
+        <v>11.08</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.55</v>
+        <v>12.92</v>
       </c>
       <c r="AS8" t="n">
-        <v>10</v>
+        <v>10.17</v>
       </c>
       <c r="AT8" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>52.09</v>
+        <v>51.42</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.09</v>
+        <v>11.83</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.27</v>
+        <v>8.17</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.82</v>
+        <v>3.67</v>
       </c>
       <c r="BD8" t="n">
-        <v>19</v>
+        <v>18.42</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.82</v>
+        <v>9.91</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.55</v>
+        <v>4.57</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.64</v>
+        <v>4.74</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS8" t="n">
-        <v>81.81999999999999</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BU8" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV8" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY8" t="n">
         <v>2.71</v>
@@ -4028,16 +4028,16 @@
         <v>3.14</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.22</v>
+        <v>4.32</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.45</v>
+        <v>4.53</v>
       </c>
       <c r="CE8" t="n">
         <v>1.31</v>
@@ -4046,7 +4046,7 @@
         <v>2.49</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CH8" t="n">
         <v>1.51</v>
@@ -4073,10 +4073,10 @@
         <v>1.21</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
@@ -4091,7 +4091,7 @@
         <v>1.54</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CW8" t="n">
         <v>1.69</v>
@@ -4109,88 +4109,88 @@
         <v>1.96</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DC8" t="n">
         <v>1.76</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="DE8" t="n">
         <v>0.04</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="DH8" t="n">
-        <v>72.73</v>
+        <v>73</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="DM8" t="n">
-        <v>31.27</v>
+        <v>30.87</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="DO8" t="n">
         <v>1.91</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.28</v>
+        <v>11.35</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.46</v>
+        <v>12.65</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.460000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.41</v>
+        <v>51.09</v>
       </c>
       <c r="DW8" t="n">
         <v>0.13</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.18</v>
+        <v>12.04</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.140000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.41</v>
+        <v>18.13</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="9">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
         <v>14</v>
@@ -4615,82 +4615,82 @@
         <v>0.08</v>
       </c>
       <c r="F10" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="G10" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="H10" t="n">
-        <v>93.5</v>
+        <v>92.69</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>4.31</v>
       </c>
       <c r="L10" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="M10" t="n">
-        <v>42.92</v>
+        <v>42.77</v>
       </c>
       <c r="N10" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="O10" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="P10" t="n">
-        <v>10.83</v>
+        <v>11.08</v>
       </c>
       <c r="Q10" t="n">
         <v>12.92</v>
       </c>
       <c r="R10" t="n">
-        <v>6.08</v>
+        <v>6.15</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="T10" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="U10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>57.33</v>
+        <v>57.23</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.92</v>
+        <v>14.31</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.42</v>
+        <v>8.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.25</v>
+        <v>17.31</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AF10" t="n">
         <v>0.14</v>
@@ -4774,70 +4774,70 @@
         <v>1.93</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.81</v>
+        <v>8.93</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.35</v>
+        <v>4.37</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.42</v>
+        <v>4.52</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>76.92</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>57.69</v>
+        <v>55.56</v>
       </c>
       <c r="BU10" t="n">
-        <v>46.15</v>
+        <v>44.44</v>
       </c>
       <c r="BV10" t="n">
-        <v>26.92</v>
+        <v>25.93</v>
       </c>
       <c r="BW10" t="n">
-        <v>19.23</v>
+        <v>18.52</v>
       </c>
       <c r="BX10" t="n">
-        <v>57.69</v>
+        <v>55.56</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
       <c r="CC10" t="n">
         <v>3.07</v>
@@ -4882,7 +4882,7 @@
         <v>1.71</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
@@ -4897,7 +4897,7 @@
         <v>1.57</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CW10" t="n">
         <v>1.69</v>
@@ -4921,82 +4921,82 @@
         <v>1.72</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="DE10" t="n">
         <v>0.11</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="DH10" t="n">
-        <v>78.04000000000001</v>
+        <v>78.22</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.92</v>
+        <v>4.08</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="DM10" t="n">
-        <v>35.27</v>
+        <v>35.48</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.58</v>
+        <v>10.71</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.12</v>
+        <v>13.11</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.19</v>
+        <v>7.18</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.88</v>
+        <v>55.89</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.35</v>
+        <v>13.56</v>
       </c>
       <c r="DY10" t="n">
-        <v>8</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.34</v>
+        <v>5.33</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.27</v>
+        <v>18.26</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
         <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>0.18</v>
@@ -5096,139 +5096,139 @@
         <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="AI11" t="n">
-        <v>86.81999999999999</v>
+        <v>84.92</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.45</v>
+        <v>4.58</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AN11" t="n">
-        <v>41.82</v>
+        <v>40.83</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.27</v>
+        <v>12.08</v>
       </c>
       <c r="AR11" t="n">
-        <v>11.55</v>
+        <v>12</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.27</v>
+        <v>9.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>47.36</v>
+        <v>47.58</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BA11" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.09</v>
+        <v>8.92</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="BD11" t="n">
-        <v>19.27</v>
+        <v>19.33</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.68</v>
+        <v>9.83</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BJ11" t="n">
         <v>1.09</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.82</v>
+        <v>3.91</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.64</v>
+        <v>4.74</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU11" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV11" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX11" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BY11" t="n">
         <v>2.22</v>
@@ -5237,31 +5237,31 @@
         <v>2.24</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.78</v>
+        <v>3.73</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="CE11" t="n">
         <v>1.3</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CH11" t="n">
         <v>1.53</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.63</v>
@@ -5270,34 +5270,34 @@
         <v>1.4</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CN11" t="n">
         <v>2.06</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV11" t="n">
         <v>2.33</v>
@@ -5309,97 +5309,97 @@
         <v>1.49</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.49</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="DE11" t="n">
         <v>0.13</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.73</v>
+        <v>2.79</v>
       </c>
       <c r="DH11" t="n">
-        <v>84.45999999999999</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="DI11" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DM11" t="n">
-        <v>41.96</v>
+        <v>41.43</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.31</v>
+        <v>12.21</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.32</v>
+        <v>11.56</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.18</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.72</v>
+        <v>49.74</v>
       </c>
       <c r="DW11" t="n">
         <v>0.22</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.54</v>
+        <v>15.35</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.77</v>
+        <v>10.61</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.72</v>
+        <v>21.65</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>12</v>
@@ -5421,49 +5421,49 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="G12" t="n">
-        <v>2.83</v>
+        <v>2.54</v>
       </c>
       <c r="H12" t="n">
-        <v>89.58</v>
+        <v>88.23</v>
       </c>
       <c r="I12" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="J12" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="K12" t="n">
-        <v>5.5</v>
+        <v>5.08</v>
       </c>
       <c r="L12" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="M12" t="n">
-        <v>39.75</v>
+        <v>37.85</v>
       </c>
       <c r="N12" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="P12" t="n">
-        <v>11.92</v>
+        <v>12.31</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.58</v>
+        <v>11.31</v>
       </c>
       <c r="R12" t="n">
-        <v>7.75</v>
+        <v>7.77</v>
       </c>
       <c r="S12" t="n">
         <v>0.92</v>
       </c>
       <c r="T12" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="U12" t="n">
         <v>0.08</v>
@@ -5475,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>51.92</v>
+        <v>50.77</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.67</v>
+        <v>14.08</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.08</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="AC12" t="n">
-        <v>16.33</v>
+        <v>16.23</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.33</v>
+        <v>2.54</v>
       </c>
       <c r="AF12" t="n">
         <v>0.08</v>
@@ -5580,70 +5580,70 @@
         <v>2.25</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.960000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.12</v>
+        <v>3.92</v>
       </c>
       <c r="BQ12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>92</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>72</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>48</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>24</v>
+      </c>
+      <c r="BV12" t="n">
         <v>4</v>
       </c>
-      <c r="BR12" t="n">
-        <v>91.67</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>70.83</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>45.83</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>20.83</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>4.17</v>
-      </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>41.67</v>
+        <v>44</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CC12" t="n">
         <v>2.67</v>
@@ -5655,28 +5655,28 @@
         <v>1.33</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI12" t="n">
         <v>2.08</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CK12" t="n">
         <v>1.43</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CN12" t="n">
         <v>2</v>
@@ -5685,10 +5685,10 @@
         <v>1.24</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CR12" t="n">
         <v>1.38</v>
@@ -5703,10 +5703,10 @@
         <v>1.5</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CX12" t="n">
         <v>1.51</v>
@@ -5718,58 +5718,58 @@
         <v>2.44</v>
       </c>
       <c r="DA12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB12" t="n">
         <v>1.27</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="DE12" t="n">
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DG12" t="n">
         <v>1.88</v>
       </c>
-      <c r="DG12" t="n">
-        <v>2</v>
-      </c>
       <c r="DH12" t="n">
-        <v>83.5</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.54</v>
+        <v>4.36</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="DM12" t="n">
-        <v>36.96</v>
+        <v>36.08</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.71</v>
+        <v>11.92</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.08</v>
+        <v>11.92</v>
       </c>
       <c r="DR12" t="n">
-        <v>9</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DS12" t="n">
         <v>0.12</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>51.38</v>
+        <v>50.8</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DX12" t="n">
-        <v>14</v>
+        <v>13.72</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.58</v>
+        <v>9.32</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.88</v>
+        <v>18.72</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="H13" t="n">
-        <v>93.3</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="M13" t="n">
-        <v>42.8</v>
+        <v>42</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="O13" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="P13" t="n">
-        <v>11</v>
+        <v>10.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.6</v>
+        <v>12.36</v>
       </c>
       <c r="R13" t="n">
-        <v>7.6</v>
+        <v>7.55</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>52.7</v>
+        <v>51.45</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.6</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.4</v>
+        <v>8.82</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>22</v>
+        <v>21.73</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>2.25</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="BH13" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="BN13" t="n">
         <v>1.91</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.45</v>
+        <v>5.3</v>
       </c>
       <c r="BR13" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU13" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BV13" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BW13" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.49</v>
+        <v>3.41</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="CC13" t="n">
         <v>5.15</v>
@@ -6058,13 +6058,13 @@
         <v>1.33</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI13" t="n">
         <v>1.95</v>
@@ -6073,13 +6073,13 @@
         <v>1.77</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN13" t="n">
         <v>1.99</v>
@@ -6088,10 +6088,10 @@
         <v>1.25</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CR13" t="n">
         <v>1.38</v>
@@ -6124,55 +6124,55 @@
         <v>2</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="DH13" t="n">
-        <v>83.59</v>
+        <v>83.48</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.95</v>
+        <v>4.91</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="DM13" t="n">
-        <v>35.41</v>
+        <v>35.35</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.23</v>
+        <v>12</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.64</v>
+        <v>12.52</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.23</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="DS13" t="n">
         <v>0.04</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.23</v>
+        <v>48.78</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.63</v>
+        <v>11.87</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.73</v>
+        <v>7.96</v>
       </c>
       <c r="DZ13" t="n">
         <v>3.91</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.27</v>
+        <v>20.22</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
         <v>0.09</v>
@@ -6308,136 +6308,136 @@
         <v>0.08</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AI14" t="n">
-        <v>71.75</v>
+        <v>72.62</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.83</v>
+        <v>3.69</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AN14" t="n">
-        <v>37.33</v>
+        <v>37.54</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AP14" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.83</v>
+        <v>13.38</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.83</v>
+        <v>10.54</v>
       </c>
       <c r="AS14" t="n">
-        <v>13.33</v>
+        <v>13.69</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>44.25</v>
+        <v>45.54</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.75</v>
+        <v>10.31</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.33</v>
+        <v>6.77</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.58</v>
+        <v>17.38</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.42</v>
+        <v>3.23</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.83</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.61</v>
+        <v>4.5</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS14" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BV14" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BY14" t="n">
         <v>1.91</v>
@@ -6446,16 +6446,16 @@
         <v>2.01</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.39</v>
+        <v>3.31</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="CE14" t="n">
         <v>1.37</v>
@@ -6464,13 +6464,13 @@
         <v>2.76</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CH14" t="n">
         <v>1.4</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.8</v>
@@ -6479,10 +6479,10 @@
         <v>1.5</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CN14" t="n">
         <v>1.85</v>
@@ -6491,10 +6491,10 @@
         <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CR14" t="n">
         <v>1.41</v>
@@ -6509,7 +6509,7 @@
         <v>1.44</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CW14" t="n">
         <v>1.85</v>
@@ -6533,82 +6533,82 @@
         <v>2</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="DE14" t="n">
         <v>0.08</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="DH14" t="n">
-        <v>82.43000000000001</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="DI14" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.22</v>
+        <v>4.13</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM14" t="n">
-        <v>41.83</v>
+        <v>41.75</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.83</v>
+        <v>12.62</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.17</v>
+        <v>11</v>
       </c>
       <c r="DR14" t="n">
-        <v>11.52</v>
+        <v>11.79</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.09</v>
+        <v>51.5</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.39</v>
+        <v>11.63</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.78</v>
+        <v>7.96</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.61</v>
+        <v>3.67</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.61</v>
+        <v>18.46</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
         <v>0.09</v>
@@ -6711,136 +6711,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>50.36</v>
+        <v>54.58</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="AN15" t="n">
-        <v>22.36</v>
+        <v>22.08</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.73</v>
+        <v>10.58</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.55</v>
+        <v>12.33</v>
       </c>
       <c r="AS15" t="n">
-        <v>11.18</v>
+        <v>10.83</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>32.27</v>
+        <v>33.08</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.82</v>
+        <v>9.33</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.36</v>
+        <v>5.75</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="BD15" t="n">
-        <v>16</v>
+        <v>16.25</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.359999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.59</v>
+        <v>4.35</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.73</v>
+        <v>4.48</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS15" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU15" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX15" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BY15" t="n">
         <v>3.35</v>
@@ -6849,22 +6849,22 @@
         <v>3.72</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.23</v>
+        <v>4.2</v>
       </c>
       <c r="CC15" t="n">
-        <v>7.34</v>
+        <v>7.07</v>
       </c>
       <c r="CD15" t="n">
-        <v>7.82</v>
+        <v>7.51</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CG15" t="n">
         <v>2.9</v>
@@ -6873,19 +6873,19 @@
         <v>1.4</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.8</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CN15" t="n">
         <v>1.87</v>
@@ -6897,7 +6897,7 @@
         <v>1.85</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CR15" t="n">
         <v>1.4</v>
@@ -6912,7 +6912,7 @@
         <v>1.49</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW15" t="n">
         <v>1.92</v>
@@ -6921,13 +6921,13 @@
         <v>1.51</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB15" t="n">
         <v>1.28</v>
@@ -6942,76 +6942,76 @@
         <v>0.04</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="DH15" t="n">
-        <v>64.59</v>
+        <v>66.17</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="DM15" t="n">
-        <v>25</v>
+        <v>24.74</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.32</v>
+        <v>12.17</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.23</v>
+        <v>12.13</v>
       </c>
       <c r="DR15" t="n">
-        <v>11</v>
+        <v>10.83</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>36.91</v>
+        <v>37.13</v>
       </c>
       <c r="DW15" t="n">
         <v>0.22</v>
       </c>
       <c r="DX15" t="n">
-        <v>8.91</v>
+        <v>9.17</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.28</v>
+        <v>17.35</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="16">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C18" t="n">
         <v>14</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
         <v>0.07000000000000001</v>
@@ -7917,139 +7917,139 @@
         <v>2.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="n">
-        <v>68.81999999999999</v>
+        <v>69.67</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>33.82</v>
+        <v>33.33</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="AR18" t="n">
-        <v>12.09</v>
+        <v>11.92</v>
       </c>
       <c r="AS18" t="n">
-        <v>11.45</v>
+        <v>11.42</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>43.73</v>
+        <v>43.58</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.73</v>
+        <v>10.42</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.55</v>
+        <v>7.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BD18" t="n">
-        <v>18.45</v>
+        <v>18.17</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.16</v>
+        <v>8.15</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="BO18" t="n">
         <v>1.04</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="BR18" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>80</v>
+        <v>76.92</v>
       </c>
       <c r="BT18" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BU18" t="n">
-        <v>40</v>
+        <v>38.46</v>
       </c>
       <c r="BV18" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BW18" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX18" t="n">
-        <v>48</v>
+        <v>46.15</v>
       </c>
       <c r="BY18" t="n">
         <v>2.38</v>
@@ -8058,16 +8058,16 @@
         <v>2.5</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.76</v>
+        <v>3.86</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.01</v>
+        <v>4.14</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.59</v>
+        <v>5.2</v>
       </c>
       <c r="CD18" t="n">
-        <v>5</v>
+        <v>5.67</v>
       </c>
       <c r="CE18" t="n">
         <v>1.13</v>
@@ -8076,34 +8076,34 @@
         <v>2.06</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CK18" t="n">
         <v>1.29</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CN18" t="n">
         <v>1.69</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CQ18" t="n">
         <v>2.3</v>
@@ -8112,7 +8112,7 @@
         <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CT18" t="n">
         <v>3.27</v>
@@ -8121,10 +8121,10 @@
         <v>1.6</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CX18" t="n">
         <v>1.55</v>
@@ -8133,94 +8133,94 @@
         <v>1.85</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB18" t="n">
         <v>1.2</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="DH18" t="n">
-        <v>78.84</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DM18" t="n">
-        <v>36.36</v>
+        <v>36.04</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.44</v>
+        <v>12.54</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12.96</v>
+        <v>12.85</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.08</v>
+        <v>9.15</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.44</v>
+        <v>47.23</v>
       </c>
       <c r="DW18" t="n">
         <v>0.08</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.88</v>
+        <v>11.7</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.8</v>
+        <v>7.65</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.52</v>
+        <v>17.43</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="19">
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
         <v>14</v>
@@ -8242,82 +8242,82 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="H19" t="n">
-        <v>92</v>
+        <v>93.2</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="K19" t="n">
-        <v>5.79</v>
+        <v>5.67</v>
       </c>
       <c r="L19" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="M19" t="n">
-        <v>46.07</v>
+        <v>46.73</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="O19" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="P19" t="n">
-        <v>12.29</v>
+        <v>12</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.07</v>
+        <v>11.33</v>
       </c>
       <c r="R19" t="n">
-        <v>8.789999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="T19" t="n">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="U19" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V19" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>58.14</v>
+        <v>58.13</v>
       </c>
       <c r="Y19" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="Z19" t="n">
-        <v>20.07</v>
+        <v>19.53</v>
       </c>
       <c r="AA19" t="n">
-        <v>13.5</v>
+        <v>13.13</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.57</v>
+        <v>6.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.57</v>
+        <v>18.47</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AF19" t="n">
         <v>0.07000000000000001</v>
@@ -8401,70 +8401,70 @@
         <v>2.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.18</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="BJ19" t="n">
         <v>0.86</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.29</v>
+        <v>4.31</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="BR19" t="n">
-        <v>82.14</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="BS19" t="n">
-        <v>67.86</v>
+        <v>65.52</v>
       </c>
       <c r="BT19" t="n">
-        <v>53.57</v>
+        <v>51.72</v>
       </c>
       <c r="BU19" t="n">
-        <v>42.86</v>
+        <v>41.38</v>
       </c>
       <c r="BV19" t="n">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="BW19" t="n">
-        <v>14.29</v>
+        <v>13.79</v>
       </c>
       <c r="BX19" t="n">
-        <v>53.57</v>
+        <v>51.72</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.12</v>
+        <v>4.19</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.5</v>
+        <v>4.59</v>
       </c>
       <c r="CC19" t="n">
         <v>2.33</v>
@@ -8476,7 +8476,7 @@
         <v>1.27</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CG19" t="n">
         <v>3.46</v>
@@ -8485,16 +8485,16 @@
         <v>1.59</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK19" t="n">
         <v>1.49</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CM19" t="n">
         <v>2.41</v>
@@ -8506,7 +8506,7 @@
         <v>1.16</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CQ19" t="n">
         <v>2.47</v>
@@ -8515,19 +8515,19 @@
         <v>1.36</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CT19" t="n">
         <v>3.21</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX19" t="n">
         <v>1.55</v>
@@ -8545,82 +8545,82 @@
         <v>1.2</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="DE19" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DH19" t="n">
-        <v>83.45999999999999</v>
+        <v>84.38</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.54</v>
+        <v>5.49</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="DM19" t="n">
-        <v>40.82</v>
+        <v>41.34</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.14</v>
+        <v>12.97</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.07</v>
+        <v>12.17</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.720000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.46</v>
+        <v>55.55</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.54</v>
+        <v>17.34</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.75</v>
+        <v>11.62</v>
       </c>
       <c r="DZ19" t="n">
-        <v>5.79</v>
+        <v>5.72</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.1</v>
+        <v>19.03</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="EC19" t="n">
         <v>2.1</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
         <v>0.08</v>
@@ -1472,49 +1472,49 @@
         <v>0.08</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="AI2" t="n">
-        <v>101.75</v>
+        <v>101.15</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.08</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.25</v>
+        <v>5.08</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AN2" t="n">
-        <v>49.83</v>
+        <v>48.77</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.33</v>
+        <v>9.92</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.83</v>
+        <v>13.08</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.42</v>
+        <v>6.77</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AV2" t="n">
         <v>0.08</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>54</v>
+        <v>53.54</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.08</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.92</v>
+        <v>10.69</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.58</v>
+        <v>7.46</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.25</v>
+        <v>17.46</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="BF2" t="n">
         <v>2.08</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="BO2" t="n">
         <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.96</v>
+        <v>3.88</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.17</v>
+        <v>5.2</v>
       </c>
       <c r="BR2" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS2" t="n">
-        <v>79.17</v>
+        <v>76</v>
       </c>
       <c r="BT2" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV2" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY2" t="n">
         <v>1.45</v>
@@ -1610,25 +1610,25 @@
         <v>1.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.34</v>
+        <v>4.3</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="CE2" t="n">
         <v>1.27</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CH2" t="n">
         <v>1.44</v>
@@ -1640,25 +1640,25 @@
         <v>1.72</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CN2" t="n">
         <v>1.86</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="CR2" t="n">
         <v>1.4</v>
@@ -1673,7 +1673,7 @@
         <v>1.53</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CW2" t="n">
         <v>1.83</v>
@@ -1682,34 +1682,34 @@
         <v>1.54</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.97</v>
+        <v>3.01</v>
       </c>
       <c r="DE2" t="n">
         <v>0.08</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="DH2" t="n">
-        <v>100.92</v>
+        <v>100.64</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
@@ -1718,28 +1718,28 @@
         <v>2</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.21</v>
+        <v>6.08</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="DM2" t="n">
-        <v>54.71</v>
+        <v>53.96</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.79</v>
+        <v>10.56</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.29</v>
+        <v>12.44</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.42</v>
+        <v>6.6</v>
       </c>
       <c r="DS2" t="n">
         <v>0.16</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>55.29</v>
+        <v>55</v>
       </c>
       <c r="DW2" t="n">
         <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.96</v>
+        <v>13.72</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.08</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.88</v>
+        <v>4.76</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.79</v>
+        <v>18.84</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="3">
@@ -1878,7 +1878,7 @@
         <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AI3" t="n">
         <v>65.42</v>
@@ -1890,10 +1890,10 @@
         <v>2.42</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="AN3" t="n">
         <v>21.67</v>
@@ -1902,10 +1902,10 @@
         <v>1.08</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.75</v>
+        <v>9.5</v>
       </c>
       <c r="AR3" t="n">
         <v>12.5</v>
@@ -1935,19 +1935,19 @@
         <v>0.17</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.42</v>
+        <v>9.33</v>
       </c>
       <c r="BB3" t="n">
         <v>6.67</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="BD3" t="n">
-        <v>17</v>
+        <v>17.08</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF3" t="n">
         <v>2.17</v>
@@ -1956,7 +1956,7 @@
         <v>3.13</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.17</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="BI3" t="n">
         <v>3.13</v>
@@ -1980,10 +1980,10 @@
         <v>1.65</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.09</v>
+        <v>4.3</v>
       </c>
       <c r="BR3" t="n">
         <v>95.65000000000001</v>
@@ -2100,7 +2100,7 @@
         <v>1.85</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="DE3" t="n">
         <v>0.26</v>
@@ -2109,7 +2109,7 @@
         <v>1.65</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="DH3" t="n">
         <v>70.44</v>
@@ -2121,10 +2121,10 @@
         <v>2.48</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="DM3" t="n">
         <v>28.48</v>
@@ -2133,10 +2133,10 @@
         <v>0.74</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.57</v>
+        <v>11.44</v>
       </c>
       <c r="DQ3" t="n">
         <v>13.05</v>
@@ -2160,16 +2160,16 @@
         <v>0.17</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.26</v>
+        <v>10.21</v>
       </c>
       <c r="DY3" t="n">
         <v>6.91</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.56</v>
+        <v>16.61</v>
       </c>
       <c r="EB3" t="n">
         <v>1.09</v>
@@ -2200,7 +2200,7 @@
         <v>0.64</v>
       </c>
       <c r="G4" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="H4" t="n">
         <v>68.18000000000001</v>
@@ -2212,10 +2212,10 @@
         <v>1.73</v>
       </c>
       <c r="K4" t="n">
-        <v>4.45</v>
+        <v>4.36</v>
       </c>
       <c r="L4" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="M4" t="n">
         <v>24.91</v>
@@ -2224,10 +2224,10 @@
         <v>0.91</v>
       </c>
       <c r="O4" t="n">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="P4" t="n">
-        <v>10.55</v>
+        <v>10.27</v>
       </c>
       <c r="Q4" t="n">
         <v>12</v>
@@ -2359,7 +2359,7 @@
         <v>3.22</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.390000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="BI4" t="n">
         <v>3.22</v>
@@ -2383,10 +2383,10 @@
         <v>1.04</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.74</v>
+        <v>3.96</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.22</v>
+        <v>4.39</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2419,7 +2419,7 @@
         <v>3.66</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="CC4" t="n">
         <v>4.04</v>
@@ -2503,7 +2503,7 @@
         <v>1.78</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="DE4" t="n">
         <v>0.09</v>
@@ -2512,7 +2512,7 @@
         <v>0.92</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="DH4" t="n">
         <v>73.91</v>
@@ -2524,10 +2524,10 @@
         <v>1.96</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.56</v>
+        <v>4.52</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DM4" t="n">
         <v>32.39</v>
@@ -2536,10 +2536,10 @@
         <v>0.92</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.09</v>
+        <v>2.26</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.26</v>
+        <v>11.13</v>
       </c>
       <c r="DQ4" t="n">
         <v>12.43</v>
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
         <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F5" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.08</v>
+        <v>3.79</v>
       </c>
       <c r="H5" t="n">
-        <v>107.38</v>
+        <v>105.5</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="K5" t="n">
-        <v>7.15</v>
+        <v>6.79</v>
       </c>
       <c r="L5" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="M5" t="n">
-        <v>59.31</v>
+        <v>57.57</v>
       </c>
       <c r="N5" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="P5" t="n">
-        <v>11.69</v>
+        <v>12.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.46</v>
+        <v>10.57</v>
       </c>
       <c r="R5" t="n">
-        <v>7.15</v>
+        <v>7.29</v>
       </c>
       <c r="S5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>59.92</v>
+        <v>58.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.92</v>
+        <v>19.79</v>
       </c>
       <c r="AA5" t="n">
-        <v>13</v>
+        <v>12.93</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.92</v>
+        <v>6.86</v>
       </c>
       <c r="AC5" t="n">
-        <v>22.15</v>
+        <v>21.79</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AF5" t="n">
         <v>0.23</v>
@@ -2759,70 +2759,70 @@
         <v>1.54</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.539999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.38</v>
+        <v>5.26</v>
       </c>
       <c r="BR5" t="n">
-        <v>92.31</v>
+        <v>92.59</v>
       </c>
       <c r="BS5" t="n">
-        <v>80.77</v>
+        <v>81.48</v>
       </c>
       <c r="BT5" t="n">
-        <v>50</v>
+        <v>51.85</v>
       </c>
       <c r="BU5" t="n">
-        <v>30.77</v>
+        <v>29.63</v>
       </c>
       <c r="BV5" t="n">
-        <v>26.92</v>
+        <v>25.93</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BX5" t="n">
-        <v>65.38</v>
+        <v>66.67</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="CC5" t="n">
         <v>2.43</v>
@@ -2834,16 +2834,16 @@
         <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CH5" t="n">
         <v>1.5</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.72</v>
@@ -2867,28 +2867,28 @@
         <v>1.73</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CR5" t="n">
         <v>1.37</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CT5" t="n">
         <v>3.2</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV5" t="n">
         <v>2.2</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY5" t="n">
         <v>1.86</v>
@@ -2906,82 +2906,82 @@
         <v>1.78</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="DE5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>101.56</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>48.52</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="DS5" t="n">
         <v>0.19</v>
       </c>
-      <c r="DF5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>102.35</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DJ5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="DK5" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>49.04</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="DP5" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="DQ5" t="n">
-        <v>12.31</v>
-      </c>
-      <c r="DR5" t="n">
-        <v>7.69</v>
-      </c>
-      <c r="DS5" t="n">
-        <v>0.2</v>
-      </c>
       <c r="DT5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.34</v>
+        <v>55.74</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX5" t="n">
-        <v>17.23</v>
+        <v>17.26</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.23</v>
+        <v>11.26</v>
       </c>
       <c r="DZ5" t="n">
         <v>6</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.04</v>
+        <v>21.85</v>
       </c>
       <c r="EB5" t="n">
         <v>1.86</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="6">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="H6" t="n">
-        <v>77.92</v>
+        <v>79.38</v>
       </c>
       <c r="I6" t="n">
         <v>0.08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="K6" t="n">
-        <v>5.75</v>
+        <v>5.69</v>
       </c>
       <c r="L6" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="M6" t="n">
-        <v>34.5</v>
+        <v>34.77</v>
       </c>
       <c r="N6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="P6" t="n">
-        <v>10.92</v>
+        <v>11.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.75</v>
+        <v>11.23</v>
       </c>
       <c r="R6" t="n">
-        <v>8.67</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="T6" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="U6" t="n">
         <v>0.08</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>54.67</v>
+        <v>54.46</v>
       </c>
       <c r="Y6" t="n">
         <v>0.08</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.67</v>
+        <v>14.77</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.58</v>
+        <v>9.77</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="AC6" t="n">
-        <v>15.92</v>
+        <v>15.69</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AF6" t="n">
         <v>0.17</v>
@@ -3162,70 +3162,70 @@
         <v>1.75</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.119999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.88</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.38</v>
+        <v>4.28</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.54</v>
+        <v>4.6</v>
       </c>
       <c r="BR6" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS6" t="n">
-        <v>70.83</v>
+        <v>68</v>
       </c>
       <c r="BT6" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BU6" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BV6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX6" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="CC6" t="n">
         <v>2.35</v>
@@ -3234,13 +3234,13 @@
         <v>2.42</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CH6" t="n">
         <v>1.39</v>
@@ -3252,25 +3252,25 @@
         <v>1.69</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO6" t="n">
         <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
@@ -3285,73 +3285,73 @@
         <v>1.48</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.12</v>
+        <v>88.48</v>
       </c>
       <c r="DI6" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.58</v>
+        <v>5.56</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.75</v>
+        <v>40.64</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.34</v>
+        <v>11.48</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.75</v>
+        <v>10.52</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.92</v>
+        <v>7.8</v>
       </c>
       <c r="DS6" t="n">
         <v>0.08</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.34</v>
+        <v>54.24</v>
       </c>
       <c r="DW6" t="n">
         <v>0.12</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.62</v>
+        <v>14.68</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.04</v>
+        <v>10.12</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.58</v>
+        <v>4.56</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.5</v>
+        <v>17.32</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3691,16 +3691,16 @@
         <v>2.07</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX7" t="n">
         <v>1.58</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DA7" t="n">
         <v>1.83</v>
@@ -3911,7 +3911,7 @@
         <v>0.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>30.58</v>
+        <v>30.67</v>
       </c>
       <c r="AO8" t="n">
         <v>0.83</v>
@@ -4142,7 +4142,7 @@
         <v>0.39</v>
       </c>
       <c r="DM8" t="n">
-        <v>30.87</v>
+        <v>30.91</v>
       </c>
       <c r="DN8" t="n">
         <v>0.65</v>
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0.17</v>
@@ -4293,49 +4293,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AI9" t="n">
-        <v>75.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AN9" t="n">
-        <v>35.9</v>
+        <v>33.73</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.5</v>
+        <v>11.82</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.7</v>
+        <v>13.18</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.9</v>
+        <v>11.27</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>44</v>
+        <v>44.18</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.4</v>
+        <v>5.64</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="BD9" t="n">
-        <v>18.8</v>
+        <v>18.55</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.359999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.73</v>
+        <v>4.78</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS9" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU9" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV9" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX9" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BY9" t="n">
         <v>3.42</v>
@@ -4431,16 +4431,16 @@
         <v>3.82</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.87</v>
+        <v>5.68</v>
       </c>
       <c r="CD9" t="n">
-        <v>7.46</v>
+        <v>7.17</v>
       </c>
       <c r="CE9" t="n">
         <v>1.32</v>
@@ -4455,10 +4455,10 @@
         <v>1.48</v>
       </c>
       <c r="CI9" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK9" t="n">
         <v>1.45</v>
@@ -4467,7 +4467,7 @@
         <v>1.88</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CN9" t="n">
         <v>1.96</v>
@@ -4479,7 +4479,7 @@
         <v>1.81</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CR9" t="n">
         <v>1.39</v>
@@ -4494,10 +4494,10 @@
         <v>1.53</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX9" t="n">
         <v>1.53</v>
@@ -4509,58 +4509,58 @@
         <v>2.41</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DB9" t="n">
         <v>1.26</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="DE9" t="n">
         <v>0.09</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="DH9" t="n">
-        <v>77.41</v>
+        <v>77.05</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.64</v>
+        <v>3.79</v>
       </c>
       <c r="DL9" t="n">
         <v>0.13</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.64</v>
+        <v>34.61</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.27</v>
+        <v>11.43</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.64</v>
+        <v>12.43</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.359999999999999</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0.09</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>42.91</v>
+        <v>43.04</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX9" t="n">
-        <v>9</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.86</v>
+        <v>5.96</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.14</v>
+        <v>3.26</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.96</v>
+        <v>16.92</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="10">
@@ -4636,7 +4636,7 @@
         <v>0.31</v>
       </c>
       <c r="M10" t="n">
-        <v>42.77</v>
+        <v>42.85</v>
       </c>
       <c r="N10" t="n">
         <v>0.46</v>
@@ -4897,7 +4897,7 @@
         <v>1.57</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CW10" t="n">
         <v>1.69</v>
@@ -4912,7 +4912,7 @@
         <v>2.43</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DB10" t="n">
         <v>1.22</v>
@@ -4948,7 +4948,7 @@
         <v>0.37</v>
       </c>
       <c r="DM10" t="n">
-        <v>35.48</v>
+        <v>35.52</v>
       </c>
       <c r="DN10" t="n">
         <v>0.52</v>
@@ -5246,7 +5246,7 @@
         <v>3.73</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="CE11" t="n">
         <v>1.3</v>
@@ -5291,13 +5291,13 @@
         <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV11" t="n">
         <v>2.33</v>
@@ -5309,13 +5309,13 @@
         <v>1.49</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.49</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DB11" t="n">
         <v>1.23</v>
@@ -5424,7 +5424,7 @@
         <v>1.46</v>
       </c>
       <c r="G12" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="H12" t="n">
         <v>88.23</v>
@@ -5439,7 +5439,7 @@
         <v>5.08</v>
       </c>
       <c r="L12" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="M12" t="n">
         <v>37.85</v>
@@ -5448,13 +5448,13 @@
         <v>1.38</v>
       </c>
       <c r="O12" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="P12" t="n">
-        <v>12.31</v>
+        <v>11.85</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.31</v>
+        <v>11.46</v>
       </c>
       <c r="R12" t="n">
         <v>7.77</v>
@@ -5583,7 +5583,7 @@
         <v>2.4</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI12" t="n">
         <v>2.4</v>
@@ -5607,10 +5607,10 @@
         <v>1.44</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BR12" t="n">
         <v>92</v>
@@ -5703,7 +5703,7 @@
         <v>1.5</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CW12" t="n">
         <v>1.75</v>
@@ -5736,7 +5736,7 @@
         <v>1.92</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="DH12" t="n">
         <v>83.04000000000001</v>
@@ -5751,7 +5751,7 @@
         <v>4.36</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DM12" t="n">
         <v>36.08</v>
@@ -5760,13 +5760,13 @@
         <v>0.84</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.92</v>
+        <v>11.68</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.92</v>
+        <v>12</v>
       </c>
       <c r="DR12" t="n">
         <v>8.960000000000001</v>
@@ -6371,10 +6371,10 @@
         <v>10.31</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.77</v>
+        <v>6.85</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.54</v>
+        <v>3.46</v>
       </c>
       <c r="BD14" t="n">
         <v>17.38</v>
@@ -6596,10 +6596,10 @@
         <v>11.63</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.96</v>
+        <v>8</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="EA14" t="n">
         <v>18.46</v>
@@ -6711,10 +6711,10 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AI15" t="n">
         <v>54.58</v>
@@ -6723,13 +6723,13 @@
         <v>0.17</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="AL15" t="n">
         <v>3.33</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="AN15" t="n">
         <v>22.08</v>
@@ -6738,10 +6738,10 @@
         <v>1.42</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.58</v>
+        <v>10.08</v>
       </c>
       <c r="AR15" t="n">
         <v>12.33</v>
@@ -6768,22 +6768,22 @@
         <v>33.08</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.33</v>
+        <v>9.25</v>
       </c>
       <c r="BB15" t="n">
         <v>5.75</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="BD15" t="n">
         <v>16.25</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="BF15" t="n">
         <v>2.08</v>
@@ -6792,7 +6792,7 @@
         <v>2.65</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.300000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="BI15" t="n">
         <v>2.65</v>
@@ -6816,10 +6816,10 @@
         <v>1.26</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.35</v>
+        <v>4.57</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.48</v>
+        <v>4.65</v>
       </c>
       <c r="BR15" t="n">
         <v>95.65000000000001</v>
@@ -6858,7 +6858,7 @@
         <v>7.07</v>
       </c>
       <c r="CD15" t="n">
-        <v>7.51</v>
+        <v>7.49</v>
       </c>
       <c r="CE15" t="n">
         <v>1.3</v>
@@ -6924,7 +6924,7 @@
         <v>1.8</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="DA15" t="n">
         <v>2.01</v>
@@ -6942,10 +6942,10 @@
         <v>0.04</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="DH15" t="n">
         <v>66.17</v>
@@ -6954,13 +6954,13 @@
         <v>0.13</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="DK15" t="n">
         <v>3.17</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DM15" t="n">
         <v>24.74</v>
@@ -6969,10 +6969,10 @@
         <v>1.26</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.17</v>
+        <v>11.91</v>
       </c>
       <c r="DQ15" t="n">
         <v>12.13</v>
@@ -6993,22 +6993,22 @@
         <v>37.13</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.17</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="DY15" t="n">
         <v>5.7</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.47</v>
+        <v>3.43</v>
       </c>
       <c r="EA15" t="n">
         <v>17.35</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="EC15" t="n">
         <v>2.48</v>
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
@@ -7033,82 +7033,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="H16" t="n">
-        <v>65.91</v>
+        <v>67.17</v>
       </c>
       <c r="I16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J16" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="K16" t="n">
-        <v>4.27</v>
+        <v>4.17</v>
       </c>
       <c r="L16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M16" t="n">
-        <v>35.82</v>
+        <v>33.83</v>
       </c>
       <c r="N16" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="O16" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="P16" t="n">
-        <v>13.45</v>
+        <v>13</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.36</v>
+        <v>14.33</v>
       </c>
       <c r="R16" t="n">
-        <v>10.18</v>
+        <v>9.92</v>
       </c>
       <c r="S16" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T16" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="V16" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>42.55</v>
+        <v>43.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.18</v>
+        <v>12.58</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.36</v>
+        <v>7.92</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.82</v>
+        <v>4.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>18.45</v>
+        <v>19.42</v>
       </c>
       <c r="AD16" t="n">
         <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AF16" t="n">
         <v>0.09</v>
@@ -7192,70 +7192,70 @@
         <v>2.91</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.36</v>
+        <v>10.35</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL16" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.86</v>
+        <v>5.87</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT16" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BU16" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BV16" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW16" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX16" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.62</v>
+        <v>3.47</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.26</v>
+        <v>4.23</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.71</v>
+        <v>4.68</v>
       </c>
       <c r="CC16" t="n">
         <v>6.88</v>
@@ -7267,13 +7267,13 @@
         <v>1.27</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI16" t="n">
         <v>2.19</v>
@@ -7300,13 +7300,13 @@
         <v>1.62</v>
       </c>
       <c r="CQ16" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CS16" t="n">
         <v>2.47</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CS16" t="n">
-        <v>2.46</v>
       </c>
       <c r="CT16" t="n">
         <v>3.21</v>
@@ -7336,85 +7336,85 @@
         <v>1.2</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DE16" t="n">
         <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="DH16" t="n">
-        <v>72.36</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="DI16" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.22</v>
+        <v>3.09</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM16" t="n">
-        <v>33.64</v>
+        <v>32.69</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.68</v>
+        <v>11.52</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.86</v>
+        <v>13.87</v>
       </c>
       <c r="DR16" t="n">
-        <v>11.32</v>
+        <v>11.13</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>42.91</v>
+        <v>43.39</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.5</v>
+        <v>10.78</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.41</v>
+        <v>6.74</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.09</v>
+        <v>4.04</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.18</v>
+        <v>17.74</v>
       </c>
       <c r="EB16" t="n">
         <v>1.2</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
         <v>0.2</v>
@@ -7517,49 +7517,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>92.15000000000001</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK17" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.08</v>
+        <v>4.93</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AN17" t="n">
-        <v>41.85</v>
+        <v>40</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12</v>
+        <v>11.71</v>
       </c>
       <c r="AR17" t="n">
-        <v>12.31</v>
+        <v>12.86</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.460000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>53</v>
+        <v>53.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BA17" t="n">
-        <v>14.08</v>
+        <v>13.71</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.69</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.38</v>
+        <v>5.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>17.85</v>
+        <v>18.29</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="BG17" t="n">
         <v>2.86</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.539999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI17" t="n">
         <v>2.86</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.21</v>
+        <v>4.17</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="BR17" t="n">
-        <v>89.29000000000001</v>
+        <v>89.66</v>
       </c>
       <c r="BS17" t="n">
-        <v>75</v>
+        <v>75.86</v>
       </c>
       <c r="BT17" t="n">
-        <v>46.43</v>
+        <v>48.28</v>
       </c>
       <c r="BU17" t="n">
-        <v>28.57</v>
+        <v>27.59</v>
       </c>
       <c r="BV17" t="n">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="BW17" t="n">
-        <v>14.29</v>
+        <v>13.79</v>
       </c>
       <c r="BX17" t="n">
-        <v>53.57</v>
+        <v>55.17</v>
       </c>
       <c r="BY17" t="n">
         <v>1.64</v>
@@ -7655,25 +7655,25 @@
         <v>1.65</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.15</v>
+        <v>4.12</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="CE17" t="n">
         <v>1.28</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CG17" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CH17" t="n">
         <v>1.43</v>
@@ -7700,28 +7700,28 @@
         <v>1.19</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CR17" t="n">
         <v>1.38</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CT17" t="n">
         <v>3.14</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV17" t="n">
         <v>2.12</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX17" t="n">
         <v>1.52</v>
@@ -7733,7 +7733,7 @@
         <v>2.43</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB17" t="n">
         <v>1.25</v>
@@ -7742,82 +7742,82 @@
         <v>1.81</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.95999999999999</v>
+        <v>92.66</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.68</v>
+        <v>5.59</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DM17" t="n">
-        <v>48.04</v>
+        <v>46.93</v>
       </c>
       <c r="DN17" t="n">
         <v>0.93</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.79</v>
+        <v>11.65</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.18</v>
+        <v>13.41</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.25</v>
+        <v>7.45</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.46</v>
+        <v>54.65</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.97</v>
+        <v>15.72</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.29</v>
+        <v>10</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.67</v>
+        <v>5.72</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.57</v>
+        <v>18.76</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58.5</v>
+        <v>58.57</v>
       </c>
       <c r="Y5" t="n">
         <v>0.14</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.74</v>
+        <v>55.78</v>
       </c>
       <c r="DW5" t="n">
         <v>0.22</v>
@@ -4347,25 +4347,25 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>44.18</v>
+        <v>44.09</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.09</v>
       </c>
       <c r="BA9" t="n">
-        <v>9</v>
+        <v>9.09</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.64</v>
+        <v>5.73</v>
       </c>
       <c r="BC9" t="n">
         <v>3.36</v>
       </c>
       <c r="BD9" t="n">
-        <v>18.55</v>
+        <v>18.64</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BF9" t="n">
         <v>2.36</v>
@@ -4572,25 +4572,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.04</v>
+        <v>43</v>
       </c>
       <c r="DW9" t="n">
         <v>0.13</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.220000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.96</v>
+        <v>6</v>
       </c>
       <c r="DZ9" t="n">
         <v>3.26</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.92</v>
+        <v>16.96</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="EC9" t="n">
         <v>2.61</v>
@@ -4648,7 +4648,7 @@
         <v>11.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.92</v>
+        <v>13</v>
       </c>
       <c r="R10" t="n">
         <v>6.15</v>
@@ -4675,10 +4675,10 @@
         <v>0.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.31</v>
+        <v>14.38</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.85</v>
+        <v>8.92</v>
       </c>
       <c r="AB10" t="n">
         <v>5.46</v>
@@ -4960,7 +4960,7 @@
         <v>10.71</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.11</v>
+        <v>13.15</v>
       </c>
       <c r="DR10" t="n">
         <v>7.18</v>
@@ -4981,10 +4981,10 @@
         <v>0.14</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.56</v>
+        <v>13.59</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.220000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="DZ10" t="n">
         <v>5.33</v>
@@ -7087,7 +7087,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>43.5</v>
+        <v>43.58</v>
       </c>
       <c r="Y16" t="n">
         <v>0.42</v>
@@ -7102,7 +7102,7 @@
         <v>4.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.42</v>
+        <v>19.33</v>
       </c>
       <c r="AD16" t="n">
         <v>1.36</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.39</v>
+        <v>43.43</v>
       </c>
       <c r="DW16" t="n">
         <v>0.31</v>
@@ -7408,7 +7408,7 @@
         <v>4.04</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.74</v>
+        <v>17.69</v>
       </c>
       <c r="EB16" t="n">
         <v>1.2</v>
@@ -7571,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>53.5</v>
+        <v>53.43</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.21</v>
@@ -7796,7 +7796,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.65</v>
+        <v>54.62</v>
       </c>
       <c r="DW17" t="n">
         <v>0.17</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
         <v>0.08</v>
@@ -1469,139 +1469,139 @@
         <v>1.58</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BN2" t="n">
         <v>1.54</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>101.15</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>48.77</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>9.92</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>53.54</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>10.69</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7.46</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>17.46</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1.48</v>
       </c>
       <c r="BO2" t="n">
         <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="BR2" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS2" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BT2" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BU2" t="n">
-        <v>24</v>
+        <v>26.92</v>
       </c>
       <c r="BV2" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BW2" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX2" t="n">
-        <v>48</v>
+        <v>46.15</v>
       </c>
       <c r="BY2" t="n">
         <v>1.45</v>
@@ -1610,40 +1610,40 @@
         <v>1.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM2" t="n">
         <v>2.39</v>
@@ -1655,31 +1655,31 @@
         <v>1.19</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="CR2" t="n">
         <v>1.4</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY2" t="n">
         <v>1.86</v>
@@ -1694,85 +1694,85 @@
         <v>1.26</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="DH2" t="n">
-        <v>100.64</v>
+        <v>101.38</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.08</v>
+        <v>6.11</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM2" t="n">
-        <v>53.96</v>
+        <v>54.23</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.56</v>
+        <v>10.58</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.44</v>
+        <v>12.46</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.6</v>
+        <v>6.66</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>55</v>
+        <v>55.46</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.72</v>
+        <v>13.96</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.960000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.76</v>
+        <v>4.85</v>
       </c>
       <c r="EA2" t="n">
         <v>18.84</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="F3" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="H3" t="n">
-        <v>75.91</v>
+        <v>77.33</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="K3" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="M3" t="n">
-        <v>35.91</v>
+        <v>35.75</v>
       </c>
       <c r="N3" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="P3" t="n">
-        <v>13.55</v>
+        <v>13.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.64</v>
+        <v>13.75</v>
       </c>
       <c r="R3" t="n">
-        <v>9.550000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="S3" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="T3" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="V3" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>43.45</v>
+        <v>45.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.18</v>
+        <v>11.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.18</v>
+        <v>7.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.09</v>
+        <v>16.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AF3" t="n">
         <v>0.08</v>
@@ -1953,70 +1953,70 @@
         <v>2.17</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.13</v>
+        <v>3.21</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.130000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.13</v>
+        <v>3.21</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="BP3" t="n">
         <v>4.04</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.3</v>
+        <v>4.12</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS3" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT3" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BU3" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BV3" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BW3" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.39</v>
+        <v>3.31</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="CC3" t="n">
         <v>4.66</v>
@@ -2025,13 +2025,13 @@
         <v>5.23</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CH3" t="n">
         <v>1.47</v>
@@ -2049,31 +2049,31 @@
         <v>1.83</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CN3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CO3" t="n">
         <v>1.23</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="CR3" t="n">
         <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV3" t="n">
         <v>2.16</v>
@@ -2082,100 +2082,100 @@
         <v>1.76</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DA3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB3" t="n">
         <v>1.27</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="DH3" t="n">
-        <v>70.44</v>
+        <v>71.38</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="DL3" t="n">
         <v>0.05</v>
       </c>
       <c r="DM3" t="n">
-        <v>28.48</v>
+        <v>28.71</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.44</v>
+        <v>11.66</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.05</v>
+        <v>13.12</v>
       </c>
       <c r="DR3" t="n">
-        <v>10.18</v>
+        <v>10.08</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.48</v>
+        <v>45.29</v>
       </c>
       <c r="DW3" t="n">
         <v>0.17</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.21</v>
+        <v>10.54</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.91</v>
+        <v>7.12</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.31</v>
+        <v>3.42</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.61</v>
+        <v>16.66</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,139 +2275,139 @@
         <v>1.36</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AG4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>77.08</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM4" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>79.17</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>39.25</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>12.83</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>8.83</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>48.08</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>17.83</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.22</v>
       </c>
       <c r="BN4" t="n">
         <v>2.17</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BP4" t="n">
         <v>3.96</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.39</v>
+        <v>4.21</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT4" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>34.78</v>
+        <v>37.5</v>
       </c>
       <c r="BV4" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX4" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BY4" t="n">
         <v>3.13</v>
@@ -2416,25 +2416,25 @@
         <v>3.34</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.49</v>
+        <v>4.39</v>
       </c>
       <c r="CE4" t="n">
         <v>1.26</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CH4" t="n">
         <v>1.42</v>
@@ -2443,7 +2443,7 @@
         <v>2.05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CK4" t="n">
         <v>1.39</v>
@@ -2458,127 +2458,127 @@
         <v>1.87</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="CR4" t="n">
         <v>1.37</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB4" t="n">
         <v>1.24</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="DH4" t="n">
-        <v>73.91</v>
+        <v>73</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.52</v>
+        <v>4.33</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM4" t="n">
-        <v>32.39</v>
+        <v>32.46</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.13</v>
+        <v>11.38</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.43</v>
+        <v>12.62</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.74</v>
+        <v>8.84</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.74</v>
+        <v>47.25</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.74</v>
+        <v>10.67</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.91</v>
+        <v>6.87</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.3</v>
+        <v>20.54</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="5">
@@ -2588,55 +2588,55 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
         <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="H5" t="n">
-        <v>105.5</v>
+        <v>104.47</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>2.57</v>
+        <v>2.87</v>
       </c>
       <c r="K5" t="n">
-        <v>6.79</v>
+        <v>6.47</v>
       </c>
       <c r="L5" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="M5" t="n">
-        <v>57.57</v>
+        <v>55.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.93</v>
+        <v>1.13</v>
       </c>
       <c r="O5" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="P5" t="n">
-        <v>12.29</v>
+        <v>12.27</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.57</v>
+        <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>7.29</v>
+        <v>7.6</v>
       </c>
       <c r="S5" t="n">
         <v>1.07</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58.57</v>
+        <v>57.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.79</v>
+        <v>19.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.93</v>
+        <v>12.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.86</v>
+        <v>6.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.79</v>
+        <v>22.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.29</v>
+        <v>2.6</v>
       </c>
       <c r="AF5" t="n">
         <v>0.23</v>
@@ -2762,67 +2762,67 @@
         <v>2.93</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.369999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="BI5" t="n">
         <v>2.93</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.26</v>
+        <v>5.14</v>
       </c>
       <c r="BR5" t="n">
-        <v>92.59</v>
+        <v>92.86</v>
       </c>
       <c r="BS5" t="n">
-        <v>81.48</v>
+        <v>82.14</v>
       </c>
       <c r="BT5" t="n">
-        <v>51.85</v>
+        <v>53.57</v>
       </c>
       <c r="BU5" t="n">
-        <v>29.63</v>
+        <v>28.57</v>
       </c>
       <c r="BV5" t="n">
-        <v>25.93</v>
+        <v>25</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="BX5" t="n">
-        <v>66.67</v>
+        <v>67.86</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="CC5" t="n">
         <v>2.43</v>
@@ -2831,19 +2831,19 @@
         <v>2.61</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF5" t="n">
         <v>2.51</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.72</v>
@@ -2855,25 +2855,25 @@
         <v>1.93</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CR5" t="n">
         <v>1.37</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CT5" t="n">
         <v>3.2</v>
@@ -2888,16 +2888,16 @@
         <v>1.74</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB5" t="n">
         <v>1.24</v>
@@ -2912,76 +2912,76 @@
         <v>0.18</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="DG5" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="DH5" t="n">
-        <v>101.56</v>
+        <v>101.15</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.63</v>
+        <v>5.5</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="DM5" t="n">
-        <v>48.52</v>
+        <v>47.79</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.08</v>
+        <v>11.11</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.29</v>
+        <v>12.46</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.74</v>
+        <v>7.89</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.78</v>
+        <v>55.14</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX5" t="n">
-        <v>17.26</v>
+        <v>17.04</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.26</v>
+        <v>11.14</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.85</v>
+        <v>22.07</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
         <v>0.15</v>
@@ -3081,52 +3081,52 @@
         <v>2.23</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AI6" t="n">
-        <v>98.33</v>
+        <v>97.38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.42</v>
+        <v>5.15</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AN6" t="n">
-        <v>47</v>
+        <v>46.69</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.75</v>
+        <v>12.08</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.75</v>
+        <v>10.15</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.17</v>
+        <v>7.08</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AV6" t="n">
         <v>0.08</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>54</v>
+        <v>54.62</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA6" t="n">
-        <v>14.58</v>
+        <v>14.38</v>
       </c>
       <c r="BB6" t="n">
-        <v>10.5</v>
+        <v>10.38</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.08</v>
+        <v>19.92</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.08</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.88</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.28</v>
+        <v>4.19</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS6" t="n">
-        <v>68</v>
+        <v>69.23</v>
       </c>
       <c r="BT6" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BU6" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="BV6" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BW6" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BX6" t="n">
-        <v>52</v>
+        <v>53.85</v>
       </c>
       <c r="BY6" t="n">
         <v>1.96</v>
@@ -3222,16 +3222,16 @@
         <v>2.02</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CB6" t="n">
         <v>3.85</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="CE6" t="n">
         <v>1.3</v>
@@ -3255,22 +3255,22 @@
         <v>1.39</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN6" t="n">
         <v>1.92</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP6" t="n">
         <v>1.82</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
@@ -3279,7 +3279,7 @@
         <v>2.77</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CU6" t="n">
         <v>1.48</v>
@@ -3291,19 +3291,19 @@
         <v>1.79</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC6" t="n">
         <v>1.89</v>
@@ -3312,46 +3312,46 @@
         <v>3.14</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.48</v>
+        <v>88.38</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.56</v>
+        <v>5.42</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.64</v>
+        <v>40.73</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.48</v>
+        <v>11.66</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.52</v>
+        <v>10.69</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.8</v>
+        <v>7.73</v>
       </c>
       <c r="DS6" t="n">
         <v>0.08</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.24</v>
+        <v>54.54</v>
       </c>
       <c r="DW6" t="n">
         <v>0.12</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.68</v>
+        <v>14.58</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.12</v>
+        <v>10.07</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.32</v>
+        <v>17.81</v>
       </c>
       <c r="EB6" t="n">
         <v>1.41</v>
       </c>
       <c r="EC6" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="7">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>70.09</v>
+        <v>71.42</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="K8" t="n">
-        <v>4.82</v>
+        <v>4.58</v>
       </c>
       <c r="L8" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M8" t="n">
-        <v>31.18</v>
+        <v>30.58</v>
       </c>
       <c r="N8" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="O8" t="n">
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>11.64</v>
+        <v>11.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.36</v>
+        <v>12.67</v>
       </c>
       <c r="R8" t="n">
-        <v>8.91</v>
+        <v>8.83</v>
       </c>
       <c r="S8" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="U8" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="V8" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>50.73</v>
+        <v>50.42</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.27</v>
+        <v>12</v>
       </c>
       <c r="AA8" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>17.82</v>
+        <v>18.08</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="AF8" t="n">
         <v>0.08</v>
@@ -3968,70 +3968,70 @@
         <v>2.17</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.91</v>
+        <v>9.83</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.74</v>
+        <v>4.67</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS8" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT8" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BU8" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV8" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX8" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="CC8" t="n">
         <v>4.32</v>
@@ -4043,10 +4043,10 @@
         <v>1.31</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CH8" t="n">
         <v>1.51</v>
@@ -4073,25 +4073,25 @@
         <v>1.21</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CT8" t="n">
         <v>3.24</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CW8" t="n">
         <v>1.69</v>
@@ -4100,97 +4100,97 @@
         <v>1.51</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.45</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DB8" t="n">
         <v>1.23</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="DH8" t="n">
-        <v>73</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.78</v>
+        <v>4.66</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM8" t="n">
-        <v>30.91</v>
+        <v>30.62</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.35</v>
+        <v>11.5</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.65</v>
+        <v>12.8</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.57</v>
+        <v>9.5</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.09</v>
+        <v>50.92</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.04</v>
+        <v>11.92</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.09</v>
+        <v>7.96</v>
       </c>
       <c r="DZ8" t="n">
         <v>3.96</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.13</v>
+        <v>18.25</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>0.17</v>
@@ -4293,49 +4293,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AI9" t="n">
-        <v>75</v>
+        <v>74.92</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AN9" t="n">
-        <v>33.73</v>
+        <v>33.17</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.82</v>
+        <v>12</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.18</v>
+        <v>13.17</v>
       </c>
       <c r="AS9" t="n">
-        <v>11.27</v>
+        <v>10.67</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>44.09</v>
+        <v>44</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.09</v>
+        <v>9.33</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.73</v>
+        <v>6</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="BD9" t="n">
-        <v>18.64</v>
+        <v>18.67</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.390000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BJ9" t="n">
         <v>0.96</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BP9" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>95.83</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>79.17</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BW9" t="n">
         <v>4.17</v>
       </c>
-      <c r="BQ9" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>95.65000000000001</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>78.26000000000001</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>65.22</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>39.13</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>13.04</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>4.35</v>
-      </c>
       <c r="BX9" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BY9" t="n">
         <v>3.42</v>
@@ -4431,22 +4431,22 @@
         <v>3.82</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.89</v>
+        <v>3.92</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.21</v>
+        <v>4.22</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.68</v>
+        <v>5.71</v>
       </c>
       <c r="CD9" t="n">
-        <v>7.17</v>
+        <v>7.1</v>
       </c>
       <c r="CE9" t="n">
         <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CG9" t="n">
         <v>3.14</v>
@@ -4455,7 +4455,7 @@
         <v>1.48</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.77</v>
@@ -4464,7 +4464,7 @@
         <v>1.45</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM9" t="n">
         <v>2.52</v>
@@ -4473,19 +4473,19 @@
         <v>1.96</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CR9" t="n">
         <v>1.39</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CT9" t="n">
         <v>3.14</v>
@@ -4500,13 +4500,13 @@
         <v>1.78</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY9" t="n">
         <v>1.84</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DA9" t="n">
         <v>1.97</v>
@@ -4518,55 +4518,55 @@
         <v>1.83</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="DH9" t="n">
-        <v>77.05</v>
+        <v>76.92</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.61</v>
+        <v>34.3</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.43</v>
+        <v>11.54</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.43</v>
+        <v>12.46</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.609999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
@@ -4575,25 +4575,25 @@
         <v>43</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.26</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.96</v>
+        <v>17.05</v>
       </c>
       <c r="EB9" t="n">
         <v>1.04</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
         <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
         <v>0.08</v>
@@ -4693,139 +4693,139 @@
         <v>1.69</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AI10" t="n">
-        <v>64.79000000000001</v>
+        <v>69.13</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.86</v>
+        <v>4.13</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AN10" t="n">
-        <v>28.71</v>
+        <v>30.4</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.36</v>
+        <v>10.07</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.29</v>
+        <v>13.07</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.140000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT10" t="n">
         <v>1.93</v>
       </c>
       <c r="AU10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>55.27</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BO10" t="n">
         <v>1.79</v>
       </c>
-      <c r="AV10" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>54.64</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>12.86</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>8.93</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1.78</v>
-      </c>
       <c r="BP10" t="n">
-        <v>4.37</v>
+        <v>4.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>74.06999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT10" t="n">
-        <v>55.56</v>
+        <v>53.57</v>
       </c>
       <c r="BU10" t="n">
-        <v>44.44</v>
+        <v>42.86</v>
       </c>
       <c r="BV10" t="n">
-        <v>25.93</v>
+        <v>25</v>
       </c>
       <c r="BW10" t="n">
-        <v>18.52</v>
+        <v>17.86</v>
       </c>
       <c r="BX10" t="n">
-        <v>55.56</v>
+        <v>53.57</v>
       </c>
       <c r="BY10" t="n">
         <v>1.77</v>
@@ -4834,16 +4834,16 @@
         <v>1.89</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.15</v>
+        <v>4.13</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.63</v>
+        <v>3.57</v>
       </c>
       <c r="CE10" t="n">
         <v>1.31</v>
@@ -4852,7 +4852,7 @@
         <v>2.42</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CH10" t="n">
         <v>1.52</v>
@@ -4885,19 +4885,19 @@
         <v>2.7</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CT10" t="n">
         <v>3.29</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CW10" t="n">
         <v>1.69</v>
@@ -4912,91 +4912,91 @@
         <v>2.43</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB10" t="n">
         <v>1.22</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="DE10" t="n">
         <v>0.11</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="DG10" t="n">
         <v>1.97</v>
       </c>
       <c r="DH10" t="n">
-        <v>78.22</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.08</v>
+        <v>4.21</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="DM10" t="n">
-        <v>35.52</v>
+        <v>36.18</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.71</v>
+        <v>10.54</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.15</v>
+        <v>13.04</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.18</v>
+        <v>7.25</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.89</v>
+        <v>56.18</v>
       </c>
       <c r="DW10" t="n">
         <v>0.14</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.59</v>
+        <v>14</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.26</v>
+        <v>8.5</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.26</v>
+        <v>18.39</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F11" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="G11" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="H11" t="n">
-        <v>82.09</v>
+        <v>81.42</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J11" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="K11" t="n">
-        <v>5.64</v>
+        <v>5.42</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="M11" t="n">
-        <v>42.09</v>
+        <v>41.08</v>
       </c>
       <c r="N11" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="O11" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
-        <v>12.36</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.09</v>
+        <v>11.42</v>
       </c>
       <c r="R11" t="n">
-        <v>9.09</v>
+        <v>9.58</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="T11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>52.09</v>
+        <v>51.58</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.09</v>
+        <v>16.67</v>
       </c>
       <c r="AA11" t="n">
-        <v>12.45</v>
+        <v>11.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.64</v>
+        <v>4.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>24.18</v>
+        <v>24.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AF11" t="n">
         <v>0.08</v>
@@ -5186,55 +5186,55 @@
         <v>3.17</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BU11" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BV11" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX11" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.22</v>
+        <v>2.47</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.24</v>
+        <v>2.55</v>
       </c>
       <c r="CA11" t="n">
         <v>3.74</v>
@@ -5252,31 +5252,31 @@
         <v>1.3</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CH11" t="n">
         <v>1.53</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL11" t="n">
         <v>1.79</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO11" t="n">
         <v>1.2</v>
@@ -5285,31 +5285,31 @@
         <v>1.68</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CU11" t="n">
         <v>1.53</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX11" t="n">
         <v>1.49</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.49</v>
@@ -5324,49 +5324,49 @@
         <v>1.74</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="DH11" t="n">
-        <v>83.56999999999999</v>
+        <v>83.17</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM11" t="n">
-        <v>41.43</v>
+        <v>40.96</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.21</v>
+        <v>12.04</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.56</v>
+        <v>11.71</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.300000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DS11" t="n">
         <v>0.08</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.74</v>
+        <v>49.58</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.35</v>
+        <v>15.21</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.61</v>
+        <v>10.42</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.74</v>
+        <v>4.79</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.65</v>
+        <v>21.7</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
         <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5502,136 +5502,136 @@
         <v>0.08</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AI12" t="n">
-        <v>77.42</v>
+        <v>78.92</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.92</v>
+        <v>2.69</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AN12" t="n">
-        <v>34.17</v>
+        <v>34.69</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11.5</v>
+        <v>11.92</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.58</v>
+        <v>12.15</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.25</v>
+        <v>10.38</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>50.83</v>
+        <v>50.23</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BA12" t="n">
-        <v>13.33</v>
+        <v>13.38</v>
       </c>
       <c r="BB12" t="n">
         <v>9.08</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.25</v>
+        <v>4.31</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.42</v>
+        <v>21.23</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BP12" t="n">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="BR12" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS12" t="n">
-        <v>72</v>
+        <v>73.08</v>
       </c>
       <c r="BT12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BV12" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BY12" t="n">
         <v>1.97</v>
@@ -5640,16 +5640,16 @@
         <v>2.12</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.84</v>
+        <v>3.87</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.67</v>
+        <v>2.87</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="CE12" t="n">
         <v>1.33</v>
@@ -5658,13 +5658,13 @@
         <v>2.56</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CH12" t="n">
         <v>1.46</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.71</v>
@@ -5688,7 +5688,7 @@
         <v>1.8</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CR12" t="n">
         <v>1.38</v>
@@ -5709,10 +5709,10 @@
         <v>1.75</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.44</v>
@@ -5733,43 +5733,43 @@
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="DH12" t="n">
-        <v>83.04000000000001</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.36</v>
+        <v>4.38</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DM12" t="n">
-        <v>36.08</v>
+        <v>36.27</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DO12" t="n">
         <v>1.96</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.68</v>
+        <v>11.88</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12</v>
+        <v>11.81</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.960000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="DS12" t="n">
         <v>0.12</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.72</v>
+        <v>13.73</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.32</v>
+        <v>9.31</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.4</v>
+        <v>4.42</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.72</v>
+        <v>18.73</v>
       </c>
       <c r="EB12" t="n">
         <v>1.44</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F13" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="G13" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="H13" t="n">
-        <v>92.18000000000001</v>
+        <v>89.83</v>
       </c>
       <c r="I13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J13" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="K13" t="n">
-        <v>4.18</v>
+        <v>4.08</v>
       </c>
       <c r="L13" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="M13" t="n">
-        <v>42</v>
+        <v>40.08</v>
       </c>
       <c r="N13" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="O13" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="P13" t="n">
-        <v>10.64</v>
+        <v>10.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.36</v>
+        <v>12.08</v>
       </c>
       <c r="R13" t="n">
-        <v>7.55</v>
+        <v>7.83</v>
       </c>
       <c r="S13" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="T13" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>51.45</v>
+        <v>49.92</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>13.17</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.82</v>
+        <v>8.83</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.18</v>
+        <v>4.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>21.73</v>
+        <v>21.08</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>2.25</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="BH13" t="n">
         <v>9.83</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.87</v>
+        <v>0.96</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.17</v>
+        <v>4.29</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.3</v>
+        <v>5.21</v>
       </c>
       <c r="BR13" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS13" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT13" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BV13" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BW13" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BX13" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.41</v>
+        <v>3.52</v>
       </c>
       <c r="CA13" t="n">
         <v>3.71</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="CC13" t="n">
         <v>5.15</v>
@@ -6055,61 +6055,61 @@
         <v>5.66</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CH13" t="n">
         <v>1.46</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CK13" t="n">
         <v>1.45</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CO13" t="n">
         <v>1.25</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CX13" t="n">
         <v>1.52</v>
@@ -6118,7 +6118,7 @@
         <v>1.81</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DA13" t="n">
         <v>2</v>
@@ -6127,52 +6127,52 @@
         <v>1.29</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="DE13" t="n">
         <v>0.04</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="DH13" t="n">
-        <v>83.48</v>
+        <v>82.66</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM13" t="n">
-        <v>35.35</v>
+        <v>34.66</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DP13" t="n">
-        <v>12</v>
+        <v>11.96</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.52</v>
+        <v>12.38</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.130000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DS13" t="n">
         <v>0.04</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.78</v>
+        <v>48.12</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.87</v>
+        <v>12</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.96</v>
+        <v>8</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.22</v>
+        <v>19.95</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="14">
@@ -6215,61 +6215,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
         <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="F14" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="G14" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="H14" t="n">
-        <v>94.09</v>
+        <v>92.25</v>
       </c>
       <c r="I14" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
       <c r="L14" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="M14" t="n">
-        <v>46.73</v>
+        <v>44.33</v>
       </c>
       <c r="N14" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="O14" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="P14" t="n">
-        <v>11.73</v>
+        <v>11.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>11.55</v>
+        <v>11.08</v>
       </c>
       <c r="R14" t="n">
-        <v>9.550000000000001</v>
+        <v>10.08</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="T14" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>58.55</v>
+        <v>56.67</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.18</v>
+        <v>13.17</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.359999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="AC14" t="n">
-        <v>19.73</v>
+        <v>19.42</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>0.08</v>
@@ -6386,67 +6386,67 @@
         <v>3.23</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.710000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.12</v>
+        <v>4.28</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS14" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BU14" t="n">
-        <v>41.67</v>
+        <v>40</v>
       </c>
       <c r="BV14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>70.83</v>
+        <v>68</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CB14" t="n">
         <v>3.66</v>
@@ -6461,19 +6461,19 @@
         <v>1.37</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CH14" t="n">
         <v>1.4</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CK14" t="n">
         <v>1.5</v>
@@ -6491,28 +6491,28 @@
         <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CU14" t="n">
         <v>1.44</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX14" t="n">
         <v>1.56</v>
@@ -6533,82 +6533,82 @@
         <v>2</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DG14" t="n">
         <v>1.92</v>
       </c>
       <c r="DH14" t="n">
-        <v>82.45999999999999</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM14" t="n">
-        <v>41.75</v>
+        <v>40.8</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="DO14" t="n">
         <v>2.12</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.62</v>
+        <v>12.52</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="DR14" t="n">
-        <v>11.79</v>
+        <v>11.96</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.5</v>
+        <v>50.88</v>
       </c>
       <c r="DW14" t="n">
         <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.63</v>
+        <v>11.68</v>
       </c>
       <c r="DY14" t="n">
-        <v>8</v>
+        <v>7.96</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.46</v>
+        <v>18.36</v>
       </c>
       <c r="EB14" t="n">
         <v>1.29</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="15">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7111,52 +7111,52 @@
         <v>2.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AI16" t="n">
-        <v>78.81999999999999</v>
+        <v>81.25</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.18</v>
+        <v>4.33</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>31.45</v>
+        <v>32.92</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.91</v>
+        <v>10.25</v>
       </c>
       <c r="AR16" t="n">
-        <v>13.36</v>
+        <v>13.58</v>
       </c>
       <c r="AS16" t="n">
-        <v>12.45</v>
+        <v>11.67</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>43.27</v>
+        <v>44.08</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.82</v>
+        <v>9.25</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.45</v>
+        <v>5.83</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="BD16" t="n">
-        <v>15.91</v>
+        <v>16.75</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.35</v>
+        <v>10.25</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.43</v>
+        <v>4.46</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.87</v>
+        <v>5.75</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT16" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BU16" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BV16" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX16" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BY16" t="n">
         <v>3.24</v>
@@ -7255,13 +7255,13 @@
         <v>4.23</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="CC16" t="n">
-        <v>6.88</v>
+        <v>6.67</v>
       </c>
       <c r="CD16" t="n">
-        <v>7.91</v>
+        <v>7.67</v>
       </c>
       <c r="CE16" t="n">
         <v>1.27</v>
@@ -7270,7 +7270,7 @@
         <v>2.32</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="CH16" t="n">
         <v>1.58</v>
@@ -7288,7 +7288,7 @@
         <v>1.71</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CN16" t="n">
         <v>2.11</v>
@@ -7300,13 +7300,13 @@
         <v>1.62</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CR16" t="n">
         <v>1.37</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CT16" t="n">
         <v>3.21</v>
@@ -7315,7 +7315,7 @@
         <v>1.61</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CW16" t="n">
         <v>1.68</v>
@@ -7336,85 +7336,85 @@
         <v>1.2</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="DE16" t="n">
         <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="DH16" t="n">
-        <v>72.73999999999999</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="DI16" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="DM16" t="n">
-        <v>32.69</v>
+        <v>33.38</v>
       </c>
       <c r="DN16" t="n">
         <v>1.08</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.52</v>
+        <v>11.62</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.87</v>
+        <v>13.96</v>
       </c>
       <c r="DR16" t="n">
-        <v>11.13</v>
+        <v>10.8</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.43</v>
+        <v>43.83</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.78</v>
+        <v>10.92</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.74</v>
+        <v>6.88</v>
       </c>
       <c r="DZ16" t="n">
         <v>4.04</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.69</v>
+        <v>18.04</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="17">
@@ -7424,91 +7424,91 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D17" t="n">
         <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="F17" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="H17" t="n">
-        <v>93.67</v>
+        <v>92.69</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="K17" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>53.4</v>
+        <v>52.62</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="P17" t="n">
-        <v>11.6</v>
+        <v>11.19</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.93</v>
+        <v>14.38</v>
       </c>
       <c r="R17" t="n">
-        <v>6.2</v>
+        <v>6.44</v>
       </c>
       <c r="S17" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>55.73</v>
+        <v>55.81</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.6</v>
+        <v>17.06</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.67</v>
+        <v>11.38</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.93</v>
+        <v>5.69</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.2</v>
+        <v>19.19</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -7595,70 +7595,70 @@
         <v>2.64</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.380000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BO17" t="n">
         <v>1.07</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.17</v>
+        <v>4.2</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="BR17" t="n">
-        <v>89.66</v>
+        <v>90</v>
       </c>
       <c r="BS17" t="n">
-        <v>75.86</v>
+        <v>76.67</v>
       </c>
       <c r="BT17" t="n">
-        <v>48.28</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>27.59</v>
+        <v>26.67</v>
       </c>
       <c r="BV17" t="n">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
       <c r="BW17" t="n">
-        <v>13.79</v>
+        <v>13.33</v>
       </c>
       <c r="BX17" t="n">
-        <v>55.17</v>
+        <v>56.67</v>
       </c>
       <c r="BY17" t="n">
         <v>1.64</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CA17" t="n">
         <v>3.8</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.12</v>
+        <v>4.14</v>
       </c>
       <c r="CC17" t="n">
         <v>2.48</v>
@@ -7673,7 +7673,7 @@
         <v>2.44</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CH17" t="n">
         <v>1.43</v>
@@ -7685,13 +7685,13 @@
         <v>1.74</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL17" t="n">
         <v>1.82</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CN17" t="n">
         <v>1.86</v>
@@ -7721,7 +7721,7 @@
         <v>2.12</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX17" t="n">
         <v>1.52</v>
@@ -7748,43 +7748,43 @@
         <v>0.1</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.66</v>
+        <v>92.17</v>
       </c>
       <c r="DI17" t="n">
         <v>0.03</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.59</v>
+        <v>5.5</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="DM17" t="n">
-        <v>46.93</v>
+        <v>46.73</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.65</v>
+        <v>11.43</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.41</v>
+        <v>13.67</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.45</v>
+        <v>7.54</v>
       </c>
       <c r="DS17" t="n">
         <v>0.1</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.62</v>
+        <v>54.7</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.72</v>
+        <v>15.5</v>
       </c>
       <c r="DY17" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.72</v>
+        <v>5.6</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.76</v>
+        <v>18.77</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="F18" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="G18" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="H18" t="n">
-        <v>86.70999999999999</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="I18" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="K18" t="n">
-        <v>3.29</v>
+        <v>3.6</v>
       </c>
       <c r="L18" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="M18" t="n">
-        <v>38.36</v>
+        <v>37.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="P18" t="n">
-        <v>12.79</v>
+        <v>12.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.64</v>
+        <v>13.8</v>
       </c>
       <c r="R18" t="n">
-        <v>7.21</v>
+        <v>7.27</v>
       </c>
       <c r="S18" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="T18" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="V18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>50.36</v>
+        <v>50.8</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>12.79</v>
+        <v>12.87</v>
       </c>
       <c r="AA18" t="n">
-        <v>8</v>
+        <v>8.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>16.79</v>
+        <v>17.33</v>
       </c>
       <c r="AD18" t="n">
         <v>1.42</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="AF18" t="n">
         <v>0.08</v>
@@ -7998,67 +7998,67 @@
         <v>2.83</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.15</v>
+        <v>8.26</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="BJ18" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="BO18" t="n">
         <v>1.04</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="BR18" t="n">
-        <v>88.45999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS18" t="n">
-        <v>76.92</v>
+        <v>77.78</v>
       </c>
       <c r="BT18" t="n">
-        <v>50</v>
+        <v>48.15</v>
       </c>
       <c r="BU18" t="n">
-        <v>38.46</v>
+        <v>37.04</v>
       </c>
       <c r="BV18" t="n">
-        <v>19.23</v>
+        <v>18.52</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BX18" t="n">
-        <v>46.15</v>
+        <v>48.15</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="CB18" t="n">
         <v>4.14</v>
@@ -8070,34 +8070,34 @@
         <v>5.67</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CH18" t="n">
         <v>1.39</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CL18" t="n">
         <v>1.69</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO18" t="n">
         <v>1.03</v>
@@ -8106,13 +8106,13 @@
         <v>1.62</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CT18" t="n">
         <v>3.27</v>
@@ -8121,10 +8121,10 @@
         <v>1.6</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CX18" t="n">
         <v>1.55</v>
@@ -8145,82 +8145,82 @@
         <v>1.65</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="DH18" t="n">
-        <v>78.84999999999999</v>
+        <v>79.89</v>
       </c>
       <c r="DI18" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.39</v>
+        <v>3.56</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="DM18" t="n">
-        <v>36.04</v>
+        <v>35.81</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.54</v>
+        <v>12.33</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12.85</v>
+        <v>12.96</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.15</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.23</v>
+        <v>47.59</v>
       </c>
       <c r="DW18" t="n">
         <v>0.08</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.7</v>
+        <v>11.78</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.65</v>
+        <v>7.71</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.43</v>
+        <v>17.7</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19" t="n">
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
         <v>0.07000000000000001</v>
@@ -8323,136 +8323,136 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AI19" t="n">
-        <v>74.93000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.29</v>
+        <v>5.4</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN19" t="n">
-        <v>35.57</v>
+        <v>36</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14</v>
+        <v>14.07</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.07</v>
+        <v>12.73</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.640000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AU19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="BE19" t="n">
         <v>1.36</v>
       </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>52.79</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>19.64</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.31</v>
-      </c>
       <c r="BF19" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BG19" t="n">
         <v>2.83</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.140000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="BI19" t="n">
         <v>2.83</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.31</v>
+        <v>4.37</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="BR19" t="n">
-        <v>82.76000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="BS19" t="n">
-        <v>65.52</v>
+        <v>66.67</v>
       </c>
       <c r="BT19" t="n">
-        <v>51.72</v>
+        <v>53.33</v>
       </c>
       <c r="BU19" t="n">
-        <v>41.38</v>
+        <v>40</v>
       </c>
       <c r="BV19" t="n">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
       <c r="BW19" t="n">
-        <v>13.79</v>
+        <v>13.33</v>
       </c>
       <c r="BX19" t="n">
-        <v>51.72</v>
+        <v>50</v>
       </c>
       <c r="BY19" t="n">
         <v>1.55</v>
@@ -8461,31 +8461,31 @@
         <v>1.55</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.59</v>
+        <v>4.57</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="CE19" t="n">
         <v>1.27</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CH19" t="n">
         <v>1.59</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.64</v>
@@ -8500,37 +8500,37 @@
         <v>2.41</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CR19" t="n">
         <v>1.36</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CT19" t="n">
         <v>3.21</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY19" t="n">
         <v>1.9</v>
@@ -8545,85 +8545,85 @@
         <v>1.2</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="DE19" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="DN19" t="n">
         <v>1.14</v>
       </c>
-      <c r="DG19" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="DH19" t="n">
-        <v>84.38</v>
-      </c>
-      <c r="DI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ19" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="DK19" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="DL19" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="DM19" t="n">
-        <v>41.34</v>
-      </c>
-      <c r="DN19" t="n">
-        <v>1.07</v>
-      </c>
       <c r="DO19" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.97</v>
+        <v>13.04</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.17</v>
+        <v>12.03</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.550000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.55</v>
+        <v>55.5</v>
       </c>
       <c r="DW19" t="n">
         <v>0.1</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.34</v>
+        <v>17.43</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.62</v>
+        <v>11.66</v>
       </c>
       <c r="DZ19" t="n">
-        <v>5.72</v>
+        <v>5.76</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.03</v>
+        <v>19.54</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1827,10 +1827,10 @@
         <v>13.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.75</v>
+        <v>13.83</v>
       </c>
       <c r="R3" t="n">
-        <v>9.42</v>
+        <v>9.5</v>
       </c>
       <c r="S3" t="n">
         <v>1.58</v>
@@ -1854,19 +1854,19 @@
         <v>0.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.75</v>
+        <v>12</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.58</v>
+        <v>7.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.25</v>
+        <v>16.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE3" t="n">
         <v>2.33</v>
@@ -2139,10 +2139,10 @@
         <v>11.66</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.12</v>
+        <v>13.16</v>
       </c>
       <c r="DR3" t="n">
-        <v>10.08</v>
+        <v>10.12</v>
       </c>
       <c r="DS3" t="n">
         <v>0.38</v>
@@ -2160,19 +2160,19 @@
         <v>0.17</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.54</v>
+        <v>10.66</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.12</v>
+        <v>7.21</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.66</v>
+        <v>16.79</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="EC3" t="n">
         <v>2.25</v>
@@ -2311,10 +2311,10 @@
         <v>12.31</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.15</v>
+        <v>13.23</v>
       </c>
       <c r="AS4" t="n">
-        <v>9</v>
+        <v>9.08</v>
       </c>
       <c r="AT4" t="n">
         <v>1.77</v>
@@ -2542,10 +2542,10 @@
         <v>11.38</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.62</v>
+        <v>12.67</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.84</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DS4" t="n">
         <v>0.25</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
@@ -1391,82 +1391,82 @@
         <v>0.08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="G2" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="H2" t="n">
-        <v>100.08</v>
+        <v>100.85</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="K2" t="n">
-        <v>7.17</v>
+        <v>6.77</v>
       </c>
       <c r="L2" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="M2" t="n">
-        <v>59.58</v>
+        <v>58.54</v>
       </c>
       <c r="N2" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="O2" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="P2" t="n">
-        <v>11.25</v>
+        <v>11.31</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.75</v>
+        <v>11.92</v>
       </c>
       <c r="R2" t="n">
-        <v>6.42</v>
+        <v>6.08</v>
       </c>
       <c r="S2" t="n">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="T2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>56.77</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.92</v>
       </c>
-      <c r="U2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>56.58</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>10.58</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>6.42</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>20.33</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE2" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AF2" t="n">
         <v>0.07000000000000001</v>
@@ -1550,70 +1550,70 @@
         <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.23</v>
+        <v>9.15</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="BL2" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
         <v>4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.12</v>
+        <v>5.04</v>
       </c>
       <c r="BR2" t="n">
-        <v>92.31</v>
+        <v>92.59</v>
       </c>
       <c r="BS2" t="n">
-        <v>76.92</v>
+        <v>77.78</v>
       </c>
       <c r="BT2" t="n">
-        <v>46.15</v>
+        <v>48.15</v>
       </c>
       <c r="BU2" t="n">
-        <v>26.92</v>
+        <v>29.63</v>
       </c>
       <c r="BV2" t="n">
-        <v>7.69</v>
+        <v>11.11</v>
       </c>
       <c r="BW2" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BX2" t="n">
-        <v>46.15</v>
+        <v>48.15</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.28</v>
+        <v>4.24</v>
       </c>
       <c r="CC2" t="n">
         <v>2.29</v>
@@ -1625,10 +1625,10 @@
         <v>1.28</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CH2" t="n">
         <v>1.43</v>
@@ -1637,28 +1637,28 @@
         <v>1.9</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="CR2" t="n">
         <v>1.4</v>
@@ -1673,7 +1673,7 @@
         <v>1.52</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CW2" t="n">
         <v>1.84</v>
@@ -1682,64 +1682,64 @@
         <v>1.55</v>
       </c>
       <c r="CY2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DC2" t="n">
         <v>1.86</v>
       </c>
-      <c r="CZ2" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>1.84</v>
-      </c>
       <c r="DD2" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="DE2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.42</v>
+        <v>3.33</v>
       </c>
       <c r="DH2" t="n">
-        <v>101.38</v>
+        <v>101.71</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.11</v>
+        <v>5.96</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="DM2" t="n">
-        <v>54.23</v>
+        <v>53.93</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.58</v>
+        <v>10.63</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.46</v>
+        <v>12.52</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.66</v>
+        <v>6.48</v>
       </c>
       <c r="DS2" t="n">
         <v>0.15</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>55.46</v>
+        <v>55.59</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.96</v>
+        <v>13.93</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.119999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="DZ2" t="n">
         <v>4.85</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.84</v>
+        <v>18.96</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
         <v>0.42</v>
@@ -1875,136 +1875,136 @@
         <v>0.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>65.42</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.67</v>
+        <v>22.15</v>
       </c>
       <c r="AO3" t="n">
         <v>1.08</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.5</v>
+        <v>12.77</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.75</v>
+        <v>10.46</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AU3" t="n">
         <v>0.92</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>45.42</v>
+        <v>45.54</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.33</v>
+        <v>9.23</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.67</v>
+        <v>6.62</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BD3" t="n">
-        <v>17.08</v>
+        <v>17.77</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.92</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL3" t="n">
         <v>0.88</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS3" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT3" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BU3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BV3" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BW3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX3" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BY3" t="n">
         <v>3.04</v>
@@ -2013,34 +2013,34 @@
         <v>3.31</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.66</v>
+        <v>4.57</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.23</v>
+        <v>5.14</v>
       </c>
       <c r="CE3" t="n">
         <v>1.33</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK3" t="n">
         <v>1.44</v>
@@ -2049,133 +2049,133 @@
         <v>1.83</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CO3" t="n">
         <v>1.23</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CW3" t="n">
         <v>1.76</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB3" t="n">
         <v>1.27</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="DG3" t="n">
         <v>1.8</v>
       </c>
       <c r="DH3" t="n">
-        <v>71.38</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="DM3" t="n">
-        <v>28.71</v>
+        <v>28.68</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.66</v>
+        <v>11.84</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.16</v>
+        <v>13.28</v>
       </c>
       <c r="DR3" t="n">
-        <v>10.12</v>
+        <v>10</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>45.29</v>
+        <v>45.36</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.66</v>
+        <v>10.56</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.21</v>
+        <v>7.16</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.79</v>
+        <v>17.16</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>13</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="G4" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="H4" t="n">
-        <v>68.18000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="K4" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="L4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="M4" t="n">
-        <v>24.91</v>
+        <v>24.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="O4" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="P4" t="n">
-        <v>10.27</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="n">
-        <v>12</v>
+        <v>11.92</v>
       </c>
       <c r="R4" t="n">
-        <v>8.640000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="S4" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="T4" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="U4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>47.36</v>
+        <v>48.17</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.36</v>
+        <v>6.17</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AC4" t="n">
-        <v>23</v>
+        <v>22.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AF4" t="n">
         <v>0.23</v>
@@ -2356,70 +2356,70 @@
         <v>2.08</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>83.33</v>
+        <v>80</v>
       </c>
       <c r="BT4" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BU4" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BV4" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX4" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="CA4" t="n">
         <v>3.64</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CC4" t="n">
         <v>3.96</v>
@@ -2428,10 +2428,10 @@
         <v>4.39</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CG4" t="n">
         <v>3.01</v>
@@ -2446,16 +2446,16 @@
         <v>1.6</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL4" t="n">
         <v>1.78</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO4" t="n">
         <v>1.16</v>
@@ -2464,16 +2464,16 @@
         <v>1.74</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CR4" t="n">
         <v>1.37</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CU4" t="n">
         <v>1.5</v>
@@ -2497,88 +2497,88 @@
         <v>1.97</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="DE4" t="n">
         <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="DH4" t="n">
-        <v>73</v>
+        <v>74.2</v>
       </c>
       <c r="DI4" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM4" t="n">
-        <v>32.46</v>
+        <v>31.96</v>
       </c>
       <c r="DN4" t="n">
         <v>1</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.38</v>
+        <v>11.2</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.67</v>
+        <v>12.6</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.880000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.25</v>
+        <v>47.64</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.67</v>
+        <v>10.48</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.87</v>
+        <v>6.76</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.54</v>
+        <v>20.44</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
         <v>0.13</v>
@@ -2678,139 +2678,139 @@
         <v>2.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
-        <v>97.31</v>
+        <v>97</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.38</v>
+        <v>4.14</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AN5" t="n">
-        <v>38.77</v>
+        <v>38.43</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AP5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>52.14</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="BE5" t="n">
         <v>1.54</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>9.77</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>14.15</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8.23</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>52.77</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>14.54</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>21.92</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BF5" t="n">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.18</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.14</v>
+        <v>5.24</v>
       </c>
       <c r="BR5" t="n">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>82.14</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>53.57</v>
+        <v>51.72</v>
       </c>
       <c r="BU5" t="n">
-        <v>28.57</v>
+        <v>27.59</v>
       </c>
       <c r="BV5" t="n">
-        <v>25</v>
+        <v>24.14</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="BX5" t="n">
-        <v>67.86</v>
+        <v>65.52</v>
       </c>
       <c r="BY5" t="n">
         <v>1.77</v>
@@ -2819,13 +2819,13 @@
         <v>1.85</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="CD5" t="n">
         <v>2.61</v>
@@ -2837,13 +2837,13 @@
         <v>2.51</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CH5" t="n">
         <v>1.49</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.72</v>
@@ -2855,13 +2855,13 @@
         <v>1.93</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP5" t="n">
         <v>1.74</v>
@@ -2894,7 +2894,7 @@
         <v>1.87</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DA5" t="n">
         <v>1.94</v>
@@ -2906,49 +2906,49 @@
         <v>1.78</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.93</v>
+        <v>2.83</v>
       </c>
       <c r="DH5" t="n">
-        <v>101.15</v>
+        <v>100.86</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.5</v>
+        <v>5.35</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="DM5" t="n">
-        <v>47.79</v>
+        <v>47.31</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.11</v>
+        <v>11.03</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.46</v>
+        <v>12.35</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.89</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DS5" t="n">
         <v>0.18</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.14</v>
+        <v>54.76</v>
       </c>
       <c r="DW5" t="n">
         <v>0.21</v>
       </c>
       <c r="DX5" t="n">
-        <v>17.04</v>
+        <v>16.76</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.14</v>
+        <v>10.83</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.89</v>
+        <v>5.93</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.07</v>
+        <v>21.72</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="n">
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
         <v>0.15</v>
@@ -3081,139 +3081,139 @@
         <v>2.23</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AI6" t="n">
-        <v>97.38</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.15</v>
+        <v>5.07</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AN6" t="n">
-        <v>46.69</v>
+        <v>44.71</v>
       </c>
       <c r="AO6" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.08</v>
+        <v>11.64</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.15</v>
+        <v>10.79</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.08</v>
+        <v>6.93</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>54.62</v>
+        <v>54.57</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BA6" t="n">
-        <v>14.38</v>
+        <v>14.07</v>
       </c>
       <c r="BB6" t="n">
-        <v>10.38</v>
+        <v>10.07</v>
       </c>
       <c r="BC6" t="n">
         <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.92</v>
+        <v>19.86</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.880000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.19</v>
+        <v>4.11</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="BR6" t="n">
-        <v>92.31</v>
+        <v>92.59</v>
       </c>
       <c r="BS6" t="n">
-        <v>69.23</v>
+        <v>70.37</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.69</v>
+        <v>55.56</v>
       </c>
       <c r="BU6" t="n">
-        <v>26.92</v>
+        <v>25.93</v>
       </c>
       <c r="BV6" t="n">
-        <v>23.08</v>
+        <v>22.22</v>
       </c>
       <c r="BW6" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BX6" t="n">
-        <v>53.85</v>
+        <v>51.85</v>
       </c>
       <c r="BY6" t="n">
         <v>1.96</v>
@@ -3222,46 +3222,46 @@
         <v>2.02</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="CE6" t="n">
         <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CH6" t="n">
         <v>1.39</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.69</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL6" t="n">
         <v>1.74</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO6" t="n">
         <v>1.21</v>
@@ -3291,100 +3291,100 @@
         <v>1.79</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC6" t="n">
         <v>1.89</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.38</v>
+        <v>87.89</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.42</v>
+        <v>5.37</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.73</v>
+        <v>39.92</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.66</v>
+        <v>11.44</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.69</v>
+        <v>11</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.73</v>
+        <v>7.63</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.54</v>
+        <v>54.52</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.58</v>
+        <v>14.41</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.07</v>
+        <v>9.93</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.81</v>
+        <v>17.85</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
         <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="G7" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="H7" t="n">
-        <v>92.43000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="J7" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="K7" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="L7" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="M7" t="n">
-        <v>36.93</v>
+        <v>37.13</v>
       </c>
       <c r="N7" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="P7" t="n">
-        <v>11.5</v>
+        <v>11.47</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.29</v>
+        <v>12.47</v>
       </c>
       <c r="R7" t="n">
-        <v>8.210000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="U7" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="V7" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>51.64</v>
+        <v>51.73</v>
       </c>
       <c r="Y7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.71</v>
+        <v>12.53</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.5</v>
+        <v>8.33</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AF7" t="n">
         <v>0.15</v>
@@ -3565,70 +3565,70 @@
         <v>2.23</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.890000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.15</v>
+        <v>4.21</v>
       </c>
       <c r="BR7" t="n">
-        <v>96.3</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>85.19</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>62.96</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>35.71</v>
       </c>
       <c r="BV7" t="n">
-        <v>14.81</v>
+        <v>14.29</v>
       </c>
       <c r="BW7" t="n">
-        <v>11.11</v>
+        <v>10.71</v>
       </c>
       <c r="BX7" t="n">
-        <v>74.06999999999999</v>
+        <v>75</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CC7" t="n">
         <v>4.02</v>
@@ -3640,10 +3640,10 @@
         <v>1.36</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CH7" t="n">
         <v>1.43</v>
@@ -3658,7 +3658,7 @@
         <v>1.53</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CM7" t="n">
         <v>2.35</v>
@@ -3673,16 +3673,16 @@
         <v>1.9</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CR7" t="n">
         <v>1.4</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CU7" t="n">
         <v>1.46</v>
@@ -3691,10 +3691,10 @@
         <v>2.07</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY7" t="n">
         <v>1.99</v>
@@ -3703,91 +3703,91 @@
         <v>2.31</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DB7" t="n">
         <v>1.3</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="DH7" t="n">
-        <v>84.59</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="DI7" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="DK7" t="n">
         <v>4.04</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM7" t="n">
-        <v>37.52</v>
+        <v>37.6</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.07</v>
+        <v>12.04</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.96</v>
+        <v>13.04</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.140000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.92</v>
+        <v>49.07</v>
       </c>
       <c r="DW7" t="n">
         <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.85</v>
+        <v>11.78</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.93</v>
+        <v>7.86</v>
       </c>
       <c r="DZ7" t="n">
         <v>3.93</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.41</v>
+        <v>21.96</v>
       </c>
       <c r="EB7" t="n">
         <v>1.3</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
@@ -3809,82 +3809,82 @@
         <v>0.08</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="H8" t="n">
-        <v>71.42</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>0.08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.67</v>
+        <v>2.46</v>
       </c>
       <c r="K8" t="n">
-        <v>4.58</v>
+        <v>4.92</v>
       </c>
       <c r="L8" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="M8" t="n">
-        <v>30.58</v>
+        <v>32.92</v>
       </c>
       <c r="N8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="P8" t="n">
-        <v>11.92</v>
+        <v>12.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.67</v>
+        <v>12.62</v>
       </c>
       <c r="R8" t="n">
-        <v>8.83</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="T8" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="U8" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="V8" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>50.42</v>
+        <v>50.62</v>
       </c>
       <c r="Y8" t="n">
         <v>0.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>12</v>
+        <v>13.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.75</v>
+        <v>8.77</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="AC8" t="n">
         <v>18.08</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AF8" t="n">
         <v>0.08</v>
@@ -3968,70 +3968,70 @@
         <v>2.17</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.83</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BO8" t="n">
         <v>1.12</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.58</v>
+        <v>4.64</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.67</v>
+        <v>4.76</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS8" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT8" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="BU8" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BV8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="CC8" t="n">
         <v>4.32</v>
@@ -4046,7 +4046,7 @@
         <v>2.48</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CH8" t="n">
         <v>1.51</v>
@@ -4058,22 +4058,22 @@
         <v>1.66</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM8" t="n">
         <v>2.56</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO8" t="n">
         <v>1.21</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CQ8" t="n">
         <v>2.76</v>
@@ -4100,13 +4100,13 @@
         <v>1.51</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.45</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DB8" t="n">
         <v>1.23</v>
@@ -4121,76 +4121,76 @@
         <v>0.08</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="DH8" t="n">
-        <v>73.54000000000001</v>
+        <v>74.72</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.66</v>
+        <v>4.84</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM8" t="n">
-        <v>30.62</v>
+        <v>31.84</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.5</v>
+        <v>11.68</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.8</v>
+        <v>12.76</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.5</v>
+        <v>9.32</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.92</v>
+        <v>51</v>
       </c>
       <c r="DW8" t="n">
         <v>0.12</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.92</v>
+        <v>12.52</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.96</v>
+        <v>8.48</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.25</v>
+        <v>18.24</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="G9" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="H9" t="n">
-        <v>78.92</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="J9" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="K9" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="L9" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="M9" t="n">
-        <v>35.42</v>
+        <v>34.62</v>
       </c>
       <c r="N9" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="O9" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="P9" t="n">
-        <v>11.08</v>
+        <v>10.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.75</v>
+        <v>12.62</v>
       </c>
       <c r="R9" t="n">
-        <v>8.08</v>
+        <v>7.92</v>
       </c>
       <c r="S9" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="U9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>42</v>
+        <v>41.31</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.42</v>
+        <v>9.69</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.25</v>
+        <v>6.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="AC9" t="n">
-        <v>15.42</v>
+        <v>15.69</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>2.25</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.460000000000001</v>
+        <v>9.52</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="BJ9" t="n">
         <v>0.96</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.75</v>
+        <v>4.84</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS9" t="n">
-        <v>79.17</v>
+        <v>76</v>
       </c>
       <c r="BT9" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BU9" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BV9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX9" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.42</v>
+        <v>3.49</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.22</v>
+        <v>4.19</v>
       </c>
       <c r="CC9" t="n">
         <v>5.71</v>
@@ -4446,10 +4446,10 @@
         <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CH9" t="n">
         <v>1.48</v>
@@ -4467,31 +4467,31 @@
         <v>1.87</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN9" t="n">
         <v>1.96</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP9" t="n">
         <v>1.8</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CR9" t="n">
         <v>1.39</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV9" t="n">
         <v>2.13</v>
@@ -4500,16 +4500,16 @@
         <v>1.78</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB9" t="n">
         <v>1.26</v>
@@ -4518,49 +4518,49 @@
         <v>1.83</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="DE9" t="n">
         <v>0.08</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="DH9" t="n">
-        <v>76.92</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="DI9" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="DL9" t="n">
         <v>0.12</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.3</v>
+        <v>33.92</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.54</v>
+        <v>11.24</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.46</v>
+        <v>12.88</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.380000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="DS9" t="n">
         <v>0.08</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43</v>
+        <v>42.6</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.380000000000001</v>
+        <v>9.52</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.12</v>
+        <v>6.24</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.05</v>
+        <v>17.12</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
         <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="G10" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="H10" t="n">
-        <v>92.69</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="K10" t="n">
-        <v>4.31</v>
+        <v>4.64</v>
       </c>
       <c r="L10" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="M10" t="n">
-        <v>42.85</v>
+        <v>43.93</v>
       </c>
       <c r="N10" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="P10" t="n">
-        <v>11.08</v>
+        <v>10.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>13</v>
+        <v>12.71</v>
       </c>
       <c r="R10" t="n">
-        <v>6.15</v>
+        <v>6.36</v>
       </c>
       <c r="S10" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="U10" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="V10" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>57.23</v>
+        <v>57.14</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.38</v>
+        <v>14.57</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.92</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.46</v>
+        <v>5.29</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.31</v>
+        <v>18.14</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AF10" t="n">
         <v>0.13</v>
@@ -4774,70 +4774,70 @@
         <v>1.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.039999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.5</v>
+        <v>4.62</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>75</v>
+        <v>75.86</v>
       </c>
       <c r="BT10" t="n">
-        <v>53.57</v>
+        <v>51.72</v>
       </c>
       <c r="BU10" t="n">
-        <v>42.86</v>
+        <v>41.38</v>
       </c>
       <c r="BV10" t="n">
-        <v>25</v>
+        <v>24.14</v>
       </c>
       <c r="BW10" t="n">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="BX10" t="n">
-        <v>53.57</v>
+        <v>51.72</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.13</v>
+        <v>4.11</v>
       </c>
       <c r="CC10" t="n">
         <v>3.01</v>
@@ -4849,19 +4849,19 @@
         <v>1.31</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI10" t="n">
         <v>2.15</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CK10" t="n">
         <v>1.45</v>
@@ -4870,19 +4870,19 @@
         <v>1.9</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO10" t="n">
         <v>1.2</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CR10" t="n">
         <v>1.36</v>
@@ -4897,7 +4897,7 @@
         <v>1.56</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CW10" t="n">
         <v>1.69</v>
@@ -4906,16 +4906,16 @@
         <v>1.52</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DA10" t="n">
         <v>1.95</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC10" t="n">
         <v>1.73</v>
@@ -4924,79 +4924,79 @@
         <v>2.78</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.97</v>
+        <v>2.17</v>
       </c>
       <c r="DH10" t="n">
-        <v>80.06999999999999</v>
+        <v>80.38</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.21</v>
+        <v>4.38</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.18</v>
+        <v>36.93</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.54</v>
+        <v>10.45</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.04</v>
+        <v>12.9</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.25</v>
+        <v>7.31</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>56.18</v>
+        <v>56.17</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX10" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.5</v>
+        <v>8.69</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.5</v>
+        <v>5.41</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.39</v>
+        <v>18.76</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
         <v>0.17</v>
@@ -5099,13 +5099,13 @@
         <v>0.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="AI11" t="n">
-        <v>84.92</v>
+        <v>84.69</v>
       </c>
       <c r="AJ11" t="n">
         <v>0.08</v>
@@ -5114,34 +5114,34 @@
         <v>2.92</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AN11" t="n">
-        <v>40.83</v>
+        <v>39.38</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.08</v>
+        <v>11.92</v>
       </c>
       <c r="AR11" t="n">
-        <v>12</v>
+        <v>12.23</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.5</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AV11" t="n">
         <v>0.08</v>
@@ -5153,82 +5153,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>47.58</v>
+        <v>47.54</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BA11" t="n">
-        <v>13.75</v>
+        <v>13.46</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.92</v>
+        <v>8.69</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.83</v>
+        <v>4.77</v>
       </c>
       <c r="BD11" t="n">
-        <v>19.33</v>
+        <v>18.85</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.83</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="BP11" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.71</v>
+        <v>4.8</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT11" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BU11" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BV11" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX11" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BY11" t="n">
         <v>2.47</v>
@@ -5237,40 +5237,40 @@
         <v>2.55</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.73</v>
+        <v>3.66</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.16</v>
+        <v>4.1</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF11" t="n">
         <v>2.4</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI11" t="n">
         <v>2.22</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK11" t="n">
         <v>1.41</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CM11" t="n">
         <v>2.69</v>
@@ -5282,10 +5282,10 @@
         <v>1.2</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
@@ -5309,7 +5309,7 @@
         <v>1.49</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.49</v>
@@ -5321,52 +5321,52 @@
         <v>1.23</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="DE11" t="n">
         <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="DH11" t="n">
-        <v>83.17</v>
+        <v>83.12</v>
       </c>
       <c r="DI11" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="DK11" t="n">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM11" t="n">
-        <v>40.96</v>
+        <v>40.2</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.04</v>
+        <v>11.96</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.71</v>
+        <v>11.84</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.539999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="DS11" t="n">
         <v>0.08</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.58</v>
+        <v>49.48</v>
       </c>
       <c r="DW11" t="n">
         <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.21</v>
+        <v>15</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.42</v>
+        <v>10.24</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.79</v>
+        <v>4.76</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.7</v>
+        <v>21.36</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
         <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5499,139 +5499,139 @@
         <v>2.54</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>78.92</v>
+        <v>83.29000000000001</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.69</v>
+        <v>4</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AN12" t="n">
-        <v>34.69</v>
+        <v>37.93</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11.92</v>
+        <v>11.57</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.15</v>
+        <v>12.36</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.38</v>
+        <v>10.21</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>50.23</v>
+        <v>51.43</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BA12" t="n">
-        <v>13.38</v>
+        <v>13.86</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.08</v>
+        <v>9.57</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.23</v>
+        <v>21.36</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.77</v>
+        <v>8.85</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="BJ12" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN12" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="BP12" t="n">
         <v>4.04</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.96</v>
+        <v>4.07</v>
       </c>
       <c r="BR12" t="n">
-        <v>92.31</v>
+        <v>92.59</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.08</v>
+        <v>70.37</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>48.15</v>
       </c>
       <c r="BU12" t="n">
-        <v>23.08</v>
+        <v>22.22</v>
       </c>
       <c r="BV12" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>46.15</v>
+        <v>44.44</v>
       </c>
       <c r="BY12" t="n">
         <v>1.97</v>
@@ -5643,13 +5643,13 @@
         <v>3.66</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.87</v>
+        <v>2.79</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="CE12" t="n">
         <v>1.33</v>
@@ -5658,13 +5658,13 @@
         <v>2.56</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CH12" t="n">
         <v>1.46</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.71</v>
@@ -5685,16 +5685,16 @@
         <v>1.24</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CR12" t="n">
         <v>1.38</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CT12" t="n">
         <v>3.17</v>
@@ -5712,13 +5712,13 @@
         <v>1.52</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB12" t="n">
         <v>1.27</v>
@@ -5727,82 +5727,82 @@
         <v>1.87</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="DE12" t="n">
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="DH12" t="n">
-        <v>83.56999999999999</v>
+        <v>85.67</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.38</v>
+        <v>4.52</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="DM12" t="n">
-        <v>36.27</v>
+        <v>37.89</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.88</v>
+        <v>11.7</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.81</v>
+        <v>11.93</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.07</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50.5</v>
+        <v>51.11</v>
       </c>
       <c r="DW12" t="n">
         <v>0.34</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.73</v>
+        <v>13.97</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.31</v>
+        <v>9.56</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.42</v>
+        <v>4.41</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.73</v>
+        <v>18.89</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
         <v>0.08</v>
@@ -5905,49 +5905,49 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AH13" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AI13" t="n">
-        <v>75.5</v>
+        <v>75.38</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.58</v>
+        <v>5.54</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AN13" t="n">
-        <v>29.25</v>
+        <v>27.85</v>
       </c>
       <c r="AO13" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.25</v>
+        <v>12.62</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.67</v>
+        <v>12.92</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.58</v>
+        <v>10.38</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AV13" t="n">
         <v>0.08</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>46.33</v>
+        <v>46.08</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.83</v>
+        <v>10.85</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.17</v>
+        <v>7.23</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="BD13" t="n">
-        <v>18.83</v>
+        <v>19.46</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.21</v>
+        <v>3.12</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.83</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.21</v>
+        <v>3.12</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL13" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM13" t="n">
         <v>0.96</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.29</v>
+        <v>4.32</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.21</v>
+        <v>5.16</v>
       </c>
       <c r="BR13" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BS13" t="n">
-        <v>70.83</v>
+        <v>68</v>
       </c>
       <c r="BT13" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BU13" t="n">
-        <v>41.67</v>
+        <v>40</v>
       </c>
       <c r="BV13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW13" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY13" t="n">
         <v>3.33</v>
@@ -6043,16 +6043,16 @@
         <v>3.52</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.15</v>
+        <v>5.08</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.66</v>
+        <v>5.48</v>
       </c>
       <c r="CE13" t="n">
         <v>1.34</v>
@@ -6061,7 +6061,7 @@
         <v>2.65</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CH13" t="n">
         <v>1.46</v>
@@ -6079,10 +6079,10 @@
         <v>1.84</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CO13" t="n">
         <v>1.25</v>
@@ -6091,13 +6091,13 @@
         <v>1.85</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CR13" t="n">
         <v>1.39</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CT13" t="n">
         <v>3.14</v>
@@ -6106,22 +6106,22 @@
         <v>1.47</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CX13" t="n">
         <v>1.52</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.42</v>
       </c>
       <c r="DA13" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB13" t="n">
         <v>1.29</v>
@@ -6136,43 +6136,43 @@
         <v>0.04</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="DH13" t="n">
-        <v>82.66</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="DI13" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.83</v>
+        <v>4.84</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="DM13" t="n">
-        <v>34.66</v>
+        <v>33.72</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.96</v>
+        <v>11.68</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.38</v>
+        <v>12.52</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="DS13" t="n">
         <v>0.04</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.12</v>
+        <v>47.92</v>
       </c>
       <c r="DW13" t="n">
         <v>0.16</v>
       </c>
       <c r="DX13" t="n">
-        <v>12</v>
+        <v>11.96</v>
       </c>
       <c r="DY13" t="n">
         <v>8</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.95</v>
+        <v>20.24</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
         <v>0.17</v>
@@ -6305,139 +6305,139 @@
         <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AI14" t="n">
-        <v>72.62</v>
+        <v>76.64</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.54</v>
+        <v>3.43</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="AN14" t="n">
-        <v>37.54</v>
+        <v>38.93</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.38</v>
+        <v>13.36</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.54</v>
+        <v>10.71</v>
       </c>
       <c r="AS14" t="n">
-        <v>13.69</v>
+        <v>13.14</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>45.54</v>
+        <v>47.29</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.31</v>
+        <v>10.71</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.85</v>
+        <v>7.29</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.38</v>
+        <v>18.07</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.84</v>
+        <v>8.77</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BJ14" t="n">
         <v>0.88</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.48</v>
+        <v>4.42</v>
       </c>
       <c r="BR14" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS14" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BT14" t="n">
-        <v>48</v>
+        <v>46.15</v>
       </c>
       <c r="BU14" t="n">
-        <v>40</v>
+        <v>38.46</v>
       </c>
       <c r="BV14" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>68</v>
+        <v>69.23</v>
       </c>
       <c r="BY14" t="n">
         <v>1.97</v>
@@ -6452,10 +6452,10 @@
         <v>3.66</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CE14" t="n">
         <v>1.37</v>
@@ -6470,22 +6470,22 @@
         <v>1.4</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.79</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO14" t="n">
         <v>1.28</v>
@@ -6494,7 +6494,7 @@
         <v>1.92</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CR14" t="n">
         <v>1.4</v>
@@ -6509,19 +6509,19 @@
         <v>1.44</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY14" t="n">
         <v>1.97</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DA14" t="n">
         <v>1.84</v>
@@ -6530,85 +6530,85 @@
         <v>1.31</v>
       </c>
       <c r="DC14" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="DE14" t="n">
         <v>0.12</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="DG14" t="n">
         <v>1.92</v>
       </c>
       <c r="DH14" t="n">
-        <v>82.04000000000001</v>
+        <v>83.84</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="DM14" t="n">
-        <v>40.8</v>
+        <v>41.42</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.52</v>
+        <v>12.54</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.8</v>
+        <v>10.88</v>
       </c>
       <c r="DR14" t="n">
-        <v>11.96</v>
+        <v>11.73</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.88</v>
+        <v>51.62</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.68</v>
+        <v>11.85</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.96</v>
+        <v>8.16</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.36</v>
+        <v>18.69</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
         <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="G15" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="H15" t="n">
-        <v>78.81999999999999</v>
+        <v>78.67</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J15" t="n">
-        <v>3.27</v>
+        <v>3.67</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="L15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M15" t="n">
-        <v>27.64</v>
+        <v>28.67</v>
       </c>
       <c r="N15" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="P15" t="n">
-        <v>13.91</v>
+        <v>13.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.91</v>
+        <v>12.08</v>
       </c>
       <c r="R15" t="n">
-        <v>10.82</v>
+        <v>10.58</v>
       </c>
       <c r="S15" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="U15" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="V15" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>41.55</v>
+        <v>41.33</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>9</v>
+        <v>10.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.64</v>
+        <v>6.42</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.36</v>
+        <v>3.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>18.55</v>
+        <v>19.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.91</v>
+        <v>3.33</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6789,70 +6789,70 @@
         <v>2.08</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.26</v>
+        <v>9.25</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.65</v>
+        <v>4.71</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS15" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT15" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BU15" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX15" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="CC15" t="n">
         <v>7.07</v>
@@ -6873,49 +6873,49 @@
         <v>1.4</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.8</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN15" t="n">
         <v>1.87</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP15" t="n">
         <v>1.85</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS15" t="n">
         <v>2.79</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CU15" t="n">
         <v>1.49</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CX15" t="n">
         <v>1.51</v>
@@ -6927,91 +6927,91 @@
         <v>2.45</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DB15" t="n">
         <v>1.28</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="DE15" t="n">
         <v>0.04</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="DH15" t="n">
-        <v>66.17</v>
+        <v>66.62</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
       <c r="DL15" t="n">
         <v>0.17</v>
       </c>
       <c r="DM15" t="n">
-        <v>24.74</v>
+        <v>25.38</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.91</v>
+        <v>11.75</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.13</v>
+        <v>12.2</v>
       </c>
       <c r="DR15" t="n">
-        <v>10.83</v>
+        <v>10.7</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>37.13</v>
+        <v>37.2</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.130000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.7</v>
+        <v>6.08</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.43</v>
+        <v>3.58</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.35</v>
+        <v>17.88</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7114,136 +7114,136 @@
         <v>0.08</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AI16" t="n">
-        <v>81.25</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.08</v>
+        <v>3.38</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AN16" t="n">
-        <v>32.92</v>
+        <v>33.38</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AP16" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.25</v>
+        <v>10.08</v>
       </c>
       <c r="AR16" t="n">
-        <v>13.58</v>
+        <v>13.38</v>
       </c>
       <c r="AS16" t="n">
-        <v>11.67</v>
+        <v>11.77</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>44.08</v>
+        <v>45.38</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.25</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.83</v>
+        <v>6.08</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.75</v>
+        <v>17.46</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.25</v>
+        <v>10.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.75</v>
+        <v>5.76</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT16" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BU16" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BV16" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX16" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BY16" t="n">
         <v>3.24</v>
@@ -7252,16 +7252,16 @@
         <v>3.47</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.23</v>
+        <v>4.21</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.66</v>
+        <v>4.62</v>
       </c>
       <c r="CC16" t="n">
-        <v>6.67</v>
+        <v>6.44</v>
       </c>
       <c r="CD16" t="n">
-        <v>7.67</v>
+        <v>7.38</v>
       </c>
       <c r="CE16" t="n">
         <v>1.27</v>
@@ -7270,7 +7270,7 @@
         <v>2.32</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CH16" t="n">
         <v>1.58</v>
@@ -7285,13 +7285,13 @@
         <v>1.39</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CO16" t="n">
         <v>1.17</v>
@@ -7300,19 +7300,19 @@
         <v>1.62</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CV16" t="n">
         <v>2.29</v>
@@ -7321,7 +7321,7 @@
         <v>1.68</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CY16" t="n">
         <v>1.71</v>
@@ -7330,91 +7330,91 @@
         <v>2.5</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DB16" t="n">
         <v>1.2</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="DE16" t="n">
         <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="DH16" t="n">
-        <v>74.20999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="DI16" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="DM16" t="n">
-        <v>33.38</v>
+        <v>33.6</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.62</v>
+        <v>11.48</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.96</v>
+        <v>13.84</v>
       </c>
       <c r="DR16" t="n">
-        <v>10.8</v>
+        <v>10.88</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.83</v>
+        <v>44.52</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.92</v>
+        <v>11</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.88</v>
+        <v>6.96</v>
       </c>
       <c r="DZ16" t="n">
         <v>4.04</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.04</v>
+        <v>18.36</v>
       </c>
       <c r="EB16" t="n">
         <v>1.22</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C17" t="n">
         <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
         <v>0.19</v>
@@ -7514,139 +7514,139 @@
         <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AI17" t="n">
-        <v>91.56999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="AJ17" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="AL17" t="n">
         <v>4.93</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>40</v>
+        <v>38.33</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.71</v>
+        <v>11.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>12.86</v>
+        <v>12.87</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.789999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>53.43</v>
+        <v>52.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>13.71</v>
+        <v>13.53</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.210000000000001</v>
+        <v>8</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="BD17" t="n">
-        <v>18.29</v>
+        <v>17.73</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.33</v>
+        <v>9.26</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BL17" t="n">
         <v>1.1</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.93</v>
+        <v>4.87</v>
       </c>
       <c r="BR17" t="n">
-        <v>90</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>76.67</v>
+        <v>77.42</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>51.61</v>
       </c>
       <c r="BU17" t="n">
-        <v>26.67</v>
+        <v>29.03</v>
       </c>
       <c r="BV17" t="n">
-        <v>16.67</v>
+        <v>19.35</v>
       </c>
       <c r="BW17" t="n">
-        <v>13.33</v>
+        <v>12.9</v>
       </c>
       <c r="BX17" t="n">
-        <v>56.67</v>
+        <v>58.06</v>
       </c>
       <c r="BY17" t="n">
         <v>1.64</v>
@@ -7655,55 +7655,55 @@
         <v>1.64</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CG17" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CH17" t="n">
         <v>1.43</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK17" t="n">
         <v>1.43</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="CR17" t="n">
         <v>1.38</v>
@@ -7718,106 +7718,106 @@
         <v>1.49</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CW17" t="n">
         <v>1.78</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.17</v>
+        <v>91.13</v>
       </c>
       <c r="DI17" t="n">
         <v>0.03</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.5</v>
+        <v>5.48</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="DM17" t="n">
-        <v>46.73</v>
+        <v>45.71</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.43</v>
+        <v>11.49</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.67</v>
+        <v>13.65</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.54</v>
+        <v>7.71</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.7</v>
+        <v>54.26</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.5</v>
+        <v>15.35</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.9</v>
+        <v>9.74</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.6</v>
+        <v>5.61</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.77</v>
+        <v>18.48</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="18">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F18" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="G18" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="H18" t="n">
-        <v>88.06999999999999</v>
+        <v>86.44</v>
       </c>
       <c r="I18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="J18" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="L18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="M18" t="n">
-        <v>37.8</v>
+        <v>38</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="P18" t="n">
-        <v>12.4</v>
+        <v>12.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.8</v>
+        <v>13.88</v>
       </c>
       <c r="R18" t="n">
-        <v>7.27</v>
+        <v>7.31</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="V18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>50.8</v>
+        <v>49.5</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>12.87</v>
+        <v>12.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.07</v>
+        <v>8</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>17.33</v>
+        <v>17.31</v>
       </c>
       <c r="AD18" t="n">
         <v>1.42</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AF18" t="n">
         <v>0.08</v>
@@ -7998,70 +7998,70 @@
         <v>2.83</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.26</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.07</v>
+        <v>4.04</v>
       </c>
       <c r="BR18" t="n">
-        <v>88.89</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="BS18" t="n">
-        <v>77.78</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>48.15</v>
+        <v>46.43</v>
       </c>
       <c r="BU18" t="n">
-        <v>37.04</v>
+        <v>35.71</v>
       </c>
       <c r="BV18" t="n">
-        <v>18.52</v>
+        <v>17.86</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="BX18" t="n">
-        <v>48.15</v>
+        <v>50</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="CC18" t="n">
         <v>5.2</v>
@@ -8073,7 +8073,7 @@
         <v>1.14</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CG18" t="n">
         <v>2.99</v>
@@ -8082,31 +8082,31 @@
         <v>1.39</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.48</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CN18" t="n">
         <v>1.7</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
@@ -8130,97 +8130,97 @@
         <v>1.55</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB18" t="n">
         <v>1.2</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="DH18" t="n">
-        <v>79.89</v>
+        <v>79.25</v>
       </c>
       <c r="DI18" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM18" t="n">
-        <v>35.81</v>
+        <v>36</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.33</v>
+        <v>12.25</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12.96</v>
+        <v>13.04</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.109999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.59</v>
+        <v>46.96</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.78</v>
+        <v>11.75</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.71</v>
+        <v>7.68</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.7</v>
+        <v>17.68</v>
       </c>
       <c r="EB18" t="n">
         <v>1.29</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="19">
@@ -8230,94 +8230,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="F19" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="H19" t="n">
-        <v>93.2</v>
+        <v>92.69</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>5.67</v>
+        <v>5.44</v>
       </c>
       <c r="L19" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="M19" t="n">
-        <v>46.73</v>
+        <v>44.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="O19" t="n">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="P19" t="n">
-        <v>12</v>
+        <v>11.88</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.33</v>
+        <v>11.5</v>
       </c>
       <c r="R19" t="n">
-        <v>8.470000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="S19" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="T19" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U19" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="V19" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>58.13</v>
+        <v>57.38</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.53</v>
+        <v>19.06</v>
       </c>
       <c r="AA19" t="n">
-        <v>13.13</v>
+        <v>12.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.4</v>
+        <v>6.31</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.47</v>
+        <v>18.62</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AF19" t="n">
         <v>0.07000000000000001</v>
@@ -8401,70 +8401,70 @@
         <v>2.53</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.17</v>
+        <v>9.06</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.37</v>
+        <v>4.29</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="BR19" t="n">
-        <v>83.33</v>
+        <v>83.87</v>
       </c>
       <c r="BS19" t="n">
-        <v>66.67</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>53.33</v>
+        <v>51.61</v>
       </c>
       <c r="BU19" t="n">
-        <v>40</v>
+        <v>38.71</v>
       </c>
       <c r="BV19" t="n">
-        <v>16.67</v>
+        <v>16.13</v>
       </c>
       <c r="BW19" t="n">
-        <v>13.33</v>
+        <v>12.9</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>48.39</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.57</v>
+        <v>4.54</v>
       </c>
       <c r="CC19" t="n">
         <v>2.29</v>
@@ -8473,16 +8473,16 @@
         <v>2.36</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI19" t="n">
         <v>2.19</v>
@@ -8497,10 +8497,10 @@
         <v>1.91</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO19" t="n">
         <v>1.17</v>
@@ -8509,7 +8509,7 @@
         <v>1.61</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CR19" t="n">
         <v>1.36</v>
@@ -8524,40 +8524,40 @@
         <v>1.62</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CW19" t="n">
         <v>1.69</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DA19" t="n">
         <v>1.9</v>
-      </c>
-      <c r="CZ19" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="DA19" t="n">
-        <v>1.91</v>
       </c>
       <c r="DB19" t="n">
         <v>1.2</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DH19" t="n">
         <v>84.90000000000001</v>
@@ -8566,64 +8566,64 @@
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.54</v>
+        <v>5.42</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="DM19" t="n">
-        <v>41.36</v>
+        <v>40.39</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.04</v>
+        <v>12.94</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.03</v>
+        <v>12.1</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.57</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.5</v>
+        <v>55.2</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.43</v>
+        <v>17.26</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.66</v>
+        <v>11.52</v>
       </c>
       <c r="DZ19" t="n">
-        <v>5.76</v>
+        <v>5.74</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.54</v>
+        <v>19.58</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1421,7 +1421,7 @@
         <v>3.08</v>
       </c>
       <c r="P2" t="n">
-        <v>11.31</v>
+        <v>11.46</v>
       </c>
       <c r="Q2" t="n">
         <v>11.92</v>
@@ -1607,7 +1607,7 @@
         <v>1.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CA2" t="n">
         <v>3.92</v>
@@ -1679,13 +1679,13 @@
         <v>1.84</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DA2" t="n">
         <v>1.94</v>
@@ -1733,7 +1733,7 @@
         <v>2.56</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.63</v>
+        <v>10.7</v>
       </c>
       <c r="DQ2" t="n">
         <v>12.52</v>
@@ -2227,7 +2227,7 @@
         <v>2.08</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Q4" t="n">
         <v>11.92</v>
@@ -2266,7 +2266,7 @@
         <v>2.58</v>
       </c>
       <c r="AC4" t="n">
-        <v>22.58</v>
+        <v>22.75</v>
       </c>
       <c r="AD4" t="n">
         <v>0.88</v>
@@ -2539,7 +2539,7 @@
         <v>2.12</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.2</v>
+        <v>11.44</v>
       </c>
       <c r="DQ4" t="n">
         <v>12.6</v>
@@ -2572,7 +2572,7 @@
         <v>3.72</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.44</v>
+        <v>20.52</v>
       </c>
       <c r="EB4" t="n">
         <v>1.14</v>
@@ -2711,13 +2711,13 @@
         <v>1.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.710000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.79</v>
+        <v>13.93</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>9.07</v>
       </c>
       <c r="AT5" t="n">
         <v>1.14</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>52.14</v>
+        <v>52</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.29</v>
@@ -2828,7 +2828,7 @@
         <v>2.46</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CE5" t="n">
         <v>1.32</v>
@@ -2942,13 +2942,13 @@
         <v>2.17</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.03</v>
+        <v>11.07</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.35</v>
+        <v>12.41</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.279999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="DS5" t="n">
         <v>0.18</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.76</v>
+        <v>54.69</v>
       </c>
       <c r="DW5" t="n">
         <v>0.21</v>
@@ -3114,13 +3114,13 @@
         <v>2.64</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.64</v>
+        <v>12</v>
       </c>
       <c r="AR6" t="n">
         <v>10.79</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.93</v>
+        <v>7.07</v>
       </c>
       <c r="AT6" t="n">
         <v>1.29</v>
@@ -3345,13 +3345,13 @@
         <v>2.63</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.44</v>
+        <v>11.63</v>
       </c>
       <c r="DQ6" t="n">
         <v>11</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.63</v>
+        <v>7.7</v>
       </c>
       <c r="DS6" t="n">
         <v>0.07000000000000001</v>
@@ -3839,7 +3839,7 @@
         <v>2.15</v>
       </c>
       <c r="P8" t="n">
-        <v>12.23</v>
+        <v>12.15</v>
       </c>
       <c r="Q8" t="n">
         <v>12.62</v>
@@ -3863,25 +3863,25 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>50.62</v>
+        <v>50.69</v>
       </c>
       <c r="Y8" t="n">
         <v>0.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.15</v>
+        <v>13.23</v>
       </c>
       <c r="AA8" t="n">
         <v>8.77</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.38</v>
+        <v>4.46</v>
       </c>
       <c r="AC8" t="n">
         <v>18.08</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
         <v>2.38</v>
@@ -4151,7 +4151,7 @@
         <v>2</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.68</v>
+        <v>11.64</v>
       </c>
       <c r="DQ8" t="n">
         <v>12.76</v>
@@ -4169,25 +4169,25 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51</v>
+        <v>51.04</v>
       </c>
       <c r="DW8" t="n">
         <v>0.12</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.52</v>
+        <v>12.56</v>
       </c>
       <c r="DY8" t="n">
         <v>8.48</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
       <c r="EA8" t="n">
         <v>18.24</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="EC8" t="n">
         <v>2.28</v>
@@ -4272,19 +4272,19 @@
         <v>0.23</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.69</v>
+        <v>9.77</v>
       </c>
       <c r="AA9" t="n">
         <v>6.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.23</v>
+        <v>3.31</v>
       </c>
       <c r="AC9" t="n">
         <v>15.69</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AE9" t="n">
         <v>2.85</v>
@@ -4578,19 +4578,19 @@
         <v>0.16</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.52</v>
+        <v>9.56</v>
       </c>
       <c r="DY9" t="n">
         <v>6.24</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="EA9" t="n">
         <v>17.12</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="EC9" t="n">
         <v>2.56</v>
@@ -4645,13 +4645,13 @@
         <v>2.14</v>
       </c>
       <c r="P10" t="n">
-        <v>10.86</v>
+        <v>11.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.71</v>
+        <v>12.79</v>
       </c>
       <c r="R10" t="n">
-        <v>6.36</v>
+        <v>6.43</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -4669,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>57.14</v>
+        <v>57.29</v>
       </c>
       <c r="Y10" t="n">
         <v>0.14</v>
@@ -4684,7 +4684,7 @@
         <v>5.29</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.14</v>
+        <v>18.21</v>
       </c>
       <c r="AD10" t="n">
         <v>1.61</v>
@@ -4957,13 +4957,13 @@
         <v>2.21</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.45</v>
+        <v>10.59</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.9</v>
+        <v>12.93</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.31</v>
+        <v>7.35</v>
       </c>
       <c r="DS10" t="n">
         <v>0.2</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>56.17</v>
+        <v>56.25</v>
       </c>
       <c r="DW10" t="n">
         <v>0.13</v>
@@ -4990,7 +4990,7 @@
         <v>5.41</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.76</v>
+        <v>18.79</v>
       </c>
       <c r="EB10" t="n">
         <v>1.47</v>
@@ -5129,7 +5129,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.92</v>
+        <v>12.15</v>
       </c>
       <c r="AR11" t="n">
         <v>12.23</v>
@@ -5153,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>47.54</v>
+        <v>47.46</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.31</v>
@@ -5240,7 +5240,7 @@
         <v>3.73</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="CC11" t="n">
         <v>3.66</v>
@@ -5360,7 +5360,7 @@
         <v>1.56</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.96</v>
+        <v>12.08</v>
       </c>
       <c r="DQ11" t="n">
         <v>11.84</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.48</v>
+        <v>49.44</v>
       </c>
       <c r="DW11" t="n">
         <v>0.2</v>
@@ -5562,10 +5562,10 @@
         <v>0.36</v>
       </c>
       <c r="BA12" t="n">
-        <v>13.86</v>
+        <v>13.93</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.57</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BC12" t="n">
         <v>4.29</v>
@@ -5787,10 +5787,10 @@
         <v>0.34</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.97</v>
+        <v>14</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.56</v>
+        <v>9.59</v>
       </c>
       <c r="DZ12" t="n">
         <v>4.41</v>
@@ -5935,13 +5935,13 @@
         <v>2.23</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.62</v>
+        <v>12.77</v>
       </c>
       <c r="AR13" t="n">
         <v>12.92</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.38</v>
+        <v>10.46</v>
       </c>
       <c r="AT13" t="n">
         <v>1.92</v>
@@ -6166,13 +6166,13 @@
         <v>2</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.68</v>
+        <v>11.76</v>
       </c>
       <c r="DQ13" t="n">
         <v>12.52</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DS13" t="n">
         <v>0.04</v>
@@ -6371,16 +6371,16 @@
         <v>10.71</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.29</v>
+        <v>7.21</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="BD14" t="n">
         <v>18.07</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BF14" t="n">
         <v>3.14</v>
@@ -6596,10 +6596,10 @@
         <v>11.85</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.16</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.69</v>
+        <v>3.73</v>
       </c>
       <c r="EA14" t="n">
         <v>18.69</v>
@@ -7547,7 +7547,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.8</v>
+        <v>11.87</v>
       </c>
       <c r="AR17" t="n">
         <v>12.87</v>
@@ -7658,13 +7658,13 @@
         <v>3.78</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="CC17" t="n">
         <v>2.53</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CE17" t="n">
         <v>1.29</v>
@@ -7724,7 +7724,7 @@
         <v>1.78</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY17" t="n">
         <v>1.88</v>
@@ -7778,7 +7778,7 @@
         <v>2.74</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.49</v>
+        <v>11.52</v>
       </c>
       <c r="DQ17" t="n">
         <v>13.65</v>
@@ -8272,7 +8272,7 @@
         <v>2.88</v>
       </c>
       <c r="P19" t="n">
-        <v>11.88</v>
+        <v>12</v>
       </c>
       <c r="Q19" t="n">
         <v>11.5</v>
@@ -8302,19 +8302,19 @@
         <v>0.06</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.06</v>
+        <v>19.12</v>
       </c>
       <c r="AA19" t="n">
-        <v>12.75</v>
+        <v>12.81</v>
       </c>
       <c r="AB19" t="n">
         <v>6.31</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.62</v>
+        <v>18.69</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AE19" t="n">
         <v>1.88</v>
@@ -8584,7 +8584,7 @@
         <v>2.71</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.94</v>
+        <v>13</v>
       </c>
       <c r="DQ19" t="n">
         <v>12.1</v>
@@ -8608,16 +8608,16 @@
         <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.26</v>
+        <v>17.29</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.52</v>
+        <v>11.55</v>
       </c>
       <c r="DZ19" t="n">
         <v>5.74</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.58</v>
+        <v>19.61</v>
       </c>
       <c r="EB19" t="n">
         <v>1.67</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="G2" t="n">
-        <v>3.54</v>
+        <v>3.29</v>
       </c>
       <c r="H2" t="n">
-        <v>100.85</v>
+        <v>100.57</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="K2" t="n">
-        <v>6.77</v>
+        <v>6.36</v>
       </c>
       <c r="L2" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="M2" t="n">
-        <v>58.54</v>
+        <v>57.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="O2" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="P2" t="n">
-        <v>11.46</v>
+        <v>11.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.92</v>
+        <v>12.07</v>
       </c>
       <c r="R2" t="n">
-        <v>6.08</v>
+        <v>6.21</v>
       </c>
       <c r="S2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="U2" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="V2" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>56.77</v>
+        <v>57.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.69</v>
+        <v>16.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.38</v>
+        <v>10.29</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.31</v>
+        <v>6.21</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.46</v>
+        <v>20.71</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
         <v>0.07000000000000001</v>
@@ -1550,28 +1550,28 @@
         <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.15</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BO2" t="n">
         <v>1.04</v>
@@ -1580,40 +1580,40 @@
         <v>4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.04</v>
+        <v>4.86</v>
       </c>
       <c r="BR2" t="n">
-        <v>92.59</v>
+        <v>92.86</v>
       </c>
       <c r="BS2" t="n">
-        <v>77.78</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>48.15</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>29.63</v>
+        <v>28.57</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.11</v>
+        <v>10.71</v>
       </c>
       <c r="BW2" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BX2" t="n">
-        <v>48.15</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CA2" t="n">
         <v>3.92</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="CC2" t="n">
         <v>2.29</v>
@@ -1622,52 +1622,52 @@
         <v>2.44</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CH2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CK2" t="n">
         <v>1.43</v>
       </c>
-      <c r="CI2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.42</v>
-      </c>
       <c r="CL2" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO2" t="n">
         <v>1.2</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CR2" t="n">
         <v>1.4</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CU2" t="n">
         <v>1.52</v>
@@ -1676,19 +1676,19 @@
         <v>2.05</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DB2" t="n">
         <v>1.27</v>
@@ -1697,61 +1697,61 @@
         <v>1.86</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="DE2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.33</v>
+        <v>3.22</v>
       </c>
       <c r="DH2" t="n">
-        <v>101.71</v>
+        <v>101.54</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.96</v>
+        <v>5.79</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM2" t="n">
-        <v>53.93</v>
+        <v>53.57</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.7</v>
+        <v>10.75</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.52</v>
+        <v>12.57</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.48</v>
+        <v>6.54</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>55.59</v>
+        <v>56</v>
       </c>
       <c r="DW2" t="n">
         <v>0.11</v>
@@ -1760,19 +1760,19 @@
         <v>13.93</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.07</v>
+        <v>9.08</v>
       </c>
       <c r="DZ2" t="n">
         <v>4.85</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.96</v>
+        <v>19.14</v>
       </c>
       <c r="EB2" t="n">
         <v>1.61</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
         <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="G3" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="H3" t="n">
-        <v>77.33</v>
+        <v>78.69</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="K3" t="n">
-        <v>3.83</v>
+        <v>3.69</v>
       </c>
       <c r="L3" t="n">
         <v>-0.08</v>
       </c>
       <c r="M3" t="n">
-        <v>35.75</v>
+        <v>36.85</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="P3" t="n">
-        <v>13.83</v>
+        <v>13.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.83</v>
+        <v>13.46</v>
       </c>
       <c r="R3" t="n">
-        <v>9.5</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>45.17</v>
+        <v>45</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="Z3" t="n">
         <v>12</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.75</v>
+        <v>7.77</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD3" t="n">
         <v>1.32</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AF3" t="n">
         <v>0.08</v>
@@ -1953,70 +1953,70 @@
         <v>2.15</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.880000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.96</v>
+        <v>3.88</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="BR3" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS3" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BT3" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BU3" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BV3" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="BW3" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BX3" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.31</v>
+        <v>3.22</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="CC3" t="n">
         <v>4.57</v>
@@ -2028,10 +2028,10 @@
         <v>1.33</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CH3" t="n">
         <v>1.46</v>
@@ -2043,31 +2043,31 @@
         <v>1.74</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP3" t="n">
         <v>1.83</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CR3" t="n">
         <v>1.4</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CT3" t="n">
         <v>3.08</v>
@@ -2082,16 +2082,16 @@
         <v>1.76</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="DB3" t="n">
         <v>1.27</v>
@@ -2100,82 +2100,82 @@
         <v>1.88</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DH3" t="n">
-        <v>71.68000000000001</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="DL3" t="n">
         <v>0.08</v>
       </c>
       <c r="DM3" t="n">
-        <v>28.68</v>
+        <v>29.5</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.84</v>
+        <v>11.96</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.28</v>
+        <v>13.12</v>
       </c>
       <c r="DR3" t="n">
         <v>10</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>45.36</v>
+        <v>45.27</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.56</v>
+        <v>10.62</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.16</v>
+        <v>7.19</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.16</v>
+        <v>17.38</v>
       </c>
       <c r="EB3" t="n">
         <v>1.12</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
         <v>13</v>
@@ -2197,28 +2197,28 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="G4" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="H4" t="n">
-        <v>71.08</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="J4" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="K4" t="n">
-        <v>4.33</v>
+        <v>4.54</v>
       </c>
       <c r="L4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="M4" t="n">
-        <v>24.5</v>
+        <v>26.08</v>
       </c>
       <c r="N4" t="n">
         <v>0.92</v>
@@ -2227,52 +2227,52 @@
         <v>2.08</v>
       </c>
       <c r="P4" t="n">
-        <v>10.5</v>
+        <v>10.69</v>
       </c>
       <c r="Q4" t="n">
         <v>11.92</v>
       </c>
       <c r="R4" t="n">
-        <v>8.5</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="T4" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="U4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.17</v>
+        <v>48.85</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.75</v>
+        <v>9.23</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.17</v>
+        <v>6.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.58</v>
+        <v>3.08</v>
       </c>
       <c r="AC4" t="n">
-        <v>22.75</v>
+        <v>22.46</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AF4" t="n">
         <v>0.23</v>
@@ -2356,70 +2356,70 @@
         <v>2.08</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.2</v>
+        <v>4.23</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BT4" t="n">
-        <v>60</v>
+        <v>61.54</v>
       </c>
       <c r="BU4" t="n">
-        <v>36</v>
+        <v>38.46</v>
       </c>
       <c r="BV4" t="n">
-        <v>28</v>
+        <v>30.77</v>
       </c>
       <c r="BW4" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX4" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.01</v>
+        <v>2.91</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="CC4" t="n">
         <v>3.96</v>
@@ -2431,7 +2431,7 @@
         <v>1.27</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CG4" t="n">
         <v>3.01</v>
@@ -2443,16 +2443,16 @@
         <v>2.05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CN4" t="n">
         <v>1.86</v>
@@ -2473,13 +2473,13 @@
         <v>2.71</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CU4" t="n">
         <v>1.5</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CW4" t="n">
         <v>1.69</v>
@@ -2488,13 +2488,13 @@
         <v>1.54</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB4" t="n">
         <v>1.25</v>
@@ -2509,76 +2509,76 @@
         <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="DH4" t="n">
-        <v>74.2</v>
+        <v>74.81</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DM4" t="n">
-        <v>31.96</v>
+        <v>32.46</v>
       </c>
       <c r="DN4" t="n">
         <v>1</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.44</v>
+        <v>11.5</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.6</v>
+        <v>12.58</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.64</v>
+        <v>48</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.48</v>
+        <v>10.66</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.76</v>
+        <v>6.73</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.72</v>
+        <v>3.92</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.52</v>
+        <v>20.46</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" t="n">
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>0.13</v>
@@ -2678,139 +2678,139 @@
         <v>2.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AH5" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AI5" t="n">
-        <v>97</v>
+        <v>94.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>38.43</v>
+        <v>38.93</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.789999999999999</v>
+        <v>10.27</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.93</v>
+        <v>14.07</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.07</v>
+        <v>8.93</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>52</v>
+        <v>52.07</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.14</v>
+        <v>14.27</v>
       </c>
       <c r="BB5" t="n">
         <v>8.93</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.21</v>
+        <v>5.33</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.21</v>
+        <v>21.67</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="BG5" t="n">
         <v>2.9</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.210000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="BI5" t="n">
         <v>2.9</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL5" t="n">
         <v>0.83</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.24</v>
+        <v>5.13</v>
       </c>
       <c r="BR5" t="n">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="BS5" t="n">
-        <v>82.76000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="BT5" t="n">
-        <v>51.72</v>
+        <v>53.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>27.59</v>
+        <v>26.67</v>
       </c>
       <c r="BV5" t="n">
-        <v>24.14</v>
+        <v>23.33</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
       <c r="BX5" t="n">
-        <v>65.52</v>
+        <v>66.67</v>
       </c>
       <c r="BY5" t="n">
         <v>1.77</v>
@@ -2819,28 +2819,28 @@
         <v>1.85</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.08</v>
+        <v>4.12</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CI5" t="n">
         <v>2.07</v>
@@ -2852,10 +2852,10 @@
         <v>1.49</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CN5" t="n">
         <v>1.9</v>
@@ -2867,13 +2867,13 @@
         <v>1.74</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CR5" t="n">
         <v>1.37</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="CT5" t="n">
         <v>3.2</v>
@@ -2909,79 +2909,79 @@
         <v>2.92</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="DH5" t="n">
-        <v>100.86</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="DI5" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM5" t="n">
-        <v>47.31</v>
+        <v>47.26</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.97</v>
+        <v>0.93</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.07</v>
+        <v>11.27</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.41</v>
+        <v>12.54</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.31</v>
+        <v>8.26</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.69</v>
+        <v>54.64</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.76</v>
+        <v>16.74</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.83</v>
+        <v>10.76</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.93</v>
+        <v>5.96</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.72</v>
+        <v>21.94</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="6">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" t="n">
         <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
         <v>0.2</v>
@@ -3484,139 +3484,139 @@
         <v>2.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AI7" t="n">
-        <v>76.15000000000001</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.77</v>
+        <v>3.71</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AN7" t="n">
-        <v>38.15</v>
+        <v>37.86</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.69</v>
+        <v>12.79</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.69</v>
+        <v>13.64</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.15</v>
+        <v>10.43</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>46</v>
+        <v>45.07</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.92</v>
+        <v>10.93</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.31</v>
+        <v>7.29</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="BD7" t="n">
-        <v>20.77</v>
+        <v>21</v>
       </c>
       <c r="BE7" t="n">
         <v>1.22</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.859999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BL7" t="n">
         <v>0.86</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="BP7" t="n">
         <v>4</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.21</v>
+        <v>4.07</v>
       </c>
       <c r="BR7" t="n">
-        <v>96.43000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="BS7" t="n">
-        <v>85.70999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>64.29000000000001</v>
+        <v>65.52</v>
       </c>
       <c r="BU7" t="n">
-        <v>35.71</v>
+        <v>34.48</v>
       </c>
       <c r="BV7" t="n">
-        <v>14.29</v>
+        <v>13.79</v>
       </c>
       <c r="BW7" t="n">
-        <v>10.71</v>
+        <v>10.34</v>
       </c>
       <c r="BX7" t="n">
-        <v>75</v>
+        <v>75.86</v>
       </c>
       <c r="BY7" t="n">
         <v>2.68</v>
@@ -3625,22 +3625,22 @@
         <v>2.82</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.02</v>
+        <v>4.2</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.63</v>
+        <v>4.66</v>
       </c>
       <c r="CE7" t="n">
         <v>1.36</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CG7" t="n">
         <v>2.92</v>
@@ -3649,22 +3649,22 @@
         <v>1.43</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO7" t="n">
         <v>1.26</v>
@@ -3673,22 +3673,22 @@
         <v>1.9</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CR7" t="n">
         <v>1.4</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CU7" t="n">
         <v>1.46</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CW7" t="n">
         <v>1.82</v>
@@ -3697,13 +3697,13 @@
         <v>1.59</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DB7" t="n">
         <v>1.3</v>
@@ -3712,82 +3712,82 @@
         <v>1.98</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="DH7" t="n">
-        <v>84.20999999999999</v>
+        <v>84.48</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM7" t="n">
-        <v>37.6</v>
+        <v>37.48</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.04</v>
+        <v>12.11</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.04</v>
+        <v>13.03</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.109999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49.07</v>
+        <v>48.51</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.78</v>
+        <v>11.76</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.86</v>
+        <v>7.83</v>
       </c>
       <c r="DZ7" t="n">
         <v>3.93</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.96</v>
+        <v>22.03</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="8">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
         <v>0.15</v>
@@ -4293,49 +4293,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AI9" t="n">
-        <v>74.92</v>
+        <v>75.38</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.58</v>
+        <v>3.31</v>
       </c>
       <c r="AM9" t="n">
         <v>-0.08</v>
       </c>
       <c r="AN9" t="n">
-        <v>33.17</v>
+        <v>32.85</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12</v>
+        <v>12.15</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.17</v>
+        <v>13.23</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.67</v>
+        <v>10.69</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>44</v>
+        <v>43.92</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.08</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.33</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BB9" t="n">
         <v>6</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="BD9" t="n">
-        <v>18.67</v>
+        <v>18.54</v>
       </c>
       <c r="BE9" t="n">
         <v>1.07</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.52</v>
+        <v>9.42</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.52</v>
+        <v>0.65</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.28</v>
+        <v>4.19</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="BR9" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS9" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BT9" t="n">
-        <v>60</v>
+        <v>61.54</v>
       </c>
       <c r="BU9" t="n">
-        <v>36</v>
+        <v>38.46</v>
       </c>
       <c r="BV9" t="n">
-        <v>12</v>
+        <v>15.38</v>
       </c>
       <c r="BW9" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX9" t="n">
-        <v>72</v>
+        <v>73.08</v>
       </c>
       <c r="BY9" t="n">
         <v>3.49</v>
@@ -4437,19 +4437,19 @@
         <v>4.19</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.71</v>
+        <v>5.65</v>
       </c>
       <c r="CD9" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="CE9" t="n">
         <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CH9" t="n">
         <v>1.48</v>
@@ -4461,34 +4461,34 @@
         <v>1.77</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP9" t="n">
         <v>1.8</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS9" t="n">
         <v>2.68</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CU9" t="n">
         <v>1.52</v>
@@ -4500,16 +4500,16 @@
         <v>1.78</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB9" t="n">
         <v>1.26</v>
@@ -4524,13 +4524,13 @@
         <v>0.08</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="DH9" t="n">
-        <v>76.59999999999999</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="DI9" t="n">
         <v>0.12</v>
@@ -4539,28 +4539,28 @@
         <v>2.84</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="DL9" t="n">
         <v>0.12</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.92</v>
+        <v>33.74</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.24</v>
+        <v>11.34</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.88</v>
+        <v>12.92</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.24</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DS9" t="n">
         <v>0.08</v>
@@ -4572,19 +4572,19 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>42.6</v>
+        <v>42.62</v>
       </c>
       <c r="DW9" t="n">
         <v>0.16</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.56</v>
+        <v>9.57</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.24</v>
+        <v>6.23</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="EA9" t="n">
         <v>17.12</v>
@@ -4593,7 +4593,7 @@
         <v>1.06</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
         <v>15</v>
@@ -4615,82 +4615,82 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="H10" t="n">
-        <v>92.43000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.64</v>
+        <v>4.73</v>
       </c>
       <c r="L10" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="M10" t="n">
-        <v>43.93</v>
+        <v>44.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="O10" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="P10" t="n">
-        <v>11.14</v>
+        <v>11.07</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.79</v>
+        <v>12.87</v>
       </c>
       <c r="R10" t="n">
-        <v>6.43</v>
+        <v>6.47</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="T10" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="U10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="V10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>57.29</v>
+        <v>58.53</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.57</v>
+        <v>14.67</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.289999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.29</v>
+        <v>5.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.21</v>
+        <v>17.87</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AF10" t="n">
         <v>0.13</v>
@@ -4774,67 +4774,67 @@
         <v>1.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.07</v>
+        <v>9.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="BJ10" t="n">
         <v>1.1</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.41</v>
+        <v>4.47</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>75.86</v>
+        <v>76.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>51.72</v>
+        <v>53.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>41.38</v>
+        <v>43.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>24.14</v>
+        <v>23.33</v>
       </c>
       <c r="BW10" t="n">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
       <c r="BX10" t="n">
-        <v>51.72</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.79</v>
+        <v>3.81</v>
       </c>
       <c r="CB10" t="n">
         <v>4.11</v>
@@ -4852,22 +4852,22 @@
         <v>2.43</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CH10" t="n">
         <v>1.51</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CM10" t="n">
         <v>2.48</v>
@@ -4879,13 +4879,13 @@
         <v>1.2</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS10" t="n">
         <v>2.54</v>
@@ -4897,13 +4897,13 @@
         <v>1.56</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY10" t="n">
         <v>1.86</v>
@@ -4921,49 +4921,49 @@
         <v>1.73</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="DE10" t="n">
         <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="DH10" t="n">
-        <v>80.38</v>
+        <v>81.86</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.38</v>
+        <v>4.43</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.93</v>
+        <v>37.3</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.59</v>
+        <v>10.57</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.93</v>
+        <v>12.97</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.35</v>
+        <v>7.33</v>
       </c>
       <c r="DS10" t="n">
         <v>0.2</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>56.25</v>
+        <v>56.9</v>
       </c>
       <c r="DW10" t="n">
         <v>0.13</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.1</v>
+        <v>14.17</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.69</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.41</v>
+        <v>5.46</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.79</v>
+        <v>18.6</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
         <v>0.17</v>
@@ -5096,139 +5096,139 @@
         <v>2.17</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG11" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AI11" t="n">
-        <v>84.69</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.54</v>
+        <v>4.79</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AN11" t="n">
-        <v>39.38</v>
+        <v>39.93</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AP11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO11" t="n">
         <v>1.69</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>12.15</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>12.23</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>47.46</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>13.46</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>18.85</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>1.68</v>
-      </c>
       <c r="BP11" t="n">
-        <v>4.08</v>
+        <v>4.23</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.8</v>
+        <v>4.92</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BT11" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BU11" t="n">
-        <v>36</v>
+        <v>34.62</v>
       </c>
       <c r="BV11" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BW11" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX11" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BY11" t="n">
         <v>2.47</v>
@@ -5240,43 +5240,43 @@
         <v>3.73</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="CE11" t="n">
         <v>1.31</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CH11" t="n">
         <v>1.52</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK11" t="n">
         <v>1.41</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CO11" t="n">
         <v>1.2</v>
@@ -5285,7 +5285,7 @@
         <v>1.69</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
@@ -5306,100 +5306,100 @@
         <v>1.67</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DB11" t="n">
         <v>1.23</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="DE11" t="n">
         <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="DH11" t="n">
-        <v>83.12</v>
+        <v>82.77</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.96</v>
+        <v>5.08</v>
       </c>
       <c r="DL11" t="n">
         <v>0.16</v>
       </c>
       <c r="DM11" t="n">
-        <v>40.2</v>
+        <v>40.46</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.08</v>
+        <v>12.16</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.84</v>
+        <v>12.11</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.52</v>
+        <v>9.57</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.44</v>
+        <v>49.69</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX11" t="n">
-        <v>15</v>
+        <v>14.89</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.24</v>
+        <v>10.15</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.76</v>
+        <v>4.73</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.36</v>
+        <v>21.31</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
         <v>14</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="G12" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="H12" t="n">
-        <v>88.23</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="J12" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="K12" t="n">
-        <v>5.08</v>
+        <v>5.29</v>
       </c>
       <c r="L12" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="M12" t="n">
-        <v>37.85</v>
+        <v>38.93</v>
       </c>
       <c r="N12" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="O12" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="P12" t="n">
-        <v>11.85</v>
+        <v>12.29</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.46</v>
+        <v>11.86</v>
       </c>
       <c r="R12" t="n">
-        <v>7.77</v>
+        <v>8.07</v>
       </c>
       <c r="S12" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="T12" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="U12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>50.77</v>
+        <v>50.29</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.08</v>
+        <v>14.21</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.539999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.54</v>
+        <v>4.86</v>
       </c>
       <c r="AC12" t="n">
-        <v>16.23</v>
+        <v>16.71</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AF12" t="n">
         <v>0.07000000000000001</v>
@@ -5580,67 +5580,67 @@
         <v>2.14</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.85</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
         <v>0.96</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.04</v>
+        <v>4.18</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.07</v>
+        <v>4.21</v>
       </c>
       <c r="BR12" t="n">
-        <v>92.59</v>
+        <v>92.86</v>
       </c>
       <c r="BS12" t="n">
-        <v>70.37</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>48.15</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>22.22</v>
+        <v>21.43</v>
       </c>
       <c r="BV12" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>44.44</v>
+        <v>46.43</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="CB12" t="n">
         <v>3.86</v>
@@ -5655,10 +5655,10 @@
         <v>1.33</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CH12" t="n">
         <v>1.46</v>
@@ -5670,22 +5670,22 @@
         <v>1.71</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CN12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CO12" t="n">
         <v>1.24</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CQ12" t="n">
         <v>2.98</v>
@@ -5724,52 +5724,52 @@
         <v>1.27</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="DE12" t="n">
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="DH12" t="n">
-        <v>85.67</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.52</v>
+        <v>4.65</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="DM12" t="n">
-        <v>37.89</v>
+        <v>38.43</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.7</v>
+        <v>11.93</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.93</v>
+        <v>12.11</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.039999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DS12" t="n">
         <v>0.11</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>51.11</v>
+        <v>50.86</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DX12" t="n">
-        <v>14</v>
+        <v>14.07</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.59</v>
+        <v>9.5</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.41</v>
+        <v>4.58</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.89</v>
+        <v>19.04</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="13">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
         <v>13</v>
@@ -5824,49 +5824,49 @@
         <v>0.08</v>
       </c>
       <c r="F13" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="G13" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="H13" t="n">
-        <v>89.83</v>
+        <v>88.31</v>
       </c>
       <c r="I13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="J13" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="K13" t="n">
-        <v>4.08</v>
+        <v>3.92</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="M13" t="n">
-        <v>40.08</v>
+        <v>38.38</v>
       </c>
       <c r="N13" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="O13" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="P13" t="n">
-        <v>10.67</v>
+        <v>10.54</v>
       </c>
       <c r="Q13" t="n">
         <v>12.08</v>
       </c>
       <c r="R13" t="n">
-        <v>7.83</v>
+        <v>7.92</v>
       </c>
       <c r="S13" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="T13" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>49.92</v>
+        <v>49.08</v>
       </c>
       <c r="Y13" t="n">
         <v>0.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.17</v>
+        <v>13.62</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.83</v>
+        <v>8.69</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.33</v>
+        <v>4.92</v>
       </c>
       <c r="AC13" t="n">
-        <v>21.08</v>
+        <v>20.54</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>2.38</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="BM13" t="n">
         <v>0.96</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.32</v>
+        <v>4.27</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.16</v>
+        <v>5.19</v>
       </c>
       <c r="BR13" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>68</v>
+        <v>69.23</v>
       </c>
       <c r="BT13" t="n">
-        <v>60</v>
+        <v>61.54</v>
       </c>
       <c r="BU13" t="n">
-        <v>40</v>
+        <v>42.31</v>
       </c>
       <c r="BV13" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BW13" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BX13" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.52</v>
+        <v>3.57</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="CC13" t="n">
         <v>5.08</v>
@@ -6064,19 +6064,19 @@
         <v>2.97</v>
       </c>
       <c r="CH13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CK13" t="n">
         <v>1.46</v>
       </c>
-      <c r="CI13" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="CJ13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="CK13" t="n">
-        <v>1.45</v>
-      </c>
       <c r="CL13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CM13" t="n">
         <v>2.51</v>
@@ -6097,19 +6097,19 @@
         <v>1.39</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CX13" t="n">
         <v>1.52</v>
@@ -6127,52 +6127,52 @@
         <v>1.29</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="DE13" t="n">
         <v>0.04</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="DH13" t="n">
-        <v>82.31999999999999</v>
+        <v>81.84</v>
       </c>
       <c r="DI13" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.84</v>
+        <v>4.73</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM13" t="n">
-        <v>33.72</v>
+        <v>33.12</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="DO13" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.76</v>
+        <v>11.66</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.52</v>
+        <v>12.5</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="DS13" t="n">
         <v>0.04</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.92</v>
+        <v>47.58</v>
       </c>
       <c r="DW13" t="n">
         <v>0.16</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.96</v>
+        <v>12.24</v>
       </c>
       <c r="DY13" t="n">
-        <v>8</v>
+        <v>7.96</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.96</v>
+        <v>4.27</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.24</v>
+        <v>20</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="14">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
         <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F14" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="G14" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="H14" t="n">
-        <v>92.25</v>
+        <v>89.69</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="K14" t="n">
-        <v>4.58</v>
+        <v>4.38</v>
       </c>
       <c r="L14" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="M14" t="n">
-        <v>44.33</v>
+        <v>42.31</v>
       </c>
       <c r="N14" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="O14" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="P14" t="n">
-        <v>11.58</v>
+        <v>11.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>11.08</v>
+        <v>10.46</v>
       </c>
       <c r="R14" t="n">
-        <v>10.08</v>
+        <v>10.31</v>
       </c>
       <c r="S14" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>56.67</v>
+        <v>55.31</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.17</v>
+        <v>13.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.17</v>
+        <v>8.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>4</v>
+        <v>4.23</v>
       </c>
       <c r="AC14" t="n">
-        <v>19.42</v>
+        <v>19.15</v>
       </c>
       <c r="AD14" t="n">
         <v>1.43</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
         <v>0.07000000000000001</v>
@@ -6386,64 +6386,64 @@
         <v>3.14</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.77</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.27</v>
+        <v>4.37</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.42</v>
+        <v>4.59</v>
       </c>
       <c r="BR14" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS14" t="n">
-        <v>84.62</v>
+        <v>85.19</v>
       </c>
       <c r="BT14" t="n">
-        <v>46.15</v>
+        <v>48.15</v>
       </c>
       <c r="BU14" t="n">
-        <v>38.46</v>
+        <v>40.74</v>
       </c>
       <c r="BV14" t="n">
-        <v>23.08</v>
+        <v>25.93</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>69.23</v>
+        <v>70.37</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="CA14" t="n">
         <v>3.48</v>
@@ -6461,28 +6461,28 @@
         <v>1.37</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="CG14" t="n">
         <v>2.91</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI14" t="n">
         <v>1.99</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CN14" t="n">
         <v>1.84</v>
@@ -6491,25 +6491,25 @@
         <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CR14" t="n">
         <v>1.4</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CU14" t="n">
         <v>1.44</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CW14" t="n">
         <v>1.83</v>
@@ -6527,88 +6527,88 @@
         <v>1.84</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="DG14" t="n">
         <v>1.92</v>
       </c>
       <c r="DH14" t="n">
-        <v>83.84</v>
+        <v>82.92</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.11</v>
+        <v>4.03</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM14" t="n">
-        <v>41.42</v>
+        <v>40.56</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.54</v>
+        <v>12.33</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.88</v>
+        <v>10.59</v>
       </c>
       <c r="DR14" t="n">
-        <v>11.73</v>
+        <v>11.78</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.62</v>
+        <v>51.15</v>
       </c>
       <c r="DW14" t="n">
         <v>0.11</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.85</v>
+        <v>11.88</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.109999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.73</v>
+        <v>3.85</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.69</v>
+        <v>18.59</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" t="n">
         <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
         <v>0.08</v>
@@ -6711,49 +6711,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AI15" t="n">
-        <v>54.58</v>
+        <v>53.46</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AN15" t="n">
-        <v>22.08</v>
+        <v>23.08</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ15" t="n">
         <v>10.08</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.33</v>
+        <v>12.38</v>
       </c>
       <c r="AS15" t="n">
-        <v>10.83</v>
+        <v>10.69</v>
       </c>
       <c r="AT15" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AV15" t="n">
         <v>0.08</v>
@@ -6765,82 +6765,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>33.08</v>
+        <v>32.38</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.75</v>
+        <v>5.54</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="BD15" t="n">
-        <v>16.25</v>
+        <v>16.69</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.25</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.71</v>
+        <v>4.68</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS15" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT15" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BU15" t="n">
-        <v>33.33</v>
+        <v>36</v>
       </c>
       <c r="BV15" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX15" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BY15" t="n">
         <v>3.22</v>
@@ -6849,25 +6849,25 @@
         <v>3.58</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="CC15" t="n">
-        <v>7.07</v>
+        <v>7.04</v>
       </c>
       <c r="CD15" t="n">
-        <v>7.49</v>
+        <v>7.39</v>
       </c>
       <c r="CE15" t="n">
         <v>1.3</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CH15" t="n">
         <v>1.4</v>
@@ -6876,37 +6876,37 @@
         <v>1.83</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CK15" t="n">
         <v>1.39</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CU15" t="n">
         <v>1.49</v>
@@ -6915,13 +6915,13 @@
         <v>1.97</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX15" t="n">
         <v>1.51</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.45</v>
@@ -6936,49 +6936,49 @@
         <v>1.9</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="DE15" t="n">
         <v>0.04</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="DH15" t="n">
-        <v>66.62</v>
+        <v>65.56</v>
       </c>
       <c r="DI15" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="DM15" t="n">
-        <v>25.38</v>
+        <v>25.76</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.75</v>
+        <v>11.68</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.2</v>
+        <v>12.24</v>
       </c>
       <c r="DR15" t="n">
-        <v>10.7</v>
+        <v>10.64</v>
       </c>
       <c r="DS15" t="n">
         <v>0.2</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>37.2</v>
+        <v>36.68</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.67</v>
+        <v>9.52</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.08</v>
+        <v>5.96</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.88</v>
+        <v>18.04</v>
       </c>
       <c r="EB15" t="n">
         <v>1.03</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="16">
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
         <v>13</v>
@@ -7033,82 +7033,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="G16" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="H16" t="n">
-        <v>67.17</v>
+        <v>66.92</v>
       </c>
       <c r="I16" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="J16" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="K16" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="M16" t="n">
-        <v>33.83</v>
+        <v>33.38</v>
       </c>
       <c r="N16" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O16" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="P16" t="n">
-        <v>13</v>
+        <v>12.69</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.33</v>
+        <v>14.54</v>
       </c>
       <c r="R16" t="n">
         <v>9.92</v>
       </c>
       <c r="S16" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="U16" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V16" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>43.58</v>
+        <v>43.85</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.58</v>
+        <v>12.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.92</v>
+        <v>7.62</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.67</v>
+        <v>4.46</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.33</v>
+        <v>19.77</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AF16" t="n">
         <v>0.08</v>
@@ -7192,70 +7192,70 @@
         <v>2.85</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.2</v>
+        <v>10.04</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BL16" t="n">
         <v>0.88</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.76</v>
+        <v>5.62</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BT16" t="n">
-        <v>72</v>
+        <v>73.08</v>
       </c>
       <c r="BU16" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BV16" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BW16" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX16" t="n">
-        <v>60</v>
+        <v>61.54</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.47</v>
+        <v>3.81</v>
       </c>
       <c r="CA16" t="n">
         <v>4.21</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="CC16" t="n">
         <v>6.44</v>
@@ -7279,19 +7279,19 @@
         <v>2.19</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CO16" t="n">
         <v>1.17</v>
@@ -7300,37 +7300,37 @@
         <v>1.62</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CT16" t="n">
         <v>3.22</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CW16" t="n">
         <v>1.68</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DB16" t="n">
         <v>1.2</v>
@@ -7345,43 +7345,43 @@
         <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="DH16" t="n">
-        <v>74.59999999999999</v>
+        <v>74.19</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.2</v>
+        <v>4.12</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DM16" t="n">
-        <v>33.6</v>
+        <v>33.38</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.48</v>
+        <v>11.38</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.84</v>
+        <v>13.96</v>
       </c>
       <c r="DR16" t="n">
-        <v>10.88</v>
+        <v>10.84</v>
       </c>
       <c r="DS16" t="n">
         <v>0.16</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.52</v>
+        <v>44.62</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DX16" t="n">
-        <v>11</v>
+        <v>10.81</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.96</v>
+        <v>6.85</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.36</v>
+        <v>18.62</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" t="n">
         <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
         <v>0.19</v>
@@ -7514,139 +7514,139 @@
         <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="AI17" t="n">
-        <v>89.47</v>
+        <v>91</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.93</v>
+        <v>5.06</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>38.33</v>
+        <v>38.88</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.87</v>
+        <v>11.88</v>
       </c>
       <c r="AR17" t="n">
-        <v>12.87</v>
+        <v>12.75</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.07</v>
+        <v>8.94</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>52.6</v>
+        <v>53.12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="BA17" t="n">
-        <v>13.53</v>
+        <v>13.81</v>
       </c>
       <c r="BB17" t="n">
-        <v>8</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.53</v>
+        <v>5.44</v>
       </c>
       <c r="BD17" t="n">
-        <v>17.73</v>
+        <v>18</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.26</v>
+        <v>9.25</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.19</v>
+        <v>4.16</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.87</v>
+        <v>4.91</v>
       </c>
       <c r="BR17" t="n">
-        <v>90.31999999999999</v>
+        <v>90.62</v>
       </c>
       <c r="BS17" t="n">
-        <v>77.42</v>
+        <v>78.12</v>
       </c>
       <c r="BT17" t="n">
-        <v>51.61</v>
+        <v>53.12</v>
       </c>
       <c r="BU17" t="n">
-        <v>29.03</v>
+        <v>31.25</v>
       </c>
       <c r="BV17" t="n">
-        <v>19.35</v>
+        <v>18.75</v>
       </c>
       <c r="BW17" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="BX17" t="n">
-        <v>58.06</v>
+        <v>59.38</v>
       </c>
       <c r="BY17" t="n">
         <v>1.64</v>
@@ -7655,22 +7655,22 @@
         <v>1.64</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="CE17" t="n">
         <v>1.29</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CG17" t="n">
         <v>2.98</v>
@@ -7685,16 +7685,16 @@
         <v>1.75</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CM17" t="n">
         <v>2.38</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO17" t="n">
         <v>1.2</v>
@@ -7709,10 +7709,10 @@
         <v>1.38</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CU17" t="n">
         <v>1.49</v>
@@ -7721,7 +7721,7 @@
         <v>2.11</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CX17" t="n">
         <v>1.54</v>
@@ -7739,85 +7739,85 @@
         <v>1.26</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="DH17" t="n">
-        <v>91.13</v>
+        <v>91.84</v>
       </c>
       <c r="DI17" t="n">
         <v>0.03</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.48</v>
+        <v>5.53</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="DM17" t="n">
-        <v>45.71</v>
+        <v>45.75</v>
       </c>
       <c r="DN17" t="n">
         <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.52</v>
+        <v>11.54</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.65</v>
+        <v>13.57</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.71</v>
+        <v>7.69</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.26</v>
+        <v>54.46</v>
       </c>
       <c r="DW17" t="n">
         <v>0.19</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.35</v>
+        <v>15.43</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.74</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.61</v>
+        <v>5.56</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.48</v>
+        <v>18.6</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
         <v>0.12</v>
@@ -7920,13 +7920,13 @@
         <v>0.08</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AI18" t="n">
-        <v>69.67</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="AJ18" t="n">
         <v>0.08</v>
@@ -7935,121 +7935,121 @@
         <v>3.08</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AN18" t="n">
-        <v>33.33</v>
+        <v>34.38</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="AR18" t="n">
-        <v>11.92</v>
+        <v>12.15</v>
       </c>
       <c r="AS18" t="n">
-        <v>11.42</v>
+        <v>11</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>43.58</v>
+        <v>44.62</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.42</v>
+        <v>10.92</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.25</v>
+        <v>7.69</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="BD18" t="n">
-        <v>18.17</v>
+        <v>18.85</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="BG18" t="n">
         <v>2.79</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.210000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI18" t="n">
         <v>2.79</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="BR18" t="n">
-        <v>89.29000000000001</v>
+        <v>89.66</v>
       </c>
       <c r="BS18" t="n">
-        <v>78.56999999999999</v>
+        <v>79.31</v>
       </c>
       <c r="BT18" t="n">
-        <v>46.43</v>
+        <v>48.28</v>
       </c>
       <c r="BU18" t="n">
-        <v>35.71</v>
+        <v>34.48</v>
       </c>
       <c r="BV18" t="n">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="BX18" t="n">
-        <v>50</v>
+        <v>51.72</v>
       </c>
       <c r="BY18" t="n">
         <v>2.31</v>
@@ -8058,169 +8058,169 @@
         <v>2.42</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.13</v>
+        <v>4.11</v>
       </c>
       <c r="CC18" t="n">
-        <v>5.2</v>
+        <v>5.07</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.67</v>
+        <v>5.51</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CH18" t="n">
         <v>1.39</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CN18" t="n">
         <v>1.7</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CW18" t="n">
         <v>1.64</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="DE18" t="n">
         <v>0.1</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="DH18" t="n">
-        <v>79.25</v>
+        <v>79.28</v>
       </c>
       <c r="DI18" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM18" t="n">
-        <v>36</v>
+        <v>36.38</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.25</v>
+        <v>12.14</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.04</v>
+        <v>13.1</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.07</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.96</v>
+        <v>47.31</v>
       </c>
       <c r="DW18" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.75</v>
+        <v>11.93</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.68</v>
+        <v>7.86</v>
       </c>
       <c r="DZ18" t="n">
         <v>4.07</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.68</v>
+        <v>18</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C19" t="n">
         <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
         <v>0.12</v>
@@ -8320,52 +8320,52 @@
         <v>1.88</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="AI19" t="n">
-        <v>76.59999999999999</v>
+        <v>79.19</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.4</v>
+        <v>5.94</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="AN19" t="n">
-        <v>36</v>
+        <v>38.38</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.53</v>
+        <v>2.81</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14.07</v>
+        <v>13.31</v>
       </c>
       <c r="AR19" t="n">
-        <v>12.73</v>
+        <v>12.44</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.67</v>
+        <v>8.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8377,82 +8377,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>52.87</v>
+        <v>53.38</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="BA19" t="n">
-        <v>15.33</v>
+        <v>15.88</v>
       </c>
       <c r="BB19" t="n">
-        <v>10.2</v>
+        <v>10.56</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.13</v>
+        <v>5.31</v>
       </c>
       <c r="BD19" t="n">
-        <v>20.6</v>
+        <v>20.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.06</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.32</v>
+        <v>4.47</v>
       </c>
       <c r="BR19" t="n">
-        <v>83.87</v>
+        <v>84.38</v>
       </c>
       <c r="BS19" t="n">
-        <v>67.73999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="BT19" t="n">
-        <v>51.61</v>
+        <v>53.12</v>
       </c>
       <c r="BU19" t="n">
-        <v>38.71</v>
+        <v>40.62</v>
       </c>
       <c r="BV19" t="n">
-        <v>16.13</v>
+        <v>18.75</v>
       </c>
       <c r="BW19" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="BX19" t="n">
-        <v>48.39</v>
+        <v>50</v>
       </c>
       <c r="BY19" t="n">
         <v>1.58</v>
@@ -8461,16 +8461,16 @@
         <v>1.58</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.15</v>
+        <v>4.13</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.54</v>
+        <v>4.51</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CE19" t="n">
         <v>1.28</v>
@@ -8479,7 +8479,7 @@
         <v>2.33</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CH19" t="n">
         <v>1.58</v>
@@ -8491,13 +8491,13 @@
         <v>1.64</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CN19" t="n">
         <v>1.85</v>
@@ -8506,19 +8506,19 @@
         <v>1.17</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CR19" t="n">
         <v>1.36</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="CU19" t="n">
         <v>1.62</v>
@@ -8542,88 +8542,88 @@
         <v>1.9</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC19" t="n">
         <v>1.66</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="DH19" t="n">
-        <v>84.90000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.42</v>
+        <v>5.69</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="DM19" t="n">
-        <v>40.39</v>
+        <v>41.44</v>
       </c>
       <c r="DN19" t="n">
         <v>1.16</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="DP19" t="n">
-        <v>13</v>
+        <v>12.66</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.1</v>
+        <v>11.97</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.710000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.2</v>
+        <v>55.38</v>
       </c>
       <c r="DW19" t="n">
         <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.29</v>
+        <v>17.5</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.55</v>
+        <v>11.68</v>
       </c>
       <c r="DZ19" t="n">
-        <v>5.74</v>
+        <v>5.81</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.61</v>
+        <v>19.72</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
         <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
         <v>0.08</v>
@@ -3890,49 +3890,49 @@
         <v>0.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.67</v>
+        <v>79.77</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.75</v>
+        <v>4.69</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AN8" t="n">
-        <v>30.67</v>
+        <v>33.46</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.08</v>
+        <v>11.15</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.92</v>
+        <v>12.54</v>
       </c>
       <c r="AS8" t="n">
-        <v>10.17</v>
+        <v>9.77</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>51.42</v>
+        <v>52.38</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.83</v>
+        <v>12.31</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.17</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.67</v>
+        <v>3.92</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.42</v>
+        <v>18.54</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.960000000000001</v>
+        <v>10</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.64</v>
+        <v>4.62</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.76</v>
+        <v>4.85</v>
       </c>
       <c r="BR8" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS8" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BT8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BU8" t="n">
-        <v>20</v>
+        <v>23.08</v>
       </c>
       <c r="BV8" t="n">
-        <v>12</v>
+        <v>15.38</v>
       </c>
       <c r="BW8" t="n">
-        <v>4</v>
+        <v>7.69</v>
       </c>
       <c r="BX8" t="n">
-        <v>52</v>
+        <v>53.85</v>
       </c>
       <c r="BY8" t="n">
         <v>2.59</v>
@@ -4028,16 +4028,16 @@
         <v>2.94</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.32</v>
+        <v>4.14</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.53</v>
+        <v>4.35</v>
       </c>
       <c r="CE8" t="n">
         <v>1.31</v>
@@ -4046,28 +4046,28 @@
         <v>2.48</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CH8" t="n">
         <v>1.51</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CK8" t="n">
         <v>1.45</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CM8" t="n">
         <v>2.56</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO8" t="n">
         <v>1.21</v>
@@ -4076,7 +4076,7 @@
         <v>1.74</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
@@ -4094,7 +4094,7 @@
         <v>2.28</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX8" t="n">
         <v>1.51</v>
@@ -4121,76 +4121,76 @@
         <v>0.08</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="DH8" t="n">
-        <v>74.72</v>
+        <v>76.81</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.84</v>
+        <v>4.81</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="DM8" t="n">
-        <v>31.84</v>
+        <v>33.19</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="DO8" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.64</v>
+        <v>11.65</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.76</v>
+        <v>12.58</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.32</v>
+        <v>9.15</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.04</v>
+        <v>51.54</v>
       </c>
       <c r="DW8" t="n">
         <v>0.12</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.56</v>
+        <v>12.77</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.48</v>
+        <v>8.57</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.08</v>
+        <v>4.19</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.24</v>
+        <v>18.31</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
         <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F9" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="G9" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="H9" t="n">
-        <v>78.15000000000001</v>
+        <v>77.36</v>
       </c>
       <c r="I9" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="J9" t="n">
-        <v>3.23</v>
+        <v>3.07</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>4.07</v>
       </c>
       <c r="L9" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="M9" t="n">
-        <v>34.62</v>
+        <v>34.93</v>
       </c>
       <c r="N9" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="P9" t="n">
-        <v>10.54</v>
+        <v>10.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.62</v>
+        <v>12.5</v>
       </c>
       <c r="R9" t="n">
-        <v>7.92</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="T9" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="U9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="V9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>41.31</v>
+        <v>40.93</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.77</v>
+        <v>10.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.46</v>
+        <v>6.71</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.31</v>
+        <v>3.79</v>
       </c>
       <c r="AC9" t="n">
-        <v>15.69</v>
+        <v>15.43</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>2.31</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.42</v>
+        <v>9.48</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BP9" t="n">
         <v>4.19</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.85</v>
+        <v>4.93</v>
       </c>
       <c r="BR9" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.92</v>
+        <v>77.78</v>
       </c>
       <c r="BT9" t="n">
-        <v>61.54</v>
+        <v>62.96</v>
       </c>
       <c r="BU9" t="n">
-        <v>38.46</v>
+        <v>40.74</v>
       </c>
       <c r="BV9" t="n">
-        <v>15.38</v>
+        <v>18.52</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.85</v>
+        <v>7.41</v>
       </c>
       <c r="BX9" t="n">
-        <v>73.08</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.49</v>
+        <v>3.46</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="CC9" t="n">
         <v>5.65</v>
@@ -4455,10 +4455,10 @@
         <v>1.48</v>
       </c>
       <c r="CI9" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CK9" t="n">
         <v>1.46</v>
@@ -4467,13 +4467,13 @@
         <v>1.88</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CN9" t="n">
         <v>1.95</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP9" t="n">
         <v>1.8</v>
@@ -4494,7 +4494,7 @@
         <v>1.52</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CW9" t="n">
         <v>1.78</v>
@@ -4518,82 +4518,82 @@
         <v>1.83</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="DH9" t="n">
-        <v>76.76000000000001</v>
+        <v>76.41</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.74</v>
+        <v>33.93</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.34</v>
+        <v>11.19</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.92</v>
+        <v>12.85</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>42.62</v>
+        <v>42.37</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.57</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.23</v>
+        <v>6.37</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.34</v>
+        <v>3.59</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.12</v>
+        <v>16.93</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="10">
@@ -4615,7 +4615,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="G10" t="n">
         <v>2.53</v>
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="K10" t="n">
         <v>4.73</v>
@@ -4690,7 +4690,7 @@
         <v>1.63</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AF10" t="n">
         <v>0.13</v>
@@ -4927,7 +4927,7 @@
         <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="DG10" t="n">
         <v>2.2</v>
@@ -4939,7 +4939,7 @@
         <v>-0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="DK10" t="n">
         <v>4.43</v>
@@ -4996,7 +4996,7 @@
         <v>1.48</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="11">
@@ -5006,61 +5006,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
         <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F11" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H11" t="n">
-        <v>81.42</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>0.08</v>
       </c>
       <c r="J11" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="K11" t="n">
-        <v>5.42</v>
+        <v>5.31</v>
       </c>
       <c r="L11" t="n">
         <v>-0.08</v>
       </c>
       <c r="M11" t="n">
-        <v>41.08</v>
+        <v>40.77</v>
       </c>
       <c r="N11" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="O11" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>11.77</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.42</v>
+        <v>11.38</v>
       </c>
       <c r="R11" t="n">
-        <v>9.58</v>
+        <v>9.77</v>
       </c>
       <c r="S11" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T11" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="U11" t="n">
         <v>0.08</v>
@@ -5072,28 +5072,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>51.58</v>
+        <v>51.31</v>
       </c>
       <c r="Y11" t="n">
         <v>0.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>16.67</v>
+        <v>16.23</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.92</v>
+        <v>11.69</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.75</v>
+        <v>4.54</v>
       </c>
       <c r="AC11" t="n">
-        <v>24.08</v>
+        <v>24.23</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AF11" t="n">
         <v>0.07000000000000001</v>
@@ -5177,70 +5177,70 @@
         <v>2.57</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.19</v>
+        <v>10.22</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.23</v>
+        <v>4.3</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.92</v>
+        <v>4.93</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>84.62</v>
+        <v>81.48</v>
       </c>
       <c r="BT11" t="n">
-        <v>57.69</v>
+        <v>55.56</v>
       </c>
       <c r="BU11" t="n">
-        <v>34.62</v>
+        <v>33.33</v>
       </c>
       <c r="BV11" t="n">
-        <v>19.23</v>
+        <v>18.52</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BX11" t="n">
-        <v>65.38</v>
+        <v>62.96</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="CC11" t="n">
         <v>3.74</v>
@@ -5270,7 +5270,7 @@
         <v>1.41</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM11" t="n">
         <v>2.68</v>
@@ -5300,7 +5300,7 @@
         <v>1.53</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CW11" t="n">
         <v>1.67</v>
@@ -5327,46 +5327,46 @@
         <v>2.79</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="DH11" t="n">
-        <v>82.77</v>
+        <v>82.78</v>
       </c>
       <c r="DI11" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.08</v>
+        <v>5.04</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM11" t="n">
-        <v>40.46</v>
+        <v>40.33</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.16</v>
+        <v>12.04</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.11</v>
+        <v>12.07</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.57</v>
+        <v>9.67</v>
       </c>
       <c r="DS11" t="n">
         <v>0.07000000000000001</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.69</v>
+        <v>49.63</v>
       </c>
       <c r="DW11" t="n">
         <v>0.19</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.89</v>
+        <v>14.74</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.15</v>
+        <v>10.11</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.73</v>
+        <v>4.63</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.31</v>
+        <v>21.48</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="12">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
         <v>0.15</v>
@@ -6308,136 +6308,136 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AI14" t="n">
-        <v>76.64</v>
+        <v>77.47</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.43</v>
+        <v>3.33</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.71</v>
+        <v>3.93</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.93</v>
+        <v>39.2</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.36</v>
+        <v>12.93</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.71</v>
+        <v>10.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>13.14</v>
+        <v>13</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>47.29</v>
+        <v>47.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.71</v>
+        <v>11.33</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.21</v>
+        <v>7.73</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>18.07</v>
+        <v>18.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.96</v>
+        <v>2.89</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.039999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.96</v>
+        <v>2.89</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.37</v>
+        <v>4.43</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.59</v>
+        <v>4.61</v>
       </c>
       <c r="BR14" t="n">
-        <v>96.3</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="BS14" t="n">
-        <v>85.19</v>
+        <v>82.14</v>
       </c>
       <c r="BT14" t="n">
-        <v>48.15</v>
+        <v>46.43</v>
       </c>
       <c r="BU14" t="n">
-        <v>40.74</v>
+        <v>39.29</v>
       </c>
       <c r="BV14" t="n">
-        <v>25.93</v>
+        <v>25</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>70.37</v>
+        <v>67.86</v>
       </c>
       <c r="BY14" t="n">
         <v>2.09</v>
@@ -6452,31 +6452,31 @@
         <v>3.66</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="CE14" t="n">
         <v>1.37</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CH14" t="n">
         <v>1.41</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.78</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL14" t="n">
         <v>1.99</v>
@@ -6488,13 +6488,13 @@
         <v>1.84</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CR14" t="n">
         <v>1.4</v>
@@ -6509,10 +6509,10 @@
         <v>1.44</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CX14" t="n">
         <v>1.57</v>
@@ -6530,85 +6530,85 @@
         <v>1.3</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="DE14" t="n">
         <v>0.11</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="DH14" t="n">
-        <v>82.92</v>
+        <v>83.14</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.03</v>
+        <v>4.14</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="DM14" t="n">
-        <v>40.56</v>
+        <v>40.64</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.33</v>
+        <v>12.14</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.59</v>
+        <v>10.64</v>
       </c>
       <c r="DR14" t="n">
-        <v>11.78</v>
+        <v>11.75</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.15</v>
+        <v>51.18</v>
       </c>
       <c r="DW14" t="n">
         <v>0.11</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.88</v>
+        <v>12.18</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.029999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.85</v>
+        <v>3.89</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.59</v>
+        <v>18.64</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
@@ -8383,10 +8383,10 @@
         <v>0.12</v>
       </c>
       <c r="BA19" t="n">
-        <v>15.88</v>
+        <v>15.94</v>
       </c>
       <c r="BB19" t="n">
-        <v>10.56</v>
+        <v>10.62</v>
       </c>
       <c r="BC19" t="n">
         <v>5.31</v>
@@ -8608,10 +8608,10 @@
         <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.5</v>
+        <v>17.53</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.68</v>
+        <v>11.72</v>
       </c>
       <c r="DZ19" t="n">
         <v>5.81</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
         <v>0.07000000000000001</v>
@@ -1472,49 +1472,49 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="AI2" t="n">
-        <v>102.5</v>
+        <v>102.8</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.21</v>
+        <v>5.27</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.29</v>
+        <v>0.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>49.64</v>
+        <v>48.67</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.07</v>
+        <v>13.47</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.86</v>
+        <v>7.27</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AV2" t="n">
         <v>0.07000000000000001</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>54.5</v>
+        <v>55.53</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.36</v>
+        <v>11.87</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.86</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.57</v>
+        <v>17.47</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="BF2" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.960000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="BM2" t="n">
         <v>0.79</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BP2" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.86</v>
+        <v>4.66</v>
       </c>
       <c r="BR2" t="n">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>78.56999999999999</v>
+        <v>79.31</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>51.72</v>
       </c>
       <c r="BU2" t="n">
-        <v>28.57</v>
+        <v>27.59</v>
       </c>
       <c r="BV2" t="n">
-        <v>10.71</v>
+        <v>10.34</v>
       </c>
       <c r="BW2" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>51.72</v>
       </c>
       <c r="BY2" t="n">
         <v>1.49</v>
@@ -1610,25 +1610,25 @@
         <v>1.58</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="CE2" t="n">
         <v>1.29</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CH2" t="n">
         <v>1.42</v>
@@ -1640,106 +1640,106 @@
         <v>1.75</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL2" t="n">
         <v>1.83</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="CR2" t="n">
         <v>1.4</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="DE2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.22</v>
+        <v>3.07</v>
       </c>
       <c r="DH2" t="n">
-        <v>101.54</v>
+        <v>101.72</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.79</v>
+        <v>5.8</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="DM2" t="n">
-        <v>53.57</v>
+        <v>52.93</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.75</v>
+        <v>10.55</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.57</v>
+        <v>12.79</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.54</v>
+        <v>6.76</v>
       </c>
       <c r="DS2" t="n">
         <v>0.14</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>56</v>
+        <v>56.48</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.93</v>
+        <v>14.11</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.08</v>
+        <v>9.17</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.85</v>
+        <v>4.93</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.14</v>
+        <v>19.03</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="EC2" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
         <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="F3" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="H3" t="n">
-        <v>78.69</v>
+        <v>77</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="K3" t="n">
-        <v>3.69</v>
+        <v>3.57</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>36.85</v>
+        <v>35.64</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="O3" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="P3" t="n">
-        <v>13.92</v>
+        <v>14.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.46</v>
+        <v>13.21</v>
       </c>
       <c r="R3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="S3" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="T3" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="U3" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="V3" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>45</v>
+        <v>44.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>12</v>
+        <v>11.64</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.77</v>
+        <v>7.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.23</v>
+        <v>4.14</v>
       </c>
       <c r="AC3" t="n">
-        <v>17</v>
+        <v>16.43</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AF3" t="n">
         <v>0.08</v>
@@ -1953,70 +1953,70 @@
         <v>2.15</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.77</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.88</v>
+        <v>3.96</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.19</v>
+        <v>4.15</v>
       </c>
       <c r="BR3" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS3" t="n">
-        <v>80.77</v>
+        <v>81.48</v>
       </c>
       <c r="BT3" t="n">
-        <v>57.69</v>
+        <v>59.26</v>
       </c>
       <c r="BU3" t="n">
-        <v>50</v>
+        <v>48.15</v>
       </c>
       <c r="BV3" t="n">
-        <v>26.92</v>
+        <v>25.93</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BX3" t="n">
-        <v>57.69</v>
+        <v>59.26</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.96</v>
+        <v>3.09</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="CA3" t="n">
         <v>3.62</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="CC3" t="n">
         <v>4.57</v>
@@ -2028,7 +2028,7 @@
         <v>1.33</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CG3" t="n">
         <v>3.04</v>
@@ -2046,13 +2046,13 @@
         <v>1.46</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CO3" t="n">
         <v>1.24</v>
@@ -2061,7 +2061,7 @@
         <v>1.83</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CR3" t="n">
         <v>1.4</v>
@@ -2073,13 +2073,13 @@
         <v>3.08</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX3" t="n">
         <v>1.58</v>
@@ -2094,88 +2094,88 @@
         <v>1.96</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="DE3" t="n">
         <v>0.23</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="DH3" t="n">
-        <v>72.56999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.46</v>
+        <v>3.41</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="DM3" t="n">
-        <v>29.5</v>
+        <v>29.14</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.96</v>
+        <v>12.11</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="DR3" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>45.27</v>
+        <v>44.78</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.62</v>
+        <v>10.48</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.19</v>
+        <v>7.08</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.38</v>
+        <v>17.08</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="n">
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,139 +2275,139 @@
         <v>1.62</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>77.08</v>
+        <v>75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.31</v>
+        <v>4.07</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="AN4" t="n">
-        <v>38.85</v>
+        <v>36.93</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.31</v>
+        <v>11.93</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.23</v>
+        <v>13.36</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.08</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>47.15</v>
+        <v>46.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.08</v>
+        <v>11.93</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.31</v>
+        <v>7.43</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.77</v>
+        <v>4.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.46</v>
+        <v>18.93</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.15</v>
+        <v>8.26</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="BO4" t="n">
         <v>1.04</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.23</v>
+        <v>4.3</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>80.77</v>
+        <v>81.48</v>
       </c>
       <c r="BT4" t="n">
-        <v>61.54</v>
+        <v>62.96</v>
       </c>
       <c r="BU4" t="n">
-        <v>38.46</v>
+        <v>37.04</v>
       </c>
       <c r="BV4" t="n">
-        <v>30.77</v>
+        <v>29.63</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BX4" t="n">
-        <v>65.38</v>
+        <v>62.96</v>
       </c>
       <c r="BY4" t="n">
         <v>2.91</v>
@@ -2416,16 +2416,16 @@
         <v>3.13</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.65</v>
+        <v>3.69</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.96</v>
+        <v>4.16</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.39</v>
+        <v>4.57</v>
       </c>
       <c r="CE4" t="n">
         <v>1.27</v>
@@ -2434,13 +2434,13 @@
         <v>2.41</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CH4" t="n">
         <v>1.42</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.61</v>
@@ -2449,7 +2449,7 @@
         <v>1.41</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM4" t="n">
         <v>2.42</v>
@@ -2461,16 +2461,16 @@
         <v>1.16</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CR4" t="n">
         <v>1.37</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CT4" t="n">
         <v>3.21</v>
@@ -2479,22 +2479,22 @@
         <v>1.5</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB4" t="n">
         <v>1.25</v>
@@ -2506,76 +2506,76 @@
         <v>2.92</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="DH4" t="n">
-        <v>74.81</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.42</v>
+        <v>4.3</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="DM4" t="n">
-        <v>32.46</v>
+        <v>31.71</v>
       </c>
       <c r="DN4" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.5</v>
+        <v>11.33</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.58</v>
+        <v>12.67</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.81</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>48</v>
+        <v>47.63</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.66</v>
+        <v>10.63</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.73</v>
+        <v>6.81</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.92</v>
+        <v>3.82</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.46</v>
+        <v>20.63</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="EC4" t="n">
         <v>1.85</v>
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
         <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="H5" t="n">
-        <v>104.47</v>
+        <v>105.31</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="J5" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="K5" t="n">
-        <v>6.47</v>
+        <v>6.69</v>
       </c>
       <c r="L5" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>55.6</v>
+        <v>53.56</v>
       </c>
       <c r="N5" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="O5" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="P5" t="n">
-        <v>12.27</v>
+        <v>11.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>10.88</v>
       </c>
       <c r="R5" t="n">
-        <v>7.6</v>
+        <v>7.31</v>
       </c>
       <c r="S5" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="V5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>57.2</v>
+        <v>57.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.2</v>
+        <v>19.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.6</v>
+        <v>12.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.6</v>
+        <v>6.88</v>
       </c>
       <c r="AC5" t="n">
-        <v>22.2</v>
+        <v>22.12</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AF5" t="n">
         <v>0.2</v>
@@ -2762,67 +2762,67 @@
         <v>2.9</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.1</v>
+        <v>9.16</v>
       </c>
       <c r="BI5" t="n">
         <v>2.9</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.47</v>
+        <v>3.52</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.13</v>
+        <v>5.16</v>
       </c>
       <c r="BR5" t="n">
-        <v>93.33</v>
+        <v>93.55</v>
       </c>
       <c r="BS5" t="n">
-        <v>83.33</v>
+        <v>83.87</v>
       </c>
       <c r="BT5" t="n">
-        <v>53.33</v>
+        <v>54.84</v>
       </c>
       <c r="BU5" t="n">
-        <v>26.67</v>
+        <v>25.81</v>
       </c>
       <c r="BV5" t="n">
-        <v>23.33</v>
+        <v>22.58</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.67</v>
+        <v>6.45</v>
       </c>
       <c r="BX5" t="n">
-        <v>66.67</v>
+        <v>64.52</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.89</v>
+        <v>3.92</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.12</v>
+        <v>4.15</v>
       </c>
       <c r="CC5" t="n">
         <v>2.4</v>
@@ -2837,13 +2837,13 @@
         <v>2.5</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CH5" t="n">
         <v>1.5</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.72</v>
@@ -2855,7 +2855,7 @@
         <v>1.94</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CN5" t="n">
         <v>1.9</v>
@@ -2864,10 +2864,10 @@
         <v>1.21</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CR5" t="n">
         <v>1.37</v>
@@ -2882,22 +2882,22 @@
         <v>1.53</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CX5" t="n">
         <v>1.54</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.39</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DB5" t="n">
         <v>1.24</v>
@@ -2906,79 +2906,79 @@
         <v>1.78</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="DE5" t="n">
         <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.76</v>
+        <v>2.87</v>
       </c>
       <c r="DH5" t="n">
-        <v>99.59999999999999</v>
+        <v>100.19</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.3</v>
+        <v>5.45</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="DM5" t="n">
-        <v>47.26</v>
+        <v>46.48</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.27</v>
+        <v>11.13</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.54</v>
+        <v>12.42</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.26</v>
+        <v>8.09</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.64</v>
+        <v>54.87</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.74</v>
+        <v>17.1</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.76</v>
+        <v>10.97</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.96</v>
+        <v>6.13</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.94</v>
+        <v>21.9</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="EC5" t="n">
         <v>2.1</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n">
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
         <v>0.15</v>
@@ -3081,139 +3081,139 @@
         <v>2.23</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AI6" t="n">
-        <v>95.79000000000001</v>
+        <v>95.53</v>
       </c>
       <c r="AJ6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.07</v>
+        <v>5.2</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AN6" t="n">
-        <v>44.71</v>
+        <v>43.07</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.79</v>
+        <v>11.13</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.07</v>
+        <v>6.93</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>54.57</v>
+        <v>55.47</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="BA6" t="n">
-        <v>14.07</v>
+        <v>13.93</v>
       </c>
       <c r="BB6" t="n">
-        <v>10.07</v>
+        <v>9.93</v>
       </c>
       <c r="BC6" t="n">
         <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.86</v>
+        <v>20</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.779999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.93</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.11</v>
+        <v>4.18</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.48</v>
+        <v>4.43</v>
       </c>
       <c r="BR6" t="n">
-        <v>92.59</v>
+        <v>92.86</v>
       </c>
       <c r="BS6" t="n">
-        <v>70.37</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>55.56</v>
+        <v>57.14</v>
       </c>
       <c r="BU6" t="n">
-        <v>25.93</v>
+        <v>25</v>
       </c>
       <c r="BV6" t="n">
-        <v>22.22</v>
+        <v>21.43</v>
       </c>
       <c r="BW6" t="n">
-        <v>11.11</v>
+        <v>10.71</v>
       </c>
       <c r="BX6" t="n">
-        <v>51.85</v>
+        <v>53.57</v>
       </c>
       <c r="BY6" t="n">
         <v>1.96</v>
@@ -3225,16 +3225,16 @@
         <v>3.55</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF6" t="n">
         <v>2.54</v>
@@ -3249,37 +3249,37 @@
         <v>1.94</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO6" t="n">
         <v>1.21</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CU6" t="n">
         <v>1.48</v>
@@ -3306,85 +3306,85 @@
         <v>1.28</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="DE6" t="n">
         <v>0.14</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DH6" t="n">
-        <v>87.89</v>
+        <v>88.03</v>
       </c>
       <c r="DI6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.37</v>
+        <v>5.43</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="DM6" t="n">
-        <v>39.92</v>
+        <v>39.22</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.63</v>
+        <v>11.54</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11</v>
+        <v>11.18</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.52</v>
+        <v>55</v>
       </c>
       <c r="DW6" t="n">
         <v>0.11</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.41</v>
+        <v>14.32</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.93</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.48</v>
+        <v>4.46</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.85</v>
+        <v>18</v>
       </c>
       <c r="EB6" t="n">
         <v>1.39</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" t="n">
         <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
         <v>0.2</v>
@@ -3484,52 +3484,52 @@
         <v>2.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AI7" t="n">
-        <v>77.29000000000001</v>
+        <v>76.73</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.21</v>
+        <v>0.47</v>
       </c>
       <c r="AN7" t="n">
-        <v>37.86</v>
+        <v>36</v>
       </c>
       <c r="AO7" t="n">
         <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.79</v>
+        <v>12.73</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.64</v>
+        <v>13.53</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.43</v>
+        <v>10.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AV7" t="n">
         <v>0.07000000000000001</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>45.07</v>
+        <v>44.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.93</v>
+        <v>10.73</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.29</v>
+        <v>7.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.64</v>
+        <v>3.53</v>
       </c>
       <c r="BD7" t="n">
-        <v>21</v>
+        <v>21.33</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.69</v>
+        <v>8.73</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BP7" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="BQ7" t="n">
         <v>4.07</v>
       </c>
       <c r="BR7" t="n">
-        <v>96.55</v>
+        <v>96.67</v>
       </c>
       <c r="BS7" t="n">
-        <v>86.20999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>65.52</v>
+        <v>66.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>34.48</v>
+        <v>36.67</v>
       </c>
       <c r="BV7" t="n">
-        <v>13.79</v>
+        <v>13.33</v>
       </c>
       <c r="BW7" t="n">
-        <v>10.34</v>
+        <v>10</v>
       </c>
       <c r="BX7" t="n">
-        <v>75.86</v>
+        <v>76.67</v>
       </c>
       <c r="BY7" t="n">
         <v>2.68</v>
@@ -3625,40 +3625,40 @@
         <v>2.82</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.2</v>
+        <v>4.42</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.66</v>
+        <v>4.77</v>
       </c>
       <c r="CE7" t="n">
         <v>1.36</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CH7" t="n">
         <v>1.43</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CK7" t="n">
         <v>1.54</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CM7" t="n">
         <v>2.34</v>
@@ -3673,7 +3673,7 @@
         <v>1.9</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CR7" t="n">
         <v>1.4</v>
@@ -3703,58 +3703,58 @@
         <v>2.3</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DB7" t="n">
         <v>1.3</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="DE7" t="n">
         <v>0.2</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="DH7" t="n">
-        <v>84.48</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="DK7" t="n">
         <v>4</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.24</v>
+        <v>0.37</v>
       </c>
       <c r="DM7" t="n">
-        <v>37.48</v>
+        <v>36.57</v>
       </c>
       <c r="DN7" t="n">
         <v>1.1</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.11</v>
+        <v>12.1</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.03</v>
+        <v>13</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.279999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="DS7" t="n">
         <v>0.17</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.51</v>
+        <v>48.06</v>
       </c>
       <c r="DW7" t="n">
         <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.76</v>
+        <v>11.63</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.83</v>
+        <v>7.76</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.93</v>
+        <v>3.86</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.03</v>
+        <v>22.17</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="8">
@@ -4272,10 +4272,10 @@
         <v>0.21</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.5</v>
+        <v>10.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.71</v>
+        <v>6.64</v>
       </c>
       <c r="AB9" t="n">
         <v>3.79</v>
@@ -4578,10 +4578,10 @@
         <v>0.15</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.960000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.37</v>
+        <v>6.33</v>
       </c>
       <c r="DZ9" t="n">
         <v>3.59</v>
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
         <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
         <v>0.07000000000000001</v>
@@ -4669,16 +4669,16 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>58.53</v>
+        <v>58.6</v>
       </c>
       <c r="Y10" t="n">
         <v>0.13</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.67</v>
+        <v>14.73</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.27</v>
+        <v>9.33</v>
       </c>
       <c r="AB10" t="n">
         <v>5.4</v>
@@ -4693,139 +4693,139 @@
         <v>1.53</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AI10" t="n">
-        <v>69.13</v>
+        <v>64.94</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="AK10" t="n">
         <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>30.4</v>
+        <v>28.88</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.07</v>
+        <v>10.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.07</v>
+        <v>12.81</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>55.27</v>
+        <v>54.56</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="BA10" t="n">
-        <v>13.67</v>
+        <v>13.06</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.130000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.53</v>
+        <v>5.19</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.33</v>
+        <v>19.25</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="BH10" t="n">
         <v>9.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.47</v>
+        <v>4.48</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.6</v>
+        <v>4.58</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>76.67</v>
+        <v>74.19</v>
       </c>
       <c r="BT10" t="n">
-        <v>53.33</v>
+        <v>51.61</v>
       </c>
       <c r="BU10" t="n">
-        <v>43.33</v>
+        <v>41.94</v>
       </c>
       <c r="BV10" t="n">
-        <v>23.33</v>
+        <v>22.58</v>
       </c>
       <c r="BW10" t="n">
-        <v>16.67</v>
+        <v>16.13</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>48.39</v>
       </c>
       <c r="BY10" t="n">
         <v>1.78</v>
@@ -4834,16 +4834,16 @@
         <v>1.93</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="CE10" t="n">
         <v>1.31</v>
@@ -4852,7 +4852,7 @@
         <v>2.43</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CH10" t="n">
         <v>1.51</v>
@@ -4861,7 +4861,7 @@
         <v>2.14</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CK10" t="n">
         <v>1.46</v>
@@ -4879,16 +4879,16 @@
         <v>1.2</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CT10" t="n">
         <v>3.29</v>
@@ -4912,91 +4912,91 @@
         <v>2.42</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB10" t="n">
         <v>1.23</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="DE10" t="n">
         <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DH10" t="n">
-        <v>81.86</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="DL10" t="n">
         <v>0.36</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.3</v>
+        <v>36.29</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.57</v>
+        <v>10.78</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.97</v>
+        <v>12.84</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.33</v>
+        <v>7.39</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>56.9</v>
+        <v>56.51</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.17</v>
+        <v>13.87</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.46</v>
+        <v>5.29</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.6</v>
+        <v>18.58</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="11">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
         <v>14</v>
@@ -5421,49 +5421,49 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G12" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="H12" t="n">
-        <v>87.06999999999999</v>
+        <v>86.87</v>
       </c>
       <c r="I12" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="J12" t="n">
-        <v>2.86</v>
+        <v>3.07</v>
       </c>
       <c r="K12" t="n">
-        <v>5.29</v>
+        <v>5.07</v>
       </c>
       <c r="L12" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="M12" t="n">
-        <v>38.93</v>
+        <v>37.73</v>
       </c>
       <c r="N12" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="O12" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="P12" t="n">
-        <v>12.29</v>
+        <v>12.13</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.86</v>
+        <v>11.8</v>
       </c>
       <c r="R12" t="n">
-        <v>8.07</v>
+        <v>7.87</v>
       </c>
       <c r="S12" t="n">
         <v>0.93</v>
       </c>
       <c r="T12" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="U12" t="n">
         <v>0.07000000000000001</v>
@@ -5475,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>50.29</v>
+        <v>49.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.21</v>
+        <v>14.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.359999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.86</v>
+        <v>4.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>16.71</v>
+        <v>16.73</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AF12" t="n">
         <v>0.07000000000000001</v>
@@ -5580,67 +5580,67 @@
         <v>2.14</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.109999999999999</v>
+        <v>9</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.18</v>
+        <v>4.1</v>
       </c>
       <c r="BQ12" t="n">
         <v>4.21</v>
       </c>
       <c r="BR12" t="n">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>71.43000000000001</v>
+        <v>72.41</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>51.72</v>
       </c>
       <c r="BU12" t="n">
-        <v>21.43</v>
+        <v>20.69</v>
       </c>
       <c r="BV12" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>46.43</v>
+        <v>48.28</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB12" t="n">
         <v>3.86</v>
@@ -5670,10 +5670,10 @@
         <v>1.71</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM12" t="n">
         <v>2.59</v>
@@ -5685,10 +5685,10 @@
         <v>1.24</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CR12" t="n">
         <v>1.38</v>
@@ -5703,7 +5703,7 @@
         <v>1.5</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CW12" t="n">
         <v>1.75</v>
@@ -5724,85 +5724,85 @@
         <v>1.27</v>
       </c>
       <c r="DC12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="DF12" t="n">
         <v>1.86</v>
       </c>
-      <c r="DD12" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="DE12" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="DF12" t="n">
-        <v>1.82</v>
-      </c>
       <c r="DG12" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="DH12" t="n">
-        <v>85.18000000000001</v>
+        <v>85.14</v>
       </c>
       <c r="DI12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>37.83</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>9</v>
+      </c>
+      <c r="DS12" t="n">
         <v>0.1</v>
       </c>
-      <c r="DJ12" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="DK12" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="DL12" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="DM12" t="n">
-        <v>38.43</v>
-      </c>
-      <c r="DN12" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="DO12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="DP12" t="n">
-        <v>11.93</v>
-      </c>
-      <c r="DQ12" t="n">
-        <v>12.11</v>
-      </c>
-      <c r="DR12" t="n">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="DS12" t="n">
-        <v>0.11</v>
-      </c>
       <c r="DT12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50.86</v>
+        <v>50.48</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.07</v>
+        <v>14.28</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.5</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.04</v>
+        <v>18.97</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="n">
         <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
         <v>0.08</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="AI13" t="n">
-        <v>75.38</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.54</v>
+        <v>5.43</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AN13" t="n">
-        <v>27.85</v>
+        <v>28.14</v>
       </c>
       <c r="AO13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.08</v>
       </c>
-      <c r="AP13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>12.77</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>12.92</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>10.46</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>46.08</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>10.85</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>19.46</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.06</v>
-      </c>
       <c r="BF13" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="BG13" t="n">
         <v>3.15</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.77</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BI13" t="n">
         <v>3.15</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BL13" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="BM13" t="n">
         <v>0.96</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.27</v>
+        <v>4.19</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.19</v>
+        <v>5.15</v>
       </c>
       <c r="BR13" t="n">
-        <v>88.45999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS13" t="n">
-        <v>69.23</v>
+        <v>70.37</v>
       </c>
       <c r="BT13" t="n">
-        <v>61.54</v>
+        <v>62.96</v>
       </c>
       <c r="BU13" t="n">
-        <v>42.31</v>
+        <v>40.74</v>
       </c>
       <c r="BV13" t="n">
-        <v>23.08</v>
+        <v>22.22</v>
       </c>
       <c r="BW13" t="n">
-        <v>15.38</v>
+        <v>14.81</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>51.85</v>
       </c>
       <c r="BY13" t="n">
         <v>3.34</v>
@@ -6043,25 +6043,25 @@
         <v>3.57</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CB13" t="n">
         <v>3.93</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.08</v>
+        <v>4.99</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.48</v>
+        <v>5.41</v>
       </c>
       <c r="CE13" t="n">
         <v>1.34</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CH13" t="n">
         <v>1.45</v>
@@ -6073,10 +6073,10 @@
         <v>1.77</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CM13" t="n">
         <v>2.51</v>
@@ -6115,13 +6115,13 @@
         <v>1.52</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.42</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DB13" t="n">
         <v>1.29</v>
@@ -6136,43 +6136,43 @@
         <v>0.04</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="DH13" t="n">
-        <v>81.84</v>
+        <v>82.41</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.73</v>
+        <v>4.7</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DM13" t="n">
-        <v>33.12</v>
+        <v>33.07</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.66</v>
+        <v>11.56</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.5</v>
+        <v>12.48</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.19</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DS13" t="n">
         <v>0.04</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.58</v>
+        <v>48.04</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.24</v>
+        <v>12.19</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.96</v>
+        <v>7.85</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="EA13" t="n">
-        <v>20</v>
+        <v>19.67</v>
       </c>
       <c r="EB13" t="n">
         <v>1.27</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="14">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
         <v>13</v>
@@ -6630,82 +6630,82 @@
         <v>0.08</v>
       </c>
       <c r="F15" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="G15" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="H15" t="n">
-        <v>78.67</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="I15" t="n">
         <v>0.08</v>
       </c>
       <c r="J15" t="n">
-        <v>3.67</v>
+        <v>3.54</v>
       </c>
       <c r="K15" t="n">
-        <v>3.25</v>
+        <v>3.69</v>
       </c>
       <c r="L15" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="M15" t="n">
-        <v>28.67</v>
+        <v>27.31</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="O15" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="P15" t="n">
-        <v>13.42</v>
+        <v>13.31</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.08</v>
+        <v>11.62</v>
       </c>
       <c r="R15" t="n">
-        <v>10.58</v>
+        <v>10.38</v>
       </c>
       <c r="S15" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="U15" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="V15" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>41.33</v>
+        <v>40.46</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.08</v>
+        <v>10.46</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.42</v>
+        <v>6.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.67</v>
+        <v>3.54</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.5</v>
+        <v>19.46</v>
       </c>
       <c r="AD15" t="n">
         <v>1.11</v>
       </c>
       <c r="AE15" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6744,7 +6744,7 @@
         <v>10.08</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.38</v>
+        <v>12.46</v>
       </c>
       <c r="AS15" t="n">
         <v>10.69</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>32.38</v>
+        <v>32.31</v>
       </c>
       <c r="AZ15" t="n">
         <v>0.38</v>
@@ -6789,70 +6789,70 @@
         <v>2.15</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.279999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL15" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.56</v>
+        <v>4.35</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.68</v>
+        <v>4.46</v>
       </c>
       <c r="BR15" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS15" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BT15" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BU15" t="n">
-        <v>36</v>
+        <v>34.62</v>
       </c>
       <c r="BV15" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BW15" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX15" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.22</v>
+        <v>3.31</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.58</v>
+        <v>3.67</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="CC15" t="n">
         <v>7.04</v>
@@ -6864,10 +6864,10 @@
         <v>1.3</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CH15" t="n">
         <v>1.4</v>
@@ -6876,109 +6876,109 @@
         <v>1.83</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV15" t="n">
         <v>1.97</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="DA15" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="DE15" t="n">
         <v>0.04</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DH15" t="n">
-        <v>65.56</v>
+        <v>66</v>
       </c>
       <c r="DI15" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.32</v>
+        <v>3.53</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DM15" t="n">
-        <v>25.76</v>
+        <v>25.19</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.68</v>
+        <v>11.7</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.24</v>
+        <v>12.04</v>
       </c>
       <c r="DR15" t="n">
-        <v>10.64</v>
+        <v>10.53</v>
       </c>
       <c r="DS15" t="n">
         <v>0.2</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>36.68</v>
+        <v>36.38</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.52</v>
+        <v>9.73</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.96</v>
+        <v>6.23</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.04</v>
+        <v>18.08</v>
       </c>
       <c r="EB15" t="n">
         <v>1.03</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="n">
         <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7111,139 +7111,139 @@
         <v>2.31</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="AI16" t="n">
-        <v>81.45999999999999</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.38</v>
+        <v>3.21</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.23</v>
+        <v>4.43</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AN16" t="n">
-        <v>33.38</v>
+        <v>34.29</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.08</v>
+        <v>10.57</v>
       </c>
       <c r="AR16" t="n">
-        <v>13.38</v>
+        <v>13.43</v>
       </c>
       <c r="AS16" t="n">
-        <v>11.77</v>
+        <v>11.71</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>45.38</v>
+        <v>45.43</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.539999999999999</v>
+        <v>10.07</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.08</v>
+        <v>6.21</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.46</v>
+        <v>3.86</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.46</v>
+        <v>17.57</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.04</v>
+        <v>10.07</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.62</v>
+        <v>5.59</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>76.92</v>
+        <v>77.78</v>
       </c>
       <c r="BT16" t="n">
-        <v>73.08</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="BU16" t="n">
-        <v>50</v>
+        <v>48.15</v>
       </c>
       <c r="BV16" t="n">
-        <v>19.23</v>
+        <v>18.52</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BX16" t="n">
-        <v>61.54</v>
+        <v>62.96</v>
       </c>
       <c r="BY16" t="n">
         <v>3.4</v>
@@ -7255,13 +7255,13 @@
         <v>4.21</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.65</v>
+        <v>4.64</v>
       </c>
       <c r="CC16" t="n">
-        <v>6.44</v>
+        <v>6.39</v>
       </c>
       <c r="CD16" t="n">
-        <v>7.38</v>
+        <v>7.26</v>
       </c>
       <c r="CE16" t="n">
         <v>1.27</v>
@@ -7270,7 +7270,7 @@
         <v>2.32</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CH16" t="n">
         <v>1.58</v>
@@ -7279,19 +7279,19 @@
         <v>2.19</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CO16" t="n">
         <v>1.17</v>
@@ -7315,28 +7315,28 @@
         <v>1.61</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CW16" t="n">
         <v>1.68</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DB16" t="n">
         <v>1.2</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DD16" t="n">
         <v>2.54</v>
@@ -7345,76 +7345,76 @@
         <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="DH16" t="n">
-        <v>74.19</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.12</v>
+        <v>4.22</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM16" t="n">
-        <v>33.38</v>
+        <v>33.85</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.38</v>
+        <v>11.59</v>
       </c>
       <c r="DQ16" t="n">
         <v>13.96</v>
       </c>
       <c r="DR16" t="n">
-        <v>10.84</v>
+        <v>10.85</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.62</v>
+        <v>44.67</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.81</v>
+        <v>11.04</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.85</v>
+        <v>6.89</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.96</v>
+        <v>4.15</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.62</v>
+        <v>18.63</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="17">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D17" t="n">
         <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="F17" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="G17" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="H17" t="n">
-        <v>92.69</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="K17" t="n">
         <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="M17" t="n">
-        <v>52.62</v>
+        <v>50.35</v>
       </c>
       <c r="N17" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="O17" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="P17" t="n">
-        <v>11.19</v>
+        <v>11.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>14.38</v>
+        <v>14.53</v>
       </c>
       <c r="R17" t="n">
-        <v>6.44</v>
+        <v>6.18</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="T17" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="V17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>55.81</v>
+        <v>55.82</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.06</v>
+        <v>16.82</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.38</v>
+        <v>11.35</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.69</v>
+        <v>5.47</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.19</v>
+        <v>19.71</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AF17" t="n">
         <v>0.06</v>
@@ -7595,70 +7595,70 @@
         <v>2.56</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.25</v>
+        <v>9.24</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL17" t="n">
         <v>1.12</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.91</v>
+        <v>4.88</v>
       </c>
       <c r="BR17" t="n">
-        <v>90.62</v>
+        <v>90.91</v>
       </c>
       <c r="BS17" t="n">
-        <v>78.12</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>53.12</v>
+        <v>51.52</v>
       </c>
       <c r="BU17" t="n">
-        <v>31.25</v>
+        <v>30.3</v>
       </c>
       <c r="BV17" t="n">
-        <v>18.75</v>
+        <v>18.18</v>
       </c>
       <c r="BW17" t="n">
-        <v>12.5</v>
+        <v>12.12</v>
       </c>
       <c r="BX17" t="n">
-        <v>59.38</v>
+        <v>57.58</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="CC17" t="n">
         <v>2.48</v>
@@ -7682,13 +7682,13 @@
         <v>2.02</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK17" t="n">
         <v>1.44</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM17" t="n">
         <v>2.38</v>
@@ -7712,7 +7712,7 @@
         <v>2.74</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CU17" t="n">
         <v>1.49</v>
@@ -7721,7 +7721,7 @@
         <v>2.11</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX17" t="n">
         <v>1.54</v>
@@ -7730,10 +7730,10 @@
         <v>1.88</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DB17" t="n">
         <v>1.26</v>
@@ -7748,76 +7748,76 @@
         <v>0.12</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="DH17" t="n">
-        <v>91.84</v>
+        <v>89.09</v>
       </c>
       <c r="DI17" t="n">
         <v>0.03</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.53</v>
+        <v>2.46</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.53</v>
+        <v>5.54</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="DM17" t="n">
-        <v>45.75</v>
+        <v>44.79</v>
       </c>
       <c r="DN17" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.54</v>
+        <v>11.46</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.57</v>
+        <v>13.67</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.69</v>
+        <v>7.52</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.46</v>
+        <v>54.51</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.43</v>
+        <v>15.36</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.880000000000001</v>
+        <v>9.91</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.56</v>
+        <v>5.46</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.6</v>
+        <v>18.88</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="18">
@@ -7827,10 +7827,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -7839,49 +7839,49 @@
         <v>0.12</v>
       </c>
       <c r="F18" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="G18" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="H18" t="n">
-        <v>86.44</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="I18" t="n">
         <v>0.06</v>
       </c>
       <c r="J18" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="K18" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="L18" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="M18" t="n">
-        <v>38</v>
+        <v>38.59</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="O18" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>12.25</v>
+        <v>12.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.88</v>
+        <v>14.06</v>
       </c>
       <c r="R18" t="n">
-        <v>7.31</v>
+        <v>7.47</v>
       </c>
       <c r="S18" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="T18" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="U18" t="n">
         <v>0.12</v>
@@ -7893,28 +7893,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>49.5</v>
+        <v>49.76</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="Z18" t="n">
-        <v>12.75</v>
+        <v>12.94</v>
       </c>
       <c r="AA18" t="n">
-        <v>8</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>17.31</v>
+        <v>17.59</v>
       </c>
       <c r="AD18" t="n">
         <v>1.42</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AF18" t="n">
         <v>0.08</v>
@@ -7998,67 +7998,67 @@
         <v>2.85</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.140000000000001</v>
+        <v>8.23</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.66</v>
+        <v>3.73</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.03</v>
+        <v>4.07</v>
       </c>
       <c r="BR18" t="n">
-        <v>89.66</v>
+        <v>90</v>
       </c>
       <c r="BS18" t="n">
-        <v>79.31</v>
+        <v>80</v>
       </c>
       <c r="BT18" t="n">
-        <v>48.28</v>
+        <v>50</v>
       </c>
       <c r="BU18" t="n">
-        <v>34.48</v>
+        <v>33.33</v>
       </c>
       <c r="BV18" t="n">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
       <c r="BW18" t="n">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
       <c r="BX18" t="n">
-        <v>51.72</v>
+        <v>53.33</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="CB18" t="n">
         <v>4.11</v>
@@ -8070,28 +8070,28 @@
         <v>5.51</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CF18" t="n">
         <v>2.12</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI18" t="n">
         <v>2.07</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CM18" t="n">
         <v>2.22</v>
@@ -8106,7 +8106,7 @@
         <v>1.64</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
@@ -8121,22 +8121,22 @@
         <v>1.59</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="DB18" t="n">
         <v>1.21</v>
@@ -8151,76 +8151,76 @@
         <v>0.1</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="DH18" t="n">
-        <v>79.28</v>
+        <v>80.03</v>
       </c>
       <c r="DI18" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="DL18" t="n">
         <v>0.24</v>
       </c>
       <c r="DM18" t="n">
-        <v>36.38</v>
+        <v>36.77</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.14</v>
+        <v>12.2</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.1</v>
+        <v>13.23</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.960000000000001</v>
+        <v>9</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.31</v>
+        <v>47.53</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.93</v>
+        <v>12.06</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.86</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.07</v>
+        <v>4.03</v>
       </c>
       <c r="EA18" t="n">
-        <v>18</v>
+        <v>18.14</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="19">
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D19" t="n">
         <v>16</v>
@@ -8242,61 +8242,61 @@
         <v>0.12</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="G19" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="H19" t="n">
-        <v>92.69</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="K19" t="n">
-        <v>5.44</v>
+        <v>5.47</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="M19" t="n">
-        <v>44.5</v>
+        <v>44.29</v>
       </c>
       <c r="N19" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="O19" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="P19" t="n">
         <v>12</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.5</v>
+        <v>11.59</v>
       </c>
       <c r="R19" t="n">
-        <v>8.75</v>
+        <v>8.59</v>
       </c>
       <c r="S19" t="n">
         <v>1.06</v>
       </c>
       <c r="T19" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="U19" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="V19" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>57.38</v>
+        <v>57.82</v>
       </c>
       <c r="Y19" t="n">
         <v>0.06</v>
@@ -8305,19 +8305,19 @@
         <v>19.12</v>
       </c>
       <c r="AA19" t="n">
-        <v>12.81</v>
+        <v>12.88</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.31</v>
+        <v>6.24</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.69</v>
+        <v>18.65</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AF19" t="n">
         <v>0.06</v>
@@ -8401,67 +8401,67 @@
         <v>2.44</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.279999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.38</v>
+        <v>4.42</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="BR19" t="n">
-        <v>84.38</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>68.75</v>
+        <v>69.7</v>
       </c>
       <c r="BT19" t="n">
-        <v>53.12</v>
+        <v>54.55</v>
       </c>
       <c r="BU19" t="n">
-        <v>40.62</v>
+        <v>42.42</v>
       </c>
       <c r="BV19" t="n">
-        <v>18.75</v>
+        <v>18.18</v>
       </c>
       <c r="BW19" t="n">
-        <v>12.5</v>
+        <v>12.12</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>51.52</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="BZ19" t="n">
         <v>1.58</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.13</v>
+        <v>4.15</v>
       </c>
       <c r="CB19" t="n">
         <v>4.51</v>
@@ -8476,19 +8476,19 @@
         <v>1.28</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CH19" t="n">
         <v>1.58</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK19" t="n">
         <v>1.5</v>
@@ -8497,7 +8497,7 @@
         <v>1.93</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CN19" t="n">
         <v>1.85</v>
@@ -8524,10 +8524,10 @@
         <v>1.62</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CX19" t="n">
         <v>1.55</v>
@@ -8548,82 +8548,82 @@
         <v>1.66</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="DE19" t="n">
         <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="DH19" t="n">
-        <v>85.94</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.69</v>
+        <v>5.7</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="DM19" t="n">
-        <v>41.44</v>
+        <v>41.42</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.66</v>
+        <v>12.64</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.97</v>
+        <v>12</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.619999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.38</v>
+        <v>55.67</v>
       </c>
       <c r="DW19" t="n">
         <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.53</v>
+        <v>17.58</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.72</v>
+        <v>11.78</v>
       </c>
       <c r="DZ19" t="n">
-        <v>5.81</v>
+        <v>5.79</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.72</v>
+        <v>19.67</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -2633,7 +2633,7 @@
         <v>11.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.88</v>
+        <v>10.81</v>
       </c>
       <c r="R5" t="n">
         <v>7.31</v>
@@ -2945,7 +2945,7 @@
         <v>11.13</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.42</v>
+        <v>12.39</v>
       </c>
       <c r="DR5" t="n">
         <v>8.09</v>
@@ -6690,10 +6690,10 @@
         <v>0.15</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.46</v>
+        <v>10.54</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.92</v>
+        <v>7</v>
       </c>
       <c r="AB15" t="n">
         <v>3.54</v>
@@ -6702,7 +6702,7 @@
         <v>19.46</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE15" t="n">
         <v>3.23</v>
@@ -6996,10 +6996,10 @@
         <v>0.26</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.73</v>
+        <v>9.77</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.23</v>
+        <v>6.27</v>
       </c>
       <c r="DZ15" t="n">
         <v>3.5</v>
@@ -7008,7 +7008,7 @@
         <v>18.08</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="EC15" t="n">
         <v>2.69</v>
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>45.43</v>
+        <v>45.5</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.29</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.67</v>
+        <v>44.71</v>
       </c>
       <c r="DW16" t="n">
         <v>0.33</v>
@@ -7893,7 +7893,7 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>49.76</v>
+        <v>49.71</v>
       </c>
       <c r="Y18" t="n">
         <v>0.06</v>
@@ -7908,7 +7908,7 @@
         <v>4.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>17.59</v>
+        <v>17.65</v>
       </c>
       <c r="AD18" t="n">
         <v>1.42</v>
@@ -8199,7 +8199,7 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.53</v>
+        <v>47.5</v>
       </c>
       <c r="DW18" t="n">
         <v>0.1</v>
@@ -8214,7 +8214,7 @@
         <v>4.03</v>
       </c>
       <c r="EA18" t="n">
-        <v>18.14</v>
+        <v>18.17</v>
       </c>
       <c r="EB18" t="n">
         <v>1.31</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
         <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="F7" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="G7" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="H7" t="n">
-        <v>91.2</v>
+        <v>89.94</v>
       </c>
       <c r="I7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="J7" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="K7" t="n">
-        <v>4.27</v>
+        <v>4.38</v>
       </c>
       <c r="L7" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="M7" t="n">
-        <v>37.13</v>
+        <v>38.31</v>
       </c>
       <c r="N7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="O7" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>11.47</v>
+        <v>11</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.47</v>
+        <v>12.38</v>
       </c>
       <c r="R7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="T7" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U7" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="V7" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>51.73</v>
+        <v>52</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.53</v>
+        <v>13.19</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.33</v>
+        <v>8.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.2</v>
+        <v>4.44</v>
       </c>
       <c r="AC7" t="n">
-        <v>23</v>
+        <v>23.69</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AF7" t="n">
         <v>0.2</v>
@@ -3547,10 +3547,10 @@
         <v>0.13</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.73</v>
+        <v>10.67</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.2</v>
+        <v>7.13</v>
       </c>
       <c r="BC7" t="n">
         <v>3.53</v>
@@ -3559,76 +3559,76 @@
         <v>21.33</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BF7" t="n">
         <v>2.47</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.73</v>
+        <v>8.68</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.07</v>
+        <v>4.03</v>
       </c>
       <c r="BR7" t="n">
-        <v>96.67</v>
+        <v>96.77</v>
       </c>
       <c r="BS7" t="n">
-        <v>86.67</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>66.67</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="BU7" t="n">
-        <v>36.67</v>
+        <v>38.71</v>
       </c>
       <c r="BV7" t="n">
-        <v>13.33</v>
+        <v>12.9</v>
       </c>
       <c r="BW7" t="n">
-        <v>10</v>
+        <v>9.68</v>
       </c>
       <c r="BX7" t="n">
-        <v>76.67</v>
+        <v>77.42</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CA7" t="n">
         <v>3.54</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CC7" t="n">
         <v>4.42</v>
@@ -3649,10 +3649,10 @@
         <v>1.43</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CK7" t="n">
         <v>1.54</v>
@@ -3664,13 +3664,13 @@
         <v>2.34</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO7" t="n">
         <v>1.26</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CQ7" t="n">
         <v>3.2</v>
@@ -3688,7 +3688,7 @@
         <v>1.46</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CW7" t="n">
         <v>1.82</v>
@@ -3709,85 +3709,85 @@
         <v>1.3</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="DH7" t="n">
-        <v>83.95999999999999</v>
+        <v>83.55</v>
       </c>
       <c r="DI7" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="DK7" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="DM7" t="n">
-        <v>36.57</v>
+        <v>37.19</v>
       </c>
       <c r="DN7" t="n">
         <v>1.1</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.1</v>
+        <v>11.84</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13</v>
+        <v>12.94</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.5</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.06</v>
+        <v>48.32</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.63</v>
+        <v>11.97</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.76</v>
+        <v>7.97</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.17</v>
+        <v>22.55</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="8">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" t="n">
         <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10" t="n">
         <v>0.07000000000000001</v>
@@ -4693,139 +4693,139 @@
         <v>1.53</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AI10" t="n">
-        <v>64.94</v>
+        <v>65.12</v>
       </c>
       <c r="AJ10" t="n">
         <v>-0.12</v>
       </c>
       <c r="AK10" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.06</v>
+        <v>3.88</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="AN10" t="n">
         <v>28.88</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.5</v>
+        <v>10.29</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.81</v>
+        <v>12.53</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.25</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="AT10" t="n">
         <v>1.88</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>54.56</v>
+        <v>53.94</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="BA10" t="n">
-        <v>13.06</v>
+        <v>12.71</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.88</v>
+        <v>7.65</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.19</v>
+        <v>5.06</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.25</v>
+        <v>19.82</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.1</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.48</v>
+        <v>4.47</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.58</v>
+        <v>4.53</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>74.19</v>
+        <v>75</v>
       </c>
       <c r="BT10" t="n">
-        <v>51.61</v>
+        <v>53.12</v>
       </c>
       <c r="BU10" t="n">
-        <v>41.94</v>
+        <v>43.75</v>
       </c>
       <c r="BV10" t="n">
-        <v>22.58</v>
+        <v>21.88</v>
       </c>
       <c r="BW10" t="n">
-        <v>16.13</v>
+        <v>15.62</v>
       </c>
       <c r="BX10" t="n">
-        <v>48.39</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
         <v>1.78</v>
@@ -4834,22 +4834,22 @@
         <v>1.93</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.62</v>
+        <v>3.57</v>
       </c>
       <c r="CE10" t="n">
         <v>1.31</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CG10" t="n">
         <v>3.18</v>
@@ -4858,7 +4858,7 @@
         <v>1.51</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.67</v>
@@ -4870,7 +4870,7 @@
         <v>1.91</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CN10" t="n">
         <v>1.9</v>
@@ -4882,7 +4882,7 @@
         <v>1.72</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CR10" t="n">
         <v>1.36</v>
@@ -4900,7 +4900,7 @@
         <v>2.25</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CX10" t="n">
         <v>1.53</v>
@@ -4924,46 +4924,46 @@
         <v>2.8</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="DH10" t="n">
-        <v>79.29000000000001</v>
+        <v>78.94</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.38</v>
+        <v>4.28</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.29</v>
+        <v>36.06</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.78</v>
+        <v>10.66</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.84</v>
+        <v>12.69</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.39</v>
+        <v>7.56</v>
       </c>
       <c r="DS10" t="n">
         <v>0.19</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>56.51</v>
+        <v>56.12</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.87</v>
+        <v>13.66</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.58</v>
+        <v>8.44</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.29</v>
+        <v>5.22</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.58</v>
+        <v>18.91</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
         <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
         <v>0.15</v>
@@ -5099,49 +5099,49 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="AI11" t="n">
-        <v>83.93000000000001</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="AJ11" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AK11" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AN11" t="n">
-        <v>39.93</v>
+        <v>38.93</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="AP11" t="n">
         <v>1.93</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.29</v>
+        <v>12.33</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.71</v>
+        <v>12.93</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.57</v>
+        <v>10</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AV11" t="n">
         <v>0.07000000000000001</v>
@@ -5153,82 +5153,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>48.07</v>
+        <v>47.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="BA11" t="n">
-        <v>13.36</v>
+        <v>13</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.640000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.71</v>
+        <v>4.47</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.93</v>
+        <v>19.07</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.07</v>
+        <v>2.96</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.22</v>
+        <v>10.25</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.07</v>
+        <v>2.96</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.3</v>
+        <v>4.36</v>
       </c>
       <c r="BQ11" t="n">
         <v>4.93</v>
       </c>
       <c r="BR11" t="n">
-        <v>100</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="BS11" t="n">
-        <v>81.48</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>55.56</v>
+        <v>53.57</v>
       </c>
       <c r="BU11" t="n">
-        <v>33.33</v>
+        <v>32.14</v>
       </c>
       <c r="BV11" t="n">
-        <v>18.52</v>
+        <v>17.86</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="BX11" t="n">
-        <v>62.96</v>
+        <v>60.71</v>
       </c>
       <c r="BY11" t="n">
         <v>2.5</v>
@@ -5237,16 +5237,16 @@
         <v>2.58</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.14</v>
+        <v>4.08</v>
       </c>
       <c r="CE11" t="n">
         <v>1.31</v>
@@ -5255,7 +5255,7 @@
         <v>2.41</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CH11" t="n">
         <v>1.52</v>
@@ -5273,7 +5273,7 @@
         <v>1.8</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CN11" t="n">
         <v>2.04</v>
@@ -5285,7 +5285,7 @@
         <v>1.69</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
@@ -5300,7 +5300,7 @@
         <v>1.53</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW11" t="n">
         <v>1.67</v>
@@ -5321,52 +5321,52 @@
         <v>1.23</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="DE11" t="n">
         <v>0.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DH11" t="n">
-        <v>82.78</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="DI11" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="DK11" t="n">
         <v>5.04</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="DM11" t="n">
-        <v>40.33</v>
+        <v>39.78</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.04</v>
+        <v>12.07</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.07</v>
+        <v>12.21</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.67</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DS11" t="n">
         <v>0.07000000000000001</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.63</v>
+        <v>49.22</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.74</v>
+        <v>14.5</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.11</v>
+        <v>10</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.63</v>
+        <v>4.5</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.48</v>
+        <v>21.47</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="12">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
         <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="G13" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="H13" t="n">
-        <v>88.31</v>
+        <v>89.86</v>
       </c>
       <c r="I13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="J13" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="K13" t="n">
-        <v>3.92</v>
+        <v>4.07</v>
       </c>
       <c r="L13" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="M13" t="n">
-        <v>38.38</v>
+        <v>39.21</v>
       </c>
       <c r="N13" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="O13" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="P13" t="n">
-        <v>10.54</v>
+        <v>10.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.08</v>
+        <v>12.5</v>
       </c>
       <c r="R13" t="n">
-        <v>7.92</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>49.08</v>
+        <v>50</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.62</v>
+        <v>14.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.69</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.92</v>
+        <v>4.79</v>
       </c>
       <c r="AC13" t="n">
-        <v>20.54</v>
+        <v>20.79</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>2.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.630000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="BN13" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.19</v>
+        <v>4.25</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="BR13" t="n">
-        <v>88.89</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>70.37</v>
+        <v>67.86</v>
       </c>
       <c r="BT13" t="n">
-        <v>62.96</v>
+        <v>60.71</v>
       </c>
       <c r="BU13" t="n">
-        <v>40.74</v>
+        <v>39.29</v>
       </c>
       <c r="BV13" t="n">
-        <v>22.22</v>
+        <v>21.43</v>
       </c>
       <c r="BW13" t="n">
-        <v>14.81</v>
+        <v>14.29</v>
       </c>
       <c r="BX13" t="n">
-        <v>51.85</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.57</v>
+        <v>3.48</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="CC13" t="n">
         <v>4.99</v>
@@ -6058,16 +6058,16 @@
         <v>1.34</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CH13" t="n">
         <v>1.45</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.77</v>
@@ -6106,10 +6106,10 @@
         <v>1.46</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CX13" t="n">
         <v>1.52</v>
@@ -6136,43 +6136,43 @@
         <v>0.04</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="DH13" t="n">
-        <v>82.41</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="DI13" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="DM13" t="n">
-        <v>33.07</v>
+        <v>33.68</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.56</v>
+        <v>11.57</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.48</v>
+        <v>12.68</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.369999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DS13" t="n">
         <v>0.04</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.04</v>
+        <v>48.54</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.19</v>
+        <v>12.5</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.85</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.33</v>
+        <v>4.29</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.67</v>
+        <v>19.82</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="14">

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
         <v>15</v>
@@ -1391,82 +1391,82 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="G2" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="H2" t="n">
-        <v>100.57</v>
+        <v>102.4</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="K2" t="n">
-        <v>6.36</v>
+        <v>6.33</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="M2" t="n">
-        <v>57.5</v>
+        <v>58.47</v>
       </c>
       <c r="N2" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="O2" t="n">
         <v>2.93</v>
       </c>
       <c r="P2" t="n">
-        <v>11.5</v>
+        <v>11.33</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.07</v>
+        <v>11.93</v>
       </c>
       <c r="R2" t="n">
-        <v>6.21</v>
+        <v>6.33</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="T2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="V2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>57.5</v>
+        <v>58.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.5</v>
+        <v>17.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.29</v>
+        <v>11</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.21</v>
+        <v>6.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.71</v>
+        <v>21.13</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF2" t="n">
         <v>0.07000000000000001</v>
@@ -1550,28 +1550,28 @@
         <v>1.93</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BO2" t="n">
         <v>1.07</v>
@@ -1580,40 +1580,40 @@
         <v>3.83</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
       <c r="BR2" t="n">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="BS2" t="n">
-        <v>79.31</v>
+        <v>80</v>
       </c>
       <c r="BT2" t="n">
-        <v>51.72</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>27.59</v>
+        <v>26.67</v>
       </c>
       <c r="BV2" t="n">
-        <v>10.34</v>
+        <v>10</v>
       </c>
       <c r="BW2" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="BX2" t="n">
-        <v>51.72</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.2</v>
+        <v>4.28</v>
       </c>
       <c r="CC2" t="n">
         <v>2.26</v>
@@ -1628,16 +1628,16 @@
         <v>2.46</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK2" t="n">
         <v>1.44</v>
@@ -1658,34 +1658,34 @@
         <v>1.82</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CR2" t="n">
         <v>1.4</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DA2" t="n">
         <v>1.92</v>
@@ -1703,19 +1703,19 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="DG2" t="n">
         <v>3.07</v>
       </c>
       <c r="DH2" t="n">
-        <v>101.72</v>
+        <v>102.6</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="DK2" t="n">
         <v>5.8</v>
@@ -1724,55 +1724,55 @@
         <v>0.34</v>
       </c>
       <c r="DM2" t="n">
-        <v>52.93</v>
+        <v>53.57</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.55</v>
+        <v>10.5</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.79</v>
+        <v>12.7</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.76</v>
+        <v>6.8</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>56.48</v>
+        <v>56.96</v>
       </c>
       <c r="DW2" t="n">
         <v>0.1</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.11</v>
+        <v>14.73</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.17</v>
+        <v>9.57</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.93</v>
+        <v>5.16</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.03</v>
+        <v>19.3</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
         <v>0.36</v>
@@ -1872,139 +1872,139 @@
         <v>2.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AI3" t="n">
-        <v>66.45999999999999</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>22.15</v>
+        <v>22.36</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>10.29</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.77</v>
+        <v>12.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.46</v>
+        <v>10.64</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>45.54</v>
+        <v>44.93</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.23</v>
+        <v>9.43</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.62</v>
+        <v>6.64</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="BD3" t="n">
-        <v>17.77</v>
+        <v>18</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.779999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL3" t="n">
         <v>0.89</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.96</v>
+        <v>4.11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="BR3" t="n">
-        <v>96.3</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="BS3" t="n">
-        <v>81.48</v>
+        <v>82.14</v>
       </c>
       <c r="BT3" t="n">
-        <v>59.26</v>
+        <v>57.14</v>
       </c>
       <c r="BU3" t="n">
-        <v>48.15</v>
+        <v>46.43</v>
       </c>
       <c r="BV3" t="n">
-        <v>25.93</v>
+        <v>25</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.11</v>
+        <v>10.71</v>
       </c>
       <c r="BX3" t="n">
-        <v>59.26</v>
+        <v>60.71</v>
       </c>
       <c r="BY3" t="n">
         <v>3.09</v>
@@ -2013,22 +2013,22 @@
         <v>3.38</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.57</v>
+        <v>4.76</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.14</v>
+        <v>5.19</v>
       </c>
       <c r="CE3" t="n">
         <v>1.33</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CG3" t="n">
         <v>3.04</v>
@@ -2037,61 +2037,61 @@
         <v>1.46</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.74</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL3" t="n">
         <v>1.89</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO3" t="n">
         <v>1.24</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS3" t="n">
         <v>2.78</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CU3" t="n">
         <v>1.48</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX3" t="n">
         <v>1.58</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB3" t="n">
         <v>1.28</v>
@@ -2103,79 +2103,79 @@
         <v>3.16</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="DH3" t="n">
-        <v>71.93000000000001</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="DM3" t="n">
-        <v>29.14</v>
+        <v>29</v>
       </c>
       <c r="DN3" t="n">
         <v>0.89</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.11</v>
+        <v>12.18</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13</v>
+        <v>12.86</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.960000000000001</v>
+        <v>10.07</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.78</v>
+        <v>44.5</v>
       </c>
       <c r="DW3" t="n">
         <v>0.18</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.48</v>
+        <v>10.54</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.08</v>
+        <v>7.07</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.41</v>
+        <v>3.46</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.08</v>
+        <v>17.22</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
         <v>14</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="G4" t="n">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="H4" t="n">
-        <v>72.54000000000001</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="J4" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>4.54</v>
+        <v>4.21</v>
       </c>
       <c r="L4" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="M4" t="n">
-        <v>26.08</v>
+        <v>25.21</v>
       </c>
       <c r="N4" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="P4" t="n">
-        <v>10.69</v>
+        <v>10.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.92</v>
+        <v>11.79</v>
       </c>
       <c r="R4" t="n">
-        <v>8.539999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="T4" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="U4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="V4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.85</v>
+        <v>48.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.23</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.15</v>
+        <v>6.21</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AC4" t="n">
-        <v>22.46</v>
+        <v>21.71</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AF4" t="n">
         <v>0.21</v>
@@ -2356,70 +2356,70 @@
         <v>2.07</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.26</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="BM4" t="n">
         <v>1.11</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="BO4" t="n">
         <v>1.04</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.96</v>
+        <v>3.82</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.3</v>
+        <v>4.32</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>81.48</v>
+        <v>82.14</v>
       </c>
       <c r="BT4" t="n">
-        <v>62.96</v>
+        <v>60.71</v>
       </c>
       <c r="BU4" t="n">
-        <v>37.04</v>
+        <v>35.71</v>
       </c>
       <c r="BV4" t="n">
-        <v>29.63</v>
+        <v>28.57</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="BX4" t="n">
-        <v>62.96</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="CC4" t="n">
         <v>4.16</v>
@@ -2440,31 +2440,31 @@
         <v>1.42</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.61</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO4" t="n">
         <v>1.16</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CR4" t="n">
         <v>1.37</v>
@@ -2473,7 +2473,7 @@
         <v>2.7</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CU4" t="n">
         <v>1.5</v>
@@ -2506,46 +2506,46 @@
         <v>2.92</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="DH4" t="n">
-        <v>73.81999999999999</v>
+        <v>74.22</v>
       </c>
       <c r="DI4" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.3</v>
+        <v>4.14</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM4" t="n">
-        <v>31.71</v>
+        <v>31.07</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.33</v>
+        <v>11.25</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.67</v>
+        <v>12.58</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.970000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="DS4" t="n">
         <v>0.22</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.63</v>
+        <v>47.5</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.63</v>
+        <v>10.57</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.81</v>
+        <v>6.82</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.63</v>
+        <v>20.32</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" t="n">
         <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
         <v>0.12</v>
@@ -2678,139 +2678,139 @@
         <v>2.56</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AI5" t="n">
-        <v>94.73</v>
+        <v>93.38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.13</v>
+        <v>4.19</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>38.93</v>
+        <v>39.69</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.27</v>
+        <v>10.44</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.07</v>
+        <v>13.88</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.93</v>
+        <v>8.94</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>52.07</v>
+        <v>51.81</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.27</v>
+        <v>14.88</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.93</v>
+        <v>9.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.67</v>
+        <v>22.12</v>
       </c>
       <c r="BE5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BF5" t="n">
         <v>1.56</v>
       </c>
-      <c r="BF5" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BG5" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.16</v>
+        <v>9.19</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.55</v>
+        <v>0.59</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.52</v>
+        <v>3.66</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.16</v>
+        <v>5.06</v>
       </c>
       <c r="BR5" t="n">
-        <v>93.55</v>
+        <v>93.75</v>
       </c>
       <c r="BS5" t="n">
-        <v>83.87</v>
+        <v>84.38</v>
       </c>
       <c r="BT5" t="n">
-        <v>54.84</v>
+        <v>56.25</v>
       </c>
       <c r="BU5" t="n">
-        <v>25.81</v>
+        <v>28.12</v>
       </c>
       <c r="BV5" t="n">
-        <v>22.58</v>
+        <v>21.88</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="BX5" t="n">
-        <v>64.52</v>
+        <v>65.62</v>
       </c>
       <c r="BY5" t="n">
         <v>1.74</v>
@@ -2819,22 +2819,22 @@
         <v>1.82</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.15</v>
+        <v>4.13</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="CE5" t="n">
         <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CG5" t="n">
         <v>3.16</v>
@@ -2843,7 +2843,7 @@
         <v>1.5</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.72</v>
@@ -2867,7 +2867,7 @@
         <v>1.73</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CR5" t="n">
         <v>1.37</v>
@@ -2882,19 +2882,19 @@
         <v>1.53</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY5" t="n">
         <v>1.88</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DA5" t="n">
         <v>1.93</v>
@@ -2906,49 +2906,49 @@
         <v>1.78</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="DE5" t="n">
         <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="DH5" t="n">
-        <v>100.19</v>
+        <v>99.34</v>
       </c>
       <c r="DI5" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.45</v>
+        <v>5.44</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM5" t="n">
-        <v>46.48</v>
+        <v>46.62</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.13</v>
+        <v>11.19</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.39</v>
+        <v>12.34</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.09</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DS5" t="n">
         <v>0.16</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.87</v>
+        <v>54.66</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX5" t="n">
-        <v>17.1</v>
+        <v>17.32</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.97</v>
+        <v>11.19</v>
       </c>
       <c r="DZ5" t="n">
         <v>6.13</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.9</v>
+        <v>22.12</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
         <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F6" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="G6" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H6" t="n">
-        <v>79.38</v>
+        <v>79.36</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="K6" t="n">
-        <v>5.69</v>
+        <v>5.57</v>
       </c>
       <c r="L6" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>34.77</v>
+        <v>33.71</v>
       </c>
       <c r="N6" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="O6" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>11.23</v>
+        <v>11.36</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.23</v>
+        <v>11.36</v>
       </c>
       <c r="R6" t="n">
-        <v>8.380000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="T6" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="U6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>54.46</v>
+        <v>54.57</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.77</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.77</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AB6" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="AC6" t="n">
-        <v>15.69</v>
+        <v>15.86</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="AF6" t="n">
         <v>0.13</v>
@@ -3162,70 +3162,70 @@
         <v>2.07</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.789999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="BR6" t="n">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>71.43000000000001</v>
+        <v>72.41</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.14</v>
+        <v>58.62</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>24.14</v>
       </c>
       <c r="BV6" t="n">
-        <v>21.43</v>
+        <v>20.69</v>
       </c>
       <c r="BW6" t="n">
-        <v>10.71</v>
+        <v>10.34</v>
       </c>
       <c r="BX6" t="n">
-        <v>53.57</v>
+        <v>51.72</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="CC6" t="n">
         <v>2.39</v>
@@ -3234,16 +3234,16 @@
         <v>2.5</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI6" t="n">
         <v>1.94</v>
@@ -3261,28 +3261,28 @@
         <v>2.48</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CO6" t="n">
         <v>1.21</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="CT6" t="n">
         <v>3.17</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CV6" t="n">
         <v>2.11</v>
@@ -3291,100 +3291,100 @@
         <v>1.79</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="DA6" t="n">
         <v>1.92</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.03</v>
+        <v>87.72</v>
       </c>
       <c r="DI6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.43</v>
+        <v>5.38</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="DM6" t="n">
-        <v>39.22</v>
+        <v>38.55</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.54</v>
+        <v>11.59</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.18</v>
+        <v>11.24</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.6</v>
+        <v>7.62</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>55</v>
+        <v>55.04</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.32</v>
+        <v>14.45</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.859999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.46</v>
+        <v>4.55</v>
       </c>
       <c r="EA6" t="n">
         <v>18</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="7">
@@ -3442,7 +3442,7 @@
         <v>12.38</v>
       </c>
       <c r="R7" t="n">
-        <v>7.88</v>
+        <v>7.94</v>
       </c>
       <c r="S7" t="n">
         <v>1.62</v>
@@ -3460,25 +3460,25 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>52</v>
+        <v>52.06</v>
       </c>
       <c r="Y7" t="n">
         <v>0.06</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.19</v>
+        <v>13.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.75</v>
+        <v>8.81</v>
       </c>
       <c r="AB7" t="n">
         <v>4.44</v>
       </c>
       <c r="AC7" t="n">
-        <v>23.69</v>
+        <v>23.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
         <v>2.5</v>
@@ -3754,7 +3754,7 @@
         <v>12.94</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.289999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="DS7" t="n">
         <v>0.19</v>
@@ -3766,25 +3766,25 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.32</v>
+        <v>48.35</v>
       </c>
       <c r="DW7" t="n">
         <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.97</v>
+        <v>12</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.97</v>
+        <v>8</v>
       </c>
       <c r="DZ7" t="n">
         <v>4</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.55</v>
+        <v>22.58</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC7" t="n">
         <v>2.49</v>
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
         <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="G8" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="H8" t="n">
-        <v>73.84999999999999</v>
+        <v>79.64</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="K8" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="M8" t="n">
-        <v>32.92</v>
+        <v>35.43</v>
       </c>
       <c r="N8" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="O8" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="P8" t="n">
-        <v>12.15</v>
+        <v>11.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.62</v>
+        <v>12.71</v>
       </c>
       <c r="R8" t="n">
-        <v>8.539999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="T8" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="U8" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="V8" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>50.69</v>
+        <v>52.14</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.23</v>
+        <v>13.21</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.77</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>18.08</v>
+        <v>18.21</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AF8" t="n">
         <v>0.08</v>
@@ -3968,70 +3968,70 @@
         <v>2.08</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="BH8" t="n">
-        <v>10</v>
+        <v>9.93</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.62</v>
+        <v>4.63</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.85</v>
+        <v>4.78</v>
       </c>
       <c r="BR8" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS8" t="n">
-        <v>80.77</v>
+        <v>81.48</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>51.85</v>
       </c>
       <c r="BU8" t="n">
-        <v>23.08</v>
+        <v>22.22</v>
       </c>
       <c r="BV8" t="n">
-        <v>15.38</v>
+        <v>14.81</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BX8" t="n">
-        <v>53.85</v>
+        <v>51.85</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="CA8" t="n">
         <v>3.66</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.96</v>
+        <v>3.97</v>
       </c>
       <c r="CC8" t="n">
         <v>4.14</v>
@@ -4043,10 +4043,10 @@
         <v>1.31</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CH8" t="n">
         <v>1.51</v>
@@ -4058,13 +4058,13 @@
         <v>1.65</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CN8" t="n">
         <v>1.95</v>
@@ -4073,10 +4073,10 @@
         <v>1.21</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
@@ -4091,7 +4091,7 @@
         <v>1.55</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CW8" t="n">
         <v>1.68</v>
@@ -4100,13 +4100,13 @@
         <v>1.51</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.45</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB8" t="n">
         <v>1.23</v>
@@ -4115,79 +4115,79 @@
         <v>1.75</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="DH8" t="n">
-        <v>76.81</v>
+        <v>79.7</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.81</v>
+        <v>4.85</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DM8" t="n">
-        <v>33.19</v>
+        <v>34.48</v>
       </c>
       <c r="DN8" t="n">
         <v>0.74</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.65</v>
+        <v>11.55</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.58</v>
+        <v>12.63</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.15</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.54</v>
+        <v>52.26</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.77</v>
+        <v>12.78</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.57</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.19</v>
+        <v>4.22</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.31</v>
+        <v>18.37</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="EC8" t="n">
         <v>2.23</v>
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
         <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
         <v>0.14</v>
@@ -4293,49 +4293,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AI9" t="n">
-        <v>75.38</v>
+        <v>73.86</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AN9" t="n">
-        <v>32.85</v>
+        <v>31.79</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.15</v>
+        <v>12.07</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.23</v>
+        <v>12.93</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.69</v>
+        <v>11.21</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>43.92</v>
+        <v>42.86</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.380000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BB9" t="n">
-        <v>6</v>
+        <v>5.93</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="BD9" t="n">
-        <v>18.54</v>
+        <v>17.86</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.48</v>
+        <v>9.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="BJ9" t="n">
         <v>0.96</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.93</v>
+        <v>4.96</v>
       </c>
       <c r="BR9" t="n">
-        <v>96.3</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="BS9" t="n">
-        <v>77.78</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>62.96</v>
+        <v>60.71</v>
       </c>
       <c r="BU9" t="n">
-        <v>40.74</v>
+        <v>39.29</v>
       </c>
       <c r="BV9" t="n">
-        <v>18.52</v>
+        <v>17.86</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="BX9" t="n">
-        <v>74.06999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY9" t="n">
         <v>3.46</v>
@@ -4431,16 +4431,16 @@
         <v>3.75</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.89</v>
+        <v>3.93</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.17</v>
+        <v>4.26</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.65</v>
+        <v>5.8</v>
       </c>
       <c r="CD9" t="n">
-        <v>7</v>
+        <v>7.44</v>
       </c>
       <c r="CE9" t="n">
         <v>1.32</v>
@@ -4449,16 +4449,16 @@
         <v>2.56</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CH9" t="n">
         <v>1.48</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CK9" t="n">
         <v>1.46</v>
@@ -4467,7 +4467,7 @@
         <v>1.88</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN9" t="n">
         <v>1.95</v>
@@ -4476,37 +4476,37 @@
         <v>1.23</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CR9" t="n">
         <v>1.38</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY9" t="n">
         <v>1.86</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DA9" t="n">
         <v>1.95</v>
@@ -4524,43 +4524,43 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DH9" t="n">
-        <v>76.41</v>
+        <v>75.61</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="DL9" t="n">
         <v>0.11</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.93</v>
+        <v>33.36</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.19</v>
+        <v>11.18</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.85</v>
+        <v>12.72</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.369999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="DS9" t="n">
         <v>0.07000000000000001</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>42.37</v>
+        <v>41.9</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.92</v>
+        <v>9.82</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.33</v>
+        <v>6.28</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.59</v>
+        <v>3.54</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.93</v>
+        <v>16.64</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -4729,7 +4729,7 @@
         <v>10.29</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.53</v>
+        <v>12.65</v>
       </c>
       <c r="AS10" t="n">
         <v>8.529999999999999</v>
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>53.94</v>
+        <v>53.88</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.18</v>
@@ -4960,7 +4960,7 @@
         <v>10.66</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.69</v>
+        <v>12.75</v>
       </c>
       <c r="DR10" t="n">
         <v>7.56</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>56.12</v>
+        <v>56.09</v>
       </c>
       <c r="DW10" t="n">
         <v>0.16</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
         <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5502,136 +5502,136 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AI12" t="n">
-        <v>83.29000000000001</v>
+        <v>84.67</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="AL12" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AN12" t="n">
-        <v>37.93</v>
+        <v>36.47</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11.57</v>
+        <v>11.47</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.36</v>
+        <v>12.27</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>51.43</v>
+        <v>51.73</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BA12" t="n">
-        <v>13.93</v>
+        <v>13.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.640000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.36</v>
+        <v>21.73</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="BH12" t="n">
-        <v>9</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="BJ12" t="n">
         <v>0.83</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="BN12" t="n">
         <v>1.03</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.1</v>
+        <v>3.97</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.21</v>
+        <v>4.23</v>
       </c>
       <c r="BR12" t="n">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="BS12" t="n">
-        <v>72.41</v>
+        <v>73.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>51.72</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>20.69</v>
+        <v>20</v>
       </c>
       <c r="BV12" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>48.28</v>
+        <v>50</v>
       </c>
       <c r="BY12" t="n">
         <v>1.94</v>
@@ -5640,25 +5640,25 @@
         <v>2.08</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="CE12" t="n">
         <v>1.33</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CH12" t="n">
         <v>1.46</v>
@@ -5670,16 +5670,16 @@
         <v>1.71</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL12" t="n">
         <v>1.85</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CO12" t="n">
         <v>1.24</v>
@@ -5697,13 +5697,13 @@
         <v>2.73</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CU12" t="n">
         <v>1.5</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CW12" t="n">
         <v>1.75</v>
@@ -5718,7 +5718,7 @@
         <v>2.42</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB12" t="n">
         <v>1.27</v>
@@ -5727,49 +5727,49 @@
         <v>1.87</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="DH12" t="n">
-        <v>85.14</v>
+        <v>85.77</v>
       </c>
       <c r="DI12" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.55</v>
+        <v>4.57</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM12" t="n">
-        <v>37.83</v>
+        <v>37.1</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.86</v>
+        <v>11.8</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.07</v>
+        <v>12.03</v>
       </c>
       <c r="DR12" t="n">
-        <v>9</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DS12" t="n">
         <v>0.1</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50.48</v>
+        <v>50.66</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.28</v>
+        <v>14.2</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.720000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.97</v>
+        <v>19.23</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="13">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
         <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F14" t="n">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="H14" t="n">
-        <v>89.69</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="K14" t="n">
-        <v>4.38</v>
+        <v>4.43</v>
       </c>
       <c r="L14" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="M14" t="n">
-        <v>42.31</v>
+        <v>41.43</v>
       </c>
       <c r="N14" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="O14" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="P14" t="n">
-        <v>11.23</v>
+        <v>11.21</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.46</v>
+        <v>10.71</v>
       </c>
       <c r="R14" t="n">
-        <v>10.31</v>
+        <v>10.57</v>
       </c>
       <c r="S14" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="T14" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="V14" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>55.31</v>
+        <v>55.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.15</v>
+        <v>12.64</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.92</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.23</v>
+        <v>4</v>
       </c>
       <c r="AC14" t="n">
-        <v>19.15</v>
+        <v>19.07</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AF14" t="n">
         <v>0.07000000000000001</v>
@@ -6386,64 +6386,64 @@
         <v>3.07</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.109999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.43</v>
+        <v>4.55</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.61</v>
+        <v>4.52</v>
       </c>
       <c r="BR14" t="n">
-        <v>96.43000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="BS14" t="n">
-        <v>82.14</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>46.43</v>
+        <v>48.28</v>
       </c>
       <c r="BU14" t="n">
-        <v>39.29</v>
+        <v>41.38</v>
       </c>
       <c r="BV14" t="n">
-        <v>25</v>
+        <v>24.14</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>67.86</v>
+        <v>68.97</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="CA14" t="n">
         <v>3.48</v>
@@ -6458,22 +6458,22 @@
         <v>3.5</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF14" t="n">
         <v>2.72</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CH14" t="n">
         <v>1.41</v>
       </c>
       <c r="CI14" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK14" t="n">
         <v>1.51</v>
@@ -6494,7 +6494,7 @@
         <v>1.9</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CR14" t="n">
         <v>1.4</v>
@@ -6509,10 +6509,10 @@
         <v>1.44</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX14" t="n">
         <v>1.57</v>
@@ -6533,16 +6533,16 @@
         <v>1.97</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="DH14" t="n">
         <v>83.14</v>
@@ -6551,64 +6551,64 @@
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.14</v>
+        <v>4.17</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="DM14" t="n">
-        <v>40.64</v>
+        <v>40.28</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.14</v>
+        <v>12.1</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.64</v>
+        <v>10.76</v>
       </c>
       <c r="DR14" t="n">
-        <v>11.75</v>
+        <v>11.83</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.18</v>
+        <v>51.21</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.18</v>
+        <v>11.96</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.279999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.89</v>
+        <v>3.79</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.64</v>
+        <v>18.62</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
         <v>0.08</v>
@@ -6711,136 +6711,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AI15" t="n">
-        <v>53.46</v>
+        <v>54.57</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.38</v>
+        <v>3.64</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="AN15" t="n">
-        <v>23.08</v>
+        <v>22.07</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.08</v>
+        <v>9.43</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.46</v>
+        <v>12.29</v>
       </c>
       <c r="AS15" t="n">
-        <v>10.69</v>
+        <v>11.07</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>32.31</v>
+        <v>31.93</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BA15" t="n">
-        <v>9</v>
+        <v>8.93</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.54</v>
+        <v>5.36</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.46</v>
+        <v>3.57</v>
       </c>
       <c r="BD15" t="n">
-        <v>16.69</v>
+        <v>16.29</v>
       </c>
       <c r="BE15" t="n">
         <v>0.95</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.35</v>
+        <v>4.41</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.46</v>
+        <v>4.63</v>
       </c>
       <c r="BR15" t="n">
-        <v>96.15000000000001</v>
+        <v>92.59</v>
       </c>
       <c r="BS15" t="n">
-        <v>76.92</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>57.69</v>
+        <v>55.56</v>
       </c>
       <c r="BU15" t="n">
-        <v>34.62</v>
+        <v>33.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BW15" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BX15" t="n">
-        <v>46.15</v>
+        <v>44.44</v>
       </c>
       <c r="BY15" t="n">
         <v>3.31</v>
@@ -6849,25 +6849,25 @@
         <v>3.67</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.15</v>
+        <v>4.18</v>
       </c>
       <c r="CC15" t="n">
-        <v>7.04</v>
+        <v>6.96</v>
       </c>
       <c r="CD15" t="n">
-        <v>7.39</v>
+        <v>7.35</v>
       </c>
       <c r="CE15" t="n">
         <v>1.3</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CH15" t="n">
         <v>1.4</v>
@@ -6882,7 +6882,7 @@
         <v>1.41</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM15" t="n">
         <v>2.46</v>
@@ -6897,7 +6897,7 @@
         <v>1.85</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
@@ -6912,106 +6912,106 @@
         <v>1.48</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW15" t="n">
         <v>1.91</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY15" t="n">
         <v>1.83</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DA15" t="n">
         <v>1.98</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="DE15" t="n">
         <v>0.04</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="DH15" t="n">
-        <v>66</v>
+        <v>66.11</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.53</v>
+        <v>3.66</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DM15" t="n">
-        <v>25.19</v>
+        <v>24.59</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.04</v>
+        <v>11.97</v>
       </c>
       <c r="DR15" t="n">
-        <v>10.53</v>
+        <v>10.74</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>36.38</v>
+        <v>36.04</v>
       </c>
       <c r="DW15" t="n">
         <v>0.26</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.77</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.27</v>
+        <v>6.15</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.08</v>
+        <v>17.82</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C16" t="n">
         <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7114,49 +7114,49 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="AI16" t="n">
-        <v>83.06999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AN16" t="n">
-        <v>34.29</v>
+        <v>33.4</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AP16" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.57</v>
+        <v>10.73</v>
       </c>
       <c r="AR16" t="n">
-        <v>13.43</v>
+        <v>13.33</v>
       </c>
       <c r="AS16" t="n">
-        <v>11.71</v>
+        <v>11.73</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
         <v>0.07000000000000001</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.07</v>
+        <v>9.67</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.21</v>
+        <v>6</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.86</v>
+        <v>3.67</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.57</v>
+        <v>18.07</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.07</v>
+        <v>10</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BL16" t="n">
         <v>0.89</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.59</v>
+        <v>5.54</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>77.78</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>74.06999999999999</v>
+        <v>75</v>
       </c>
       <c r="BU16" t="n">
-        <v>48.15</v>
+        <v>46.43</v>
       </c>
       <c r="BV16" t="n">
-        <v>18.52</v>
+        <v>17.86</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="BX16" t="n">
-        <v>62.96</v>
+        <v>60.71</v>
       </c>
       <c r="BY16" t="n">
         <v>3.4</v>
@@ -7252,31 +7252,31 @@
         <v>3.81</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.21</v>
+        <v>4.26</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.64</v>
+        <v>4.7</v>
       </c>
       <c r="CC16" t="n">
-        <v>6.39</v>
+        <v>6.61</v>
       </c>
       <c r="CD16" t="n">
-        <v>7.26</v>
+        <v>7.43</v>
       </c>
       <c r="CE16" t="n">
         <v>1.27</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.65</v>
@@ -7288,25 +7288,25 @@
         <v>1.74</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CO16" t="n">
         <v>1.17</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CT16" t="n">
         <v>3.22</v>
@@ -7318,28 +7318,28 @@
         <v>2.27</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB16" t="n">
         <v>1.2</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="DE16" t="n">
         <v>0.04</v>
@@ -7348,10 +7348,10 @@
         <v>1.82</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="DH16" t="n">
-        <v>75.29000000000001</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="DI16" t="n">
         <v>0.07000000000000001</v>
@@ -7360,61 +7360,61 @@
         <v>3.04</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM16" t="n">
-        <v>33.85</v>
+        <v>33.39</v>
       </c>
       <c r="DN16" t="n">
         <v>1.04</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.59</v>
+        <v>11.64</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.96</v>
+        <v>13.89</v>
       </c>
       <c r="DR16" t="n">
-        <v>10.85</v>
+        <v>10.89</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.71</v>
+        <v>44.68</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.04</v>
+        <v>10.79</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.89</v>
+        <v>6.75</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.15</v>
+        <v>4.04</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.63</v>
+        <v>18.86</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="17">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
         <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F17" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="G17" t="n">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="H17" t="n">
-        <v>87.29000000000001</v>
+        <v>90.61</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="J17" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>6.11</v>
       </c>
       <c r="L17" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="M17" t="n">
-        <v>50.35</v>
+        <v>49.11</v>
       </c>
       <c r="N17" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="O17" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="P17" t="n">
-        <v>11.06</v>
+        <v>10.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>14.53</v>
+        <v>14.67</v>
       </c>
       <c r="R17" t="n">
-        <v>6.18</v>
+        <v>6.06</v>
       </c>
       <c r="S17" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="T17" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>55.82</v>
+        <v>56.78</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>16.82</v>
+        <v>16.56</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.35</v>
+        <v>11.28</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.47</v>
+        <v>5.28</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.71</v>
+        <v>19.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AF17" t="n">
         <v>0.06</v>
@@ -7595,70 +7595,70 @@
         <v>2.56</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.24</v>
+        <v>9.41</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.18</v>
+        <v>4.24</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="BR17" t="n">
-        <v>90.91</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>75.76000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="BT17" t="n">
-        <v>51.52</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>30.3</v>
+        <v>29.41</v>
       </c>
       <c r="BV17" t="n">
-        <v>18.18</v>
+        <v>17.65</v>
       </c>
       <c r="BW17" t="n">
-        <v>12.12</v>
+        <v>11.76</v>
       </c>
       <c r="BX17" t="n">
-        <v>57.58</v>
+        <v>55.88</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.08</v>
+        <v>4.09</v>
       </c>
       <c r="CC17" t="n">
         <v>2.48</v>
@@ -7673,7 +7673,7 @@
         <v>2.47</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CH17" t="n">
         <v>1.43</v>
@@ -7682,7 +7682,7 @@
         <v>2.02</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK17" t="n">
         <v>1.44</v>
@@ -7718,28 +7718,28 @@
         <v>1.49</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY17" t="n">
         <v>1.88</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DB17" t="n">
         <v>1.26</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DD17" t="n">
         <v>3.04</v>
@@ -7748,43 +7748,43 @@
         <v>0.12</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="DH17" t="n">
-        <v>89.09</v>
+        <v>90.79000000000001</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.54</v>
+        <v>5.62</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="DM17" t="n">
-        <v>44.79</v>
+        <v>44.3</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="DO17" t="n">
         <v>2.76</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.46</v>
+        <v>11.12</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.67</v>
+        <v>13.77</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.52</v>
+        <v>7.42</v>
       </c>
       <c r="DS17" t="n">
         <v>0.15</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.51</v>
+        <v>55.06</v>
       </c>
       <c r="DW17" t="n">
         <v>0.18</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.36</v>
+        <v>15.27</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.91</v>
+        <v>9.92</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.46</v>
+        <v>5.36</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.88</v>
+        <v>18.97</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C18" t="n">
         <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18" t="n">
         <v>0.12</v>
@@ -7917,139 +7917,139 @@
         <v>2.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="n">
-        <v>70.45999999999999</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.54</v>
+        <v>3.43</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AN18" t="n">
-        <v>34.38</v>
+        <v>33.57</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12</v>
+        <v>12.07</v>
       </c>
       <c r="AR18" t="n">
-        <v>12.15</v>
+        <v>12.07</v>
       </c>
       <c r="AS18" t="n">
         <v>11</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>44.62</v>
+        <v>43.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.92</v>
+        <v>10.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.69</v>
+        <v>7.29</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="BD18" t="n">
-        <v>18.85</v>
+        <v>18.93</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="BH18" t="n">
         <v>8.23</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="BO18" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.73</v>
+        <v>3.77</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.07</v>
+        <v>4.03</v>
       </c>
       <c r="BR18" t="n">
-        <v>90</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>80</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="BT18" t="n">
-        <v>50</v>
+        <v>51.61</v>
       </c>
       <c r="BU18" t="n">
-        <v>33.33</v>
+        <v>32.26</v>
       </c>
       <c r="BV18" t="n">
-        <v>16.67</v>
+        <v>16.13</v>
       </c>
       <c r="BW18" t="n">
-        <v>6.67</v>
+        <v>6.45</v>
       </c>
       <c r="BX18" t="n">
-        <v>53.33</v>
+        <v>51.61</v>
       </c>
       <c r="BY18" t="n">
         <v>2.26</v>
@@ -8058,40 +8058,40 @@
         <v>2.37</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CB18" t="n">
         <v>4.11</v>
       </c>
       <c r="CC18" t="n">
-        <v>5.07</v>
+        <v>4.99</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.51</v>
+        <v>5.42</v>
       </c>
       <c r="CE18" t="n">
         <v>1.16</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CH18" t="n">
         <v>1.4</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.5</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM18" t="n">
         <v>2.22</v>
@@ -8100,10 +8100,10 @@
         <v>1.7</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CQ18" t="n">
         <v>2.37</v>
@@ -8148,79 +8148,79 @@
         <v>2.64</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="DH18" t="n">
-        <v>80.03</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DM18" t="n">
-        <v>36.77</v>
+        <v>36.32</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.2</v>
+        <v>12.22</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.23</v>
+        <v>13.16</v>
       </c>
       <c r="DR18" t="n">
-        <v>9</v>
+        <v>9.06</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.5</v>
+        <v>46.91</v>
       </c>
       <c r="DW18" t="n">
         <v>0.1</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.06</v>
+        <v>11.84</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.029999999999999</v>
+        <v>7.84</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="EA18" t="n">
-        <v>18.17</v>
+        <v>18.23</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="19">
@@ -8230,25 +8230,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D19" t="n">
         <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F19" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="G19" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="H19" t="n">
-        <v>93.18000000000001</v>
+        <v>94</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -8257,67 +8257,67 @@
         <v>1.94</v>
       </c>
       <c r="K19" t="n">
-        <v>5.47</v>
+        <v>5.61</v>
       </c>
       <c r="L19" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>44.29</v>
+        <v>44.33</v>
       </c>
       <c r="N19" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>12</v>
+        <v>11.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.59</v>
+        <v>11.67</v>
       </c>
       <c r="R19" t="n">
-        <v>8.59</v>
+        <v>8.67</v>
       </c>
       <c r="S19" t="n">
         <v>1.06</v>
       </c>
       <c r="T19" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="U19" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="V19" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>57.82</v>
+        <v>58.11</v>
       </c>
       <c r="Y19" t="n">
         <v>0.06</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.12</v>
+        <v>19.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>12.88</v>
+        <v>13.17</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.24</v>
+        <v>6.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.65</v>
+        <v>18.83</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AF19" t="n">
         <v>0.06</v>
@@ -8401,19 +8401,19 @@
         <v>2.44</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.300000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="BL19" t="n">
         <v>0.76</v>
@@ -8422,49 +8422,49 @@
         <v>0.76</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.42</v>
+        <v>4.53</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="BR19" t="n">
-        <v>84.84999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="BS19" t="n">
-        <v>69.7</v>
+        <v>70.59</v>
       </c>
       <c r="BT19" t="n">
-        <v>54.55</v>
+        <v>52.94</v>
       </c>
       <c r="BU19" t="n">
-        <v>42.42</v>
+        <v>41.18</v>
       </c>
       <c r="BV19" t="n">
-        <v>18.18</v>
+        <v>17.65</v>
       </c>
       <c r="BW19" t="n">
-        <v>12.12</v>
+        <v>11.76</v>
       </c>
       <c r="BX19" t="n">
-        <v>51.52</v>
+        <v>52.94</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BZ19" t="n">
         <v>1.58</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.15</v>
+        <v>4.17</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.51</v>
+        <v>4.5</v>
       </c>
       <c r="CC19" t="n">
         <v>2.27</v>
@@ -8482,13 +8482,13 @@
         <v>3.42</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CK19" t="n">
         <v>1.5</v>
@@ -8497,10 +8497,10 @@
         <v>1.93</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO19" t="n">
         <v>1.17</v>
@@ -8515,82 +8515,82 @@
         <v>1.36</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CT19" t="n">
         <v>3.23</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CW19" t="n">
         <v>1.7</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB19" t="n">
         <v>1.21</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="DE19" t="n">
         <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="DH19" t="n">
-        <v>86.40000000000001</v>
+        <v>87.03</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.7</v>
+        <v>5.77</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="DM19" t="n">
-        <v>41.42</v>
+        <v>41.53</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.64</v>
+        <v>12.5</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12</v>
+        <v>12.03</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.550000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="DS19" t="n">
         <v>0.21</v>
@@ -8602,25 +8602,25 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.67</v>
+        <v>55.88</v>
       </c>
       <c r="DW19" t="n">
         <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.58</v>
+        <v>17.82</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.78</v>
+        <v>11.97</v>
       </c>
       <c r="DZ19" t="n">
-        <v>5.79</v>
+        <v>5.85</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.67</v>
+        <v>19.73</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="EC19" t="n">
         <v>2.12</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>44.93</v>
+        <v>44.86</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.14</v>
@@ -1944,7 +1944,7 @@
         <v>2.79</v>
       </c>
       <c r="BD3" t="n">
-        <v>18</v>
+        <v>18.07</v>
       </c>
       <c r="BE3" t="n">
         <v>0.96</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.5</v>
+        <v>44.46</v>
       </c>
       <c r="DW3" t="n">
         <v>0.18</v>
@@ -2169,7 +2169,7 @@
         <v>3.46</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.22</v>
+        <v>17.25</v>
       </c>
       <c r="EB3" t="n">
         <v>1.12</v>
@@ -2257,10 +2257,10 @@
         <v>0.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.210000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.21</v>
+        <v>6.14</v>
       </c>
       <c r="AB4" t="n">
         <v>3</v>
@@ -2563,10 +2563,10 @@
         <v>0.25</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.57</v>
+        <v>10.54</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.82</v>
+        <v>6.78</v>
       </c>
       <c r="DZ4" t="n">
         <v>3.75</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>54.57</v>
+        <v>54.64</v>
       </c>
       <c r="Y6" t="n">
         <v>0.07000000000000001</v>
@@ -3072,7 +3072,7 @@
         <v>5.14</v>
       </c>
       <c r="AC6" t="n">
-        <v>15.86</v>
+        <v>15.93</v>
       </c>
       <c r="AD6" t="n">
         <v>1.32</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>55.04</v>
+        <v>55.07</v>
       </c>
       <c r="DW6" t="n">
         <v>0.1</v>
@@ -3378,7 +3378,7 @@
         <v>4.55</v>
       </c>
       <c r="EA6" t="n">
-        <v>18</v>
+        <v>18.04</v>
       </c>
       <c r="EB6" t="n">
         <v>1.4</v>
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>52.14</v>
+        <v>52.07</v>
       </c>
       <c r="Y8" t="n">
         <v>0.07000000000000001</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>52.26</v>
+        <v>52.22</v>
       </c>
       <c r="DW8" t="n">
         <v>0.11</v>
@@ -4353,10 +4353,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.210000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.93</v>
+        <v>6</v>
       </c>
       <c r="BC9" t="n">
         <v>3.29</v>
@@ -4578,10 +4578,10 @@
         <v>0.14</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.82</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.28</v>
+        <v>6.32</v>
       </c>
       <c r="DZ9" t="n">
         <v>3.54</v>
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>45.4</v>
+        <v>45.33</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.27</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.68</v>
+        <v>44.64</v>
       </c>
       <c r="DW16" t="n">
         <v>0.32</v>
@@ -7974,16 +7974,16 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>43.5</v>
+        <v>43.57</v>
       </c>
       <c r="AZ18" t="n">
         <v>0.14</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.5</v>
+        <v>10.57</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.29</v>
+        <v>7.36</v>
       </c>
       <c r="BC18" t="n">
         <v>3.21</v>
@@ -8199,16 +8199,16 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.91</v>
+        <v>46.94</v>
       </c>
       <c r="DW18" t="n">
         <v>0.1</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.84</v>
+        <v>11.87</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.84</v>
+        <v>7.87</v>
       </c>
       <c r="DZ18" t="n">
         <v>4</v>
@@ -8296,22 +8296,22 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>58.11</v>
+        <v>58.17</v>
       </c>
       <c r="Y19" t="n">
         <v>0.06</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.5</v>
+        <v>19.44</v>
       </c>
       <c r="AA19" t="n">
-        <v>13.17</v>
+        <v>13.06</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.33</v>
+        <v>6.39</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.83</v>
+        <v>19.06</v>
       </c>
       <c r="AD19" t="n">
         <v>1.99</v>
@@ -8602,22 +8602,22 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.88</v>
+        <v>55.92</v>
       </c>
       <c r="DW19" t="n">
         <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>17.82</v>
+        <v>17.79</v>
       </c>
       <c r="DY19" t="n">
-        <v>11.97</v>
+        <v>11.91</v>
       </c>
       <c r="DZ19" t="n">
-        <v>5.85</v>
+        <v>5.88</v>
       </c>
       <c r="EA19" t="n">
-        <v>19.73</v>
+        <v>19.86</v>
       </c>
       <c r="EB19" t="n">
         <v>1.73</v>

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
         <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F6" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="G6" t="n">
-        <v>3.07</v>
+        <v>3.27</v>
       </c>
       <c r="H6" t="n">
-        <v>79.36</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="K6" t="n">
-        <v>5.57</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>33.71</v>
+        <v>37.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="P6" t="n">
-        <v>11.36</v>
+        <v>11.47</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.36</v>
+        <v>11.33</v>
       </c>
       <c r="R6" t="n">
-        <v>8.359999999999999</v>
+        <v>8</v>
       </c>
       <c r="S6" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="U6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="V6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>54.64</v>
+        <v>56.07</v>
       </c>
       <c r="Y6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>15</v>
+        <v>16.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.859999999999999</v>
+        <v>10.47</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.14</v>
+        <v>5.87</v>
       </c>
       <c r="AC6" t="n">
-        <v>15.93</v>
+        <v>16.13</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AF6" t="n">
         <v>0.13</v>
@@ -3162,70 +3162,70 @@
         <v>2.07</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.76</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.97</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.17</v>
+        <v>4.23</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.41</v>
+        <v>4.47</v>
       </c>
       <c r="BR6" t="n">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="BS6" t="n">
-        <v>72.41</v>
+        <v>73.33</v>
       </c>
       <c r="BT6" t="n">
-        <v>58.62</v>
+        <v>60</v>
       </c>
       <c r="BU6" t="n">
-        <v>24.14</v>
+        <v>26.67</v>
       </c>
       <c r="BV6" t="n">
-        <v>20.69</v>
+        <v>23.33</v>
       </c>
       <c r="BW6" t="n">
-        <v>10.34</v>
+        <v>10</v>
       </c>
       <c r="BX6" t="n">
-        <v>51.72</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="CC6" t="n">
         <v>2.39</v>
@@ -3237,13 +3237,13 @@
         <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI6" t="n">
         <v>1.94</v>
@@ -3255,37 +3255,37 @@
         <v>1.41</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CN6" t="n">
         <v>1.91</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="CT6" t="n">
         <v>3.17</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CW6" t="n">
         <v>1.79</v>
@@ -3294,7 +3294,7 @@
         <v>1.55</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.39</v>
@@ -3306,85 +3306,85 @@
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="DE6" t="n">
         <v>0.13</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="DH6" t="n">
-        <v>87.72</v>
+        <v>89.8</v>
       </c>
       <c r="DI6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.38</v>
+        <v>5.6</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.55</v>
+        <v>40.24</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.59</v>
+        <v>11.64</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.24</v>
+        <v>11.23</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.62</v>
+        <v>7.46</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>55.07</v>
+        <v>55.77</v>
       </c>
       <c r="DW6" t="n">
         <v>0.1</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.45</v>
+        <v>15.13</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.55</v>
+        <v>4.94</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.04</v>
+        <v>18.07</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="7">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
         <v>0.07000000000000001</v>
@@ -3887,52 +3887,52 @@
         <v>2.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="AI8" t="n">
-        <v>79.77</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.69</v>
+        <v>4.36</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AN8" t="n">
-        <v>33.46</v>
+        <v>33.14</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.15</v>
+        <v>10.79</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.54</v>
+        <v>12.57</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.77</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>52.38</v>
+        <v>50.36</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.31</v>
+        <v>11.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.380000000000001</v>
+        <v>7.79</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.92</v>
+        <v>3.71</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.54</v>
+        <v>18.21</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.93</v>
+        <v>10</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.63</v>
+        <v>4.68</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.78</v>
+        <v>4.82</v>
       </c>
       <c r="BR8" t="n">
-        <v>96.3</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="BS8" t="n">
-        <v>81.48</v>
+        <v>82.14</v>
       </c>
       <c r="BT8" t="n">
-        <v>51.85</v>
+        <v>53.57</v>
       </c>
       <c r="BU8" t="n">
-        <v>22.22</v>
+        <v>25</v>
       </c>
       <c r="BV8" t="n">
-        <v>14.81</v>
+        <v>17.86</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="BX8" t="n">
-        <v>51.85</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>2.54</v>
@@ -4028,19 +4028,19 @@
         <v>2.86</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.14</v>
+        <v>4.38</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.35</v>
+        <v>4.59</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF8" t="n">
         <v>2.47</v>
@@ -4061,13 +4061,13 @@
         <v>1.46</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO8" t="n">
         <v>1.21</v>
@@ -4076,13 +4076,13 @@
         <v>1.73</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CT8" t="n">
         <v>3.24</v>
@@ -4091,73 +4091,73 @@
         <v>1.55</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB8" t="n">
         <v>1.23</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="DE8" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="DH8" t="n">
-        <v>79.7</v>
+        <v>78.42</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.85</v>
+        <v>4.68</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM8" t="n">
-        <v>34.48</v>
+        <v>34.29</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO8" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.55</v>
+        <v>11.36</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.63</v>
+        <v>12.64</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.960000000000001</v>
+        <v>9</v>
       </c>
       <c r="DS8" t="n">
         <v>0.22</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>52.22</v>
+        <v>51.22</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.78</v>
+        <v>12.36</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.550000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.37</v>
+        <v>18.21</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="9">

--- a/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Mexico_Liga_MX_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n">
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
         <v>0.07000000000000001</v>
@@ -1469,139 +1469,139 @@
         <v>1.93</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="AI2" t="n">
-        <v>102.8</v>
+        <v>102.88</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.27</v>
+        <v>5.19</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AN2" t="n">
-        <v>48.67</v>
+        <v>47.69</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.67</v>
+        <v>9.44</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.47</v>
+        <v>13.56</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.27</v>
+        <v>7.12</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>55.53</v>
+        <v>55.88</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.87</v>
+        <v>11.75</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.130000000000001</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.47</v>
+        <v>17.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.7</v>
+        <v>4.61</v>
       </c>
       <c r="BR2" t="n">
-        <v>93.33</v>
+        <v>93.55</v>
       </c>
       <c r="BS2" t="n">
-        <v>80</v>
+        <v>77.42</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>48.39</v>
       </c>
       <c r="BU2" t="n">
-        <v>26.67</v>
+        <v>25.81</v>
       </c>
       <c r="BV2" t="n">
-        <v>10</v>
+        <v>9.68</v>
       </c>
       <c r="BW2" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>48.39</v>
       </c>
       <c r="BY2" t="n">
         <v>1.47</v>
@@ -1610,22 +1610,22 @@
         <v>1.55</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CG2" t="n">
         <v>3.03</v>
@@ -1634,7 +1634,7 @@
         <v>1.43</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.76</v>
@@ -1658,7 +1658,7 @@
         <v>1.82</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CR2" t="n">
         <v>1.4</v>
@@ -1667,22 +1667,22 @@
         <v>2.74</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX2" t="n">
         <v>1.57</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.35</v>
@@ -1691,7 +1691,7 @@
         <v>1.92</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC2" t="n">
         <v>1.87</v>
@@ -1700,46 +1700,46 @@
         <v>3.13</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="DH2" t="n">
-        <v>102.6</v>
+        <v>102.65</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.8</v>
+        <v>5.74</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="DM2" t="n">
-        <v>53.57</v>
+        <v>52.91</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.5</v>
+        <v>10.35</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.7</v>
+        <v>12.77</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.8</v>
+        <v>6.74</v>
       </c>
       <c r="DS2" t="n">
         <v>0.13</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>56.96</v>
+        <v>57.1</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.73</v>
+        <v>14.58</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.57</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.16</v>
+        <v>5.13</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.3</v>
+        <v>19.26</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="G3" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="H3" t="n">
-        <v>77</v>
+        <v>80.13</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>35.64</v>
+        <v>34.67</v>
       </c>
       <c r="N3" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="O3" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="P3" t="n">
-        <v>14.07</v>
+        <v>13.53</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.21</v>
+        <v>12.87</v>
       </c>
       <c r="R3" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="T3" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="U3" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>44.07</v>
+        <v>45.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.64</v>
+        <v>12</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.5</v>
+        <v>7.93</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.14</v>
+        <v>4.07</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.43</v>
+        <v>17.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AF3" t="n">
         <v>0.07000000000000001</v>
@@ -1953,70 +1953,70 @@
         <v>2.21</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.18</v>
+        <v>3.07</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.18</v>
+        <v>3.07</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.11</v>
+        <v>3.93</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.14</v>
+        <v>3.97</v>
       </c>
       <c r="BR3" t="n">
-        <v>96.43000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>82.14</v>
+        <v>79.31</v>
       </c>
       <c r="BT3" t="n">
-        <v>57.14</v>
+        <v>55.17</v>
       </c>
       <c r="BU3" t="n">
-        <v>46.43</v>
+        <v>44.83</v>
       </c>
       <c r="BV3" t="n">
-        <v>25</v>
+        <v>24.14</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.71</v>
+        <v>10.34</v>
       </c>
       <c r="BX3" t="n">
-        <v>60.71</v>
+        <v>58.62</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.09</v>
+        <v>3.02</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="CC3" t="n">
         <v>4.76</v>
@@ -2028,7 +2028,7 @@
         <v>1.33</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CG3" t="n">
         <v>3.04</v>
@@ -2040,28 +2040,28 @@
         <v>2.03</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK3" t="n">
         <v>1.47</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO3" t="n">
         <v>1.24</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="CR3" t="n">
         <v>1.39</v>
@@ -2100,82 +2100,82 @@
         <v>1.89</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="DH3" t="n">
-        <v>71.54000000000001</v>
+        <v>73.34</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="DM3" t="n">
-        <v>29</v>
+        <v>28.73</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.18</v>
+        <v>11.97</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.86</v>
+        <v>12.69</v>
       </c>
       <c r="DR3" t="n">
-        <v>10.07</v>
+        <v>10.21</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.46</v>
+        <v>45.14</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.54</v>
+        <v>10.76</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.07</v>
+        <v>7.31</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.25</v>
+        <v>17.72</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
         <v>14</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="G4" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="n">
-        <v>73.43000000000001</v>
+        <v>74.13</v>
       </c>
       <c r="I4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.21</v>
+        <v>4.27</v>
       </c>
       <c r="L4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>25.21</v>
+        <v>26</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="P4" t="n">
-        <v>10.57</v>
+        <v>10.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.79</v>
+        <v>12.67</v>
       </c>
       <c r="R4" t="n">
-        <v>8.789999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="U4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="V4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.5</v>
+        <v>48.47</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.140000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.14</v>
+        <v>6.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="AC4" t="n">
-        <v>21.71</v>
+        <v>21.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AF4" t="n">
         <v>0.21</v>
@@ -2359,67 +2359,67 @@
         <v>3.21</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.140000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="BI4" t="n">
         <v>3.21</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="BL4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BO4" t="n">
         <v>1.07</v>
       </c>
-      <c r="BM4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BP4" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>82.14</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>60.71</v>
+        <v>62.07</v>
       </c>
       <c r="BU4" t="n">
-        <v>35.71</v>
+        <v>34.48</v>
       </c>
       <c r="BV4" t="n">
-        <v>28.57</v>
+        <v>27.59</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="BX4" t="n">
-        <v>64.29000000000001</v>
+        <v>65.52</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="CC4" t="n">
         <v>4.16</v>
@@ -2437,7 +2437,7 @@
         <v>3.02</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI4" t="n">
         <v>2.05</v>
@@ -2449,10 +2449,10 @@
         <v>1.42</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CN4" t="n">
         <v>1.85</v>
@@ -2479,7 +2479,7 @@
         <v>1.5</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CW4" t="n">
         <v>1.7</v>
@@ -2494,7 +2494,7 @@
         <v>2.38</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB4" t="n">
         <v>1.25</v>
@@ -2503,82 +2503,82 @@
         <v>1.8</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="DE4" t="n">
         <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="DH4" t="n">
-        <v>74.22</v>
+        <v>74.55</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.14</v>
+        <v>4.17</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DM4" t="n">
-        <v>31.07</v>
+        <v>31.28</v>
       </c>
       <c r="DN4" t="n">
         <v>1.1</v>
       </c>
       <c r="DO4" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.25</v>
+        <v>11.31</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.58</v>
+        <v>13</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.07</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.5</v>
+        <v>47.52</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.54</v>
+        <v>10.48</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.78</v>
+        <v>6.73</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.32</v>
+        <v>20.31</v>
       </c>
       <c r="EB4" t="n">
         <v>1.14</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" t="n">
         <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
         <v>0.12</v>
@@ -2678,16 +2678,16 @@
         <v>2.56</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="AI5" t="n">
-        <v>93.38</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="AJ5" t="n">
         <v>0.12</v>
@@ -2696,121 +2696,121 @@
         <v>2</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.19</v>
+        <v>4.47</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AN5" t="n">
-        <v>39.69</v>
+        <v>41.65</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.44</v>
+        <v>10.35</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.88</v>
+        <v>13.76</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.94</v>
+        <v>8.76</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>51.81</v>
+        <v>52.59</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.88</v>
+        <v>15.29</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.5</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.38</v>
+        <v>5.41</v>
       </c>
       <c r="BD5" t="n">
-        <v>22.12</v>
+        <v>22.47</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.19</v>
+        <v>9.27</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="BL5" t="n">
         <v>0.91</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.06</v>
+        <v>5.15</v>
       </c>
       <c r="BR5" t="n">
-        <v>93.75</v>
+        <v>93.94</v>
       </c>
       <c r="BS5" t="n">
-        <v>84.38</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>56.25</v>
+        <v>54.55</v>
       </c>
       <c r="BU5" t="n">
-        <v>28.12</v>
+        <v>27.27</v>
       </c>
       <c r="BV5" t="n">
-        <v>21.88</v>
+        <v>21.21</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.25</v>
+        <v>6.06</v>
       </c>
       <c r="BX5" t="n">
-        <v>65.62</v>
+        <v>66.67</v>
       </c>
       <c r="BY5" t="n">
         <v>1.74</v>
@@ -2819,16 +2819,16 @@
         <v>1.82</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.13</v>
+        <v>4.15</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="CE5" t="n">
         <v>1.31</v>
@@ -2837,7 +2837,7 @@
         <v>2.49</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CH5" t="n">
         <v>1.5</v>
@@ -2846,40 +2846,40 @@
         <v>2.07</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CO5" t="n">
         <v>1.21</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CR5" t="n">
         <v>1.37</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CT5" t="n">
         <v>3.2</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CV5" t="n">
         <v>2.2</v>
@@ -2891,94 +2891,94 @@
         <v>1.55</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.38</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DB5" t="n">
         <v>1.24</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="DH5" t="n">
-        <v>99.34</v>
+        <v>100.33</v>
       </c>
       <c r="DI5" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.44</v>
+        <v>5.55</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="DM5" t="n">
-        <v>46.62</v>
+        <v>47.42</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.19</v>
+        <v>11.12</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.34</v>
+        <v>12.33</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.119999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.66</v>
+        <v>54.97</v>
       </c>
       <c r="DW5" t="n">
         <v>0.18</v>
       </c>
       <c r="DX5" t="n">
-        <v>17.32</v>
+        <v>17.45</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.19</v>
+        <v>11.33</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6.13</v>
+        <v>6.12</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.12</v>
+        <v>22.3</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="EC5" t="n">
         <v>2.06</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" t="n">
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
         <v>0.13</v>
@@ -3081,139 +3081,139 @@
         <v>2.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AI6" t="n">
-        <v>95.53</v>
+        <v>93.31</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AN6" t="n">
-        <v>43.07</v>
+        <v>41.88</v>
       </c>
       <c r="AO6" t="n">
         <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.8</v>
+        <v>11.94</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.13</v>
+        <v>10.94</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.93</v>
+        <v>7.31</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>55.47</v>
+        <v>54.44</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.93</v>
+        <v>13.81</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.93</v>
+        <v>9.75</v>
       </c>
       <c r="BC6" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="BD6" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.869999999999999</v>
+        <v>9</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.23</v>
+        <v>4.29</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.47</v>
+        <v>4.55</v>
       </c>
       <c r="BR6" t="n">
-        <v>93.33</v>
+        <v>93.55</v>
       </c>
       <c r="BS6" t="n">
-        <v>73.33</v>
+        <v>74.19</v>
       </c>
       <c r="BT6" t="n">
-        <v>60</v>
+        <v>61.29</v>
       </c>
       <c r="BU6" t="n">
-        <v>26.67</v>
+        <v>29.03</v>
       </c>
       <c r="BV6" t="n">
-        <v>23.33</v>
+        <v>25.81</v>
       </c>
       <c r="BW6" t="n">
-        <v>10</v>
+        <v>9.68</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>51.61</v>
       </c>
       <c r="BY6" t="n">
         <v>1.87</v>
@@ -3222,16 +3222,16 @@
         <v>1.93</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="CE6" t="n">
         <v>1.3</v>
@@ -3252,16 +3252,16 @@
         <v>1.7</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO6" t="n">
         <v>1.2</v>
@@ -3276,16 +3276,16 @@
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CU6" t="n">
         <v>1.5</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CW6" t="n">
         <v>1.79</v>
@@ -3306,85 +3306,85 @@
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="DH6" t="n">
-        <v>89.8</v>
+        <v>88.84</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.24</v>
+        <v>39.71</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.64</v>
+        <v>11.71</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.23</v>
+        <v>11.13</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.46</v>
+        <v>7.64</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>55.77</v>
+        <v>55.23</v>
       </c>
       <c r="DW6" t="n">
         <v>0.1</v>
       </c>
       <c r="DX6" t="n">
-        <v>15.13</v>
+        <v>15.03</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="DZ6" t="n">
         <v>4.94</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.07</v>
+        <v>17.87</v>
       </c>
       <c r="EB6" t="n">
         <v>1.48</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
         <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="F7" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="G7" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="H7" t="n">
-        <v>89.94</v>
+        <v>90</v>
       </c>
       <c r="I7" t="n">
         <v>0.12</v>
       </c>
       <c r="J7" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="K7" t="n">
-        <v>4.38</v>
+        <v>4.53</v>
       </c>
       <c r="L7" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="M7" t="n">
-        <v>38.31</v>
+        <v>39.65</v>
       </c>
       <c r="N7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="P7" t="n">
-        <v>11</v>
+        <v>11.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.38</v>
+        <v>12.24</v>
       </c>
       <c r="R7" t="n">
-        <v>7.94</v>
+        <v>7.88</v>
       </c>
       <c r="S7" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="T7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U7" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="V7" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>52.06</v>
+        <v>52.41</v>
       </c>
       <c r="Y7" t="n">
         <v>0.06</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.25</v>
+        <v>13.71</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.81</v>
+        <v>9.18</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.44</v>
+        <v>4.53</v>
       </c>
       <c r="AC7" t="n">
-        <v>23.75</v>
+        <v>23.47</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AF7" t="n">
         <v>0.2</v>
@@ -3565,70 +3565,70 @@
         <v>2.47</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.68</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="BJ7" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BL7" t="n">
         <v>0.97</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.06</v>
+        <v>4.12</v>
       </c>
       <c r="BQ7" t="n">
         <v>4.03</v>
       </c>
       <c r="BR7" t="n">
-        <v>96.77</v>
+        <v>96.88</v>
       </c>
       <c r="BS7" t="n">
-        <v>87.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>67.73999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="BU7" t="n">
-        <v>38.71</v>
+        <v>37.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.68</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BX7" t="n">
-        <v>77.42</v>
+        <v>78.12</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CC7" t="n">
         <v>4.42</v>
@@ -3661,7 +3661,7 @@
         <v>2</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CN7" t="n">
         <v>1.84</v>
@@ -3685,13 +3685,13 @@
         <v>3.08</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX7" t="n">
         <v>1.59</v>
@@ -3718,43 +3718,43 @@
         <v>0.19</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="DH7" t="n">
-        <v>83.55</v>
+        <v>83.78</v>
       </c>
       <c r="DI7" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.07</v>
+        <v>4.16</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="DM7" t="n">
-        <v>37.19</v>
+        <v>37.94</v>
       </c>
       <c r="DN7" t="n">
         <v>1.1</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="DP7" t="n">
         <v>11.84</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.94</v>
+        <v>12.84</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.32</v>
+        <v>9.25</v>
       </c>
       <c r="DS7" t="n">
         <v>0.19</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.35</v>
+        <v>48.66</v>
       </c>
       <c r="DW7" t="n">
         <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>12</v>
+        <v>12.28</v>
       </c>
       <c r="DY7" t="n">
-        <v>8</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.58</v>
+        <v>22.47</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
         <v>0.07000000000000001</v>
@@ -3890,49 +3890,49 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AI8" t="n">
-        <v>77.20999999999999</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.36</v>
+        <v>4.2</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>33.14</v>
+        <v>33.33</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10.79</v>
+        <v>11.67</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.57</v>
+        <v>12.67</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.789999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>50.36</v>
+        <v>50.47</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.5</v>
+        <v>12.07</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.79</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.71</v>
+        <v>4.07</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.21</v>
+        <v>18.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BF8" t="n">
         <v>2.07</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BH8" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.68</v>
+        <v>4.62</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.82</v>
+        <v>4.79</v>
       </c>
       <c r="BR8" t="n">
-        <v>96.43000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="BS8" t="n">
-        <v>82.14</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>53.57</v>
+        <v>55.17</v>
       </c>
       <c r="BU8" t="n">
-        <v>25</v>
+        <v>24.14</v>
       </c>
       <c r="BV8" t="n">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>51.72</v>
       </c>
       <c r="BY8" t="n">
         <v>2.54</v>
@@ -4028,22 +4028,22 @@
         <v>2.86</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CB8" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.38</v>
+        <v>4.28</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.59</v>
+        <v>4.49</v>
       </c>
       <c r="CE8" t="n">
         <v>1.3</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CG8" t="n">
         <v>3.2</v>
@@ -4064,7 +4064,7 @@
         <v>1.91</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN8" t="n">
         <v>1.94</v>
@@ -4073,7 +4073,7 @@
         <v>1.21</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CQ8" t="n">
         <v>2.74</v>
@@ -4094,7 +4094,7 @@
         <v>2.28</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX8" t="n">
         <v>1.52</v>
@@ -4115,82 +4115,82 @@
         <v>1.74</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="DE8" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="DH8" t="n">
-        <v>78.42</v>
+        <v>79.86</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.68</v>
+        <v>4.59</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM8" t="n">
-        <v>34.29</v>
+        <v>34.34</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.36</v>
+        <v>11.8</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.64</v>
+        <v>12.69</v>
       </c>
       <c r="DR8" t="n">
         <v>9</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.22</v>
+        <v>51.24</v>
       </c>
       <c r="DW8" t="n">
         <v>0.14</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.36</v>
+        <v>12.62</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.25</v>
+        <v>8.34</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.1</v>
+        <v>4.28</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.21</v>
+        <v>18.31</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
         <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F9" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="G9" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="H9" t="n">
-        <v>77.36</v>
+        <v>77.13</v>
       </c>
       <c r="I9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="M9" t="n">
-        <v>34.93</v>
+        <v>34.07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="P9" t="n">
-        <v>10.29</v>
+        <v>10.13</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.5</v>
+        <v>12.33</v>
       </c>
       <c r="R9" t="n">
-        <v>8.140000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="T9" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="V9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>40.93</v>
+        <v>40.53</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.43</v>
+        <v>10.47</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.64</v>
+        <v>6.73</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.79</v>
+        <v>3.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>15.43</v>
+        <v>15.27</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>2.29</v>
       </c>
       <c r="BG9" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.5</v>
+        <v>9.59</v>
       </c>
       <c r="BI9" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.96</v>
+        <v>5.07</v>
       </c>
       <c r="BR9" t="n">
-        <v>96.43000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.56999999999999</v>
+        <v>79.31</v>
       </c>
       <c r="BT9" t="n">
-        <v>60.71</v>
+        <v>58.62</v>
       </c>
       <c r="BU9" t="n">
-        <v>39.29</v>
+        <v>37.93</v>
       </c>
       <c r="BV9" t="n">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="BX9" t="n">
-        <v>71.43000000000001</v>
+        <v>72.41</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.46</v>
+        <v>3.55</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.75</v>
+        <v>3.83</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.26</v>
+        <v>4.27</v>
       </c>
       <c r="CC9" t="n">
         <v>5.8</v>
@@ -4446,19 +4446,19 @@
         <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CI9" t="n">
         <v>2</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CK9" t="n">
         <v>1.46</v>
@@ -4470,22 +4470,22 @@
         <v>2.5</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CR9" t="n">
         <v>1.38</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CT9" t="n">
         <v>3.18</v>
@@ -4494,73 +4494,73 @@
         <v>1.53</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY9" t="n">
         <v>1.86</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB9" t="n">
         <v>1.26</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="DE9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DG9" t="n">
         <v>2</v>
       </c>
       <c r="DH9" t="n">
-        <v>75.61</v>
+        <v>75.55</v>
       </c>
       <c r="DI9" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="DL9" t="n">
         <v>0.11</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.36</v>
+        <v>32.97</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.18</v>
+        <v>11.07</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.72</v>
+        <v>12.62</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.67</v>
+        <v>9.65</v>
       </c>
       <c r="DS9" t="n">
         <v>0.07000000000000001</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>41.9</v>
+        <v>41.65</v>
       </c>
       <c r="DW9" t="n">
         <v>0.14</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.859999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.32</v>
+        <v>6.38</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.64</v>
+        <v>16.52</v>
       </c>
       <c r="EB9" t="n">
         <v>1.09</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" t="n">
         <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="G10" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="H10" t="n">
-        <v>94.59999999999999</v>
+        <v>95.75</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="K10" t="n">
-        <v>4.73</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="M10" t="n">
-        <v>44.2</v>
+        <v>44.62</v>
       </c>
       <c r="N10" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="P10" t="n">
-        <v>11.07</v>
+        <v>10.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.87</v>
+        <v>13</v>
       </c>
       <c r="R10" t="n">
-        <v>6.47</v>
+        <v>6.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="T10" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>58.6</v>
+        <v>58.75</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.73</v>
+        <v>15.19</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.33</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.4</v>
+        <v>5.56</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.87</v>
+        <v>18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
         <v>0.18</v>
@@ -4774,70 +4774,70 @@
         <v>1.82</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.029999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.47</v>
+        <v>4.52</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.53</v>
+        <v>4.61</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>75</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>53.12</v>
+        <v>54.55</v>
       </c>
       <c r="BU10" t="n">
-        <v>43.75</v>
+        <v>45.45</v>
       </c>
       <c r="BV10" t="n">
-        <v>21.88</v>
+        <v>24.24</v>
       </c>
       <c r="BW10" t="n">
-        <v>15.62</v>
+        <v>15.15</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>51.52</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="CC10" t="n">
         <v>3.02</v>
@@ -4852,7 +4852,7 @@
         <v>2.44</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CH10" t="n">
         <v>1.51</v>
@@ -4864,16 +4864,16 @@
         <v>1.67</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CO10" t="n">
         <v>1.2</v>
@@ -4885,7 +4885,7 @@
         <v>2.73</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS10" t="n">
         <v>2.55</v>
@@ -4897,7 +4897,7 @@
         <v>1.56</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CW10" t="n">
         <v>1.69</v>
@@ -4924,79 +4924,79 @@
         <v>2.8</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="DH10" t="n">
-        <v>78.94</v>
+        <v>79.97</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.28</v>
+        <v>4.42</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.06</v>
+        <v>36.51</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.66</v>
+        <v>10.54</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.75</v>
+        <v>12.82</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.56</v>
+        <v>7.55</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>56.09</v>
+        <v>56.24</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.66</v>
+        <v>13.91</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.44</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.22</v>
+        <v>5.3</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.91</v>
+        <v>18.94</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
         <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F11" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="G11" t="n">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="H11" t="n">
-        <v>81.54000000000001</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="K11" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>40.77</v>
+        <v>41.93</v>
       </c>
       <c r="N11" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="O11" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="P11" t="n">
-        <v>11.77</v>
+        <v>11.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.38</v>
+        <v>10.93</v>
       </c>
       <c r="R11" t="n">
-        <v>9.77</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="T11" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="U11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>51.31</v>
+        <v>51.57</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z11" t="n">
-        <v>16.23</v>
+        <v>16.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.69</v>
+        <v>11.64</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.54</v>
+        <v>4.86</v>
       </c>
       <c r="AC11" t="n">
-        <v>24.23</v>
+        <v>23.43</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
         <v>0.07000000000000001</v>
@@ -5177,70 +5177,70 @@
         <v>2.53</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.25</v>
+        <v>10.14</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.36</v>
+        <v>4.31</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.93</v>
+        <v>4.9</v>
       </c>
       <c r="BR11" t="n">
-        <v>96.43000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="BS11" t="n">
-        <v>78.56999999999999</v>
+        <v>79.31</v>
       </c>
       <c r="BT11" t="n">
-        <v>53.57</v>
+        <v>55.17</v>
       </c>
       <c r="BU11" t="n">
-        <v>32.14</v>
+        <v>31.03</v>
       </c>
       <c r="BV11" t="n">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="BX11" t="n">
-        <v>60.71</v>
+        <v>58.62</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="CC11" t="n">
         <v>3.71</v>
@@ -5252,10 +5252,10 @@
         <v>1.31</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CH11" t="n">
         <v>1.52</v>
@@ -5273,10 +5273,10 @@
         <v>1.8</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CO11" t="n">
         <v>1.2</v>
@@ -5309,13 +5309,13 @@
         <v>1.5</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.48</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DB11" t="n">
         <v>1.23</v>
@@ -5324,49 +5324,49 @@
         <v>1.75</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="DH11" t="n">
-        <v>82.90000000000001</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="DI11" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.04</v>
+        <v>5.07</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="DM11" t="n">
-        <v>39.78</v>
+        <v>40.38</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DP11" t="n">
         <v>12.07</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.21</v>
+        <v>11.96</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.890000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="DS11" t="n">
         <v>0.07000000000000001</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.22</v>
+        <v>49.41</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.5</v>
+        <v>14.69</v>
       </c>
       <c r="DY11" t="n">
-        <v>10</v>
+        <v>10.03</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.5</v>
+        <v>4.66</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.47</v>
+        <v>21.17</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
         <v>15</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="H12" t="n">
-        <v>86.87</v>
+        <v>87.88</v>
       </c>
       <c r="I12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="J12" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="K12" t="n">
-        <v>5.07</v>
+        <v>5.31</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="M12" t="n">
-        <v>37.73</v>
+        <v>36.62</v>
       </c>
       <c r="N12" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="O12" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>12.13</v>
+        <v>12</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.8</v>
+        <v>11.81</v>
       </c>
       <c r="R12" t="n">
-        <v>7.87</v>
+        <v>7.94</v>
       </c>
       <c r="S12" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="U12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="V12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.6</v>
+        <v>14.69</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>16.73</v>
+        <v>16.62</v>
       </c>
       <c r="AD12" t="n">
         <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AF12" t="n">
         <v>0.07000000000000001</v>
@@ -5580,67 +5580,67 @@
         <v>2.13</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.869999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="BN12" t="n">
         <v>1.03</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="BQ12" t="n">
         <v>4.23</v>
       </c>
       <c r="BR12" t="n">
-        <v>93.33</v>
+        <v>93.55</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.33</v>
+        <v>74.19</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>48.39</v>
       </c>
       <c r="BU12" t="n">
-        <v>20</v>
+        <v>19.35</v>
       </c>
       <c r="BV12" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>51.61</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CB12" t="n">
         <v>3.85</v>
@@ -5655,7 +5655,7 @@
         <v>1.33</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CG12" t="n">
         <v>3.06</v>
@@ -5676,7 +5676,7 @@
         <v>1.85</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CN12" t="n">
         <v>1.98</v>
@@ -5688,7 +5688,7 @@
         <v>1.81</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CR12" t="n">
         <v>1.38</v>
@@ -5703,10 +5703,10 @@
         <v>1.5</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CX12" t="n">
         <v>1.52</v>
@@ -5724,85 +5724,85 @@
         <v>1.27</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DF12" t="n">
         <v>1.84</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="DH12" t="n">
-        <v>85.77</v>
+        <v>86.33</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ12" t="n">
         <v>2.87</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.57</v>
+        <v>4.71</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="DM12" t="n">
-        <v>37.1</v>
+        <v>36.55</v>
       </c>
       <c r="DN12" t="n">
         <v>0.87</v>
       </c>
       <c r="DO12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.8</v>
+        <v>11.74</v>
       </c>
       <c r="DQ12" t="n">
         <v>12.03</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.039999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50.66</v>
+        <v>50.58</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.2</v>
+        <v>14.26</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.66</v>
+        <v>9.74</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.54</v>
+        <v>4.52</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.23</v>
+        <v>19.09</v>
       </c>
       <c r="EB12" t="n">
         <v>1.48</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" t="n">
         <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
         <v>0.07000000000000001</v>
@@ -5905,49 +5905,49 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="AI13" t="n">
-        <v>76.93000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.43</v>
+        <v>5.33</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AN13" t="n">
-        <v>28.14</v>
+        <v>27.67</v>
       </c>
       <c r="AO13" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AP13" t="n">
         <v>2.07</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.5</v>
+        <v>11.67</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.86</v>
+        <v>13.13</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.71</v>
+        <v>10.67</v>
       </c>
       <c r="AT13" t="n">
         <v>1.93</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AV13" t="n">
         <v>0.07000000000000001</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>47.07</v>
+        <v>47.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.86</v>
+        <v>11.33</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.07</v>
+        <v>7.47</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.79</v>
+        <v>3.87</v>
       </c>
       <c r="BD13" t="n">
-        <v>18.86</v>
+        <v>19.13</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.68</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL13" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="BM13" t="n">
         <v>0.93</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.14</v>
+        <v>5.21</v>
       </c>
       <c r="BR13" t="n">
-        <v>85.70999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>67.86</v>
+        <v>68.97</v>
       </c>
       <c r="BT13" t="n">
-        <v>60.71</v>
+        <v>62.07</v>
       </c>
       <c r="BU13" t="n">
-        <v>39.29</v>
+        <v>37.93</v>
       </c>
       <c r="BV13" t="n">
-        <v>21.43</v>
+        <v>20.69</v>
       </c>
       <c r="BW13" t="n">
-        <v>14.29</v>
+        <v>13.79</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>51.72</v>
       </c>
       <c r="BY13" t="n">
         <v>3.24</v>
@@ -6043,22 +6043,22 @@
         <v>3.48</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.99</v>
+        <v>4.81</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.41</v>
+        <v>5.24</v>
       </c>
       <c r="CE13" t="n">
         <v>1.34</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CG13" t="n">
         <v>2.97</v>
@@ -6067,10 +6067,10 @@
         <v>1.45</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CK13" t="n">
         <v>1.45</v>
@@ -6088,10 +6088,10 @@
         <v>1.25</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CR13" t="n">
         <v>1.39</v>
@@ -6106,73 +6106,73 @@
         <v>1.46</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX13" t="n">
         <v>1.52</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.42</v>
       </c>
       <c r="DA13" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB13" t="n">
         <v>1.29</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="DH13" t="n">
-        <v>83.40000000000001</v>
+        <v>83.83</v>
       </c>
       <c r="DI13" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.75</v>
+        <v>4.72</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="DM13" t="n">
-        <v>33.68</v>
+        <v>33.24</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.57</v>
+        <v>11.17</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.68</v>
+        <v>12.83</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.460000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="DS13" t="n">
         <v>0.04</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.54</v>
+        <v>48.66</v>
       </c>
       <c r="DW13" t="n">
         <v>0.14</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.5</v>
+        <v>12.69</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.220000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.29</v>
+        <v>4.31</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.82</v>
+        <v>19.93</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="14">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
         <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="G14" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="H14" t="n">
-        <v>89.20999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="K14" t="n">
-        <v>4.43</v>
+        <v>4.27</v>
       </c>
       <c r="L14" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="M14" t="n">
-        <v>41.43</v>
+        <v>40.93</v>
       </c>
       <c r="N14" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="O14" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="P14" t="n">
-        <v>11.21</v>
+        <v>11.13</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.71</v>
+        <v>10.47</v>
       </c>
       <c r="R14" t="n">
-        <v>10.57</v>
+        <v>10.6</v>
       </c>
       <c r="S14" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="T14" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="U14" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>55.07</v>
+        <v>54</v>
       </c>
       <c r="Y14" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>12.64</v>
+        <v>12.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.640000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="AC14" t="n">
-        <v>19.07</v>
+        <v>19.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AF14" t="n">
         <v>0.07000000000000001</v>
@@ -6386,70 +6386,70 @@
         <v>3.07</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.140000000000001</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.55</v>
+        <v>4.53</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.52</v>
+        <v>4.43</v>
       </c>
       <c r="BR14" t="n">
-        <v>96.55</v>
+        <v>96.67</v>
       </c>
       <c r="BS14" t="n">
-        <v>82.76000000000001</v>
+        <v>80</v>
       </c>
       <c r="BT14" t="n">
-        <v>48.28</v>
+        <v>46.67</v>
       </c>
       <c r="BU14" t="n">
-        <v>41.38</v>
+        <v>40</v>
       </c>
       <c r="BV14" t="n">
-        <v>24.14</v>
+        <v>23.33</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>68.97</v>
+        <v>66.67</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="CA14" t="n">
         <v>3.48</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CC14" t="n">
         <v>3.23</v>
@@ -6461,7 +6461,7 @@
         <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CG14" t="n">
         <v>2.94</v>
@@ -6470,13 +6470,13 @@
         <v>1.41</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.77</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CL14" t="n">
         <v>1.99</v>
@@ -6494,7 +6494,7 @@
         <v>1.9</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CR14" t="n">
         <v>1.4</v>
@@ -6503,13 +6503,13 @@
         <v>2.92</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CU14" t="n">
         <v>1.44</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CW14" t="n">
         <v>1.81</v>
@@ -6530,22 +6530,22 @@
         <v>1.3</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="DE14" t="n">
         <v>0.1</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="DH14" t="n">
-        <v>83.14</v>
+        <v>83.34</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
@@ -6554,61 +6554,61 @@
         <v>2.76</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="DM14" t="n">
-        <v>40.28</v>
+        <v>40.07</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.1</v>
+        <v>12.03</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.76</v>
+        <v>10.64</v>
       </c>
       <c r="DR14" t="n">
-        <v>11.83</v>
+        <v>11.8</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.21</v>
+        <v>50.8</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.96</v>
+        <v>11.83</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.17</v>
+        <v>8.06</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.62</v>
+        <v>18.76</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
         <v>0.08</v>
@@ -6711,49 +6711,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AI15" t="n">
-        <v>54.57</v>
+        <v>55.47</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.64</v>
+        <v>3.87</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="AN15" t="n">
-        <v>22.07</v>
+        <v>22</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.43</v>
+        <v>9.33</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.29</v>
+        <v>11.87</v>
       </c>
       <c r="AS15" t="n">
-        <v>11.07</v>
+        <v>11.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AV15" t="n">
         <v>0.07000000000000001</v>
@@ -6765,82 +6765,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>31.93</v>
+        <v>32.2</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.93</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.36</v>
+        <v>5.73</v>
       </c>
       <c r="BC15" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>89.29000000000001</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>53.57</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>32.14</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="BW15" t="n">
         <v>3.57</v>
       </c>
-      <c r="BD15" t="n">
-        <v>16.29</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>92.59</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>74.06999999999999</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>55.56</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BX15" t="n">
-        <v>44.44</v>
+        <v>42.86</v>
       </c>
       <c r="BY15" t="n">
         <v>3.31</v>
@@ -6849,22 +6849,22 @@
         <v>3.67</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="CC15" t="n">
-        <v>6.96</v>
+        <v>6.75</v>
       </c>
       <c r="CD15" t="n">
-        <v>7.35</v>
+        <v>7.13</v>
       </c>
       <c r="CE15" t="n">
         <v>1.3</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CG15" t="n">
         <v>2.92</v>
@@ -6882,10 +6882,10 @@
         <v>1.41</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CN15" t="n">
         <v>1.85</v>
@@ -6897,7 +6897,7 @@
         <v>1.85</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
@@ -6921,70 +6921,70 @@
         <v>1.53</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.42</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="DE15" t="n">
         <v>0.04</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="DH15" t="n">
-        <v>66.11</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="DI15" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.66</v>
+        <v>3.79</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="DM15" t="n">
-        <v>24.59</v>
+        <v>24.47</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.3</v>
+        <v>11.18</v>
       </c>
       <c r="DQ15" t="n">
-        <v>11.97</v>
+        <v>11.75</v>
       </c>
       <c r="DR15" t="n">
-        <v>10.74</v>
+        <v>10.82</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
@@ -6993,25 +6993,25 @@
         <v>36.04</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.710000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.15</v>
+        <v>6.32</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.82</v>
+        <v>18.32</v>
       </c>
       <c r="EB15" t="n">
         <v>1.03</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="16">
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16" t="n">
         <v>15</v>
@@ -7033,82 +7033,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="G16" t="n">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="H16" t="n">
-        <v>66.92</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="J16" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="M16" t="n">
-        <v>33.38</v>
+        <v>32.86</v>
       </c>
       <c r="N16" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="O16" t="n">
-        <v>1.54</v>
+        <v>1.86</v>
       </c>
       <c r="P16" t="n">
-        <v>12.69</v>
+        <v>12.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.54</v>
+        <v>13.93</v>
       </c>
       <c r="R16" t="n">
-        <v>9.92</v>
+        <v>10.07</v>
       </c>
       <c r="S16" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T16" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="V16" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>43.85</v>
+        <v>44.14</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.08</v>
+        <v>12.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.62</v>
+        <v>7.71</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.46</v>
+        <v>4.79</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.77</v>
+        <v>19.71</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="AF16" t="n">
         <v>0.07000000000000001</v>
@@ -7192,70 +7192,70 @@
         <v>2.73</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="BH16" t="n">
-        <v>10</v>
+        <v>10.17</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.43</v>
+        <v>4.55</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.54</v>
+        <v>5.59</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>78.56999999999999</v>
+        <v>79.31</v>
       </c>
       <c r="BT16" t="n">
-        <v>75</v>
+        <v>75.86</v>
       </c>
       <c r="BU16" t="n">
-        <v>46.43</v>
+        <v>44.83</v>
       </c>
       <c r="BV16" t="n">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="BX16" t="n">
-        <v>60.71</v>
+        <v>62.07</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.81</v>
+        <v>3.72</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.26</v>
+        <v>4.22</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="CC16" t="n">
         <v>6.61</v>
@@ -7267,16 +7267,16 @@
         <v>1.27</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.65</v>
@@ -7285,22 +7285,22 @@
         <v>1.41</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO16" t="n">
         <v>1.17</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
@@ -7318,7 +7318,7 @@
         <v>2.27</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX16" t="n">
         <v>1.52</v>
@@ -7330,7 +7330,7 @@
         <v>2.45</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DB16" t="n">
         <v>1.2</v>
@@ -7339,49 +7339,49 @@
         <v>1.62</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="DE16" t="n">
         <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="DH16" t="n">
-        <v>76.18000000000001</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="DI16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.21</v>
+        <v>4.45</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="DM16" t="n">
-        <v>33.39</v>
+        <v>33.14</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.64</v>
+        <v>11.55</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.89</v>
+        <v>13.62</v>
       </c>
       <c r="DR16" t="n">
-        <v>10.89</v>
+        <v>10.93</v>
       </c>
       <c r="DS16" t="n">
         <v>0.14</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.64</v>
+        <v>44.76</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.79</v>
+        <v>11.04</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.75</v>
+        <v>6.83</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.04</v>
+        <v>4.21</v>
       </c>
       <c r="EA16" t="n">
         <v>18.86</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17" t="n">
         <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
         <v>0.17</v>
@@ -7514,52 +7514,52 @@
         <v>1.94</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="AI17" t="n">
-        <v>91</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="AJ17" t="n">
         <v>0.06</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.06</v>
+        <v>4.94</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AN17" t="n">
-        <v>38.88</v>
+        <v>38.47</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.88</v>
+        <v>11.71</v>
       </c>
       <c r="AR17" t="n">
-        <v>12.75</v>
+        <v>12.59</v>
       </c>
       <c r="AS17" t="n">
         <v>8.94</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AV17" t="n">
         <v>0.12</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>53.12</v>
+        <v>52.47</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="BA17" t="n">
-        <v>13.81</v>
+        <v>13.76</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.380000000000001</v>
+        <v>8.41</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.44</v>
+        <v>5.35</v>
       </c>
       <c r="BD17" t="n">
-        <v>18</v>
+        <v>18.24</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.41</v>
+        <v>9.43</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BL17" t="n">
         <v>1.09</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.24</v>
+        <v>4.29</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5</v>
+        <v>4.97</v>
       </c>
       <c r="BR17" t="n">
-        <v>88.23999999999999</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>73.53</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>51.43</v>
       </c>
       <c r="BU17" t="n">
-        <v>29.41</v>
+        <v>28.57</v>
       </c>
       <c r="BV17" t="n">
-        <v>17.65</v>
+        <v>17.14</v>
       </c>
       <c r="BW17" t="n">
-        <v>11.76</v>
+        <v>11.43</v>
       </c>
       <c r="BX17" t="n">
-        <v>55.88</v>
+        <v>57.14</v>
       </c>
       <c r="BY17" t="n">
         <v>1.63</v>
@@ -7655,22 +7655,22 @@
         <v>1.64</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="CE17" t="n">
         <v>1.29</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CG17" t="n">
         <v>2.99</v>
@@ -7688,13 +7688,13 @@
         <v>1.44</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CM17" t="n">
         <v>2.38</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO17" t="n">
         <v>1.2</v>
@@ -7703,13 +7703,13 @@
         <v>1.79</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CR17" t="n">
         <v>1.38</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CT17" t="n">
         <v>3.14</v>
@@ -7718,7 +7718,7 @@
         <v>1.49</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CW17" t="n">
         <v>1.79</v>
@@ -7739,52 +7739,52 @@
         <v>1.26</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="DH17" t="n">
-        <v>90.79000000000001</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="DI17" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.62</v>
+        <v>5.54</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="DM17" t="n">
-        <v>44.3</v>
+        <v>43.94</v>
       </c>
       <c r="DN17" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.12</v>
+        <v>11.06</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.77</v>
+        <v>13.66</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.42</v>
+        <v>7.46</v>
       </c>
       <c r="DS17" t="n">
         <v>0.15</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>55.06</v>
+        <v>54.69</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.27</v>
+        <v>15.2</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.92</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.36</v>
+        <v>5.31</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.97</v>
+   